--- a/reports/screener_2026-09-04.xlsx
+++ b/reports/screener_2026-09-04.xlsx
@@ -1302,10 +1302,10 @@
         <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>14.34883231510244</v>
+        <v>14.34883233997342</v>
       </c>
       <c r="CN2" t="n">
-        <v>26.61708394451502</v>
+        <v>26.61708399065069</v>
       </c>
       <c r="CO2" t="n">
         <v>38.73764113094029</v>
@@ -1314,13 +1314,13 @@
         <v>23.42212306847306</v>
       </c>
       <c r="CQ2" t="n">
-        <v>77.21384549512003</v>
+        <v>77.21384545128907</v>
       </c>
       <c r="CR2" t="n">
-        <v>48.83647634904256</v>
+        <v>48.83647633066641</v>
       </c>
       <c r="CS2" t="n">
-        <v>27.96937491056918</v>
+        <v>27.96937483383525</v>
       </c>
       <c r="CT2" t="n">
         <v>9.042040250118818</v>
@@ -1661,10 +1661,10 @@
         <v>1</v>
       </c>
       <c r="CM3" t="n">
-        <v>6.74149677483709</v>
+        <v>6.7414967884217</v>
       </c>
       <c r="CN3" t="n">
-        <v>12.5054765173228</v>
+        <v>12.50547654252225</v>
       </c>
       <c r="CO3" t="n">
         <v>41.30882298882631</v>
@@ -1673,7 +1673,7 @@
         <v>27.77800617149056</v>
       </c>
       <c r="CQ3" t="n">
-        <v>72.00025469489329</v>
+        <v>72.00025474574477</v>
       </c>
       <c r="CR3" t="n">
         <v>19.57807411896471</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="CM4" t="n">
-        <v>17.1663830832182</v>
+        <v>17.16638305223679</v>
       </c>
       <c r="CN4" t="n">
-        <v>31.84364061936976</v>
+        <v>31.84364056189925</v>
       </c>
       <c r="CO4" t="n">
         <v>71.20842100924612</v>
@@ -2040,19 +2040,19 @@
         <v>51.68759722785042</v>
       </c>
       <c r="CQ4" t="n">
-        <v>122.395720483912</v>
+        <v>122.3957204994831</v>
       </c>
       <c r="CR4" t="n">
-        <v>25.57411552848948</v>
+        <v>25.57411553292391</v>
       </c>
       <c r="CS4" t="n">
-        <v>59.88502635963041</v>
+        <v>59.88502642609916</v>
       </c>
       <c r="CT4" t="n">
         <v>44.43438321477654</v>
       </c>
       <c r="CU4" t="n">
-        <v>47.43886399322712</v>
+        <v>47.4388639954659</v>
       </c>
       <c r="CV4" t="n">
         <v>48.06099022131347</v>
@@ -2073,7 +2073,7 @@
         <v>67.33033098981652</v>
       </c>
       <c r="DB4" t="n">
-        <v>83.51591215926295</v>
+        <v>83.5159121679236</v>
       </c>
       <c r="DC4" t="inlineStr">
         <is>
@@ -2395,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="CM5" t="n">
-        <v>3.907370963482954</v>
+        <v>3.907370941582745</v>
       </c>
       <c r="CN5" t="n">
-        <v>7.248173137260879</v>
+        <v>7.248173096635992</v>
       </c>
       <c r="CO5" t="n">
         <v>12.71763449268681</v>
@@ -2407,19 +2407,19 @@
         <v>8.551038591084707</v>
       </c>
       <c r="CQ5" t="n">
-        <v>23.90073392772668</v>
+        <v>23.90073394611848</v>
       </c>
       <c r="CR5" t="n">
-        <v>11.13506641444498</v>
+        <v>11.1350664234246</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.912220006362892</v>
+        <v>9.912220060941721</v>
       </c>
       <c r="CT5" t="n">
         <v>5.427221201663706</v>
       </c>
       <c r="CU5" t="n">
-        <v>8.414103543855276</v>
+        <v>8.414103544002897</v>
       </c>
       <c r="CV5" t="n">
         <v>8.551038591084707</v>
@@ -2440,7 +2440,7 @@
         <v>78.97521838623484</v>
       </c>
       <c r="DB5" t="n">
-        <v>95.67681792165965</v>
+        <v>95.67681792509268</v>
       </c>
       <c r="DC5" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>-0.9216580748084957</v>
       </c>
       <c r="DO5" t="n">
-        <v>-34.16759691282044</v>
+        <v>-34.16760193805087</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -2764,10 +2764,10 @@
         <v>1</v>
       </c>
       <c r="CM6" t="n">
-        <v>3.327945782710356</v>
+        <v>3.327945787913786</v>
       </c>
       <c r="CN6" t="n">
-        <v>6.17333942692771</v>
+        <v>6.173339436580072</v>
       </c>
       <c r="CO6" t="n">
         <v>12.71999984038503</v>
@@ -2776,25 +2776,25 @@
         <v>8.573475127812586</v>
       </c>
       <c r="CQ6" t="n">
-        <v>23.80124252649136</v>
+        <v>23.80124252119723</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.53241883504053</v>
+        <v>11.53241883287747</v>
       </c>
       <c r="CS6" t="n">
-        <v>11.35989496296809</v>
+        <v>11.35989495000031</v>
       </c>
       <c r="CT6" t="n">
         <v>5.406965820956791</v>
       </c>
       <c r="CU6" t="n">
-        <v>11.3667623629403</v>
+        <v>11.36676236140136</v>
       </c>
       <c r="CV6" t="n">
-        <v>11.35989496296809</v>
+        <v>11.35989495000031</v>
       </c>
       <c r="CW6" t="n">
-        <v>10.22390546667128</v>
+        <v>10.22390545500028</v>
       </c>
       <c r="CX6" t="n">
         <v>7</v>
@@ -2806,10 +2806,10 @@
         <v>7.2</v>
       </c>
       <c r="DA6" t="n">
-        <v>124.2084560299209</v>
+        <v>124.2084557739779</v>
       </c>
       <c r="DB6" t="n">
-        <v>149.2711075783854</v>
+        <v>149.2711075446366</v>
       </c>
       <c r="DC6" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>-0.8695644061371466</v>
       </c>
       <c r="DO6" t="n">
-        <v>-40.94616015020202</v>
+        <v>-40.94615637406525</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3123,10 +3123,10 @@
         <v>1</v>
       </c>
       <c r="CM7" t="n">
-        <v>19.52675460330705</v>
+        <v>19.52675456025717</v>
       </c>
       <c r="CN7" t="n">
-        <v>36.22212978913458</v>
+        <v>36.22212970927706</v>
       </c>
       <c r="CO7" t="n">
         <v>75.52058089429198</v>
@@ -3135,23 +3135,23 @@
         <v>56.61657821085305</v>
       </c>
       <c r="CQ7" t="n">
-        <v>98.15037103580246</v>
+        <v>98.15037110641777</v>
       </c>
       <c r="CR7" t="n">
-        <v>48.15705803416046</v>
+        <v>48.15705804455569</v>
       </c>
       <c r="CS7" t="n">
-        <v>57.80670625323084</v>
+        <v>57.80670633975764</v>
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>44.85663083022352</v>
+        <v>44.85663080209548</v>
       </c>
       <c r="CV7" t="n">
-        <v>42.18959391164752</v>
+        <v>42.18959387691638</v>
       </c>
       <c r="CW7" t="n">
-        <v>37.97063452048277</v>
+        <v>37.97063448922474</v>
       </c>
       <c r="CX7" t="n">
         <v>4</v>
@@ -3163,10 +3163,10 @@
         <v>3.9</v>
       </c>
       <c r="DA7" t="n">
-        <v>-25.8965002406711</v>
+        <v>-25.89650030167426</v>
       </c>
       <c r="DB7" t="n">
-        <v>-12.45778813259845</v>
+        <v>-12.45778818749312</v>
       </c>
       <c r="DC7" t="inlineStr">
         <is>
@@ -3490,10 +3490,10 @@
         <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>6.403626929426027</v>
+        <v>6.403626923493396</v>
       </c>
       <c r="CN8" t="n">
-        <v>11.87872795408528</v>
+        <v>11.87872794308025</v>
       </c>
       <c r="CO8" t="n">
         <v>25.4012199436746</v>
@@ -3502,19 +3502,19 @@
         <v>18.64745536395598</v>
       </c>
       <c r="CQ8" t="n">
-        <v>35.23268455075863</v>
+        <v>35.23268456040559</v>
       </c>
       <c r="CR8" t="n">
-        <v>12.29886663373648</v>
+        <v>12.29886663486247</v>
       </c>
       <c r="CS8" t="n">
-        <v>20.3953979918496</v>
+        <v>20.39539800428012</v>
       </c>
       <c r="CT8" t="n">
         <v>18.89184945304214</v>
       </c>
       <c r="CU8" t="n">
-        <v>20.39231455587182</v>
+        <v>20.39231455761445</v>
       </c>
       <c r="CV8" t="n">
         <v>18.89184945304214</v>
@@ -3535,7 +3535,7 @@
         <v>8.159441596189932</v>
       </c>
       <c r="DB8" t="n">
-        <v>29.72210056918854</v>
+        <v>29.72210058027398</v>
       </c>
       <c r="DC8" t="inlineStr">
         <is>
@@ -3859,10 +3859,10 @@
         <v>1</v>
       </c>
       <c r="CM9" t="n">
-        <v>45.77695642116295</v>
+        <v>45.77695654203991</v>
       </c>
       <c r="CN9" t="n">
-        <v>84.91625416125727</v>
+        <v>84.91625438548404</v>
       </c>
       <c r="CO9" t="n">
         <v>68.18445585960495</v>
@@ -3883,7 +3883,7 @@
         <v>26.15892848466381</v>
       </c>
       <c r="CU9" t="n">
-        <v>71.11162365572162</v>
+        <v>71.11162369885957</v>
       </c>
       <c r="CV9" t="n">
         <v>65.22550777513155</v>
@@ -3904,7 +3904,7 @@
         <v>79.08163265306125</v>
       </c>
       <c r="DB9" t="n">
-        <v>116.9360167903183</v>
+        <v>116.9360169219168</v>
       </c>
       <c r="DC9" t="inlineStr">
         <is>
@@ -4236,37 +4236,37 @@
         <v>1</v>
       </c>
       <c r="CM10" t="n">
-        <v>24.36355412189999</v>
+        <v>24.36355405256904</v>
       </c>
       <c r="CN10" t="n">
-        <v>31.53570933459214</v>
+        <v>31.53570981245223</v>
       </c>
       <c r="CO10" t="n">
-        <v>32.96248398297526</v>
+        <v>32.96248457625602</v>
       </c>
       <c r="CP10" t="n">
         <v>20.75155156536448</v>
       </c>
       <c r="CQ10" t="n">
-        <v>47.31871742812845</v>
+        <v>47.31871796693122</v>
       </c>
       <c r="CR10" t="n">
-        <v>50.67250998000094</v>
+        <v>50.67251006901864</v>
       </c>
       <c r="CS10" t="n">
-        <v>15.96314803283591</v>
+        <v>15.96314843782849</v>
       </c>
       <c r="CT10" t="n">
         <v>24.59438222893265</v>
       </c>
       <c r="CU10" t="n">
-        <v>31.02025708434123</v>
+        <v>31.0202573386691</v>
       </c>
       <c r="CV10" t="n">
-        <v>28.0650457817624</v>
+        <v>28.06504602069244</v>
       </c>
       <c r="CW10" t="n">
-        <v>25.25854120358616</v>
+        <v>25.2585414186232</v>
       </c>
       <c r="CX10" t="n">
         <v>8</v>
@@ -4278,10 +4278,10 @@
         <v>3.2</v>
       </c>
       <c r="DA10" t="n">
-        <v>-22.99225063686383</v>
+        <v>-22.9922499812631</v>
       </c>
       <c r="DB10" t="n">
-        <v>-5.426043274746172</v>
+        <v>-5.42604249935631</v>
       </c>
       <c r="DC10" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
         <v>1</v>
       </c>
       <c r="CM11" t="n">
-        <v>139.3179999466606</v>
+        <v>139.3180003996247</v>
       </c>
       <c r="CN11" t="n">
-        <v>258.4348899010554</v>
+        <v>258.4348907413038</v>
       </c>
       <c r="CO11" t="n">
         <v>136.9934822165448</v>
@@ -4639,7 +4639,7 @@
         <v>58.37540514006138</v>
       </c>
       <c r="CU11" t="n">
-        <v>147.23543242837</v>
+        <v>147.2354325900216</v>
       </c>
       <c r="CV11" t="n">
         <v>131.0484820448834</v>
@@ -4660,7 +4660,7 @@
         <v>147.9891304347826</v>
       </c>
       <c r="DB11" t="n">
-        <v>209.5782762341451</v>
+        <v>209.5782765740348</v>
       </c>
       <c r="DC11" t="inlineStr">
         <is>
@@ -4994,10 +4994,10 @@
         <v>1</v>
       </c>
       <c r="CM12" t="n">
-        <v>145.9241176151541</v>
+        <v>145.9241172852467</v>
       </c>
       <c r="CN12" t="n">
-        <v>270.6892381761108</v>
+        <v>270.6892375641326</v>
       </c>
       <c r="CO12" t="n">
         <v>137.1427213113139</v>
@@ -5018,7 +5018,7 @@
         <v>57.29814214194677</v>
       </c>
       <c r="CU12" t="n">
-        <v>149.5179565088166</v>
+        <v>149.5179563910809</v>
       </c>
       <c r="CV12" t="n">
         <v>131.1912447261059</v>
@@ -5039,7 +5039,7 @@
         <v>124.5570866141732</v>
       </c>
       <c r="DB12" t="n">
-        <v>184.3627830011002</v>
+        <v>184.362782777183</v>
       </c>
       <c r="DC12" t="inlineStr">
         <is>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="CM13" t="n">
-        <v>13.58565538364201</v>
+        <v>13.58565532094829</v>
       </c>
       <c r="CN13" t="n">
-        <v>25.20139073665593</v>
+        <v>25.20139062035909</v>
       </c>
       <c r="CO13" t="n">
         <v>19.9811217441166</v>
@@ -5357,7 +5357,7 @@
         <v>12.48999788378355</v>
       </c>
       <c r="CQ13" t="n">
-        <v>33.81046386196516</v>
+        <v>33.81046379501534</v>
       </c>
       <c r="CR13" t="n">
         <v>22.8984489302328</v>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="n">
-        <v>20.41665419866183</v>
+        <v>20.41665415391419</v>
       </c>
       <c r="CV13" t="n">
         <v>21.4397853371747</v>
@@ -5388,7 +5388,7 @@
         <v>-2.398551559568773</v>
       </c>
       <c r="DB13" t="n">
-        <v>3.27088379324858</v>
+        <v>3.270883566907457</v>
       </c>
       <c r="DC13" t="inlineStr">
         <is>
@@ -5720,10 +5720,10 @@
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>3.241822753914691</v>
+        <v>3.241822751043931</v>
       </c>
       <c r="CN14" t="n">
-        <v>6.013581208511751</v>
+        <v>6.013581203186491</v>
       </c>
       <c r="CO14" t="n">
         <v>19.81979119280974</v>
@@ -5732,7 +5732,7 @@
         <v>13.58186553210178</v>
       </c>
       <c r="CQ14" t="n">
-        <v>31.89281582914272</v>
+        <v>31.89281582076967</v>
       </c>
       <c r="CR14" t="n">
         <v>10.95072400487419</v>
@@ -6087,10 +6087,10 @@
         <v>0</v>
       </c>
       <c r="CM15" t="n">
-        <v>10.89909389451577</v>
+        <v>10.89909385310484</v>
       </c>
       <c r="CN15" t="n">
-        <v>20.21781917432674</v>
+        <v>20.21781909750947</v>
       </c>
       <c r="CO15" t="n">
         <v>37.45389651797344</v>
@@ -6099,25 +6099,25 @@
         <v>36.91124241178991</v>
       </c>
       <c r="CQ15" t="n">
-        <v>41.40373337242274</v>
+        <v>41.40373335666359</v>
       </c>
       <c r="CR15" t="n">
-        <v>34.46332757732285</v>
+        <v>34.46332758610621</v>
       </c>
       <c r="CS15" t="n">
-        <v>18.32822061669933</v>
+        <v>18.32822066472938</v>
       </c>
       <c r="CT15" t="n">
         <v>32.58677052647363</v>
       </c>
       <c r="CU15" t="n">
-        <v>31.62357288528694</v>
+        <v>31.62357288017795</v>
       </c>
       <c r="CV15" t="n">
-        <v>34.46332757732285</v>
+        <v>34.46332758610621</v>
       </c>
       <c r="CW15" t="n">
-        <v>31.01699481959056</v>
+        <v>31.01699482749559</v>
       </c>
       <c r="CX15" t="n">
         <v>7</v>
@@ -6129,10 +6129,10 @@
         <v>3.8</v>
       </c>
       <c r="DA15" t="n">
-        <v>74.44878302444225</v>
+        <v>74.44878306890246</v>
       </c>
       <c r="DB15" t="n">
-        <v>77.86035806533624</v>
+        <v>77.86035803660174</v>
       </c>
       <c r="DC15" t="inlineStr">
         <is>
@@ -6464,37 +6464,37 @@
         <v>0</v>
       </c>
       <c r="CM16" t="n">
-        <v>24.64526614095033</v>
+        <v>24.6452661183992</v>
       </c>
       <c r="CN16" t="n">
-        <v>31.16419469650378</v>
+        <v>31.16419473185438</v>
       </c>
       <c r="CO16" t="n">
-        <v>34.7502116923207</v>
+        <v>34.75021176353649</v>
       </c>
       <c r="CP16" t="n">
         <v>36.07661496384414</v>
       </c>
       <c r="CQ16" t="n">
-        <v>48.86831564954903</v>
+        <v>48.86831569478055</v>
       </c>
       <c r="CR16" t="n">
-        <v>48.59901754127608</v>
+        <v>48.59901755120379</v>
       </c>
       <c r="CS16" t="n">
-        <v>16.65417716234137</v>
+        <v>16.65417721304533</v>
       </c>
       <c r="CT16" t="n">
         <v>31.14870262855163</v>
       </c>
       <c r="CU16" t="n">
-        <v>33.98831255941713</v>
+        <v>33.98831258315194</v>
       </c>
       <c r="CV16" t="n">
-        <v>32.95720319441224</v>
+        <v>32.95720324769543</v>
       </c>
       <c r="CW16" t="n">
-        <v>29.66148287497102</v>
+        <v>29.66148292292589</v>
       </c>
       <c r="CX16" t="n">
         <v>8</v>
@@ -6506,10 +6506,10 @@
         <v>2.9</v>
       </c>
       <c r="DA16" t="n">
-        <v>-13.47291735353027</v>
+        <v>-13.47291721363859</v>
       </c>
       <c r="DB16" t="n">
-        <v>-0.8508933204977365</v>
+        <v>-0.8508932512596767</v>
       </c>
       <c r="DC16" t="inlineStr">
         <is>
@@ -6835,10 +6835,10 @@
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>5.334787419611792</v>
+        <v>5.334787411855786</v>
       </c>
       <c r="CN17" t="n">
-        <v>9.896030663379873</v>
+        <v>9.896030648992484</v>
       </c>
       <c r="CO17" t="n">
         <v>8.503043610116709</v>
@@ -6909,7 +6909,7 @@
         <v>0.2717388663546538</v>
       </c>
       <c r="DO17" t="n">
-        <v>-24.4203010953975</v>
+        <v>-24.42029364136734</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="CM18" t="n">
-        <v>3.558471593280884</v>
+        <v>3.558471602966997</v>
       </c>
       <c r="CN18" t="n">
-        <v>6.600964805536039</v>
+        <v>6.60096482350378</v>
       </c>
       <c r="CO18" t="n">
         <v>19.66796809186538</v>
@@ -7206,13 +7206,13 @@
         <v>18.52055498018046</v>
       </c>
       <c r="CQ18" t="n">
-        <v>20.69777961721432</v>
+        <v>20.69777961533053</v>
       </c>
       <c r="CR18" t="n">
-        <v>15.89091661367094</v>
+        <v>15.89091661176179</v>
       </c>
       <c r="CS18" t="n">
-        <v>12.89801918797098</v>
+        <v>12.89801917568821</v>
       </c>
       <c r="CT18" t="n">
         <v>29.41436415825995</v>
@@ -7268,7 +7268,7 @@
         <v>-0.9556959875251736</v>
       </c>
       <c r="DO18" t="n">
-        <v>-30.95847443251961</v>
+        <v>-30.95849087040471</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -7561,37 +7561,37 @@
         <v>0</v>
       </c>
       <c r="CM19" t="n">
-        <v>10.71852591632453</v>
+        <v>10.71852592981897</v>
       </c>
       <c r="CN19" t="n">
-        <v>16.81931637963456</v>
+        <v>16.81931635082226</v>
       </c>
       <c r="CO19" t="n">
-        <v>20.69399626312308</v>
+        <v>20.69399620161987</v>
       </c>
       <c r="CP19" t="n">
         <v>17.56096669750601</v>
       </c>
       <c r="CQ19" t="n">
-        <v>34.52474410993924</v>
+        <v>34.52474409552667</v>
       </c>
       <c r="CR19" t="n">
-        <v>23.92681846636332</v>
+        <v>23.92681846053856</v>
       </c>
       <c r="CS19" t="n">
-        <v>10.34281215525262</v>
+        <v>10.34281212568361</v>
       </c>
       <c r="CT19" t="n">
         <v>10.6899995803833</v>
       </c>
       <c r="CU19" t="n">
-        <v>18.15964744606583</v>
+        <v>18.15964743023741</v>
       </c>
       <c r="CV19" t="n">
-        <v>17.19014153857029</v>
+        <v>17.19014152416413</v>
       </c>
       <c r="CW19" t="n">
-        <v>15.47112738471326</v>
+        <v>15.47112737174772</v>
       </c>
       <c r="CX19" t="n">
         <v>8</v>
@@ -7603,10 +7603,10 @@
         <v>3.3</v>
       </c>
       <c r="DA19" t="n">
-        <v>44.72523846589831</v>
+        <v>44.72523834461168</v>
       </c>
       <c r="DB19" t="n">
-        <v>69.87509970898147</v>
+        <v>69.87509956091387</v>
       </c>
       <c r="DC19" t="inlineStr">
         <is>
@@ -7938,37 +7938,37 @@
         <v>1</v>
       </c>
       <c r="CM20" t="n">
-        <v>9.929939038231703</v>
+        <v>9.929939060311767</v>
       </c>
       <c r="CN20" t="n">
-        <v>17.62243058466343</v>
+        <v>17.62243046603763</v>
       </c>
       <c r="CO20" t="n">
-        <v>20.83047608552275</v>
+        <v>20.83047589898358</v>
       </c>
       <c r="CP20" t="n">
         <v>12.8457780532356</v>
       </c>
       <c r="CQ20" t="n">
-        <v>29.22488345685356</v>
+        <v>29.22488338744555</v>
       </c>
       <c r="CR20" t="n">
-        <v>24.97734503099647</v>
+        <v>24.9773450146415</v>
       </c>
       <c r="CS20" t="n">
-        <v>10.24067500952215</v>
+        <v>10.24067493805693</v>
       </c>
       <c r="CT20" t="n">
         <v>9.713052205096755</v>
       </c>
       <c r="CU20" t="n">
-        <v>16.9230724330153</v>
+        <v>16.92307237797617</v>
       </c>
       <c r="CV20" t="n">
-        <v>15.23410431894952</v>
+        <v>15.23410425963662</v>
       </c>
       <c r="CW20" t="n">
-        <v>13.71069388705456</v>
+        <v>13.71069383367296</v>
       </c>
       <c r="CX20" t="n">
         <v>8</v>
@@ -7980,10 +7980,10 @@
         <v>3</v>
       </c>
       <c r="DA20" t="n">
-        <v>19.53525342511771</v>
+        <v>19.53525295971572</v>
       </c>
       <c r="DB20" t="n">
-        <v>47.5420404449481</v>
+        <v>47.54203996509516</v>
       </c>
       <c r="DC20" t="inlineStr">
         <is>
@@ -8287,10 +8287,10 @@
         <v>1</v>
       </c>
       <c r="CM21" t="n">
-        <v>4.411578442586008</v>
+        <v>4.411578432089268</v>
       </c>
       <c r="CN21" t="n">
-        <v>8.183478010997044</v>
+        <v>8.183477991525592</v>
       </c>
       <c r="CO21" t="n">
         <v>13.99193579150784</v>
@@ -8299,23 +8299,23 @@
         <v>9.385319019937953</v>
       </c>
       <c r="CQ21" t="n">
-        <v>16.2483853489335</v>
+        <v>16.24838538185653</v>
       </c>
       <c r="CR21" t="n">
-        <v>9.212292048299943</v>
+        <v>9.212292051566077</v>
       </c>
       <c r="CS21" t="n">
-        <v>10.67142030010683</v>
+        <v>10.67142032642342</v>
       </c>
       <c r="CT21" t="inlineStr"/>
       <c r="CU21" t="n">
-        <v>8.94982107334771</v>
+        <v>8.949821066672195</v>
       </c>
       <c r="CV21" t="n">
-        <v>8.697885029648493</v>
+        <v>8.697885021545835</v>
       </c>
       <c r="CW21" t="n">
-        <v>7.828096526683644</v>
+        <v>7.828096519391251</v>
       </c>
       <c r="CX21" t="n">
         <v>4</v>
@@ -8327,10 +8327,10 @@
         <v>3.2</v>
       </c>
       <c r="DA21" t="n">
-        <v>-54.88128902265463</v>
+        <v>-54.88128906468572</v>
       </c>
       <c r="DB21" t="n">
-        <v>-48.41601800247588</v>
+        <v>-48.41601804095147</v>
       </c>
       <c r="DC21" t="inlineStr">
         <is>
@@ -8642,10 +8642,10 @@
         <v>1</v>
       </c>
       <c r="CM22" t="n">
-        <v>38.13263669812871</v>
+        <v>38.13263668885346</v>
       </c>
       <c r="CN22" t="n">
-        <v>55.52111903247541</v>
+        <v>55.52111901897064</v>
       </c>
       <c r="CO22" t="n">
         <v>49.21407329373137</v>
@@ -8662,13 +8662,13 @@
       </c>
       <c r="CT22" t="inlineStr"/>
       <c r="CU22" t="n">
-        <v>50.5929985020383</v>
+        <v>50.5929984963433</v>
       </c>
       <c r="CV22" t="n">
-        <v>52.36759616310339</v>
+        <v>52.36759615635101</v>
       </c>
       <c r="CW22" t="n">
-        <v>47.13083654679306</v>
+        <v>47.13083654071591</v>
       </c>
       <c r="CX22" t="n">
         <v>4</v>
@@ -8680,10 +8680,10 @@
         <v>1.6</v>
       </c>
       <c r="DA22" t="n">
-        <v>13.05070304463469</v>
+        <v>13.05070303005771</v>
       </c>
       <c r="DB22" t="n">
-        <v>21.35524146941454</v>
+        <v>21.3552414557542</v>
       </c>
       <c r="DC22" t="inlineStr">
         <is>
@@ -9007,10 +9007,10 @@
         <v>0</v>
       </c>
       <c r="CM23" t="n">
-        <v>8.042725730627229</v>
+        <v>8.042725692874045</v>
       </c>
       <c r="CN23" t="n">
-        <v>14.91925623031351</v>
+        <v>14.91925616028136</v>
       </c>
       <c r="CO23" t="n">
         <v>35.8092168347706</v>
@@ -9019,25 +9019,25 @@
         <v>28.26533205663885</v>
       </c>
       <c r="CQ23" t="n">
-        <v>42.37839875494011</v>
+        <v>42.37839881633204</v>
       </c>
       <c r="CR23" t="n">
-        <v>26.26934026621138</v>
+        <v>26.26934027562648</v>
       </c>
       <c r="CS23" t="n">
-        <v>27.55520342712055</v>
+        <v>27.55520349529375</v>
       </c>
       <c r="CT23" t="n">
         <v>25.97235352964724</v>
       </c>
       <c r="CU23" t="n">
-        <v>28.7384430142346</v>
+        <v>28.73844302408433</v>
       </c>
       <c r="CV23" t="n">
-        <v>27.55520342712055</v>
+        <v>27.55520349529375</v>
       </c>
       <c r="CW23" t="n">
-        <v>24.7996830844085</v>
+        <v>24.79968314576438</v>
       </c>
       <c r="CX23" t="n">
         <v>7</v>
@@ -9049,10 +9049,10 @@
         <v>5.3</v>
       </c>
       <c r="DA23" t="n">
-        <v>-18.28770091367111</v>
+        <v>-18.28770071151008</v>
       </c>
       <c r="DB23" t="n">
-        <v>-5.309908886258407</v>
+        <v>-5.309908853804624</v>
       </c>
       <c r="DC23" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>3.126062068481006</v>
       </c>
       <c r="DO23" t="n">
-        <v>-13.96944189921097</v>
+        <v>-13.9694512434398</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -9384,10 +9384,10 @@
         <v>0</v>
       </c>
       <c r="CM24" t="n">
-        <v>3.282331944822721</v>
+        <v>3.282331942632095</v>
       </c>
       <c r="CN24" t="n">
-        <v>6.088725757646146</v>
+        <v>6.088725753582535</v>
       </c>
       <c r="CO24" t="n">
         <v>32.87073625430369</v>
@@ -9396,13 +9396,13 @@
         <v>27.40079604823567</v>
       </c>
       <c r="CQ24" t="n">
-        <v>42.09062502638077</v>
+        <v>42.09062502875422</v>
       </c>
       <c r="CR24" t="n">
-        <v>10.85262429563273</v>
+        <v>10.8526242958474</v>
       </c>
       <c r="CS24" t="n">
-        <v>30.004898520376</v>
+        <v>30.00489852392306</v>
       </c>
       <c r="CT24" t="n">
         <v>15.129152615152</v>
@@ -9751,10 +9751,10 @@
         <v>1</v>
       </c>
       <c r="CM25" t="n">
-        <v>3.454280439615057</v>
+        <v>3.454280447251831</v>
       </c>
       <c r="CN25" t="n">
-        <v>6.407690215485931</v>
+        <v>6.407690229652147</v>
       </c>
       <c r="CO25" t="n">
         <v>32.60530006759157</v>
@@ -9763,7 +9763,7 @@
         <v>22.82658483654052</v>
       </c>
       <c r="CQ25" t="n">
-        <v>40.32932307964481</v>
+        <v>40.32932308720063</v>
       </c>
       <c r="CR25" t="n">
         <v>10.59424454785779</v>
@@ -10090,35 +10090,35 @@
         <v>1</v>
       </c>
       <c r="CM26" t="n">
-        <v>9.776498545188147</v>
+        <v>9.776498548817115</v>
       </c>
       <c r="CN26" t="n">
-        <v>17.80202359189347</v>
+        <v>17.80202359127176</v>
       </c>
       <c r="CO26" t="n">
-        <v>30.41950848304267</v>
+        <v>30.4195084706888</v>
       </c>
       <c r="CP26" t="n">
         <v>29.46192052472633</v>
       </c>
       <c r="CQ26" t="n">
-        <v>34.13596351979948</v>
+        <v>34.13596352020357</v>
       </c>
       <c r="CR26" t="n">
-        <v>25.40854575454435</v>
+        <v>25.40854575380762</v>
       </c>
       <c r="CS26" t="n">
-        <v>14.86407026880161</v>
+        <v>14.86407026428921</v>
       </c>
       <c r="CT26" t="inlineStr"/>
       <c r="CU26" t="n">
-        <v>20.85164409366716</v>
+        <v>20.85164409114633</v>
       </c>
       <c r="CV26" t="n">
-        <v>21.60528467321891</v>
+        <v>21.60528467253969</v>
       </c>
       <c r="CW26" t="n">
-        <v>19.44475620589702</v>
+        <v>19.44475620528572</v>
       </c>
       <c r="CX26" t="n">
         <v>4</v>
@@ -10130,10 +10130,10 @@
         <v>3.1</v>
       </c>
       <c r="DA26" t="n">
-        <v>24.08906261151616</v>
+        <v>24.08906260761505</v>
       </c>
       <c r="DB26" t="n">
-        <v>33.0672877609756</v>
+        <v>33.06728774488859</v>
       </c>
       <c r="DC26" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>0.5131489603787731</v>
       </c>
       <c r="DO26" t="n">
-        <v>-13.7574412679755</v>
+        <v>-13.75743191410359</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -10445,35 +10445,35 @@
         <v>1</v>
       </c>
       <c r="CM27" t="n">
-        <v>9.277652139429566</v>
+        <v>9.277652160030563</v>
       </c>
       <c r="CN27" t="n">
-        <v>13.27564819194827</v>
+        <v>13.27564817199024</v>
       </c>
       <c r="CO27" t="n">
-        <v>16.56076855305461</v>
+        <v>16.56076849138475</v>
       </c>
       <c r="CP27" t="n">
         <v>17.47664780944146</v>
       </c>
       <c r="CQ27" t="n">
-        <v>21.53940889610869</v>
+        <v>21.53940887428282</v>
       </c>
       <c r="CR27" t="n">
-        <v>17.16868987321791</v>
+        <v>17.16868986752019</v>
       </c>
       <c r="CS27" t="n">
-        <v>8.23977507854878</v>
+        <v>8.239775043451273</v>
       </c>
       <c r="CT27" t="inlineStr"/>
       <c r="CU27" t="n">
-        <v>14.07068968941259</v>
+        <v>14.07068967273144</v>
       </c>
       <c r="CV27" t="n">
-        <v>14.91820837250144</v>
+        <v>14.9182083316875</v>
       </c>
       <c r="CW27" t="n">
-        <v>13.4263875352513</v>
+        <v>13.42638749851875</v>
       </c>
       <c r="CX27" t="n">
         <v>4</v>
@@ -10485,10 +10485,10 @@
         <v>1.9</v>
       </c>
       <c r="DA27" t="n">
-        <v>-2.282476281594181</v>
+        <v>-2.282476548934431</v>
       </c>
       <c r="DB27" t="n">
-        <v>2.406768004389237</v>
+        <v>2.406767882983463</v>
       </c>
       <c r="DC27" t="inlineStr">
         <is>
@@ -10816,37 +10816,37 @@
         <v>0</v>
       </c>
       <c r="CM28" t="n">
-        <v>17.67458142527642</v>
+        <v>17.67458159617798</v>
       </c>
       <c r="CN28" t="n">
-        <v>28.38448059056153</v>
+        <v>28.38448060874346</v>
       </c>
       <c r="CO28" t="n">
-        <v>45.95076189163861</v>
+        <v>45.95076147675917</v>
       </c>
       <c r="CP28" t="n">
         <v>53.20634261756088</v>
       </c>
       <c r="CQ28" t="n">
-        <v>55.32499940553003</v>
+        <v>55.32499944818458</v>
       </c>
       <c r="CR28" t="n">
-        <v>42.93273389305169</v>
+        <v>42.93273386196931</v>
       </c>
       <c r="CS28" t="n">
-        <v>22.93541935282174</v>
+        <v>22.93541916167177</v>
       </c>
       <c r="CT28" t="n">
         <v>32.58624815427083</v>
       </c>
       <c r="CU28" t="n">
-        <v>37.37444591633897</v>
+        <v>37.37444586566725</v>
       </c>
       <c r="CV28" t="n">
-        <v>37.75949102366126</v>
+        <v>37.75949100812007</v>
       </c>
       <c r="CW28" t="n">
-        <v>33.98354192129514</v>
+        <v>33.98354190730807</v>
       </c>
       <c r="CX28" t="n">
         <v>8</v>
@@ -10858,10 +10858,10 @@
         <v>3.1</v>
       </c>
       <c r="DA28" t="n">
-        <v>22.95058853735881</v>
+        <v>22.95058848675435</v>
       </c>
       <c r="DB28" t="n">
-        <v>35.21869298715041</v>
+        <v>35.2186928038229</v>
       </c>
       <c r="DC28" t="inlineStr">
         <is>
@@ -11175,10 +11175,10 @@
         <v>1</v>
       </c>
       <c r="CM29" t="n">
-        <v>21.46693978154572</v>
+        <v>21.46693980023627</v>
       </c>
       <c r="CN29" t="n">
-        <v>39.82117329476731</v>
+        <v>39.82117332943828</v>
       </c>
       <c r="CO29" t="n">
         <v>55.9919330381578</v>
@@ -11187,23 +11187,23 @@
         <v>42.27700822726509</v>
       </c>
       <c r="CQ29" t="n">
-        <v>57.69484333055969</v>
+        <v>57.6948432981931</v>
       </c>
       <c r="CR29" t="n">
-        <v>44.75889536530346</v>
+        <v>44.75889535946022</v>
       </c>
       <c r="CS29" t="n">
-        <v>28.51101666054624</v>
+        <v>28.51101662362118</v>
       </c>
       <c r="CT29" t="inlineStr"/>
       <c r="CU29" t="n">
-        <v>40.50973536994357</v>
+        <v>40.50973538182314</v>
       </c>
       <c r="CV29" t="n">
-        <v>42.29003433003538</v>
+        <v>42.29003434444925</v>
       </c>
       <c r="CW29" t="n">
-        <v>38.06103089703185</v>
+        <v>38.06103091000433</v>
       </c>
       <c r="CX29" t="n">
         <v>4</v>
@@ -11215,10 +11215,10 @@
         <v>2.6</v>
       </c>
       <c r="DA29" t="n">
-        <v>-9.205552100362969</v>
+        <v>-9.205552069417166</v>
       </c>
       <c r="DB29" t="n">
-        <v>-3.364176671282582</v>
+        <v>-3.364176642943906</v>
       </c>
       <c r="DC29" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>1.231582524541053</v>
       </c>
       <c r="DO29" t="n">
-        <v>-13.88059873687392</v>
+        <v>-13.88060552690588</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -11550,10 +11550,10 @@
         <v>1</v>
       </c>
       <c r="CM30" t="n">
-        <v>7.897647836613209</v>
+        <v>7.897647825800325</v>
       </c>
       <c r="CN30" t="n">
-        <v>14.6501367369175</v>
+        <v>14.6501367168596</v>
       </c>
       <c r="CO30" t="n">
         <v>5.689554995371402</v>
@@ -11574,7 +11574,7 @@
         <v>5.468016983754021</v>
       </c>
       <c r="CU30" t="n">
-        <v>7.691147608487336</v>
+        <v>7.691147604628489</v>
       </c>
       <c r="CV30" t="n">
         <v>5.911444164352368</v>
@@ -11595,7 +11595,7 @@
         <v>-20.11561757040502</v>
       </c>
       <c r="DB30" t="n">
-        <v>15.48269946996923</v>
+        <v>15.48269941202858</v>
       </c>
       <c r="DC30" t="inlineStr">
         <is>
@@ -11923,37 +11923,37 @@
         <v>1</v>
       </c>
       <c r="CM31" t="n">
-        <v>6.114135535995681</v>
+        <v>6.114135551504001</v>
       </c>
       <c r="CN31" t="n">
-        <v>8.340738435580306</v>
+        <v>8.34073842373572</v>
       </c>
       <c r="CO31" t="n">
-        <v>10.22416127343144</v>
+        <v>10.22416123297895</v>
       </c>
       <c r="CP31" t="n">
         <v>11.61068843321866</v>
       </c>
       <c r="CQ31" t="n">
-        <v>9.255439703174281</v>
+        <v>9.255439677680009</v>
       </c>
       <c r="CR31" t="n">
-        <v>14.83896368390577</v>
+        <v>14.83896367844126</v>
       </c>
       <c r="CS31" t="n">
-        <v>5.038565287865116</v>
+        <v>5.038565262754045</v>
       </c>
       <c r="CT31" t="n">
         <v>11.35371417455445</v>
       </c>
       <c r="CU31" t="n">
-        <v>9.597050815965712</v>
+        <v>9.597050804358386</v>
       </c>
       <c r="CV31" t="n">
-        <v>9.739800488302858</v>
+        <v>9.739800455329476</v>
       </c>
       <c r="CW31" t="n">
-        <v>8.765820439472574</v>
+        <v>8.765820409796529</v>
       </c>
       <c r="CX31" t="n">
         <v>8</v>
@@ -11965,10 +11965,10 @@
         <v>2.9</v>
       </c>
       <c r="DA31" t="n">
-        <v>-44.3793127400576</v>
+        <v>-44.37931292835736</v>
       </c>
       <c r="DB31" t="n">
-        <v>-39.10500839728339</v>
+        <v>-39.10500847093395</v>
       </c>
       <c r="DC31" t="inlineStr">
         <is>
@@ -12292,37 +12292,37 @@
         <v>0</v>
       </c>
       <c r="CM32" t="n">
-        <v>33.11882886863602</v>
+        <v>33.11882880409752</v>
       </c>
       <c r="CN32" t="n">
-        <v>34.05828920006064</v>
+        <v>34.05828924298923</v>
       </c>
       <c r="CO32" t="n">
-        <v>34.64295533345696</v>
+        <v>34.64295544463105</v>
       </c>
       <c r="CP32" t="n">
         <v>49.91001401454295</v>
       </c>
       <c r="CQ32" t="n">
-        <v>54.23229186947442</v>
+        <v>54.23229194888883</v>
       </c>
       <c r="CR32" t="n">
-        <v>17.39224951049831</v>
+        <v>17.39224951718627</v>
       </c>
       <c r="CS32" t="n">
-        <v>13.60670811502123</v>
+        <v>13.60670822940412</v>
       </c>
       <c r="CT32" t="n">
         <v>30.48327237497478</v>
       </c>
       <c r="CU32" t="n">
-        <v>33.43057616083317</v>
+        <v>33.43057619708934</v>
       </c>
       <c r="CV32" t="n">
-        <v>33.58855903434834</v>
+        <v>33.58855902354338</v>
       </c>
       <c r="CW32" t="n">
-        <v>30.2297031309135</v>
+        <v>30.22970312118904</v>
       </c>
       <c r="CX32" t="n">
         <v>8</v>
@@ -12334,10 +12334,10 @@
         <v>4</v>
       </c>
       <c r="DA32" t="n">
-        <v>-27.24499714563147</v>
+        <v>-27.24499716903571</v>
       </c>
       <c r="DB32" t="n">
-        <v>-19.54133146887101</v>
+        <v>-19.54133138161186</v>
       </c>
       <c r="DC32" t="inlineStr">
         <is>
@@ -12643,35 +12643,35 @@
         <v>1</v>
       </c>
       <c r="CM33" t="n">
-        <v>10.6268533482049</v>
+        <v>10.62685337831266</v>
       </c>
       <c r="CN33" t="n">
-        <v>17.64942995460184</v>
+        <v>17.64942994959144</v>
       </c>
       <c r="CO33" t="n">
-        <v>27.73251609334911</v>
+        <v>27.73251600690513</v>
       </c>
       <c r="CP33" t="n">
         <v>29.43493108570705</v>
       </c>
       <c r="CQ33" t="n">
-        <v>31.55991137560471</v>
+        <v>31.55991137143432</v>
       </c>
       <c r="CR33" t="n">
-        <v>27.78221466362887</v>
+        <v>27.78221465689651</v>
       </c>
       <c r="CS33" t="n">
-        <v>13.79408528950043</v>
+        <v>13.79408525206323</v>
       </c>
       <c r="CT33" t="inlineStr"/>
       <c r="CU33" t="n">
-        <v>20.94775351494618</v>
+        <v>20.94775349792643</v>
       </c>
       <c r="CV33" t="n">
-        <v>22.69097302397547</v>
+        <v>22.69097297824829</v>
       </c>
       <c r="CW33" t="n">
-        <v>20.42187572157793</v>
+        <v>20.42187568042346</v>
       </c>
       <c r="CX33" t="n">
         <v>4</v>
@@ -12683,10 +12683,10 @@
         <v>2.6</v>
       </c>
       <c r="DA33" t="n">
-        <v>14.79412406186809</v>
+        <v>14.79412383053324</v>
       </c>
       <c r="DB33" t="n">
-        <v>17.75015422659541</v>
+        <v>17.75015413092511</v>
       </c>
       <c r="DC33" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>0.2253572705765761</v>
       </c>
       <c r="DO33" t="n">
-        <v>-16.147447880327</v>
+        <v>-16.14745557185274</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -13022,10 +13022,10 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>27.71225740650887</v>
+        <v>27.71225737706116</v>
       </c>
       <c r="CN34" t="n">
-        <v>51.40623748907394</v>
+        <v>51.40623743444844</v>
       </c>
       <c r="CO34" t="n">
         <v>69.02703388345945</v>
@@ -13034,25 +13034,25 @@
         <v>48.07470647599711</v>
       </c>
       <c r="CQ34" t="n">
-        <v>78.40063152040356</v>
+        <v>78.40063158340526</v>
       </c>
       <c r="CR34" t="n">
-        <v>61.78172617286008</v>
+        <v>61.78172618496546</v>
       </c>
       <c r="CS34" t="n">
-        <v>36.01038477538081</v>
+        <v>36.01038484387148</v>
       </c>
       <c r="CT34" t="n">
         <v>80.3272793905405</v>
       </c>
       <c r="CU34" t="n">
-        <v>56.59253213927804</v>
+        <v>56.59253214671861</v>
       </c>
       <c r="CV34" t="n">
-        <v>56.59398183096701</v>
+        <v>56.59398180970695</v>
       </c>
       <c r="CW34" t="n">
-        <v>50.93458364787031</v>
+        <v>50.93458362873626</v>
       </c>
       <c r="CX34" t="n">
         <v>8</v>
@@ -13064,10 +13064,10 @@
         <v>2.9</v>
       </c>
       <c r="DA34" t="n">
-        <v>8.997612126731823</v>
+        <v>8.997612085785844</v>
       </c>
       <c r="DB34" t="n">
-        <v>21.10535564659612</v>
+        <v>21.10535566251859</v>
       </c>
       <c r="DC34" t="inlineStr">
         <is>
@@ -13373,10 +13373,10 @@
         <v>0</v>
       </c>
       <c r="CM35" t="n">
-        <v>11.49820300177474</v>
+        <v>11.49820300028505</v>
       </c>
       <c r="CN35" t="n">
-        <v>21.32916656829214</v>
+        <v>21.32916656552876</v>
       </c>
       <c r="CO35" t="n">
         <v>61.99144933938789</v>
@@ -13385,7 +13385,7 @@
         <v>46.3637511199616</v>
       </c>
       <c r="CQ35" t="n">
-        <v>82.98527148959519</v>
+        <v>82.98527148793602</v>
       </c>
       <c r="CR35" t="n">
         <v>11.76833333333333</v>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="CT35" t="inlineStr"/>
       <c r="CU35" t="n">
-        <v>14.8652343011334</v>
+        <v>14.86523429971571</v>
       </c>
       <c r="CV35" t="n">
         <v>11.76833333333333</v>
@@ -13416,7 +13416,7 @@
         <v>-81.99030819133732</v>
       </c>
       <c r="DB35" t="n">
-        <v>-74.72328863456794</v>
+        <v>-74.72328863697857</v>
       </c>
       <c r="DC35" t="inlineStr">
         <is>
@@ -13730,10 +13730,10 @@
         <v>0</v>
       </c>
       <c r="CM36" t="n">
-        <v>15.91082427938901</v>
+        <v>15.91082428045713</v>
       </c>
       <c r="CN36" t="n">
-        <v>29.51457903826661</v>
+        <v>29.51457904024798</v>
       </c>
       <c r="CO36" t="n">
         <v>54.72591683531388</v>
@@ -13742,23 +13742,23 @@
         <v>49.38251180555442</v>
       </c>
       <c r="CQ36" t="n">
-        <v>60.07811897687782</v>
+        <v>60.07811897656059</v>
       </c>
       <c r="CR36" t="n">
-        <v>36.56479138774561</v>
+        <v>36.56479138755189</v>
       </c>
       <c r="CS36" t="n">
-        <v>29.79907882455338</v>
+        <v>29.7990788230786</v>
       </c>
       <c r="CT36" t="inlineStr"/>
       <c r="CU36" t="n">
-        <v>34.17902788517878</v>
+        <v>34.17902788589272</v>
       </c>
       <c r="CV36" t="n">
-        <v>33.03968521300611</v>
+        <v>33.03968521389994</v>
       </c>
       <c r="CW36" t="n">
-        <v>29.7357166917055</v>
+        <v>29.73571669250994</v>
       </c>
       <c r="CX36" t="n">
         <v>4</v>
@@ -13770,10 +13770,10 @@
         <v>3.4</v>
       </c>
       <c r="DA36" t="n">
-        <v>-2.313678810761299</v>
+        <v>-2.31367880811858</v>
       </c>
       <c r="DB36" t="n">
-        <v>12.28326966334239</v>
+        <v>12.2832696656878</v>
       </c>
       <c r="DC36" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>1.4328567207472</v>
       </c>
       <c r="DO36" t="n">
-        <v>-16.50913757078116</v>
+        <v>-16.5091286271213</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -14103,10 +14103,10 @@
         <v>0</v>
       </c>
       <c r="CM37" t="n">
-        <v>13.92259622711488</v>
+        <v>13.92259633446643</v>
       </c>
       <c r="CN37" t="n">
-        <v>20.27130010667927</v>
+        <v>20.27130026298312</v>
       </c>
       <c r="CO37" t="n">
         <v>16.70574758244657</v>
@@ -14125,7 +14125,7 @@
         <v>15.45433621078142</v>
       </c>
       <c r="CU37" t="n">
-        <v>16.60794743812201</v>
+        <v>16.60794748206458</v>
       </c>
       <c r="CV37" t="n">
         <v>16.080041896614</v>
@@ -14146,7 +14146,7 @@
         <v>29.44577202071063</v>
       </c>
       <c r="DB37" t="n">
-        <v>48.55050970287868</v>
+        <v>48.55051009592491</v>
       </c>
       <c r="DC37" t="inlineStr">
         <is>
@@ -14478,10 +14478,10 @@
         <v>0</v>
       </c>
       <c r="CM38" t="n">
-        <v>9.424600981239182</v>
+        <v>9.424600952514027</v>
       </c>
       <c r="CN38" t="n">
-        <v>17.48263482019868</v>
+        <v>17.48263476691352</v>
       </c>
       <c r="CO38" t="n">
         <v>17.0502564055361</v>
@@ -14490,7 +14490,7 @@
         <v>16.93163083998861</v>
       </c>
       <c r="CQ38" t="n">
-        <v>26.97723554612757</v>
+        <v>26.97723552038159</v>
       </c>
       <c r="CR38" t="n">
         <v>19.94489718117502</v>
@@ -14502,7 +14502,7 @@
         <v>17.36889744184579</v>
       </c>
       <c r="CU38" t="n">
-        <v>17.53315802079863</v>
+        <v>17.53315800732909</v>
       </c>
       <c r="CV38" t="n">
         <v>17.20957692369095</v>
@@ -14523,7 +14523,7 @@
         <v>-22.94219434144452</v>
       </c>
       <c r="DB38" t="n">
-        <v>-12.77035976097532</v>
+        <v>-12.77035982798795</v>
       </c>
       <c r="DC38" t="inlineStr">
         <is>
@@ -15478,10 +15478,10 @@
         <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>14.34883231510244</v>
+        <v>14.34883233997342</v>
       </c>
       <c r="CN2" t="n">
-        <v>26.61708394451502</v>
+        <v>26.61708399065069</v>
       </c>
       <c r="CO2" t="n">
         <v>38.73764113094029</v>
@@ -15490,13 +15490,13 @@
         <v>23.42212306847306</v>
       </c>
       <c r="CQ2" t="n">
-        <v>77.21384549512003</v>
+        <v>77.21384545128907</v>
       </c>
       <c r="CR2" t="n">
-        <v>48.83647634904256</v>
+        <v>48.83647633066641</v>
       </c>
       <c r="CS2" t="n">
-        <v>27.96937491056918</v>
+        <v>27.96937483383525</v>
       </c>
       <c r="CT2" t="n">
         <v>9.042040250118818</v>
@@ -15837,10 +15837,10 @@
         <v>1</v>
       </c>
       <c r="CM3" t="n">
-        <v>6.74149677483709</v>
+        <v>6.7414967884217</v>
       </c>
       <c r="CN3" t="n">
-        <v>12.5054765173228</v>
+        <v>12.50547654252225</v>
       </c>
       <c r="CO3" t="n">
         <v>41.30882298882631</v>
@@ -15849,7 +15849,7 @@
         <v>27.77800617149056</v>
       </c>
       <c r="CQ3" t="n">
-        <v>72.00025469489329</v>
+        <v>72.00025474574477</v>
       </c>
       <c r="CR3" t="n">
         <v>19.57807411896471</v>
@@ -16204,10 +16204,10 @@
         <v>0</v>
       </c>
       <c r="CM4" t="n">
-        <v>17.1663830832182</v>
+        <v>17.16638305223679</v>
       </c>
       <c r="CN4" t="n">
-        <v>31.84364061936976</v>
+        <v>31.84364056189925</v>
       </c>
       <c r="CO4" t="n">
         <v>71.20842100924612</v>
@@ -16216,19 +16216,19 @@
         <v>51.68759722785042</v>
       </c>
       <c r="CQ4" t="n">
-        <v>122.395720483912</v>
+        <v>122.3957204994831</v>
       </c>
       <c r="CR4" t="n">
-        <v>25.57411552848948</v>
+        <v>25.57411553292391</v>
       </c>
       <c r="CS4" t="n">
-        <v>59.88502635963041</v>
+        <v>59.88502642609916</v>
       </c>
       <c r="CT4" t="n">
         <v>44.43438321477654</v>
       </c>
       <c r="CU4" t="n">
-        <v>47.43886399322712</v>
+        <v>47.4388639954659</v>
       </c>
       <c r="CV4" t="n">
         <v>48.06099022131347</v>
@@ -16249,7 +16249,7 @@
         <v>67.33033098981652</v>
       </c>
       <c r="DB4" t="n">
-        <v>83.51591215926295</v>
+        <v>83.5159121679236</v>
       </c>
       <c r="DC4" t="inlineStr">
         <is>
@@ -16571,10 +16571,10 @@
         <v>0</v>
       </c>
       <c r="CM5" t="n">
-        <v>3.907370963482954</v>
+        <v>3.907370941582745</v>
       </c>
       <c r="CN5" t="n">
-        <v>7.248173137260879</v>
+        <v>7.248173096635992</v>
       </c>
       <c r="CO5" t="n">
         <v>12.71763449268681</v>
@@ -16583,19 +16583,19 @@
         <v>8.551038591084707</v>
       </c>
       <c r="CQ5" t="n">
-        <v>23.90073392772668</v>
+        <v>23.90073394611848</v>
       </c>
       <c r="CR5" t="n">
-        <v>11.13506641444498</v>
+        <v>11.1350664234246</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.912220006362892</v>
+        <v>9.912220060941721</v>
       </c>
       <c r="CT5" t="n">
         <v>5.427221201663706</v>
       </c>
       <c r="CU5" t="n">
-        <v>8.414103543855276</v>
+        <v>8.414103544002897</v>
       </c>
       <c r="CV5" t="n">
         <v>8.551038591084707</v>
@@ -16616,7 +16616,7 @@
         <v>78.97521838623484</v>
       </c>
       <c r="DB5" t="n">
-        <v>95.67681792165965</v>
+        <v>95.67681792509268</v>
       </c>
       <c r="DC5" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>-0.9216580748084957</v>
       </c>
       <c r="DO5" t="n">
-        <v>-34.16759691282044</v>
+        <v>-34.16760193805087</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -16940,10 +16940,10 @@
         <v>1</v>
       </c>
       <c r="CM6" t="n">
-        <v>3.327945782710356</v>
+        <v>3.327945787913786</v>
       </c>
       <c r="CN6" t="n">
-        <v>6.17333942692771</v>
+        <v>6.173339436580072</v>
       </c>
       <c r="CO6" t="n">
         <v>12.71999984038503</v>
@@ -16952,25 +16952,25 @@
         <v>8.573475127812586</v>
       </c>
       <c r="CQ6" t="n">
-        <v>23.80124252649136</v>
+        <v>23.80124252119723</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.53241883504053</v>
+        <v>11.53241883287747</v>
       </c>
       <c r="CS6" t="n">
-        <v>11.35989496296809</v>
+        <v>11.35989495000031</v>
       </c>
       <c r="CT6" t="n">
         <v>5.406965820956791</v>
       </c>
       <c r="CU6" t="n">
-        <v>11.3667623629403</v>
+        <v>11.36676236140136</v>
       </c>
       <c r="CV6" t="n">
-        <v>11.35989496296809</v>
+        <v>11.35989495000031</v>
       </c>
       <c r="CW6" t="n">
-        <v>10.22390546667128</v>
+        <v>10.22390545500028</v>
       </c>
       <c r="CX6" t="n">
         <v>7</v>
@@ -16982,10 +16982,10 @@
         <v>7.2</v>
       </c>
       <c r="DA6" t="n">
-        <v>124.2084560299209</v>
+        <v>124.2084557739779</v>
       </c>
       <c r="DB6" t="n">
-        <v>149.2711075783854</v>
+        <v>149.2711075446366</v>
       </c>
       <c r="DC6" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>-0.8695644061371466</v>
       </c>
       <c r="DO6" t="n">
-        <v>-40.94616015020202</v>
+        <v>-40.94615637406525</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -17299,10 +17299,10 @@
         <v>1</v>
       </c>
       <c r="CM7" t="n">
-        <v>19.52675460330705</v>
+        <v>19.52675456025717</v>
       </c>
       <c r="CN7" t="n">
-        <v>36.22212978913458</v>
+        <v>36.22212970927706</v>
       </c>
       <c r="CO7" t="n">
         <v>75.52058089429198</v>
@@ -17311,23 +17311,23 @@
         <v>56.61657821085305</v>
       </c>
       <c r="CQ7" t="n">
-        <v>98.15037103580246</v>
+        <v>98.15037110641777</v>
       </c>
       <c r="CR7" t="n">
-        <v>48.15705803416046</v>
+        <v>48.15705804455569</v>
       </c>
       <c r="CS7" t="n">
-        <v>57.80670625323084</v>
+        <v>57.80670633975764</v>
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>44.85663083022352</v>
+        <v>44.85663080209548</v>
       </c>
       <c r="CV7" t="n">
-        <v>42.18959391164752</v>
+        <v>42.18959387691638</v>
       </c>
       <c r="CW7" t="n">
-        <v>37.97063452048277</v>
+        <v>37.97063448922474</v>
       </c>
       <c r="CX7" t="n">
         <v>4</v>
@@ -17339,10 +17339,10 @@
         <v>3.9</v>
       </c>
       <c r="DA7" t="n">
-        <v>-25.8965002406711</v>
+        <v>-25.89650030167426</v>
       </c>
       <c r="DB7" t="n">
-        <v>-12.45778813259845</v>
+        <v>-12.45778818749312</v>
       </c>
       <c r="DC7" t="inlineStr">
         <is>
@@ -17666,10 +17666,10 @@
         <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>6.403626929426027</v>
+        <v>6.403626923493396</v>
       </c>
       <c r="CN8" t="n">
-        <v>11.87872795408528</v>
+        <v>11.87872794308025</v>
       </c>
       <c r="CO8" t="n">
         <v>25.4012199436746</v>
@@ -17678,19 +17678,19 @@
         <v>18.64745536395598</v>
       </c>
       <c r="CQ8" t="n">
-        <v>35.23268455075863</v>
+        <v>35.23268456040559</v>
       </c>
       <c r="CR8" t="n">
-        <v>12.29886663373648</v>
+        <v>12.29886663486247</v>
       </c>
       <c r="CS8" t="n">
-        <v>20.3953979918496</v>
+        <v>20.39539800428012</v>
       </c>
       <c r="CT8" t="n">
         <v>18.89184945304214</v>
       </c>
       <c r="CU8" t="n">
-        <v>20.39231455587182</v>
+        <v>20.39231455761445</v>
       </c>
       <c r="CV8" t="n">
         <v>18.89184945304214</v>
@@ -17711,7 +17711,7 @@
         <v>8.159441596189932</v>
       </c>
       <c r="DB8" t="n">
-        <v>29.72210056918854</v>
+        <v>29.72210058027398</v>
       </c>
       <c r="DC8" t="inlineStr">
         <is>
@@ -18035,10 +18035,10 @@
         <v>1</v>
       </c>
       <c r="CM9" t="n">
-        <v>45.77695642116295</v>
+        <v>45.77695654203991</v>
       </c>
       <c r="CN9" t="n">
-        <v>84.91625416125727</v>
+        <v>84.91625438548404</v>
       </c>
       <c r="CO9" t="n">
         <v>68.18445585960495</v>
@@ -18059,7 +18059,7 @@
         <v>26.15892848466381</v>
       </c>
       <c r="CU9" t="n">
-        <v>71.11162365572162</v>
+        <v>71.11162369885957</v>
       </c>
       <c r="CV9" t="n">
         <v>65.22550777513155</v>
@@ -18080,7 +18080,7 @@
         <v>79.08163265306125</v>
       </c>
       <c r="DB9" t="n">
-        <v>116.9360167903183</v>
+        <v>116.9360169219168</v>
       </c>
       <c r="DC9" t="inlineStr">
         <is>
@@ -18412,37 +18412,37 @@
         <v>1</v>
       </c>
       <c r="CM10" t="n">
-        <v>24.36355412189999</v>
+        <v>24.36355405256904</v>
       </c>
       <c r="CN10" t="n">
-        <v>31.53570933459214</v>
+        <v>31.53570981245223</v>
       </c>
       <c r="CO10" t="n">
-        <v>32.96248398297526</v>
+        <v>32.96248457625602</v>
       </c>
       <c r="CP10" t="n">
         <v>20.75155156536448</v>
       </c>
       <c r="CQ10" t="n">
-        <v>47.31871742812845</v>
+        <v>47.31871796693122</v>
       </c>
       <c r="CR10" t="n">
-        <v>50.67250998000094</v>
+        <v>50.67251006901864</v>
       </c>
       <c r="CS10" t="n">
-        <v>15.96314803283591</v>
+        <v>15.96314843782849</v>
       </c>
       <c r="CT10" t="n">
         <v>24.59438222893265</v>
       </c>
       <c r="CU10" t="n">
-        <v>31.02025708434123</v>
+        <v>31.0202573386691</v>
       </c>
       <c r="CV10" t="n">
-        <v>28.0650457817624</v>
+        <v>28.06504602069244</v>
       </c>
       <c r="CW10" t="n">
-        <v>25.25854120358616</v>
+        <v>25.2585414186232</v>
       </c>
       <c r="CX10" t="n">
         <v>8</v>
@@ -18454,10 +18454,10 @@
         <v>3.2</v>
       </c>
       <c r="DA10" t="n">
-        <v>-22.99225063686383</v>
+        <v>-22.9922499812631</v>
       </c>
       <c r="DB10" t="n">
-        <v>-5.426043274746172</v>
+        <v>-5.42604249935631</v>
       </c>
       <c r="DC10" t="inlineStr">
         <is>
@@ -18791,10 +18791,10 @@
         <v>1</v>
       </c>
       <c r="CM11" t="n">
-        <v>139.3179999466606</v>
+        <v>139.3180003996247</v>
       </c>
       <c r="CN11" t="n">
-        <v>258.4348899010554</v>
+        <v>258.4348907413038</v>
       </c>
       <c r="CO11" t="n">
         <v>136.9934822165448</v>
@@ -18815,7 +18815,7 @@
         <v>58.37540514006138</v>
       </c>
       <c r="CU11" t="n">
-        <v>147.23543242837</v>
+        <v>147.2354325900216</v>
       </c>
       <c r="CV11" t="n">
         <v>131.0484820448834</v>
@@ -18836,7 +18836,7 @@
         <v>147.9891304347826</v>
       </c>
       <c r="DB11" t="n">
-        <v>209.5782762341451</v>
+        <v>209.5782765740348</v>
       </c>
       <c r="DC11" t="inlineStr">
         <is>
@@ -19160,10 +19160,10 @@
         <v>0</v>
       </c>
       <c r="CM12" t="n">
-        <v>6.912918059854431</v>
+        <v>6.912918036445349</v>
       </c>
       <c r="CN12" t="n">
-        <v>12.82346300102997</v>
+        <v>12.82346295760612</v>
       </c>
       <c r="CO12" t="n">
         <v>40.40975051302138</v>
@@ -19172,7 +19172,7 @@
         <v>27.23426223219501</v>
       </c>
       <c r="CQ12" t="n">
-        <v>85.90491759645251</v>
+        <v>85.90491746046615</v>
       </c>
       <c r="CR12" t="n">
         <v>51.88018214566937</v>
@@ -19742,10 +19742,10 @@
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.2135154235041195</v>
+        <v>0.213515423479547</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.310878456621998</v>
+        <v>0.3108784565862205</v>
       </c>
       <c r="CO14" t="n">
         <v>75.77889447236181</v>
@@ -20109,10 +20109,10 @@
         <v>1</v>
       </c>
       <c r="CM15" t="n">
-        <v>145.9241176151541</v>
+        <v>145.9241172852467</v>
       </c>
       <c r="CN15" t="n">
-        <v>270.6892381761108</v>
+        <v>270.6892375641326</v>
       </c>
       <c r="CO15" t="n">
         <v>137.1427213113139</v>
@@ -20133,7 +20133,7 @@
         <v>57.29814214194677</v>
       </c>
       <c r="CU15" t="n">
-        <v>149.5179565088166</v>
+        <v>149.5179563910809</v>
       </c>
       <c r="CV15" t="n">
         <v>131.1912447261059</v>
@@ -20154,7 +20154,7 @@
         <v>124.5570866141732</v>
       </c>
       <c r="DB15" t="n">
-        <v>184.3627830011002</v>
+        <v>184.362782777183</v>
       </c>
       <c r="DC15" t="inlineStr">
         <is>
@@ -20460,10 +20460,10 @@
         <v>0</v>
       </c>
       <c r="CM16" t="n">
-        <v>13.58565538364201</v>
+        <v>13.58565532094829</v>
       </c>
       <c r="CN16" t="n">
-        <v>25.20139073665593</v>
+        <v>25.20139062035909</v>
       </c>
       <c r="CO16" t="n">
         <v>19.9811217441166</v>
@@ -20472,7 +20472,7 @@
         <v>12.48999788378355</v>
       </c>
       <c r="CQ16" t="n">
-        <v>33.81046386196516</v>
+        <v>33.81046379501534</v>
       </c>
       <c r="CR16" t="n">
         <v>22.8984489302328</v>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="CT16" t="inlineStr"/>
       <c r="CU16" t="n">
-        <v>20.41665419866183</v>
+        <v>20.41665415391419</v>
       </c>
       <c r="CV16" t="n">
         <v>21.4397853371747</v>
@@ -20503,7 +20503,7 @@
         <v>-2.398551559568773</v>
       </c>
       <c r="DB16" t="n">
-        <v>3.27088379324858</v>
+        <v>3.270883566907457</v>
       </c>
       <c r="DC16" t="inlineStr">
         <is>
@@ -20835,10 +20835,10 @@
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>3.241822753914691</v>
+        <v>3.241822751043931</v>
       </c>
       <c r="CN17" t="n">
-        <v>6.013581208511751</v>
+        <v>6.013581203186491</v>
       </c>
       <c r="CO17" t="n">
         <v>19.81979119280974</v>
@@ -20847,7 +20847,7 @@
         <v>13.58186553210178</v>
       </c>
       <c r="CQ17" t="n">
-        <v>31.89281582914272</v>
+        <v>31.89281582076967</v>
       </c>
       <c r="CR17" t="n">
         <v>10.95072400487419</v>
@@ -21176,10 +21176,10 @@
         <v>0</v>
       </c>
       <c r="CM18" t="n">
-        <v>10.89032244142402</v>
+        <v>10.89032244259161</v>
       </c>
       <c r="CN18" t="n">
-        <v>20.20154812884156</v>
+        <v>20.20154813100745</v>
       </c>
       <c r="CO18" t="n">
         <v>49.68749999999999</v>
@@ -21188,23 +21188,23 @@
         <v>48.8668773108453</v>
       </c>
       <c r="CQ18" t="n">
-        <v>67.62433396472451</v>
+        <v>67.62433396664358</v>
       </c>
       <c r="CR18" t="n">
-        <v>33.80819015739106</v>
+        <v>33.80819015720991</v>
       </c>
       <c r="CS18" t="n">
-        <v>28.56587197812257</v>
+        <v>28.56587197676012</v>
       </c>
       <c r="CT18" t="inlineStr"/>
       <c r="CU18" t="n">
-        <v>28.64689018191416</v>
+        <v>28.64689018270224</v>
       </c>
       <c r="CV18" t="n">
-        <v>27.00486914311631</v>
+        <v>27.00486914410867</v>
       </c>
       <c r="CW18" t="n">
-        <v>24.30438222880468</v>
+        <v>24.30438222969781</v>
       </c>
       <c r="CX18" t="n">
         <v>4</v>
@@ -21216,10 +21216,10 @@
         <v>4.6</v>
       </c>
       <c r="DA18" t="n">
-        <v>62.02921485869788</v>
+        <v>62.02921486465205</v>
       </c>
       <c r="DB18" t="n">
-        <v>90.97926787942774</v>
+        <v>90.9792678846816</v>
       </c>
       <c r="DC18" t="inlineStr">
         <is>
@@ -21551,10 +21551,10 @@
         <v>0</v>
       </c>
       <c r="CM19" t="n">
-        <v>10.89909389451577</v>
+        <v>10.89909385310484</v>
       </c>
       <c r="CN19" t="n">
-        <v>20.21781917432674</v>
+        <v>20.21781909750947</v>
       </c>
       <c r="CO19" t="n">
         <v>37.45389651797344</v>
@@ -21563,25 +21563,25 @@
         <v>36.91124241178991</v>
       </c>
       <c r="CQ19" t="n">
-        <v>41.40373337242274</v>
+        <v>41.40373335666359</v>
       </c>
       <c r="CR19" t="n">
-        <v>34.46332757732285</v>
+        <v>34.46332758610621</v>
       </c>
       <c r="CS19" t="n">
-        <v>18.32822061669933</v>
+        <v>18.32822066472938</v>
       </c>
       <c r="CT19" t="n">
         <v>32.58677052647363</v>
       </c>
       <c r="CU19" t="n">
-        <v>31.62357288528694</v>
+        <v>31.62357288017795</v>
       </c>
       <c r="CV19" t="n">
-        <v>34.46332757732285</v>
+        <v>34.46332758610621</v>
       </c>
       <c r="CW19" t="n">
-        <v>31.01699481959056</v>
+        <v>31.01699482749559</v>
       </c>
       <c r="CX19" t="n">
         <v>7</v>
@@ -21593,10 +21593,10 @@
         <v>3.8</v>
       </c>
       <c r="DA19" t="n">
-        <v>74.44878302444225</v>
+        <v>74.44878306890246</v>
       </c>
       <c r="DB19" t="n">
-        <v>77.86035806533624</v>
+        <v>77.86035803660174</v>
       </c>
       <c r="DC19" t="inlineStr">
         <is>
@@ -21928,37 +21928,37 @@
         <v>0</v>
       </c>
       <c r="CM20" t="n">
-        <v>24.64526614095033</v>
+        <v>24.6452661183992</v>
       </c>
       <c r="CN20" t="n">
-        <v>31.16419469650378</v>
+        <v>31.16419473185438</v>
       </c>
       <c r="CO20" t="n">
-        <v>34.7502116923207</v>
+        <v>34.75021176353649</v>
       </c>
       <c r="CP20" t="n">
         <v>36.07661496384414</v>
       </c>
       <c r="CQ20" t="n">
-        <v>48.86831564954903</v>
+        <v>48.86831569478055</v>
       </c>
       <c r="CR20" t="n">
-        <v>48.59901754127608</v>
+        <v>48.59901755120379</v>
       </c>
       <c r="CS20" t="n">
-        <v>16.65417716234137</v>
+        <v>16.65417721304533</v>
       </c>
       <c r="CT20" t="n">
         <v>31.14870262855163</v>
       </c>
       <c r="CU20" t="n">
-        <v>33.98831255941713</v>
+        <v>33.98831258315194</v>
       </c>
       <c r="CV20" t="n">
-        <v>32.95720319441224</v>
+        <v>32.95720324769543</v>
       </c>
       <c r="CW20" t="n">
-        <v>29.66148287497102</v>
+        <v>29.66148292292589</v>
       </c>
       <c r="CX20" t="n">
         <v>8</v>
@@ -21970,10 +21970,10 @@
         <v>2.9</v>
       </c>
       <c r="DA20" t="n">
-        <v>-13.47291735353027</v>
+        <v>-13.47291721363859</v>
       </c>
       <c r="DB20" t="n">
-        <v>-0.8508933204977365</v>
+        <v>-0.8508932512596767</v>
       </c>
       <c r="DC20" t="inlineStr">
         <is>
@@ -22299,10 +22299,10 @@
         <v>0</v>
       </c>
       <c r="CM21" t="n">
-        <v>5.334787419611792</v>
+        <v>5.334787411855786</v>
       </c>
       <c r="CN21" t="n">
-        <v>9.896030663379873</v>
+        <v>9.896030648992484</v>
       </c>
       <c r="CO21" t="n">
         <v>8.503043610116709</v>
@@ -22373,7 +22373,7 @@
         <v>0.2717388663546538</v>
       </c>
       <c r="DO21" t="n">
-        <v>-24.4203010953975</v>
+        <v>-24.42029364136734</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -22658,10 +22658,10 @@
         <v>0</v>
       </c>
       <c r="CM22" t="n">
-        <v>3.558471593280884</v>
+        <v>3.558471602966997</v>
       </c>
       <c r="CN22" t="n">
-        <v>6.600964805536039</v>
+        <v>6.60096482350378</v>
       </c>
       <c r="CO22" t="n">
         <v>19.66796809186538</v>
@@ -22670,13 +22670,13 @@
         <v>18.52055498018046</v>
       </c>
       <c r="CQ22" t="n">
-        <v>20.69777961721432</v>
+        <v>20.69777961533053</v>
       </c>
       <c r="CR22" t="n">
-        <v>15.89091661367094</v>
+        <v>15.89091661176179</v>
       </c>
       <c r="CS22" t="n">
-        <v>12.89801918797098</v>
+        <v>12.89801917568821</v>
       </c>
       <c r="CT22" t="n">
         <v>29.41436415825995</v>
@@ -22732,7 +22732,7 @@
         <v>-0.9556959875251736</v>
       </c>
       <c r="DO22" t="n">
-        <v>-30.95847443251961</v>
+        <v>-30.95849087040471</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -23025,37 +23025,37 @@
         <v>0</v>
       </c>
       <c r="CM23" t="n">
-        <v>10.71852591632453</v>
+        <v>10.71852592981897</v>
       </c>
       <c r="CN23" t="n">
-        <v>16.81931637963456</v>
+        <v>16.81931635082226</v>
       </c>
       <c r="CO23" t="n">
-        <v>20.69399626312308</v>
+        <v>20.69399620161987</v>
       </c>
       <c r="CP23" t="n">
         <v>17.56096669750601</v>
       </c>
       <c r="CQ23" t="n">
-        <v>34.52474410993924</v>
+        <v>34.52474409552667</v>
       </c>
       <c r="CR23" t="n">
-        <v>23.92681846636332</v>
+        <v>23.92681846053856</v>
       </c>
       <c r="CS23" t="n">
-        <v>10.34281215525262</v>
+        <v>10.34281212568361</v>
       </c>
       <c r="CT23" t="n">
         <v>10.6899995803833</v>
       </c>
       <c r="CU23" t="n">
-        <v>18.15964744606583</v>
+        <v>18.15964743023741</v>
       </c>
       <c r="CV23" t="n">
-        <v>17.19014153857029</v>
+        <v>17.19014152416413</v>
       </c>
       <c r="CW23" t="n">
-        <v>15.47112738471326</v>
+        <v>15.47112737174772</v>
       </c>
       <c r="CX23" t="n">
         <v>8</v>
@@ -23067,10 +23067,10 @@
         <v>3.3</v>
       </c>
       <c r="DA23" t="n">
-        <v>44.72523846589831</v>
+        <v>44.72523834461168</v>
       </c>
       <c r="DB23" t="n">
-        <v>69.87509970898147</v>
+        <v>69.87509956091387</v>
       </c>
       <c r="DC23" t="inlineStr">
         <is>
@@ -23384,10 +23384,10 @@
         <v>0</v>
       </c>
       <c r="CM24" t="n">
-        <v>6.908311469132905</v>
+        <v>6.908311428687161</v>
       </c>
       <c r="CN24" t="n">
-        <v>12.81491777524154</v>
+        <v>12.81491770021468</v>
       </c>
       <c r="CO24" t="n">
         <v>31.4652624130249</v>
@@ -23396,7 +23396,7 @@
         <v>19.46950820333509</v>
       </c>
       <c r="CQ24" t="n">
-        <v>55.98239085524812</v>
+        <v>55.98239073603961</v>
       </c>
       <c r="CR24" t="n">
         <v>12.77531889407378</v>
@@ -23406,13 +23406,13 @@
       </c>
       <c r="CT24" t="inlineStr"/>
       <c r="CU24" t="n">
-        <v>15.99095263786828</v>
+        <v>15.99095260900013</v>
       </c>
       <c r="CV24" t="n">
-        <v>12.79511833465766</v>
+        <v>12.79511829714423</v>
       </c>
       <c r="CW24" t="n">
-        <v>11.51560650119189</v>
+        <v>11.51560646742981</v>
       </c>
       <c r="CX24" t="n">
         <v>4</v>
@@ -23424,10 +23424,10 @@
         <v>4.6</v>
       </c>
       <c r="DA24" t="n">
-        <v>2.088712533671688</v>
+        <v>2.088712234362422</v>
       </c>
       <c r="DB24" t="n">
-        <v>41.76376787604947</v>
+        <v>41.76376762012615</v>
       </c>
       <c r="DC24" t="inlineStr">
         <is>
@@ -23747,37 +23747,37 @@
         <v>1</v>
       </c>
       <c r="CM25" t="n">
-        <v>9.929939038231703</v>
+        <v>9.929939060311767</v>
       </c>
       <c r="CN25" t="n">
-        <v>17.62243058466343</v>
+        <v>17.62243046603763</v>
       </c>
       <c r="CO25" t="n">
-        <v>20.83047608552275</v>
+        <v>20.83047589898358</v>
       </c>
       <c r="CP25" t="n">
         <v>12.8457780532356</v>
       </c>
       <c r="CQ25" t="n">
-        <v>29.22488345685356</v>
+        <v>29.22488338744555</v>
       </c>
       <c r="CR25" t="n">
-        <v>24.97734503099647</v>
+        <v>24.9773450146415</v>
       </c>
       <c r="CS25" t="n">
-        <v>10.24067500952215</v>
+        <v>10.24067493805693</v>
       </c>
       <c r="CT25" t="n">
         <v>9.713052205096755</v>
       </c>
       <c r="CU25" t="n">
-        <v>16.9230724330153</v>
+        <v>16.92307237797617</v>
       </c>
       <c r="CV25" t="n">
-        <v>15.23410431894952</v>
+        <v>15.23410425963662</v>
       </c>
       <c r="CW25" t="n">
-        <v>13.71069388705456</v>
+        <v>13.71069383367296</v>
       </c>
       <c r="CX25" t="n">
         <v>8</v>
@@ -23789,10 +23789,10 @@
         <v>3</v>
       </c>
       <c r="DA25" t="n">
-        <v>19.53525342511771</v>
+        <v>19.53525295971572</v>
       </c>
       <c r="DB25" t="n">
-        <v>47.5420404449481</v>
+        <v>47.54203996509516</v>
       </c>
       <c r="DC25" t="inlineStr">
         <is>
@@ -24096,10 +24096,10 @@
         <v>1</v>
       </c>
       <c r="CM26" t="n">
-        <v>4.411578442586008</v>
+        <v>4.411578432089268</v>
       </c>
       <c r="CN26" t="n">
-        <v>8.183478010997044</v>
+        <v>8.183477991525592</v>
       </c>
       <c r="CO26" t="n">
         <v>13.99193579150784</v>
@@ -24108,23 +24108,23 @@
         <v>9.385319019937953</v>
       </c>
       <c r="CQ26" t="n">
-        <v>16.2483853489335</v>
+        <v>16.24838538185653</v>
       </c>
       <c r="CR26" t="n">
-        <v>9.212292048299943</v>
+        <v>9.212292051566077</v>
       </c>
       <c r="CS26" t="n">
-        <v>10.67142030010683</v>
+        <v>10.67142032642342</v>
       </c>
       <c r="CT26" t="inlineStr"/>
       <c r="CU26" t="n">
-        <v>8.94982107334771</v>
+        <v>8.949821066672195</v>
       </c>
       <c r="CV26" t="n">
-        <v>8.697885029648493</v>
+        <v>8.697885021545835</v>
       </c>
       <c r="CW26" t="n">
-        <v>7.828096526683644</v>
+        <v>7.828096519391251</v>
       </c>
       <c r="CX26" t="n">
         <v>4</v>
@@ -24136,10 +24136,10 @@
         <v>3.2</v>
       </c>
       <c r="DA26" t="n">
-        <v>-54.88128902265463</v>
+        <v>-54.88128906468572</v>
       </c>
       <c r="DB26" t="n">
-        <v>-48.41601800247588</v>
+        <v>-48.41601804095147</v>
       </c>
       <c r="DC26" t="inlineStr">
         <is>
@@ -24479,10 +24479,10 @@
         <v>1</v>
       </c>
       <c r="CM27" t="n">
-        <v>4.644659472928678</v>
+        <v>4.644659461827183</v>
       </c>
       <c r="CN27" t="n">
-        <v>8.615843322282698</v>
+        <v>8.615843301689424</v>
       </c>
       <c r="CO27" t="n">
         <v>24.12424807657547</v>
@@ -24491,25 +24491,25 @@
         <v>20.32750370736387</v>
       </c>
       <c r="CQ27" t="n">
-        <v>28.97489048812256</v>
+        <v>28.97489049750424</v>
       </c>
       <c r="CR27" t="n">
-        <v>16.67294824461816</v>
+        <v>16.67294824692233</v>
       </c>
       <c r="CS27" t="n">
-        <v>18.15812058475764</v>
+        <v>18.15812060241079</v>
       </c>
       <c r="CT27" t="n">
         <v>14.57260791194931</v>
       </c>
       <c r="CU27" t="n">
-        <v>18.77802319080996</v>
+        <v>18.77802319205935</v>
       </c>
       <c r="CV27" t="n">
-        <v>18.15812058475764</v>
+        <v>18.15812060241079</v>
       </c>
       <c r="CW27" t="n">
-        <v>16.34230852628188</v>
+        <v>16.34230854216971</v>
       </c>
       <c r="CX27" t="n">
         <v>7</v>
@@ -24521,10 +24521,10 @@
         <v>6.2</v>
       </c>
       <c r="DA27" t="n">
-        <v>8.012613368613675</v>
+        <v>8.012613473622521</v>
       </c>
       <c r="DB27" t="n">
-        <v>24.11119001173812</v>
+        <v>24.1111900199958</v>
       </c>
       <c r="DC27" t="inlineStr">
         <is>
@@ -24852,10 +24852,10 @@
         <v>0</v>
       </c>
       <c r="CM28" t="n">
-        <v>8.621278996717859</v>
+        <v>8.621278985813751</v>
       </c>
       <c r="CN28" t="n">
-        <v>15.99247253891163</v>
+        <v>15.99247251868451</v>
       </c>
       <c r="CO28" t="n">
         <v>13.59634032616248</v>
@@ -24876,7 +24876,7 @@
         <v>6.385031628683394</v>
       </c>
       <c r="CU28" t="n">
-        <v>11.20122792981399</v>
+        <v>11.20122792536668</v>
       </c>
       <c r="CV28" t="n">
         <v>11.06720141848175</v>
@@ -24897,7 +24897,7 @@
         <v>-27.5074130818345</v>
       </c>
       <c r="DB28" t="n">
-        <v>-18.4772335050597</v>
+        <v>-18.47723353742736</v>
       </c>
       <c r="DC28" t="inlineStr">
         <is>
@@ -25570,10 +25570,10 @@
         <v>0</v>
       </c>
       <c r="CM30" t="n">
-        <v>3.530789917652976</v>
+        <v>3.530789910936988</v>
       </c>
       <c r="CN30" t="n">
-        <v>6.549615297246271</v>
+        <v>6.549615284788112</v>
       </c>
       <c r="CO30" t="n">
         <v>27.96524414707322</v>
@@ -25582,13 +25582,13 @@
         <v>23.69499543056558</v>
       </c>
       <c r="CQ30" t="n">
-        <v>36.62717723531087</v>
+        <v>36.62717723722163</v>
       </c>
       <c r="CR30" t="n">
-        <v>9.05156606856459</v>
+        <v>9.051566069197181</v>
       </c>
       <c r="CS30" t="n">
-        <v>23.75254965042473</v>
+        <v>23.75254966096238</v>
       </c>
       <c r="CT30" t="n">
         <v>33.06089439136837</v>
@@ -25905,10 +25905,10 @@
         <v>1</v>
       </c>
       <c r="CM31" t="n">
-        <v>38.13263669812871</v>
+        <v>38.13263668885346</v>
       </c>
       <c r="CN31" t="n">
-        <v>55.52111903247541</v>
+        <v>55.52111901897064</v>
       </c>
       <c r="CO31" t="n">
         <v>49.21407329373137</v>
@@ -25925,13 +25925,13 @@
       </c>
       <c r="CT31" t="inlineStr"/>
       <c r="CU31" t="n">
-        <v>50.5929985020383</v>
+        <v>50.5929984963433</v>
       </c>
       <c r="CV31" t="n">
-        <v>52.36759616310339</v>
+        <v>52.36759615635101</v>
       </c>
       <c r="CW31" t="n">
-        <v>47.13083654679306</v>
+        <v>47.13083654071591</v>
       </c>
       <c r="CX31" t="n">
         <v>4</v>
@@ -25943,10 +25943,10 @@
         <v>1.6</v>
       </c>
       <c r="DA31" t="n">
-        <v>13.05070304463469</v>
+        <v>13.05070303005771</v>
       </c>
       <c r="DB31" t="n">
-        <v>21.35524146941454</v>
+        <v>21.3552414557542</v>
       </c>
       <c r="DC31" t="inlineStr">
         <is>
@@ -26270,10 +26270,10 @@
         <v>0</v>
       </c>
       <c r="CM32" t="n">
-        <v>8.042725730627229</v>
+        <v>8.042725692874045</v>
       </c>
       <c r="CN32" t="n">
-        <v>14.91925623031351</v>
+        <v>14.91925616028136</v>
       </c>
       <c r="CO32" t="n">
         <v>35.8092168347706</v>
@@ -26282,25 +26282,25 @@
         <v>28.26533205663885</v>
       </c>
       <c r="CQ32" t="n">
-        <v>42.37839875494011</v>
+        <v>42.37839881633204</v>
       </c>
       <c r="CR32" t="n">
-        <v>26.26934026621138</v>
+        <v>26.26934027562648</v>
       </c>
       <c r="CS32" t="n">
-        <v>27.55520342712055</v>
+        <v>27.55520349529375</v>
       </c>
       <c r="CT32" t="n">
         <v>25.97235352964724</v>
       </c>
       <c r="CU32" t="n">
-        <v>28.7384430142346</v>
+        <v>28.73844302408433</v>
       </c>
       <c r="CV32" t="n">
-        <v>27.55520342712055</v>
+        <v>27.55520349529375</v>
       </c>
       <c r="CW32" t="n">
-        <v>24.7996830844085</v>
+        <v>24.79968314576438</v>
       </c>
       <c r="CX32" t="n">
         <v>7</v>
@@ -26312,10 +26312,10 @@
         <v>5.3</v>
       </c>
       <c r="DA32" t="n">
-        <v>-18.28770091367111</v>
+        <v>-18.28770071151008</v>
       </c>
       <c r="DB32" t="n">
-        <v>-5.309908886258407</v>
+        <v>-5.309908853804624</v>
       </c>
       <c r="DC32" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>3.126062068481006</v>
       </c>
       <c r="DO32" t="n">
-        <v>-13.96944189921097</v>
+        <v>-13.9694512434398</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -26647,10 +26647,10 @@
         <v>0</v>
       </c>
       <c r="CM33" t="n">
-        <v>3.282331944822721</v>
+        <v>3.282331942632095</v>
       </c>
       <c r="CN33" t="n">
-        <v>6.088725757646146</v>
+        <v>6.088725753582535</v>
       </c>
       <c r="CO33" t="n">
         <v>32.87073625430369</v>
@@ -26659,13 +26659,13 @@
         <v>27.40079604823567</v>
       </c>
       <c r="CQ33" t="n">
-        <v>42.09062502638077</v>
+        <v>42.09062502875422</v>
       </c>
       <c r="CR33" t="n">
-        <v>10.85262429563273</v>
+        <v>10.8526242958474</v>
       </c>
       <c r="CS33" t="n">
-        <v>30.004898520376</v>
+        <v>30.00489852392306</v>
       </c>
       <c r="CT33" t="n">
         <v>15.129152615152</v>
@@ -27006,10 +27006,10 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>13.14701704068172</v>
+        <v>13.14701705493896</v>
       </c>
       <c r="CN34" t="n">
-        <v>24.38771661046459</v>
+        <v>24.38771663691178</v>
       </c>
       <c r="CO34" t="n">
         <v>59.63676767704965</v>
@@ -27018,13 +27018,13 @@
         <v>49.91430890839086</v>
       </c>
       <c r="CQ34" t="n">
-        <v>81.26958754764512</v>
+        <v>81.2695875466511</v>
       </c>
       <c r="CR34" t="n">
-        <v>33.53978665425255</v>
+        <v>33.53978665180114</v>
       </c>
       <c r="CS34" t="n">
-        <v>42.55803034452334</v>
+        <v>42.55803032161366</v>
       </c>
       <c r="CT34" t="n">
         <v>5.692431800859927</v>
@@ -27381,10 +27381,10 @@
         <v>0</v>
       </c>
       <c r="CM35" t="n">
-        <v>7.969295219567748</v>
+        <v>7.969295189440922</v>
       </c>
       <c r="CN35" t="n">
-        <v>14.78304263229817</v>
+        <v>14.78304257641291</v>
       </c>
       <c r="CO35" t="n">
         <v>62.5653070010496</v>
@@ -27393,7 +27393,7 @@
         <v>36.50745516551758</v>
       </c>
       <c r="CQ35" t="n">
-        <v>86.49861194553651</v>
+        <v>86.49861188629836</v>
       </c>
       <c r="CR35" t="n">
         <v>22.51480113099953</v>
@@ -27736,10 +27736,10 @@
         <v>0</v>
       </c>
       <c r="CM36" t="n">
-        <v>3.195182290707068</v>
+        <v>3.195182294719609</v>
       </c>
       <c r="CN36" t="n">
-        <v>5.927063149261611</v>
+        <v>5.927063156704874</v>
       </c>
       <c r="CO36" t="n">
         <v>3.991172536103332</v>
@@ -27748,7 +27748,7 @@
         <v>7.379439294118062</v>
       </c>
       <c r="CQ36" t="n">
-        <v>5.414017014609337</v>
+        <v>5.414017017058142</v>
       </c>
       <c r="CR36" t="n">
         <v>1.754303359441048</v>
@@ -27760,13 +27760,13 @@
         <v>9.959526148434405</v>
       </c>
       <c r="CU36" t="n">
-        <v>5.549783437711817</v>
+        <v>5.54978343969819</v>
       </c>
       <c r="CV36" t="n">
-        <v>5.414017014609337</v>
+        <v>5.414017017058142</v>
       </c>
       <c r="CW36" t="n">
-        <v>4.872615313148404</v>
+        <v>4.872615315352328</v>
       </c>
       <c r="CX36" t="n">
         <v>7</v>
@@ -27778,10 +27778,10 @@
         <v>5.7</v>
       </c>
       <c r="DA36" t="n">
-        <v>-29.48458146531993</v>
+        <v>-29.48458143342522</v>
       </c>
       <c r="DB36" t="n">
-        <v>-19.68475310762434</v>
+        <v>-19.68475307887799</v>
       </c>
       <c r="DC36" t="inlineStr">
         <is>
@@ -28091,35 +28091,35 @@
         <v>1</v>
       </c>
       <c r="CM37" t="n">
-        <v>17.82992266091615</v>
+        <v>17.82992267775515</v>
       </c>
       <c r="CN37" t="n">
-        <v>29.4217761441794</v>
+        <v>29.42177614165288</v>
       </c>
       <c r="CO37" t="n">
-        <v>46.10725430146911</v>
+        <v>46.107254253965</v>
       </c>
       <c r="CP37" t="n">
         <v>49.56338817261216</v>
       </c>
       <c r="CQ37" t="n">
-        <v>59.19955305458991</v>
+        <v>59.19955305859294</v>
       </c>
       <c r="CR37" t="n">
-        <v>45.48071624060144</v>
+        <v>45.4807162369368</v>
       </c>
       <c r="CS37" t="n">
-        <v>22.95208727303038</v>
+        <v>22.95208725221064</v>
       </c>
       <c r="CT37" t="inlineStr"/>
       <c r="CU37" t="n">
-        <v>34.70991733679152</v>
+        <v>34.70991732757746</v>
       </c>
       <c r="CV37" t="n">
-        <v>37.45124619239041</v>
+        <v>37.45124618929484</v>
       </c>
       <c r="CW37" t="n">
-        <v>33.70612157315137</v>
+        <v>33.70612157036536</v>
       </c>
       <c r="CX37" t="n">
         <v>4</v>
@@ -28131,10 +28131,10 @@
         <v>2.6</v>
       </c>
       <c r="DA37" t="n">
-        <v>35.69292015338328</v>
+        <v>35.69292014216745</v>
       </c>
       <c r="DB37" t="n">
-        <v>39.73396587590341</v>
+        <v>39.73396583880977</v>
       </c>
       <c r="DC37" t="inlineStr">
         <is>
@@ -28462,10 +28462,10 @@
         <v>1</v>
       </c>
       <c r="CM38" t="n">
-        <v>3.454280439615057</v>
+        <v>3.454280447251831</v>
       </c>
       <c r="CN38" t="n">
-        <v>6.407690215485931</v>
+        <v>6.407690229652147</v>
       </c>
       <c r="CO38" t="n">
         <v>32.60530006759157</v>
@@ -28474,7 +28474,7 @@
         <v>22.82658483654052</v>
       </c>
       <c r="CQ38" t="n">
-        <v>40.32932307964481</v>
+        <v>40.32932308720063</v>
       </c>
       <c r="CR38" t="n">
         <v>10.59424454785779</v>
@@ -28821,10 +28821,10 @@
         <v>0</v>
       </c>
       <c r="CM39" t="n">
-        <v>16.09429142358091</v>
+        <v>16.09429141767125</v>
       </c>
       <c r="CN39" t="n">
-        <v>29.85491059074258</v>
+        <v>29.85491057978017</v>
       </c>
       <c r="CO39" t="n">
         <v>19.95366741986068</v>
@@ -28833,7 +28833,7 @@
         <v>36.76842331976568</v>
       </c>
       <c r="CQ39" t="n">
-        <v>26.87383632857356</v>
+        <v>26.87383632506486</v>
       </c>
       <c r="CR39" t="n">
         <v>15.03391666666667</v>
@@ -28845,7 +28845,7 @@
         <v>81.2268791476879</v>
       </c>
       <c r="CU39" t="n">
-        <v>22.78397481006349</v>
+        <v>22.78397480715196</v>
       </c>
       <c r="CV39" t="n">
         <v>19.95366741986068</v>
@@ -28866,7 +28866,7 @@
         <v>-49.42748091603054</v>
       </c>
       <c r="DB39" t="n">
-        <v>-35.83786007602448</v>
+        <v>-35.83786008422367</v>
       </c>
       <c r="DC39" t="inlineStr">
         <is>
@@ -29166,35 +29166,35 @@
         <v>1</v>
       </c>
       <c r="CM40" t="n">
-        <v>9.776498545188147</v>
+        <v>9.776498548817115</v>
       </c>
       <c r="CN40" t="n">
-        <v>17.80202359189347</v>
+        <v>17.80202359127176</v>
       </c>
       <c r="CO40" t="n">
-        <v>30.41950848304267</v>
+        <v>30.4195084706888</v>
       </c>
       <c r="CP40" t="n">
         <v>29.46192052472633</v>
       </c>
       <c r="CQ40" t="n">
-        <v>34.13596351979948</v>
+        <v>34.13596352020357</v>
       </c>
       <c r="CR40" t="n">
-        <v>25.40854575454435</v>
+        <v>25.40854575380762</v>
       </c>
       <c r="CS40" t="n">
-        <v>14.86407026880161</v>
+        <v>14.86407026428921</v>
       </c>
       <c r="CT40" t="inlineStr"/>
       <c r="CU40" t="n">
-        <v>20.85164409366716</v>
+        <v>20.85164409114633</v>
       </c>
       <c r="CV40" t="n">
-        <v>21.60528467321891</v>
+        <v>21.60528467253969</v>
       </c>
       <c r="CW40" t="n">
-        <v>19.44475620589702</v>
+        <v>19.44475620528572</v>
       </c>
       <c r="CX40" t="n">
         <v>4</v>
@@ -29206,10 +29206,10 @@
         <v>3.1</v>
       </c>
       <c r="DA40" t="n">
-        <v>24.08906261151616</v>
+        <v>24.08906260761505</v>
       </c>
       <c r="DB40" t="n">
-        <v>33.0672877609756</v>
+        <v>33.06728774488859</v>
       </c>
       <c r="DC40" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>0.5131489603787731</v>
       </c>
       <c r="DO40" t="n">
-        <v>-13.7574412679755</v>
+        <v>-13.75743191410359</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -29886,10 +29886,10 @@
         <v>0</v>
       </c>
       <c r="CM42" t="n">
-        <v>1.614287367269096</v>
+        <v>1.614287383142542</v>
       </c>
       <c r="CN42" t="n">
-        <v>2.994503066284172</v>
+        <v>2.994503095729415</v>
       </c>
       <c r="CO42" t="n">
         <v>12.71611758640834</v>
@@ -29898,7 +29898,7 @@
         <v>9.286655171963359</v>
       </c>
       <c r="CQ42" t="n">
-        <v>16.05128416584712</v>
+        <v>16.05128418212758</v>
       </c>
       <c r="CR42" t="n">
         <v>6.104046666666666</v>
@@ -29956,7 +29956,7 @@
         <v>-3.034787864293342</v>
       </c>
       <c r="DO42" t="n">
-        <v>-27.93429952104404</v>
+        <v>-27.93431471010997</v>
       </c>
       <c r="DP42" t="b">
         <v>0</v>
@@ -30229,35 +30229,35 @@
         <v>1</v>
       </c>
       <c r="CM43" t="n">
-        <v>9.277652139429566</v>
+        <v>9.277652160030563</v>
       </c>
       <c r="CN43" t="n">
-        <v>13.27564819194827</v>
+        <v>13.27564817199024</v>
       </c>
       <c r="CO43" t="n">
-        <v>16.56076855305461</v>
+        <v>16.56076849138475</v>
       </c>
       <c r="CP43" t="n">
         <v>17.47664780944146</v>
       </c>
       <c r="CQ43" t="n">
-        <v>21.53940889610869</v>
+        <v>21.53940887428282</v>
       </c>
       <c r="CR43" t="n">
-        <v>17.16868987321791</v>
+        <v>17.16868986752019</v>
       </c>
       <c r="CS43" t="n">
-        <v>8.23977507854878</v>
+        <v>8.239775043451273</v>
       </c>
       <c r="CT43" t="inlineStr"/>
       <c r="CU43" t="n">
-        <v>14.07068968941259</v>
+        <v>14.07068967273144</v>
       </c>
       <c r="CV43" t="n">
-        <v>14.91820837250144</v>
+        <v>14.9182083316875</v>
       </c>
       <c r="CW43" t="n">
-        <v>13.4263875352513</v>
+        <v>13.42638749851875</v>
       </c>
       <c r="CX43" t="n">
         <v>4</v>
@@ -30269,10 +30269,10 @@
         <v>1.9</v>
       </c>
       <c r="DA43" t="n">
-        <v>-2.282476281594181</v>
+        <v>-2.282476548934431</v>
       </c>
       <c r="DB43" t="n">
-        <v>2.406768004389237</v>
+        <v>2.406767882983463</v>
       </c>
       <c r="DC43" t="inlineStr">
         <is>
@@ -30600,37 +30600,37 @@
         <v>0</v>
       </c>
       <c r="CM44" t="n">
-        <v>17.67458142527642</v>
+        <v>17.67458159617798</v>
       </c>
       <c r="CN44" t="n">
-        <v>28.38448059056153</v>
+        <v>28.38448060874346</v>
       </c>
       <c r="CO44" t="n">
-        <v>45.95076189163861</v>
+        <v>45.95076147675917</v>
       </c>
       <c r="CP44" t="n">
         <v>53.20634261756088</v>
       </c>
       <c r="CQ44" t="n">
-        <v>55.32499940553003</v>
+        <v>55.32499944818458</v>
       </c>
       <c r="CR44" t="n">
-        <v>42.93273389305169</v>
+        <v>42.93273386196931</v>
       </c>
       <c r="CS44" t="n">
-        <v>22.93541935282174</v>
+        <v>22.93541916167177</v>
       </c>
       <c r="CT44" t="n">
         <v>32.58624815427083</v>
       </c>
       <c r="CU44" t="n">
-        <v>37.37444591633897</v>
+        <v>37.37444586566725</v>
       </c>
       <c r="CV44" t="n">
-        <v>37.75949102366126</v>
+        <v>37.75949100812007</v>
       </c>
       <c r="CW44" t="n">
-        <v>33.98354192129514</v>
+        <v>33.98354190730807</v>
       </c>
       <c r="CX44" t="n">
         <v>8</v>
@@ -30642,10 +30642,10 @@
         <v>3.1</v>
       </c>
       <c r="DA44" t="n">
-        <v>22.95058853735881</v>
+        <v>22.95058848675435</v>
       </c>
       <c r="DB44" t="n">
-        <v>35.21869298715041</v>
+        <v>35.2186928038229</v>
       </c>
       <c r="DC44" t="inlineStr">
         <is>
@@ -30959,10 +30959,10 @@
         <v>1</v>
       </c>
       <c r="CM45" t="n">
-        <v>21.46693978154572</v>
+        <v>21.46693980023627</v>
       </c>
       <c r="CN45" t="n">
-        <v>39.82117329476731</v>
+        <v>39.82117332943828</v>
       </c>
       <c r="CO45" t="n">
         <v>55.9919330381578</v>
@@ -30971,23 +30971,23 @@
         <v>42.27700822726509</v>
       </c>
       <c r="CQ45" t="n">
-        <v>57.69484333055969</v>
+        <v>57.6948432981931</v>
       </c>
       <c r="CR45" t="n">
-        <v>44.75889536530346</v>
+        <v>44.75889535946022</v>
       </c>
       <c r="CS45" t="n">
-        <v>28.51101666054624</v>
+        <v>28.51101662362118</v>
       </c>
       <c r="CT45" t="inlineStr"/>
       <c r="CU45" t="n">
-        <v>40.50973536994357</v>
+        <v>40.50973538182314</v>
       </c>
       <c r="CV45" t="n">
-        <v>42.29003433003538</v>
+        <v>42.29003434444925</v>
       </c>
       <c r="CW45" t="n">
-        <v>38.06103089703185</v>
+        <v>38.06103091000433</v>
       </c>
       <c r="CX45" t="n">
         <v>4</v>
@@ -30999,10 +30999,10 @@
         <v>2.6</v>
       </c>
       <c r="DA45" t="n">
-        <v>-9.205552100362969</v>
+        <v>-9.205552069417166</v>
       </c>
       <c r="DB45" t="n">
-        <v>-3.364176671282582</v>
+        <v>-3.364176642943906</v>
       </c>
       <c r="DC45" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>1.231582524541053</v>
       </c>
       <c r="DO45" t="n">
-        <v>-13.88059873687392</v>
+        <v>-13.88060552690588</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -31334,10 +31334,10 @@
         <v>1</v>
       </c>
       <c r="CM46" t="n">
-        <v>7.897647836613209</v>
+        <v>7.897647825800325</v>
       </c>
       <c r="CN46" t="n">
-        <v>14.6501367369175</v>
+        <v>14.6501367168596</v>
       </c>
       <c r="CO46" t="n">
         <v>5.689554995371402</v>
@@ -31358,7 +31358,7 @@
         <v>5.468016983754021</v>
       </c>
       <c r="CU46" t="n">
-        <v>7.691147608487336</v>
+        <v>7.691147604628489</v>
       </c>
       <c r="CV46" t="n">
         <v>5.911444164352368</v>
@@ -31379,7 +31379,7 @@
         <v>-20.11561757040502</v>
       </c>
       <c r="DB46" t="n">
-        <v>15.48269946996923</v>
+        <v>15.48269941202858</v>
       </c>
       <c r="DC46" t="inlineStr">
         <is>
@@ -31707,37 +31707,37 @@
         <v>1</v>
       </c>
       <c r="CM47" t="n">
-        <v>6.114135535995681</v>
+        <v>6.114135551504001</v>
       </c>
       <c r="CN47" t="n">
-        <v>8.340738435580306</v>
+        <v>8.34073842373572</v>
       </c>
       <c r="CO47" t="n">
-        <v>10.22416127343144</v>
+        <v>10.22416123297895</v>
       </c>
       <c r="CP47" t="n">
         <v>11.61068843321866</v>
       </c>
       <c r="CQ47" t="n">
-        <v>9.255439703174281</v>
+        <v>9.255439677680009</v>
       </c>
       <c r="CR47" t="n">
-        <v>14.83896368390577</v>
+        <v>14.83896367844126</v>
       </c>
       <c r="CS47" t="n">
-        <v>5.038565287865116</v>
+        <v>5.038565262754045</v>
       </c>
       <c r="CT47" t="n">
         <v>11.35371417455445</v>
       </c>
       <c r="CU47" t="n">
-        <v>9.597050815965712</v>
+        <v>9.597050804358386</v>
       </c>
       <c r="CV47" t="n">
-        <v>9.739800488302858</v>
+        <v>9.739800455329476</v>
       </c>
       <c r="CW47" t="n">
-        <v>8.765820439472574</v>
+        <v>8.765820409796529</v>
       </c>
       <c r="CX47" t="n">
         <v>8</v>
@@ -31749,10 +31749,10 @@
         <v>2.9</v>
       </c>
       <c r="DA47" t="n">
-        <v>-44.3793127400576</v>
+        <v>-44.37931292835736</v>
       </c>
       <c r="DB47" t="n">
-        <v>-39.10500839728339</v>
+        <v>-39.10500847093395</v>
       </c>
       <c r="DC47" t="inlineStr">
         <is>
@@ -32076,10 +32076,10 @@
         <v>0</v>
       </c>
       <c r="CM48" t="n">
-        <v>2.590450535749491</v>
+        <v>2.590450526884343</v>
       </c>
       <c r="CN48" t="n">
-        <v>4.805285743815305</v>
+        <v>4.805285727370455</v>
       </c>
       <c r="CO48" t="n">
         <v>13.29197465681098</v>
@@ -32088,25 +32088,25 @@
         <v>15.02374045273446</v>
       </c>
       <c r="CQ48" t="n">
-        <v>10.24745785756285</v>
+        <v>10.24745785689306</v>
       </c>
       <c r="CR48" t="n">
-        <v>7.29956039391308</v>
+        <v>7.299560394763578</v>
       </c>
       <c r="CS48" t="n">
-        <v>6.7139737668843</v>
+        <v>6.71397377470123</v>
       </c>
       <c r="CT48" t="n">
         <v>10.63504853252629</v>
       </c>
       <c r="CU48" t="n">
-        <v>9.716720200606753</v>
+        <v>9.716720199400006</v>
       </c>
       <c r="CV48" t="n">
-        <v>10.24745785756285</v>
+        <v>10.24745785689306</v>
       </c>
       <c r="CW48" t="n">
-        <v>9.222712071806566</v>
+        <v>9.222712071203755</v>
       </c>
       <c r="CX48" t="n">
         <v>7</v>
@@ -32118,10 +32118,10 @@
         <v>5.8</v>
       </c>
       <c r="DA48" t="n">
-        <v>-2.918820296772995</v>
+        <v>-2.918820303118363</v>
       </c>
       <c r="DB48" t="n">
-        <v>2.281265269544774</v>
+        <v>2.28126525684218</v>
       </c>
       <c r="DC48" t="inlineStr">
         <is>
@@ -32439,10 +32439,10 @@
         <v>0</v>
       </c>
       <c r="CM49" t="n">
-        <v>7.86180718965406</v>
+        <v>7.861807093574793</v>
       </c>
       <c r="CN49" t="n">
-        <v>11.44679126813631</v>
+        <v>11.4467911282449</v>
       </c>
       <c r="CO49" t="n">
         <v>8.08480553688795</v>
@@ -32461,7 +32461,7 @@
         <v>5.466181493173686</v>
       </c>
       <c r="CU49" t="n">
-        <v>8.42303402525142</v>
+        <v>8.423033985922972</v>
       </c>
       <c r="CV49" t="n">
         <v>8.443472131649713</v>
@@ -32482,7 +32482,7 @@
         <v>15.13825800438093</v>
       </c>
       <c r="DB49" t="n">
-        <v>27.62172949940886</v>
+        <v>27.62172890352328</v>
       </c>
       <c r="DC49" t="inlineStr">
         <is>
@@ -32810,37 +32810,37 @@
         <v>0</v>
       </c>
       <c r="CM50" t="n">
-        <v>33.11882886863602</v>
+        <v>33.11882880409752</v>
       </c>
       <c r="CN50" t="n">
-        <v>34.05828920006064</v>
+        <v>34.05828924298923</v>
       </c>
       <c r="CO50" t="n">
-        <v>34.64295533345696</v>
+        <v>34.64295544463105</v>
       </c>
       <c r="CP50" t="n">
         <v>49.91001401454295</v>
       </c>
       <c r="CQ50" t="n">
-        <v>54.23229186947442</v>
+        <v>54.23229194888883</v>
       </c>
       <c r="CR50" t="n">
-        <v>17.39224951049831</v>
+        <v>17.39224951718627</v>
       </c>
       <c r="CS50" t="n">
-        <v>13.60670811502123</v>
+        <v>13.60670822940412</v>
       </c>
       <c r="CT50" t="n">
         <v>30.48327237497478</v>
       </c>
       <c r="CU50" t="n">
-        <v>33.43057616083317</v>
+        <v>33.43057619708934</v>
       </c>
       <c r="CV50" t="n">
-        <v>33.58855903434834</v>
+        <v>33.58855902354338</v>
       </c>
       <c r="CW50" t="n">
-        <v>30.2297031309135</v>
+        <v>30.22970312118904</v>
       </c>
       <c r="CX50" t="n">
         <v>8</v>
@@ -32852,10 +32852,10 @@
         <v>4</v>
       </c>
       <c r="DA50" t="n">
-        <v>-27.24499714563147</v>
+        <v>-27.24499716903571</v>
       </c>
       <c r="DB50" t="n">
-        <v>-19.54133146887101</v>
+        <v>-19.54133138161186</v>
       </c>
       <c r="DC50" t="inlineStr">
         <is>
@@ -33187,10 +33187,10 @@
         <v>0</v>
       </c>
       <c r="CM51" t="n">
-        <v>5.386293082670297</v>
+        <v>5.386293093495071</v>
       </c>
       <c r="CN51" t="n">
-        <v>9.9915736683534</v>
+        <v>9.991573688433357</v>
       </c>
       <c r="CO51" t="n">
         <v>25.37030346820809</v>
@@ -33199,25 +33199,25 @@
         <v>28.55650608967326</v>
       </c>
       <c r="CQ51" t="n">
-        <v>22.67781208984114</v>
+        <v>22.67781209635897</v>
       </c>
       <c r="CR51" t="n">
-        <v>14.10274633988771</v>
+        <v>14.10274633882044</v>
       </c>
       <c r="CS51" t="n">
-        <v>12.52009431500811</v>
+        <v>12.52009430533942</v>
       </c>
       <c r="CT51" t="n">
         <v>4.937022761450113</v>
       </c>
       <c r="CU51" t="n">
-        <v>16.94361843623457</v>
+        <v>16.94361844004694</v>
       </c>
       <c r="CV51" t="n">
-        <v>14.10274633988771</v>
+        <v>14.10274633882044</v>
       </c>
       <c r="CW51" t="n">
-        <v>12.69247170589894</v>
+        <v>12.69247170493839</v>
       </c>
       <c r="CX51" t="n">
         <v>7</v>
@@ -33229,10 +33229,10 @@
         <v>5.8</v>
       </c>
       <c r="DA51" t="n">
-        <v>-4.207760710196673</v>
+        <v>-4.207760717446085</v>
       </c>
       <c r="DB51" t="n">
-        <v>27.87636555648734</v>
+        <v>27.87636558525994</v>
       </c>
       <c r="DC51" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>0.3028006187548726</v>
       </c>
       <c r="DO51" t="n">
-        <v>-19.42115821630006</v>
+        <v>-19.42116334297406</v>
       </c>
       <c r="DP51" t="b">
         <v>0</v>
@@ -33552,10 +33552,10 @@
         <v>0</v>
       </c>
       <c r="CM52" t="n">
-        <v>11.37352803907594</v>
+        <v>11.37352796015599</v>
       </c>
       <c r="CN52" t="n">
-        <v>21.09789451248587</v>
+        <v>21.09789436608936</v>
       </c>
       <c r="CO52" t="n">
         <v>55.71325580079352</v>
@@ -33564,19 +33564,19 @@
         <v>52.70332650902633</v>
       </c>
       <c r="CQ52" t="n">
-        <v>57.57115632921651</v>
+        <v>57.57115634929421</v>
       </c>
       <c r="CR52" t="n">
-        <v>28.90928477550776</v>
+        <v>28.90928458493641</v>
       </c>
       <c r="CS52" t="n">
-        <v>34.8465878480716</v>
+        <v>34.84658794794007</v>
       </c>
       <c r="CT52" t="n">
         <v>57.18228375268124</v>
       </c>
       <c r="CU52" t="n">
-        <v>44.00339850396897</v>
+        <v>44.00339847296588</v>
       </c>
       <c r="CV52" t="n">
         <v>52.70332650902633</v>
@@ -33597,7 +33597,7 @@
         <v>41.71793285978029</v>
       </c>
       <c r="DB52" t="n">
-        <v>31.47115894561228</v>
+        <v>31.4711588529828</v>
       </c>
       <c r="DC52" t="inlineStr">
         <is>
@@ -33899,35 +33899,35 @@
         <v>1</v>
       </c>
       <c r="CM53" t="n">
-        <v>10.6268533482049</v>
+        <v>10.62685337831266</v>
       </c>
       <c r="CN53" t="n">
-        <v>17.64942995460184</v>
+        <v>17.64942994959144</v>
       </c>
       <c r="CO53" t="n">
-        <v>27.73251609334911</v>
+        <v>27.73251600690513</v>
       </c>
       <c r="CP53" t="n">
         <v>29.43493108570705</v>
       </c>
       <c r="CQ53" t="n">
-        <v>31.55991137560471</v>
+        <v>31.55991137143432</v>
       </c>
       <c r="CR53" t="n">
-        <v>27.78221466362887</v>
+        <v>27.78221465689651</v>
       </c>
       <c r="CS53" t="n">
-        <v>13.79408528950043</v>
+        <v>13.79408525206323</v>
       </c>
       <c r="CT53" t="inlineStr"/>
       <c r="CU53" t="n">
-        <v>20.94775351494618</v>
+        <v>20.94775349792643</v>
       </c>
       <c r="CV53" t="n">
-        <v>22.69097302397547</v>
+        <v>22.69097297824829</v>
       </c>
       <c r="CW53" t="n">
-        <v>20.42187572157793</v>
+        <v>20.42187568042346</v>
       </c>
       <c r="CX53" t="n">
         <v>4</v>
@@ -33939,10 +33939,10 @@
         <v>2.6</v>
       </c>
       <c r="DA53" t="n">
-        <v>14.79412406186809</v>
+        <v>14.79412383053324</v>
       </c>
       <c r="DB53" t="n">
-        <v>17.75015422659541</v>
+        <v>17.75015413092511</v>
       </c>
       <c r="DC53" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>0.2253572705765761</v>
       </c>
       <c r="DO53" t="n">
-        <v>-16.147447880327</v>
+        <v>-16.14745557185274</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -34250,35 +34250,35 @@
         <v>0</v>
       </c>
       <c r="CM54" t="n">
-        <v>27.1475195991674</v>
+        <v>27.14751956164674</v>
       </c>
       <c r="CN54" t="n">
-        <v>33.1350017085726</v>
+        <v>33.13500175059818</v>
       </c>
       <c r="CO54" t="n">
-        <v>36.86133007381309</v>
+        <v>36.86133017151097</v>
       </c>
       <c r="CP54" t="n">
         <v>42.33938507434554</v>
       </c>
       <c r="CQ54" t="n">
-        <v>44.68926971716981</v>
+        <v>44.68926978659407</v>
       </c>
       <c r="CR54" t="n">
-        <v>43.05815819868718</v>
+        <v>43.05815821043025</v>
       </c>
       <c r="CS54" t="n">
-        <v>17.32645944300522</v>
+        <v>17.32645951713102</v>
       </c>
       <c r="CT54" t="inlineStr"/>
       <c r="CU54" t="n">
-        <v>35.05050239506006</v>
+        <v>35.05050242354653</v>
       </c>
       <c r="CV54" t="n">
-        <v>34.99816589119284</v>
+        <v>34.99816596105457</v>
       </c>
       <c r="CW54" t="n">
-        <v>31.49834930207356</v>
+        <v>31.49834936494912</v>
       </c>
       <c r="CX54" t="n">
         <v>4</v>
@@ -34290,10 +34290,10 @@
         <v>1.6</v>
       </c>
       <c r="DA54" t="n">
-        <v>-31.21129357437401</v>
+        <v>-31.21129343706115</v>
       </c>
       <c r="DB54" t="n">
-        <v>-23.4538071756743</v>
+        <v>-23.45380711346319</v>
       </c>
       <c r="DC54" t="inlineStr">
         <is>
@@ -34621,10 +34621,10 @@
         <v>0</v>
       </c>
       <c r="CM55" t="n">
-        <v>15.96156246335329</v>
+        <v>15.96156250809131</v>
       </c>
       <c r="CN55" t="n">
-        <v>29.60869836952036</v>
+        <v>29.60869845250937</v>
       </c>
       <c r="CO55" t="n">
         <v>55.8955933463928</v>
@@ -34633,25 +34633,25 @@
         <v>43.14492745892942</v>
       </c>
       <c r="CQ55" t="n">
-        <v>68.20208797059848</v>
+        <v>68.20208790766242</v>
       </c>
       <c r="CR55" t="n">
-        <v>38.13201688433877</v>
+        <v>38.13201687328891</v>
       </c>
       <c r="CS55" t="n">
-        <v>38.06826131547921</v>
+        <v>38.06826123087426</v>
       </c>
       <c r="CT55" t="n">
         <v>22.28433325274179</v>
       </c>
       <c r="CU55" t="n">
-        <v>38.91218513266926</v>
+        <v>38.91218512881129</v>
       </c>
       <c r="CV55" t="n">
-        <v>38.10013909990899</v>
+        <v>38.10013905208159</v>
       </c>
       <c r="CW55" t="n">
-        <v>34.29012518991809</v>
+        <v>34.29012514687343</v>
       </c>
       <c r="CX55" t="n">
         <v>8</v>
@@ -34663,10 +34663,10 @@
         <v>4.3</v>
       </c>
       <c r="DA55" t="n">
-        <v>-6.997216752658031</v>
+        <v>-6.997216869405143</v>
       </c>
       <c r="DB55" t="n">
-        <v>5.5388832653815</v>
+        <v>5.538883254917759</v>
       </c>
       <c r="DC55" t="inlineStr">
         <is>
@@ -34994,10 +34994,10 @@
         <v>0</v>
       </c>
       <c r="CM56" t="n">
-        <v>27.71225740650887</v>
+        <v>27.71225737706116</v>
       </c>
       <c r="CN56" t="n">
-        <v>51.40623748907394</v>
+        <v>51.40623743444844</v>
       </c>
       <c r="CO56" t="n">
         <v>69.02703388345945</v>
@@ -35006,25 +35006,25 @@
         <v>48.07470647599711</v>
       </c>
       <c r="CQ56" t="n">
-        <v>78.40063152040356</v>
+        <v>78.40063158340526</v>
       </c>
       <c r="CR56" t="n">
-        <v>61.78172617286008</v>
+        <v>61.78172618496546</v>
       </c>
       <c r="CS56" t="n">
-        <v>36.01038477538081</v>
+        <v>36.01038484387148</v>
       </c>
       <c r="CT56" t="n">
         <v>80.3272793905405</v>
       </c>
       <c r="CU56" t="n">
-        <v>56.59253213927804</v>
+        <v>56.59253214671861</v>
       </c>
       <c r="CV56" t="n">
-        <v>56.59398183096701</v>
+        <v>56.59398180970695</v>
       </c>
       <c r="CW56" t="n">
-        <v>50.93458364787031</v>
+        <v>50.93458362873626</v>
       </c>
       <c r="CX56" t="n">
         <v>8</v>
@@ -35036,10 +35036,10 @@
         <v>2.9</v>
       </c>
       <c r="DA56" t="n">
-        <v>8.997612126731823</v>
+        <v>8.997612085785844</v>
       </c>
       <c r="DB56" t="n">
-        <v>21.10535564659612</v>
+        <v>21.10535566251859</v>
       </c>
       <c r="DC56" t="inlineStr">
         <is>
@@ -35371,37 +35371,37 @@
         <v>0</v>
       </c>
       <c r="CM57" t="n">
-        <v>8.751143353763721</v>
+        <v>8.751143342402919</v>
       </c>
       <c r="CN57" t="n">
-        <v>11.64085681598057</v>
+        <v>11.64085681335524</v>
       </c>
       <c r="CO57" t="n">
-        <v>16.15113539620313</v>
+        <v>16.15113541352812</v>
       </c>
       <c r="CP57" t="n">
         <v>23.9940157354355</v>
       </c>
       <c r="CQ57" t="n">
-        <v>23.54948249495867</v>
+        <v>23.54948248923467</v>
       </c>
       <c r="CR57" t="n">
-        <v>20.91483982325539</v>
+        <v>20.91483982539174</v>
       </c>
       <c r="CS57" t="n">
-        <v>7.900760713267644</v>
+        <v>7.900760724524837</v>
       </c>
       <c r="CT57" t="n">
         <v>10.33126260605547</v>
       </c>
       <c r="CU57" t="n">
-        <v>15.40418711736501</v>
+        <v>15.40418711874106</v>
       </c>
       <c r="CV57" t="n">
-        <v>13.89599610609185</v>
+        <v>13.89599611344168</v>
       </c>
       <c r="CW57" t="n">
-        <v>12.50639649548267</v>
+        <v>12.50639650209751</v>
       </c>
       <c r="CX57" t="n">
         <v>8</v>
@@ -35413,10 +35413,10 @@
         <v>3</v>
       </c>
       <c r="DA57" t="n">
-        <v>9.321651697679822</v>
+        <v>9.321651755501925</v>
       </c>
       <c r="DB57" t="n">
-        <v>34.65199023065777</v>
+        <v>34.65199024268617</v>
       </c>
       <c r="DC57" t="inlineStr">
         <is>
@@ -35718,10 +35718,10 @@
         <v>0</v>
       </c>
       <c r="CM58" t="n">
-        <v>11.49820300177474</v>
+        <v>11.49820300028505</v>
       </c>
       <c r="CN58" t="n">
-        <v>21.32916656829214</v>
+        <v>21.32916656552876</v>
       </c>
       <c r="CO58" t="n">
         <v>61.99144933938789</v>
@@ -35730,7 +35730,7 @@
         <v>46.3637511199616</v>
       </c>
       <c r="CQ58" t="n">
-        <v>82.98527148959519</v>
+        <v>82.98527148793602</v>
       </c>
       <c r="CR58" t="n">
         <v>11.76833333333333</v>
@@ -35740,7 +35740,7 @@
       </c>
       <c r="CT58" t="inlineStr"/>
       <c r="CU58" t="n">
-        <v>14.8652343011334</v>
+        <v>14.86523429971571</v>
       </c>
       <c r="CV58" t="n">
         <v>11.76833333333333</v>
@@ -35761,7 +35761,7 @@
         <v>-81.99030819133732</v>
       </c>
       <c r="DB58" t="n">
-        <v>-74.72328863456794</v>
+        <v>-74.72328863697857</v>
       </c>
       <c r="DC58" t="inlineStr">
         <is>
@@ -36075,10 +36075,10 @@
         <v>0</v>
       </c>
       <c r="CM59" t="n">
-        <v>15.91082427938901</v>
+        <v>15.91082428045713</v>
       </c>
       <c r="CN59" t="n">
-        <v>29.51457903826661</v>
+        <v>29.51457904024798</v>
       </c>
       <c r="CO59" t="n">
         <v>54.72591683531388</v>
@@ -36087,23 +36087,23 @@
         <v>49.38251180555442</v>
       </c>
       <c r="CQ59" t="n">
-        <v>60.07811897687782</v>
+        <v>60.07811897656059</v>
       </c>
       <c r="CR59" t="n">
-        <v>36.56479138774561</v>
+        <v>36.56479138755189</v>
       </c>
       <c r="CS59" t="n">
-        <v>29.79907882455338</v>
+        <v>29.7990788230786</v>
       </c>
       <c r="CT59" t="inlineStr"/>
       <c r="CU59" t="n">
-        <v>34.17902788517878</v>
+        <v>34.17902788589272</v>
       </c>
       <c r="CV59" t="n">
-        <v>33.03968521300611</v>
+        <v>33.03968521389994</v>
       </c>
       <c r="CW59" t="n">
-        <v>29.7357166917055</v>
+        <v>29.73571669250994</v>
       </c>
       <c r="CX59" t="n">
         <v>4</v>
@@ -36115,10 +36115,10 @@
         <v>3.4</v>
       </c>
       <c r="DA59" t="n">
-        <v>-2.313678810761299</v>
+        <v>-2.31367880811858</v>
       </c>
       <c r="DB59" t="n">
-        <v>12.28326966334239</v>
+        <v>12.2832696656878</v>
       </c>
       <c r="DC59" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>1.4328567207472</v>
       </c>
       <c r="DO59" t="n">
-        <v>-16.50913757078116</v>
+        <v>-16.5091286271213</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -36448,10 +36448,10 @@
         <v>0</v>
       </c>
       <c r="CM60" t="n">
-        <v>13.92259622711488</v>
+        <v>13.92259633446643</v>
       </c>
       <c r="CN60" t="n">
-        <v>20.27130010667927</v>
+        <v>20.27130026298312</v>
       </c>
       <c r="CO60" t="n">
         <v>16.70574758244657</v>
@@ -36470,7 +36470,7 @@
         <v>15.45433621078142</v>
       </c>
       <c r="CU60" t="n">
-        <v>16.60794743812201</v>
+        <v>16.60794748206458</v>
       </c>
       <c r="CV60" t="n">
         <v>16.080041896614</v>
@@ -36491,7 +36491,7 @@
         <v>29.44577202071063</v>
       </c>
       <c r="DB60" t="n">
-        <v>48.55050970287868</v>
+        <v>48.55051009592491</v>
       </c>
       <c r="DC60" t="inlineStr">
         <is>
@@ -36821,10 +36821,10 @@
         <v>0</v>
       </c>
       <c r="CM61" t="n">
-        <v>1.110511218804283</v>
+        <v>1.11051121586904</v>
       </c>
       <c r="CN61" t="n">
-        <v>2.059998310881946</v>
+        <v>2.05999830543707</v>
       </c>
       <c r="CO61" t="n">
         <v>9.339207419564895</v>
@@ -36833,13 +36833,13 @@
         <v>8.768824142136653</v>
       </c>
       <c r="CQ61" t="n">
-        <v>10.25990372433098</v>
+        <v>10.25990372426347</v>
       </c>
       <c r="CR61" t="n">
-        <v>4.217375373685608</v>
+        <v>4.217375374006328</v>
       </c>
       <c r="CS61" t="n">
-        <v>6.897005825136388</v>
+        <v>6.897005828886923</v>
       </c>
       <c r="CT61" t="n">
         <v>7.048791965539855</v>
@@ -36891,7 +36891,7 @@
         <v>0.4184096244488567</v>
       </c>
       <c r="DO61" t="n">
-        <v>-33.71840595466463</v>
+        <v>-33.71841038490954</v>
       </c>
       <c r="DP61" t="b">
         <v>0</v>
@@ -37184,10 +37184,10 @@
         <v>0</v>
       </c>
       <c r="CM62" t="n">
-        <v>8.663823183240551</v>
+        <v>8.663823172436274</v>
       </c>
       <c r="CN62" t="n">
-        <v>16.07139200491122</v>
+        <v>16.07139198486929</v>
       </c>
       <c r="CO62" t="n">
         <v>19.74227298786794</v>
@@ -37196,25 +37196,25 @@
         <v>12.2713478206253</v>
       </c>
       <c r="CQ62" t="n">
-        <v>12.65837950666264</v>
+        <v>12.65837955249128</v>
       </c>
       <c r="CR62" t="n">
-        <v>20.44668728843381</v>
+        <v>20.4466872949171</v>
       </c>
       <c r="CS62" t="n">
-        <v>9.755005108468447</v>
+        <v>9.755005139996184</v>
       </c>
       <c r="CT62" t="n">
         <v>13.40282426495203</v>
       </c>
       <c r="CU62" t="n">
-        <v>14.12646652064524</v>
+        <v>14.12646652726943</v>
       </c>
       <c r="CV62" t="n">
-        <v>13.03060188580734</v>
+        <v>13.03060190872166</v>
       </c>
       <c r="CW62" t="n">
-        <v>11.7275416972266</v>
+        <v>11.72754171784949</v>
       </c>
       <c r="CX62" t="n">
         <v>8</v>
@@ -37226,10 +37226,10 @@
         <v>2.4</v>
       </c>
       <c r="DA62" t="n">
-        <v>-77.47302845204432</v>
+        <v>-77.47302841243064</v>
       </c>
       <c r="DB62" t="n">
-        <v>-72.86502852861483</v>
+        <v>-72.8650285158907</v>
       </c>
       <c r="DC62" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>2.399687681041485</v>
       </c>
       <c r="DO62" t="n">
-        <v>-4.09943271084231</v>
+        <v>-4.099425827904291</v>
       </c>
       <c r="DP62" t="b">
         <v>0</v>
@@ -37569,10 +37569,10 @@
         <v>0</v>
       </c>
       <c r="CM63" t="n">
-        <v>12.86346422542733</v>
+        <v>12.8634642525334</v>
       </c>
       <c r="CN63" t="n">
-        <v>23.86172613816769</v>
+        <v>23.86172618844947</v>
       </c>
       <c r="CO63" t="n">
         <v>41.03334835250192</v>
@@ -37581,25 +37581,25 @@
         <v>33.52326806093615</v>
       </c>
       <c r="CQ63" t="n">
-        <v>40.24808828312476</v>
+        <v>40.2480882423156</v>
       </c>
       <c r="CR63" t="n">
-        <v>23.667314865823</v>
+        <v>23.66731486065639</v>
       </c>
       <c r="CS63" t="n">
-        <v>23.95428588405279</v>
+        <v>23.9542858381351</v>
       </c>
       <c r="CT63" t="n">
         <v>27.87070045516446</v>
       </c>
       <c r="CU63" t="n">
-        <v>28.37777453314976</v>
+        <v>28.37777453133656</v>
       </c>
       <c r="CV63" t="n">
-        <v>25.91249316960862</v>
+        <v>25.91249314664978</v>
       </c>
       <c r="CW63" t="n">
-        <v>23.32124385264776</v>
+        <v>23.3212438319848</v>
       </c>
       <c r="CX63" t="n">
         <v>8</v>
@@ -37611,10 +37611,10 @@
         <v>3.2</v>
       </c>
       <c r="DA63" t="n">
-        <v>-36.01853672288632</v>
+        <v>-36.01853677957483</v>
       </c>
       <c r="DB63" t="n">
-        <v>-22.14602485824124</v>
+        <v>-22.14602486321572</v>
       </c>
       <c r="DC63" t="inlineStr">
         <is>
@@ -37934,10 +37934,10 @@
         <v>0</v>
       </c>
       <c r="CM64" t="n">
-        <v>2.820078488016144</v>
+        <v>2.820078487862132</v>
       </c>
       <c r="CN64" t="n">
-        <v>5.231245595269947</v>
+        <v>5.231245594984254</v>
       </c>
       <c r="CO64" t="n">
         <v>13.12899589538574</v>
@@ -37946,13 +37946,13 @@
         <v>14.66350162681555</v>
       </c>
       <c r="CQ64" t="n">
-        <v>15.14141162471144</v>
+        <v>15.14141162444082</v>
       </c>
       <c r="CR64" t="n">
-        <v>9.4686868269795</v>
+        <v>9.468686826999447</v>
       </c>
       <c r="CS64" t="n">
-        <v>6.498579674593541</v>
+        <v>6.498579674732867</v>
       </c>
       <c r="CT64" t="n">
         <v>1.548212604646662</v>
@@ -38289,37 +38289,37 @@
         <v>0</v>
       </c>
       <c r="CM65" t="n">
-        <v>11.06062710106004</v>
+        <v>11.06062713723358</v>
       </c>
       <c r="CN65" t="n">
-        <v>14.33571139638076</v>
+        <v>14.33571137743339</v>
       </c>
       <c r="CO65" t="n">
-        <v>17.27401480387541</v>
+        <v>17.27401472455022</v>
       </c>
       <c r="CP65" t="n">
         <v>21.47246571889108</v>
       </c>
       <c r="CQ65" t="n">
-        <v>16.92466548287977</v>
+        <v>16.9246654346756</v>
       </c>
       <c r="CR65" t="n">
-        <v>23.12339238484428</v>
+        <v>23.12339237449257</v>
       </c>
       <c r="CS65" t="n">
-        <v>8.370034438238742</v>
+        <v>8.370034384218625</v>
       </c>
       <c r="CT65" t="n">
         <v>19.12184394629235</v>
       </c>
       <c r="CU65" t="n">
-        <v>16.4603444090578</v>
+        <v>16.46034438722343</v>
       </c>
       <c r="CV65" t="n">
-        <v>17.09934014337759</v>
+        <v>17.09934007961291</v>
       </c>
       <c r="CW65" t="n">
-        <v>15.38940612903983</v>
+        <v>15.38940607165162</v>
       </c>
       <c r="CX65" t="n">
         <v>8</v>
@@ -38331,10 +38331,10 @@
         <v>2.8</v>
       </c>
       <c r="DA65" t="n">
-        <v>-38.54071259439596</v>
+        <v>-38.5407128235821</v>
       </c>
       <c r="DB65" t="n">
-        <v>-34.26380268680135</v>
+        <v>-34.26380277399933</v>
       </c>
       <c r="DC65" t="inlineStr">
         <is>
@@ -38654,10 +38654,10 @@
         <v>0</v>
       </c>
       <c r="CM66" t="n">
-        <v>4.660126874929456</v>
+        <v>4.660126896920231</v>
       </c>
       <c r="CN66" t="n">
-        <v>8.644535352994142</v>
+        <v>8.644535393787027</v>
       </c>
       <c r="CO66" t="n">
         <v>28.50627497622841</v>
@@ -38666,13 +38666,13 @@
         <v>28.35236807680409</v>
       </c>
       <c r="CQ66" t="n">
-        <v>24.66479479279133</v>
+        <v>24.66479477791244</v>
       </c>
       <c r="CR66" t="n">
-        <v>2.961410463412237</v>
+        <v>2.961410462909572</v>
       </c>
       <c r="CS66" t="n">
-        <v>17.9303658512185</v>
+        <v>17.93036582619652</v>
       </c>
       <c r="CT66" t="n">
         <v>19.20891215999163</v>
@@ -39013,37 +39013,37 @@
         <v>0</v>
       </c>
       <c r="CM67" t="n">
-        <v>14.15683951510598</v>
+        <v>14.15683946601539</v>
       </c>
       <c r="CN67" t="n">
-        <v>14.52327154846292</v>
+        <v>14.52327153882082</v>
       </c>
       <c r="CO67" t="n">
-        <v>14.98676295694541</v>
+        <v>14.98676299896405</v>
       </c>
       <c r="CP67" t="n">
         <v>30.59566885157829</v>
       </c>
       <c r="CQ67" t="n">
-        <v>14.00921127216523</v>
+        <v>14.00921129486131</v>
       </c>
       <c r="CR67" t="n">
-        <v>30.25195518399476</v>
+        <v>30.25195519417974</v>
       </c>
       <c r="CS67" t="n">
-        <v>5.863199580855445</v>
+        <v>5.863199624271166</v>
       </c>
       <c r="CT67" t="n">
         <v>38.29441237884694</v>
       </c>
       <c r="CU67" t="n">
-        <v>19.75395155470877</v>
+        <v>19.75395155740327</v>
       </c>
       <c r="CV67" t="n">
-        <v>14.75501725270416</v>
+        <v>14.75501726889243</v>
       </c>
       <c r="CW67" t="n">
-        <v>13.27951552743375</v>
+        <v>13.27951554200319</v>
       </c>
       <c r="CX67" t="n">
         <v>6</v>
@@ -39055,10 +39055,10 @@
         <v>6.5</v>
       </c>
       <c r="DA67" t="n">
-        <v>-56.18767482211544</v>
+        <v>-56.18767477404734</v>
       </c>
       <c r="DB67" t="n">
-        <v>-34.82694852269742</v>
+        <v>-34.82694851380762</v>
       </c>
       <c r="DC67" t="inlineStr">
         <is>
@@ -39386,10 +39386,10 @@
         <v>0</v>
       </c>
       <c r="CM68" t="n">
-        <v>9.424600981239182</v>
+        <v>9.424600952514027</v>
       </c>
       <c r="CN68" t="n">
-        <v>17.48263482019868</v>
+        <v>17.48263476691352</v>
       </c>
       <c r="CO68" t="n">
         <v>17.0502564055361</v>
@@ -39398,7 +39398,7 @@
         <v>16.93163083998861</v>
       </c>
       <c r="CQ68" t="n">
-        <v>26.97723554612757</v>
+        <v>26.97723552038159</v>
       </c>
       <c r="CR68" t="n">
         <v>19.94489718117502</v>
@@ -39410,7 +39410,7 @@
         <v>17.36889744184579</v>
       </c>
       <c r="CU68" t="n">
-        <v>17.53315802079863</v>
+        <v>17.53315800732909</v>
       </c>
       <c r="CV68" t="n">
         <v>17.20957692369095</v>
@@ -39431,7 +39431,7 @@
         <v>-22.94219434144452</v>
       </c>
       <c r="DB68" t="n">
-        <v>-12.77035976097532</v>
+        <v>-12.77035982798795</v>
       </c>
       <c r="DC68" t="inlineStr">
         <is>
@@ -39755,35 +39755,35 @@
         <v>0</v>
       </c>
       <c r="CM69" t="n">
-        <v>2.878501268406359</v>
+        <v>2.878501270730353</v>
       </c>
       <c r="CN69" t="n">
-        <v>3.149870567796422</v>
+        <v>3.149870568444909</v>
       </c>
       <c r="CO69" t="n">
-        <v>3.544247206872814</v>
+        <v>3.544247204741002</v>
       </c>
       <c r="CP69" t="n">
         <v>6.959150461939593</v>
       </c>
       <c r="CQ69" t="n">
-        <v>5.35779858425864</v>
+        <v>5.357798585066147</v>
       </c>
       <c r="CR69" t="n">
-        <v>8.422443922980664</v>
+        <v>8.422443922406046</v>
       </c>
       <c r="CS69" t="n">
-        <v>1.516132263779092</v>
+        <v>1.516132261813737</v>
       </c>
       <c r="CT69" t="inlineStr"/>
       <c r="CU69" t="n">
-        <v>4.546877753719083</v>
+        <v>4.546877753591684</v>
       </c>
       <c r="CV69" t="n">
-        <v>3.544247206872814</v>
+        <v>3.544247204741002</v>
       </c>
       <c r="CW69" t="n">
-        <v>3.189822486185533</v>
+        <v>3.189822484266902</v>
       </c>
       <c r="CX69" t="n">
         <v>7</v>
@@ -39795,10 +39795,10 @@
         <v>5.6</v>
       </c>
       <c r="DA69" t="n">
-        <v>-14.93806703505245</v>
+        <v>-14.93806708621594</v>
       </c>
       <c r="DB69" t="n">
-        <v>21.25007343250889</v>
+        <v>21.25007342911158</v>
       </c>
       <c r="DC69" t="inlineStr">
         <is>
@@ -40128,25 +40128,25 @@
         <v>0</v>
       </c>
       <c r="CM70" t="n">
-        <v>0.6891133940299222</v>
+        <v>0.6891133919765345</v>
       </c>
       <c r="CN70" t="n">
-        <v>0.9671622954952606</v>
+        <v>0.9671622930578618</v>
       </c>
       <c r="CO70" t="n">
-        <v>3.407902713945675</v>
+        <v>3.407902715511942</v>
       </c>
       <c r="CP70" t="n">
         <v>7.140833667637913</v>
       </c>
       <c r="CQ70" t="n">
-        <v>2.610632641047891</v>
+        <v>2.61063263844501</v>
       </c>
       <c r="CR70" t="n">
-        <v>2.229099968079982</v>
+        <v>2.229099968172907</v>
       </c>
       <c r="CS70" t="n">
-        <v>1.690151944003226</v>
+        <v>1.690151944926594</v>
       </c>
       <c r="CT70" t="n">
         <v>6.495080194769218</v>
@@ -40465,10 +40465,10 @@
         <v>0</v>
       </c>
       <c r="CM71" t="n">
-        <v>12.00267479302119</v>
+        <v>12.00267477472071</v>
       </c>
       <c r="CN71" t="n">
-        <v>17.47589449863885</v>
+        <v>17.47589447199335</v>
       </c>
       <c r="CO71" t="n">
         <v>15.80042779828547</v>
@@ -40485,13 +40485,13 @@
       </c>
       <c r="CT71" t="inlineStr"/>
       <c r="CU71" t="n">
-        <v>13.15308260581971</v>
+        <v>13.15308259458322</v>
       </c>
       <c r="CV71" t="n">
-        <v>13.90155129565333</v>
+        <v>13.90155128650309</v>
       </c>
       <c r="CW71" t="n">
-        <v>12.511396166088</v>
+        <v>12.51139615785278</v>
       </c>
       <c r="CX71" t="n">
         <v>4</v>
@@ -40503,10 +40503,10 @@
         <v>2.4</v>
       </c>
       <c r="DA71" t="n">
-        <v>-11.82948177543187</v>
+        <v>-11.82948183346724</v>
       </c>
       <c r="DB71" t="n">
-        <v>-7.307378472350723</v>
+        <v>-7.307378551536758</v>
       </c>
       <c r="DC71" t="inlineStr">
         <is>
@@ -40826,10 +40826,10 @@
         <v>0</v>
       </c>
       <c r="CM72" t="n">
-        <v>0.5420072175453022</v>
+        <v>0.5420072205954749</v>
       </c>
       <c r="CN72" t="n">
-        <v>1.005423388546536</v>
+        <v>1.005423394204606</v>
       </c>
       <c r="CO72" t="n">
         <v>9.43764624323483</v>
@@ -40838,13 +40838,13 @@
         <v>8.675079879982691</v>
       </c>
       <c r="CQ72" t="n">
-        <v>10.27283934023934</v>
+        <v>10.27283933708304</v>
       </c>
       <c r="CR72" t="n">
-        <v>0.7349993034155926</v>
+        <v>0.7349993033565885</v>
       </c>
       <c r="CS72" t="n">
-        <v>7.987084281139095</v>
+        <v>7.987084277056502</v>
       </c>
       <c r="CT72" t="inlineStr"/>
       <c r="CU72" t="inlineStr"/>
@@ -41179,10 +41179,10 @@
         <v>0</v>
       </c>
       <c r="CM73" t="n">
-        <v>10.7057791953408</v>
+        <v>10.70577920793021</v>
       </c>
       <c r="CN73" t="n">
-        <v>19.85922040735718</v>
+        <v>19.85922043071054</v>
       </c>
       <c r="CO73" t="n">
         <v>28.52144455456774</v>
@@ -41191,25 +41191,25 @@
         <v>21.17171920104553</v>
       </c>
       <c r="CQ73" t="n">
-        <v>23.83501177037591</v>
+        <v>23.83501173952666</v>
       </c>
       <c r="CR73" t="n">
-        <v>22.6919985770867</v>
+        <v>22.6919985730501</v>
       </c>
       <c r="CS73" t="n">
-        <v>15.30865424574161</v>
+        <v>15.3086542199726</v>
       </c>
       <c r="CT73" t="n">
         <v>27.78248952102578</v>
       </c>
       <c r="CU73" t="n">
-        <v>21.23453968406766</v>
+        <v>21.23453968097865</v>
       </c>
       <c r="CV73" t="n">
-        <v>21.93185888906611</v>
+        <v>21.93185888704781</v>
       </c>
       <c r="CW73" t="n">
-        <v>19.7386730001595</v>
+        <v>19.73867299834303</v>
       </c>
       <c r="CX73" t="n">
         <v>8</v>
@@ -41221,10 +41221,10 @@
         <v>2.7</v>
       </c>
       <c r="DA73" t="n">
-        <v>-47.20868327795633</v>
+        <v>-47.2086832828145</v>
       </c>
       <c r="DB73" t="n">
-        <v>-43.20796996336267</v>
+        <v>-43.20796997162425</v>
       </c>
       <c r="DC73" t="inlineStr">
         <is>
@@ -41556,10 +41556,10 @@
         <v>0</v>
       </c>
       <c r="CM74" t="n">
-        <v>0.9179473562374241</v>
+        <v>0.9179473571863965</v>
       </c>
       <c r="CN74" t="n">
-        <v>1.702792345820421</v>
+        <v>1.702792347580765</v>
       </c>
       <c r="CO74" t="n">
         <v>6.072249031989433</v>
@@ -41568,7 +41568,7 @@
         <v>4.035265264444879</v>
       </c>
       <c r="CQ74" t="n">
-        <v>8.428205854307055</v>
+        <v>8.428205855913539</v>
       </c>
       <c r="CR74" t="n">
         <v>3.760485277130923</v>
@@ -41911,10 +41911,10 @@
         <v>0</v>
       </c>
       <c r="CM75" t="n">
-        <v>1.735754953303192</v>
+        <v>1.735754949540076</v>
       </c>
       <c r="CN75" t="n">
-        <v>3.21982543837742</v>
+        <v>3.21982543139684</v>
       </c>
       <c r="CO75" t="n">
         <v>24.06414080147791</v>
@@ -41923,13 +41923,13 @@
         <v>23.77341994112827</v>
       </c>
       <c r="CQ75" t="n">
-        <v>25.4703532338719</v>
+        <v>25.47035323011449</v>
       </c>
       <c r="CR75" t="n">
-        <v>6.70130722386185</v>
+        <v>6.701307224090082</v>
       </c>
       <c r="CS75" t="n">
-        <v>17.77589564300615</v>
+        <v>17.77589564733433</v>
       </c>
       <c r="CT75" t="n">
         <v>13.5886920342512</v>
@@ -42266,25 +42266,25 @@
         <v>0</v>
       </c>
       <c r="CM76" t="n">
-        <v>4.105009730133309</v>
+        <v>4.10500971959998</v>
       </c>
       <c r="CN76" t="n">
-        <v>7.002256971909948</v>
+        <v>7.002256959106598</v>
       </c>
       <c r="CO76" t="n">
-        <v>23.32321842550448</v>
+        <v>23.32321844270555</v>
       </c>
       <c r="CP76" t="n">
         <v>32.93553447863792</v>
       </c>
       <c r="CQ76" t="n">
-        <v>16.48731631645728</v>
+        <v>16.4873163117269</v>
       </c>
       <c r="CR76" t="n">
-        <v>20.28919693196956</v>
+        <v>20.28919693310452</v>
       </c>
       <c r="CS76" t="n">
-        <v>11.55489981911336</v>
+        <v>11.5548998262044</v>
       </c>
       <c r="CT76" t="n">
         <v>23.19375865248643</v>
@@ -42336,7 +42336,7 @@
         <v>0.05674416036882679</v>
       </c>
       <c r="DO76" t="n">
-        <v>-38.77462365715461</v>
+        <v>-38.77461953705444</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -42621,10 +42621,10 @@
         <v>0</v>
       </c>
       <c r="CM77" t="n">
-        <v>6.285911241041719</v>
+        <v>6.28591120640838</v>
       </c>
       <c r="CN77" t="n">
-        <v>11.66036535213239</v>
+        <v>11.66036528788754</v>
       </c>
       <c r="CO77" t="n">
         <v>32.87909322430473</v>
@@ -42633,25 +42633,25 @@
         <v>33.81282523448726</v>
       </c>
       <c r="CQ77" t="n">
-        <v>28.98439035719974</v>
+        <v>28.98439036293557</v>
       </c>
       <c r="CR77" t="n">
-        <v>25.24883989389977</v>
+        <v>25.24883989943697</v>
       </c>
       <c r="CS77" t="n">
-        <v>18.8088853391801</v>
+        <v>18.80888537605768</v>
       </c>
       <c r="CT77" t="n">
         <v>14.34677086089842</v>
       </c>
       <c r="CU77" t="n">
-        <v>23.6773100374432</v>
+        <v>23.67731003514402</v>
       </c>
       <c r="CV77" t="n">
-        <v>25.24883989389977</v>
+        <v>25.24883989943697</v>
       </c>
       <c r="CW77" t="n">
-        <v>22.72395590450979</v>
+        <v>22.72395590949328</v>
       </c>
       <c r="CX77" t="n">
         <v>7</v>
@@ -42663,10 +42663,10 @@
         <v>5.4</v>
       </c>
       <c r="DA77" t="n">
-        <v>-0.02658881587440654</v>
+        <v>-0.02658879394968894</v>
       </c>
       <c r="DB77" t="n">
-        <v>4.167666142916571</v>
+        <v>4.167666132801395</v>
       </c>
       <c r="DC77" t="inlineStr">
         <is>
@@ -42990,35 +42990,35 @@
         <v>0</v>
       </c>
       <c r="CM78" t="n">
-        <v>24.10609630691135</v>
+        <v>24.10609638975475</v>
       </c>
       <c r="CN78" t="n">
-        <v>29.25244931165667</v>
+        <v>29.25244933210383</v>
       </c>
       <c r="CO78" t="n">
-        <v>36.92263454113832</v>
+        <v>36.92263444005793</v>
       </c>
       <c r="CP78" t="n">
         <v>61.78228988979415</v>
       </c>
       <c r="CQ78" t="n">
-        <v>66.70460287822232</v>
+        <v>66.70460295184607</v>
       </c>
       <c r="CR78" t="n">
-        <v>41.55372100212249</v>
+        <v>41.55372099035571</v>
       </c>
       <c r="CS78" t="n">
-        <v>17.29235892650166</v>
+        <v>17.29235884900663</v>
       </c>
       <c r="CT78" t="inlineStr"/>
       <c r="CU78" t="n">
-        <v>39.65916469376385</v>
+        <v>39.65916469184559</v>
       </c>
       <c r="CV78" t="n">
-        <v>36.92263454113832</v>
+        <v>36.92263444005793</v>
       </c>
       <c r="CW78" t="n">
-        <v>33.23037108702449</v>
+        <v>33.23037099605214</v>
       </c>
       <c r="CX78" t="n">
         <v>7</v>
@@ -43030,10 +43030,10 @@
         <v>3.9</v>
       </c>
       <c r="DA78" t="n">
-        <v>32.44468268206433</v>
+        <v>32.44468231948026</v>
       </c>
       <c r="DB78" t="n">
-        <v>58.0676143984528</v>
+        <v>58.0676143908073</v>
       </c>
       <c r="DC78" t="inlineStr">
         <is>
@@ -43361,10 +43361,10 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>2.135335882280768</v>
+        <v>2.135335883556526</v>
       </c>
       <c r="CN79" t="n">
-        <v>3.961048061630823</v>
+        <v>3.961048063997356</v>
       </c>
       <c r="CO79" t="n">
         <v>16.12499952316284</v>
@@ -43373,7 +43373,7 @@
         <v>12.78795644154861</v>
       </c>
       <c r="CQ79" t="n">
-        <v>21.07497138017781</v>
+        <v>21.07497138186278</v>
       </c>
       <c r="CR79" t="n">
         <v>9.294207014285712</v>
@@ -43716,10 +43716,10 @@
         <v>0</v>
       </c>
       <c r="CM80" t="n">
-        <v>4.815933241713113</v>
+        <v>4.815933250401771</v>
       </c>
       <c r="CN80" t="n">
-        <v>8.933556163377823</v>
+        <v>8.933556179495284</v>
       </c>
       <c r="CO80" t="n">
         <v>30.21828844483058</v>
@@ -43728,19 +43728,19 @@
         <v>25.63338582679529</v>
       </c>
       <c r="CQ80" t="n">
-        <v>34.45161055487278</v>
+        <v>34.45161054378895</v>
       </c>
       <c r="CR80" t="n">
-        <v>11.76578088608928</v>
+        <v>11.7657808850967</v>
       </c>
       <c r="CS80" t="n">
-        <v>24.06579219624487</v>
+        <v>24.06579218263496</v>
       </c>
       <c r="CT80" t="n">
         <v>26.25</v>
       </c>
       <c r="CU80" t="n">
-        <v>25.3974763181388</v>
+        <v>25.39747631385775</v>
       </c>
       <c r="CV80" t="n">
         <v>25.94169291339765</v>
@@ -43761,7 +43761,7 @@
         <v>-11.05705286835093</v>
       </c>
       <c r="DB80" t="n">
-        <v>-3.247709264233145</v>
+        <v>-3.247709280541911</v>
       </c>
       <c r="DC80" t="inlineStr">
         <is>
@@ -44079,10 +44079,10 @@
         <v>0</v>
       </c>
       <c r="CM81" t="n">
-        <v>41.36674073080479</v>
+        <v>41.36674087878255</v>
       </c>
       <c r="CN81" t="n">
-        <v>60.22997450405177</v>
+        <v>60.2299747195074</v>
       </c>
       <c r="CO81" t="n">
         <v>35.35875738842788</v>
@@ -44101,13 +44101,13 @@
         <v>50.38275929312339</v>
       </c>
       <c r="CU81" t="n">
-        <v>43.8947375231395</v>
+        <v>43.89473758371173</v>
       </c>
       <c r="CV81" t="n">
-        <v>41.79773297188952</v>
+        <v>41.7977330458784</v>
       </c>
       <c r="CW81" t="n">
-        <v>37.61795967470056</v>
+        <v>37.61795974129056</v>
       </c>
       <c r="CX81" t="n">
         <v>6</v>
@@ -44119,10 +44119,10 @@
         <v>6.6</v>
       </c>
       <c r="DA81" t="n">
-        <v>-33.86434780538751</v>
+        <v>-33.86434768831649</v>
       </c>
       <c r="DB81" t="n">
-        <v>-22.82922521296291</v>
+        <v>-22.82922510647165</v>
       </c>
       <c r="DC81" t="inlineStr">
         <is>
@@ -44442,10 +44442,10 @@
         <v>0</v>
       </c>
       <c r="CM82" t="n">
-        <v>14.18574111972025</v>
+        <v>14.18574108782111</v>
       </c>
       <c r="CN82" t="n">
-        <v>26.31454977708106</v>
+        <v>26.31454971790815</v>
       </c>
       <c r="CO82" t="n">
         <v>37.04143720876227</v>
@@ -44454,25 +44454,25 @@
         <v>25.8401544888617</v>
       </c>
       <c r="CQ82" t="n">
-        <v>39.6358573403912</v>
+        <v>39.63585741703417</v>
       </c>
       <c r="CR82" t="n">
-        <v>41.79465738163416</v>
+        <v>41.79465739799126</v>
       </c>
       <c r="CS82" t="n">
-        <v>20.88726868708314</v>
+        <v>20.88726876110701</v>
       </c>
       <c r="CT82" t="n">
         <v>26.58328431841265</v>
       </c>
       <c r="CU82" t="n">
-        <v>29.0353687902433</v>
+        <v>29.03536879973729</v>
       </c>
       <c r="CV82" t="n">
-        <v>26.44891704774685</v>
+        <v>26.4489170181604</v>
       </c>
       <c r="CW82" t="n">
-        <v>23.80402534297217</v>
+        <v>23.80402531634436</v>
       </c>
       <c r="CX82" t="n">
         <v>8</v>
@@ -44484,10 +44484,10 @@
         <v>2.9</v>
       </c>
       <c r="DA82" t="n">
-        <v>-21.59412099993195</v>
+        <v>-21.59412108763882</v>
       </c>
       <c r="DB82" t="n">
-        <v>-4.363082323709211</v>
+        <v>-4.363082292437848</v>
       </c>
       <c r="DC82" t="inlineStr">
         <is>
@@ -44807,10 +44807,10 @@
         <v>0</v>
       </c>
       <c r="CM83" t="n">
-        <v>10.30515410453524</v>
+        <v>10.3051541765418</v>
       </c>
       <c r="CN83" t="n">
-        <v>19.11606086391288</v>
+        <v>19.11606099748504</v>
       </c>
       <c r="CO83" t="n">
         <v>13.92043917855315</v>
@@ -44831,7 +44831,7 @@
         <v>12.84315041940997</v>
       </c>
       <c r="CU83" t="n">
-        <v>15.35077739759401</v>
+        <v>15.35077742329135</v>
       </c>
       <c r="CV83" t="n">
         <v>13.33695414803924</v>
@@ -44852,7 +44852,7 @@
         <v>-23.93372030193791</v>
       </c>
       <c r="DB83" t="n">
-        <v>-2.720040194172801</v>
+        <v>-2.720040031325288</v>
       </c>
       <c r="DC83" t="inlineStr">
         <is>
@@ -45172,10 +45172,10 @@
         <v>0</v>
       </c>
       <c r="CM84" t="n">
-        <v>2.656011983676128</v>
+        <v>2.656011983420766</v>
       </c>
       <c r="CN84" t="n">
-        <v>4.926902229719218</v>
+        <v>4.92690222924552</v>
       </c>
       <c r="CO84" t="n">
         <v>25.41899625515882</v>
@@ -45184,7 +45184,7 @@
         <v>19.49200968885813</v>
       </c>
       <c r="CQ84" t="n">
-        <v>33.11004126323493</v>
+        <v>33.11004126281825</v>
       </c>
       <c r="CR84" t="n">
         <v>10.38593205872702</v>
@@ -45531,10 +45531,10 @@
         <v>0</v>
       </c>
       <c r="CM85" t="n">
-        <v>6.80282755312559</v>
+        <v>6.802827532049957</v>
       </c>
       <c r="CN85" t="n">
-        <v>12.61924511104797</v>
+        <v>12.61924507195267</v>
       </c>
       <c r="CO85" t="n">
         <v>7.958604169614386</v>
@@ -45555,7 +45555,7 @@
         <v>38.97525852693097</v>
       </c>
       <c r="CU85" t="n">
-        <v>10.40409276909183</v>
+        <v>10.40409276049598</v>
       </c>
       <c r="CV85" t="n">
         <v>7.958604169614386</v>
@@ -45576,7 +45576,7 @@
         <v>-35.47077922077923</v>
       </c>
       <c r="DB85" t="n">
-        <v>-6.269437733890904</v>
+        <v>-6.269437811330969</v>
       </c>
       <c r="DC85" t="inlineStr">
         <is>
@@ -45896,35 +45896,35 @@
         <v>0</v>
       </c>
       <c r="CM86" t="n">
-        <v>1.329575627142334</v>
+        <v>1.329575621128058</v>
       </c>
       <c r="CN86" t="n">
-        <v>1.787970928349853</v>
+        <v>1.787970922844959</v>
       </c>
       <c r="CO86" t="n">
-        <v>3.657425215139434</v>
+        <v>3.657425220422971</v>
       </c>
       <c r="CP86" t="n">
         <v>7.182036549729029</v>
       </c>
       <c r="CQ86" t="n">
-        <v>3.690251190602114</v>
+        <v>3.6902511848637</v>
       </c>
       <c r="CR86" t="n">
-        <v>1.338423448773225</v>
+        <v>1.338423448955536</v>
       </c>
       <c r="CS86" t="n">
-        <v>1.795233805591728</v>
+        <v>1.795233808957797</v>
       </c>
       <c r="CT86" t="inlineStr"/>
       <c r="CU86" t="n">
-        <v>2.266480035933115</v>
+        <v>2.266480034528837</v>
       </c>
       <c r="CV86" t="n">
-        <v>1.79160236697079</v>
+        <v>1.791602365901378</v>
       </c>
       <c r="CW86" t="n">
-        <v>1.612442130273711</v>
+        <v>1.612442129311241</v>
       </c>
       <c r="CX86" t="n">
         <v>6</v>
@@ -45936,10 +45936,10 @@
         <v>5.4</v>
       </c>
       <c r="DA86" t="n">
-        <v>-44.20615668707126</v>
+        <v>-44.20615672037476</v>
       </c>
       <c r="DB86" t="n">
-        <v>-21.57508810857758</v>
+        <v>-21.57508815716849</v>
       </c>
       <c r="DC86" t="inlineStr">
         <is>
@@ -46267,10 +46267,10 @@
         <v>0</v>
       </c>
       <c r="CM87" t="n">
-        <v>1.377772800765975</v>
+        <v>1.377772800503275</v>
       </c>
       <c r="CN87" t="n">
-        <v>2.555768545420883</v>
+        <v>2.555768544933575</v>
       </c>
       <c r="CO87" t="n">
         <v>10.39322363767291</v>
@@ -46279,13 +46279,13 @@
         <v>10.22375130073559</v>
       </c>
       <c r="CQ87" t="n">
-        <v>9.835571855802792</v>
+        <v>9.83557185591361</v>
       </c>
       <c r="CR87" t="n">
-        <v>1.868392251401784</v>
+        <v>1.868392251412359</v>
       </c>
       <c r="CS87" t="n">
-        <v>7.03300763315314</v>
+        <v>7.033007633460143</v>
       </c>
       <c r="CT87" t="n">
         <v>12.04041800117484</v>
@@ -46622,25 +46622,25 @@
         <v>0</v>
       </c>
       <c r="CM88" t="n">
-        <v>13.2193566082259</v>
+        <v>13.21935662650175</v>
       </c>
       <c r="CN88" t="n">
-        <v>13.22957925457071</v>
+        <v>13.22957926204111</v>
       </c>
       <c r="CO88" t="n">
-        <v>13.24687186776813</v>
+        <v>13.2468718569344</v>
       </c>
       <c r="CP88" t="n">
         <v>32.57919652771017</v>
       </c>
       <c r="CQ88" t="n">
-        <v>11.83565786350301</v>
+        <v>11.83565786124041</v>
       </c>
       <c r="CR88" t="n">
-        <v>24.51176402095319</v>
+        <v>24.511764018493</v>
       </c>
       <c r="CS88" t="n">
-        <v>4.96155638496877</v>
+        <v>4.961556373276609</v>
       </c>
       <c r="CT88" t="n">
         <v>52.78009373526422</v>
@@ -47340,10 +47340,10 @@
         <v>0</v>
       </c>
       <c r="CM90" t="n">
-        <v>3.383236100967605</v>
+        <v>3.383236084754814</v>
       </c>
       <c r="CN90" t="n">
-        <v>4.925991763008834</v>
+        <v>4.925991739403009</v>
       </c>
       <c r="CO90" t="n">
         <v>4.345361418407098</v>
@@ -47701,10 +47701,10 @@
         <v>0</v>
       </c>
       <c r="CM91" t="n">
-        <v>4.913572764169745</v>
+        <v>4.913572775517932</v>
       </c>
       <c r="CN91" t="n">
-        <v>9.114677477534876</v>
+        <v>9.114677498585765</v>
       </c>
       <c r="CO91" t="n">
         <v>32.34981869328296</v>
@@ -47713,13 +47713,13 @@
         <v>34.95455687527223</v>
       </c>
       <c r="CQ91" t="n">
-        <v>27.58750279006355</v>
+        <v>27.58750279175195</v>
       </c>
       <c r="CR91" t="n">
-        <v>11.10529429159846</v>
+        <v>11.10529429086175</v>
       </c>
       <c r="CS91" t="n">
-        <v>18.64714225775308</v>
+        <v>18.64714224676803</v>
       </c>
       <c r="CT91" t="n">
         <v>46.20055014188909</v>
@@ -48056,25 +48056,25 @@
         <v>0</v>
       </c>
       <c r="CM92" t="n">
-        <v>0.1365068423508819</v>
+        <v>0.1365068429769334</v>
       </c>
       <c r="CN92" t="n">
-        <v>0.1559108850169299</v>
+        <v>0.1559108857056716</v>
       </c>
       <c r="CO92" t="n">
-        <v>0.7492218008403249</v>
+        <v>0.749221800713936</v>
       </c>
       <c r="CP92" t="n">
         <v>3.095196412037962</v>
       </c>
       <c r="CQ92" t="n">
-        <v>0.2572541513206405</v>
+        <v>0.2572541516749456</v>
       </c>
       <c r="CR92" t="n">
-        <v>0.5416204958998517</v>
+        <v>0.5416204958898752</v>
       </c>
       <c r="CS92" t="n">
-        <v>0.3349334272387466</v>
+        <v>0.3349334271307651</v>
       </c>
       <c r="CT92" t="inlineStr"/>
       <c r="CU92" t="inlineStr"/>
@@ -48415,10 +48415,10 @@
         <v>0</v>
       </c>
       <c r="CM93" t="n">
-        <v>6.397417153471935</v>
+        <v>6.397417148493972</v>
       </c>
       <c r="CN93" t="n">
-        <v>9.314639375455137</v>
+        <v>9.314639368207223</v>
       </c>
       <c r="CO93" t="n">
         <v>3.748248950052818</v>
@@ -48768,10 +48768,10 @@
         <v>0</v>
       </c>
       <c r="CM94" t="n">
-        <v>12.66669287178369</v>
+        <v>12.66669287399413</v>
       </c>
       <c r="CN94" t="n">
-        <v>23.49671527715874</v>
+        <v>23.49671528125911</v>
       </c>
       <c r="CO94" t="n">
         <v>14.98448006805406</v>
@@ -48792,7 +48792,7 @@
         <v>22.80124355576588</v>
       </c>
       <c r="CU94" t="n">
-        <v>19.95929137381555</v>
+        <v>19.9592913746044</v>
       </c>
       <c r="CV94" t="n">
         <v>18.89286181190997</v>
@@ -48813,7 +48813,7 @@
         <v>-32.36445487854582</v>
       </c>
       <c r="DB94" t="n">
-        <v>-20.60743095310525</v>
+        <v>-20.60743094996742</v>
       </c>
       <c r="DC94" t="inlineStr">
         <is>
@@ -49109,10 +49109,10 @@
         <v>0</v>
       </c>
       <c r="CM95" t="n">
-        <v>12.45258433986284</v>
+        <v>12.45258438185869</v>
       </c>
       <c r="CN95" t="n">
-        <v>18.13096279884029</v>
+        <v>18.13096285998625</v>
       </c>
       <c r="CO95" t="inlineStr"/>
       <c r="CP95" t="inlineStr"/>
@@ -49123,13 +49123,13 @@
       <c r="CS95" t="inlineStr"/>
       <c r="CT95" t="inlineStr"/>
       <c r="CU95" t="n">
-        <v>18.97041571290104</v>
+        <v>18.97041574728165</v>
       </c>
       <c r="CV95" t="n">
-        <v>18.13096279884029</v>
+        <v>18.13096285998625</v>
       </c>
       <c r="CW95" t="n">
-        <v>16.31786651895627</v>
+        <v>16.31786657398763</v>
       </c>
       <c r="CX95" t="n">
         <v>3</v>
@@ -49141,10 +49141,10 @@
         <v>2.1</v>
       </c>
       <c r="DA95" t="n">
-        <v>-72.55194901674642</v>
+        <v>-72.55194892417894</v>
       </c>
       <c r="DB95" t="n">
-        <v>-68.09013377721097</v>
+        <v>-68.09013371937984</v>
       </c>
       <c r="DC95" t="inlineStr">
         <is>
@@ -49478,10 +49478,10 @@
         <v>0</v>
       </c>
       <c r="CM96" t="n">
-        <v>4.925587017966399</v>
+        <v>4.925587001491358</v>
       </c>
       <c r="CN96" t="n">
-        <v>7.171654698159077</v>
+        <v>7.171654674171419</v>
       </c>
       <c r="CO96" t="n">
         <v>5.841409764450903</v>
@@ -49500,13 +49500,13 @@
         <v>7.680081469140733</v>
       </c>
       <c r="CU96" t="n">
-        <v>6.566379717721506</v>
+        <v>6.566379710977722</v>
       </c>
       <c r="CV96" t="n">
-        <v>6.50653223130499</v>
+        <v>6.506532219311161</v>
       </c>
       <c r="CW96" t="n">
-        <v>5.855879008174491</v>
+        <v>5.855878997380045</v>
       </c>
       <c r="CX96" t="n">
         <v>6</v>
@@ -49518,10 +49518,10 @@
         <v>5.9</v>
       </c>
       <c r="DA96" t="n">
-        <v>-23.45256293891286</v>
+        <v>-23.45256308001673</v>
       </c>
       <c r="DB96" t="n">
-        <v>-14.16497208022426</v>
+        <v>-14.1649721683783</v>
       </c>
       <c r="DC96" t="inlineStr">
         <is>
@@ -49841,10 +49841,10 @@
         <v>0</v>
       </c>
       <c r="CM97" t="n">
-        <v>3.22996433119012</v>
+        <v>3.22996433520729</v>
       </c>
       <c r="CN97" t="n">
-        <v>5.991583834357673</v>
+        <v>5.991583841809523</v>
       </c>
       <c r="CO97" t="n">
         <v>14.24099764995627</v>
@@ -49853,23 +49853,23 @@
         <v>15.31578992542467</v>
       </c>
       <c r="CQ97" t="n">
-        <v>13.16146647248731</v>
+        <v>13.1614664740454</v>
       </c>
       <c r="CR97" t="n">
-        <v>14.93686465742552</v>
+        <v>14.93686465661174</v>
       </c>
       <c r="CS97" t="n">
-        <v>7.207353944929872</v>
+        <v>7.207353941012969</v>
       </c>
       <c r="CT97" t="inlineStr"/>
       <c r="CU97" t="n">
-        <v>11.80900941409689</v>
+        <v>11.8090094148101</v>
       </c>
       <c r="CV97" t="n">
-        <v>13.70123206122179</v>
+        <v>13.70123206200084</v>
       </c>
       <c r="CW97" t="n">
-        <v>12.33110885509961</v>
+        <v>12.33110885580075</v>
       </c>
       <c r="CX97" t="n">
         <v>6</v>
@@ -49881,10 +49881,10 @@
         <v>4.7</v>
       </c>
       <c r="DA97" t="n">
-        <v>58.90603726021337</v>
+        <v>58.90603726924866</v>
       </c>
       <c r="DB97" t="n">
-        <v>52.17795187872676</v>
+        <v>52.17795188791761</v>
       </c>
       <c r="DC97" t="inlineStr">
         <is>
@@ -50210,10 +50210,10 @@
         <v>0</v>
       </c>
       <c r="CM98" t="n">
-        <v>58.65081395270905</v>
+        <v>58.65081362158386</v>
       </c>
       <c r="CN98" t="n">
-        <v>85.39558511514439</v>
+        <v>85.39558463302612</v>
       </c>
       <c r="CO98" t="n">
         <v>24.28937089198329</v>
@@ -50581,10 +50581,10 @@
         <v>0</v>
       </c>
       <c r="CM99" t="n">
-        <v>35.87629961111006</v>
+        <v>35.87629932900714</v>
       </c>
       <c r="CN99" t="n">
-        <v>66.55053577860916</v>
+        <v>66.55053525530823</v>
       </c>
       <c r="CO99" t="n">
         <v>4.727868169088458</v>
@@ -50936,10 +50936,10 @@
         <v>0</v>
       </c>
       <c r="CM100" t="n">
-        <v>9.104082279581489</v>
+        <v>9.104082299018605</v>
       </c>
       <c r="CN100" t="n">
-        <v>16.88807262862366</v>
+        <v>16.88807266467951</v>
       </c>
       <c r="CO100" t="n">
         <v>40.34279204639602</v>
@@ -50948,19 +50948,19 @@
         <v>40.6980099339037</v>
       </c>
       <c r="CQ100" t="n">
-        <v>32.91704588177266</v>
+        <v>32.91704586994907</v>
       </c>
       <c r="CR100" t="n">
-        <v>49.93410689003473</v>
+        <v>49.93410688478379</v>
       </c>
       <c r="CS100" t="n">
-        <v>22.18690974395743</v>
+        <v>22.18690972235424</v>
       </c>
       <c r="CT100" t="n">
         <v>52.35439300971267</v>
       </c>
       <c r="CU100" t="n">
-        <v>36.47447573348584</v>
+        <v>36.47447573311128</v>
       </c>
       <c r="CV100" t="n">
         <v>40.34279204639602</v>
@@ -50981,7 +50981,7 @@
         <v>-1.201325600662806</v>
       </c>
       <c r="DB100" t="n">
-        <v>-0.7497258952766317</v>
+        <v>-0.7497258962958275</v>
       </c>
       <c r="DC100" t="inlineStr">
         <is>
@@ -51301,10 +51301,10 @@
         <v>0</v>
       </c>
       <c r="CM101" t="n">
-        <v>2.092381675144099</v>
+        <v>2.092381673636715</v>
       </c>
       <c r="CN101" t="n">
-        <v>3.881368007392304</v>
+        <v>3.881368004596106</v>
       </c>
       <c r="CO101" t="n">
         <v>10.15032146883479</v>
@@ -51313,19 +51313,19 @@
         <v>8.470043037007597</v>
       </c>
       <c r="CQ101" t="n">
-        <v>9.817377098580597</v>
+        <v>9.817377101668169</v>
       </c>
       <c r="CR101" t="n">
-        <v>7.521390902963949</v>
+        <v>7.521390903306457</v>
       </c>
       <c r="CS101" t="n">
-        <v>7.521523640516421</v>
+        <v>7.521523642958505</v>
       </c>
       <c r="CT101" t="n">
         <v>14.41306252244503</v>
       </c>
       <c r="CU101" t="n">
-        <v>8.825012382534386</v>
+        <v>8.825012382973808</v>
       </c>
       <c r="CV101" t="n">
         <v>8.470043037007597</v>
@@ -51346,7 +51346,7 @@
         <v>-62.39250833175431</v>
       </c>
       <c r="DB101" t="n">
-        <v>-56.46269273193681</v>
+        <v>-56.46269272976896</v>
       </c>
       <c r="DC101" t="inlineStr">
         <is>
@@ -51652,35 +51652,35 @@
         <v>0</v>
       </c>
       <c r="CM102" t="n">
-        <v>13.60549010739646</v>
+        <v>13.60549015875526</v>
       </c>
       <c r="CN102" t="n">
-        <v>16.14563406612907</v>
+        <v>16.14563409297981</v>
       </c>
       <c r="CO102" t="n">
-        <v>21.42970896250219</v>
+        <v>21.4297089172464</v>
       </c>
       <c r="CP102" t="n">
         <v>42.41036028560193</v>
       </c>
       <c r="CQ102" t="n">
-        <v>26.43094016219927</v>
+        <v>26.43094018572041</v>
       </c>
       <c r="CR102" t="n">
-        <v>15.65417287910898</v>
+        <v>15.65417287562044</v>
       </c>
       <c r="CS102" t="n">
-        <v>9.884596487593242</v>
+        <v>9.884596451481841</v>
       </c>
       <c r="CT102" t="inlineStr"/>
       <c r="CU102" t="n">
-        <v>16.70875150378418</v>
+        <v>16.70875151115047</v>
       </c>
       <c r="CV102" t="n">
-        <v>15.89990347261902</v>
+        <v>15.89990348430012</v>
       </c>
       <c r="CW102" t="n">
-        <v>14.30991312535712</v>
+        <v>14.30991313587011</v>
       </c>
       <c r="CX102" t="n">
         <v>4</v>
@@ -51692,10 +51692,10 @@
         <v>1.6</v>
       </c>
       <c r="DA102" t="n">
-        <v>-36.25874102873091</v>
+        <v>-36.25874098190246</v>
       </c>
       <c r="DB102" t="n">
-        <v>-25.57349249017822</v>
+        <v>-25.57349245736622</v>
       </c>
       <c r="DC102" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>0.8535513571607867</v>
       </c>
       <c r="DO102" t="n">
-        <v>-18.08446382079795</v>
+        <v>-18.08445807231789</v>
       </c>
       <c r="DP102" t="b">
         <v>0</v>
@@ -52027,10 +52027,10 @@
         <v>0</v>
       </c>
       <c r="CM103" t="n">
-        <v>8.303309932867645</v>
+        <v>8.303309923197489</v>
       </c>
       <c r="CN103" t="n">
-        <v>15.40263992546948</v>
+        <v>15.40263990753134</v>
       </c>
       <c r="CO103" t="n">
         <v>10.31598191535957</v>
@@ -52051,7 +52051,7 @@
         <v>11.57306829296474</v>
       </c>
       <c r="CU103" t="n">
-        <v>12.6488409946823</v>
+        <v>12.64884099123127</v>
       </c>
       <c r="CV103" t="n">
         <v>10.94452510416216</v>
@@ -52072,7 +52072,7 @@
         <v>-40.26638732283001</v>
       </c>
       <c r="DB103" t="n">
-        <v>-23.29386797908608</v>
+        <v>-23.29386800001413</v>
       </c>
       <c r="DC103" t="inlineStr">
         <is>
@@ -52404,37 +52404,37 @@
         <v>0</v>
       </c>
       <c r="CM104" t="n">
-        <v>4.982255730606066</v>
+        <v>4.982255763131928</v>
       </c>
       <c r="CN104" t="n">
-        <v>7.147480703091988</v>
+        <v>7.147480710563958</v>
       </c>
       <c r="CO104" t="n">
-        <v>10.70833409297613</v>
+        <v>10.70833403426296</v>
       </c>
       <c r="CP104" t="n">
         <v>14.54062870725391</v>
       </c>
       <c r="CQ104" t="n">
-        <v>7.241976172052023</v>
+        <v>7.241976140055904</v>
       </c>
       <c r="CR104" t="n">
-        <v>8.443565477384078</v>
+        <v>8.443565473267835</v>
       </c>
       <c r="CS104" t="n">
-        <v>5.329827813919455</v>
+        <v>5.329827780659808</v>
       </c>
       <c r="CT104" t="n">
         <v>10.99014349695177</v>
       </c>
       <c r="CU104" t="n">
-        <v>8.673026524279427</v>
+        <v>8.67302651326851</v>
       </c>
       <c r="CV104" t="n">
-        <v>7.842770824718051</v>
+        <v>7.84277080666187</v>
       </c>
       <c r="CW104" t="n">
-        <v>7.058493742246246</v>
+        <v>7.058493725995683</v>
       </c>
       <c r="CX104" t="n">
         <v>8</v>
@@ -52446,10 +52446,10 @@
         <v>2.9</v>
       </c>
       <c r="DA104" t="n">
-        <v>-68.97365388023628</v>
+        <v>-68.97365395166733</v>
       </c>
       <c r="DB104" t="n">
-        <v>-61.87680648668383</v>
+        <v>-61.87680653508347</v>
       </c>
       <c r="DC104" t="inlineStr">
         <is>
@@ -52769,10 +52769,10 @@
         <v>0</v>
       </c>
       <c r="CM105" t="n">
-        <v>10.23710456473382</v>
+        <v>10.23710461032054</v>
       </c>
       <c r="CN105" t="n">
-        <v>18.98982896758124</v>
+        <v>18.9898290521446</v>
       </c>
       <c r="CO105" t="n">
         <v>85.63087184126204</v>
@@ -52781,13 +52781,13 @@
         <v>75.61388439108377</v>
       </c>
       <c r="CQ105" t="n">
-        <v>102.4806943544638</v>
+        <v>102.4806943376925</v>
       </c>
       <c r="CR105" t="n">
-        <v>15.99314352241694</v>
+        <v>15.99314352011496</v>
       </c>
       <c r="CS105" t="n">
-        <v>69.23820787862185</v>
+        <v>69.23820781267064</v>
       </c>
       <c r="CT105" t="n">
         <v>22.15363857936098</v>
@@ -53128,37 +53128,37 @@
         <v>0</v>
       </c>
       <c r="CM106" t="n">
-        <v>17.0298709885493</v>
+        <v>17.02987093832519</v>
       </c>
       <c r="CN106" t="n">
-        <v>25.12863953284756</v>
+        <v>25.12863950587515</v>
       </c>
       <c r="CO106" t="n">
-        <v>43.17340772795892</v>
+        <v>43.17340780894378</v>
       </c>
       <c r="CP106" t="n">
         <v>61.92338218449162</v>
       </c>
       <c r="CQ106" t="n">
-        <v>34.39888701611265</v>
+        <v>34.39888703377872</v>
       </c>
       <c r="CR106" t="n">
-        <v>26.6927085200329</v>
+        <v>26.69270852437185</v>
       </c>
       <c r="CS106" t="n">
-        <v>21.55377240661545</v>
+        <v>21.5537724501939</v>
       </c>
       <c r="CT106" t="n">
         <v>22.74915071652201</v>
       </c>
       <c r="CU106" t="n">
-        <v>31.5812273866413</v>
+        <v>31.58122739531278</v>
       </c>
       <c r="CV106" t="n">
-        <v>25.91067402644023</v>
+        <v>25.9106740151235</v>
       </c>
       <c r="CW106" t="n">
-        <v>23.31960662379621</v>
+        <v>23.31960661361115</v>
       </c>
       <c r="CX106" t="n">
         <v>8</v>
@@ -53170,10 +53170,10 @@
         <v>3.6</v>
       </c>
       <c r="DA106" t="n">
-        <v>-58.17110919498438</v>
+        <v>-58.17110921325354</v>
       </c>
       <c r="DB106" t="n">
-        <v>-43.35205849929811</v>
+        <v>-43.3520584837439</v>
       </c>
       <c r="DC106" t="inlineStr">
         <is>
@@ -53517,25 +53517,25 @@
         <v>0</v>
       </c>
       <c r="CM107" t="n">
-        <v>19.74422611701657</v>
+        <v>19.74422615408849</v>
       </c>
       <c r="CN107" t="n">
-        <v>20.81901951297207</v>
+        <v>20.81901952839438</v>
       </c>
       <c r="CO107" t="n">
-        <v>22.67893469093263</v>
+        <v>22.6789346651506</v>
       </c>
       <c r="CP107" t="n">
         <v>51.15469290785368</v>
       </c>
       <c r="CQ107" t="n">
-        <v>18.12400024560203</v>
+        <v>18.12400023564574</v>
       </c>
       <c r="CR107" t="n">
-        <v>23.14674993622047</v>
+        <v>23.14674993313622</v>
       </c>
       <c r="CS107" t="n">
-        <v>9.251671459168437</v>
+        <v>9.251671433787523</v>
       </c>
       <c r="CT107" t="n">
         <v>121.0340831371104</v>
@@ -53872,10 +53872,10 @@
         <v>0</v>
       </c>
       <c r="CM108" t="n">
-        <v>2.308795151704667</v>
+        <v>2.30879514807204</v>
       </c>
       <c r="CN108" t="n">
-        <v>4.282815006412157</v>
+        <v>4.282814999673634</v>
       </c>
       <c r="CO108" t="inlineStr"/>
       <c r="CP108" t="inlineStr"/>
@@ -53886,13 +53886,13 @@
         <v>9.788598190877345</v>
       </c>
       <c r="CU108" t="n">
-        <v>5.460069449664723</v>
+        <v>5.460069446207673</v>
       </c>
       <c r="CV108" t="n">
-        <v>4.282815006412157</v>
+        <v>4.282814999673634</v>
       </c>
       <c r="CW108" t="n">
-        <v>3.854533505770942</v>
+        <v>3.854533499706271</v>
       </c>
       <c r="CX108" t="n">
         <v>3</v>
@@ -53904,10 +53904,10 @@
         <v>4.2</v>
       </c>
       <c r="DA108" t="n">
-        <v>-50.64617754146703</v>
+        <v>-50.64617761911967</v>
       </c>
       <c r="DB108" t="n">
-        <v>-30.08873892870336</v>
+        <v>-30.08873897296776</v>
       </c>
       <c r="DC108" t="inlineStr">
         <is>
@@ -54235,10 +54235,10 @@
         <v>0</v>
       </c>
       <c r="CM109" t="n">
-        <v>2.288286006939481</v>
+        <v>2.288285996794644</v>
       </c>
       <c r="CN109" t="n">
-        <v>4.244770542872736</v>
+        <v>4.244770524054065</v>
       </c>
       <c r="CO109" t="n">
         <v>12.12775768334331</v>
@@ -54247,25 +54247,25 @@
         <v>13.42256100698398</v>
       </c>
       <c r="CQ109" t="n">
-        <v>8.497290988888818</v>
+        <v>8.497290993621979</v>
       </c>
       <c r="CR109" t="n">
-        <v>5.723505654385608</v>
+        <v>5.723505655254661</v>
       </c>
       <c r="CS109" t="n">
-        <v>6.353086980025411</v>
+        <v>6.353086989354603</v>
       </c>
       <c r="CT109" t="n">
         <v>12.85999965667725</v>
       </c>
       <c r="CU109" t="n">
-        <v>9.032710359025302</v>
+        <v>9.032710358469979</v>
       </c>
       <c r="CV109" t="n">
-        <v>8.497290988888818</v>
+        <v>8.497290993621979</v>
       </c>
       <c r="CW109" t="n">
-        <v>7.647561889999936</v>
+        <v>7.647561894259781</v>
       </c>
       <c r="CX109" t="n">
         <v>7</v>
@@ -54277,10 +54277,10 @@
         <v>5.9</v>
       </c>
       <c r="DA109" t="n">
-        <v>-40.53217656169126</v>
+        <v>-40.53217652856647</v>
       </c>
       <c r="DB109" t="n">
-        <v>-29.76119284470366</v>
+        <v>-29.76119284902188</v>
       </c>
       <c r="DC109" t="inlineStr">
         <is>
@@ -54600,25 +54600,25 @@
         <v>0</v>
       </c>
       <c r="CM110" t="n">
-        <v>0.7081894193505306</v>
+        <v>0.7081894167676014</v>
       </c>
       <c r="CN110" t="n">
-        <v>1.295936845130162</v>
+        <v>1.295936842709595</v>
       </c>
       <c r="CO110" t="n">
-        <v>3.377655397600054</v>
+        <v>3.377655403610311</v>
       </c>
       <c r="CP110" t="n">
         <v>3.9650539013691</v>
       </c>
       <c r="CQ110" t="n">
-        <v>2.282150458622891</v>
+        <v>2.282150459318896</v>
       </c>
       <c r="CR110" t="n">
-        <v>2.625382003933226</v>
+        <v>2.625382004265233</v>
       </c>
       <c r="CS110" t="n">
-        <v>1.648360169317574</v>
+        <v>1.648360171492814</v>
       </c>
       <c r="CT110" t="n">
         <v>9.207389804930452</v>
@@ -54953,10 +54953,10 @@
         <v>0</v>
       </c>
       <c r="CM111" t="n">
-        <v>64.79503928388357</v>
+        <v>64.79503914059254</v>
       </c>
       <c r="CN111" t="n">
-        <v>94.34157719733446</v>
+        <v>94.34157698870274</v>
       </c>
       <c r="CO111" t="n">
         <v>24.49777849613394</v>
@@ -55304,10 +55304,10 @@
         <v>0</v>
       </c>
       <c r="CM112" t="n">
-        <v>0.07108092265919706</v>
+        <v>0.07108092301721451</v>
       </c>
       <c r="CN112" t="n">
-        <v>0.1318551115328105</v>
+        <v>0.1318551121969329</v>
       </c>
       <c r="CO112" t="inlineStr"/>
       <c r="CP112" t="inlineStr"/>
@@ -55647,10 +55647,10 @@
         <v>0</v>
       </c>
       <c r="CM113" t="n">
-        <v>4.791995451717604</v>
+        <v>4.791995452485938</v>
       </c>
       <c r="CN113" t="n">
-        <v>8.889151562936155</v>
+        <v>8.889151564361413</v>
       </c>
       <c r="CO113" t="n">
         <v>41.68025800547819</v>
@@ -55659,13 +55659,13 @@
         <v>41.39375437682286</v>
       </c>
       <c r="CQ113" t="n">
-        <v>34.44390370039639</v>
+        <v>34.44390369935719</v>
       </c>
       <c r="CR113" t="n">
-        <v>17.70853835541891</v>
+        <v>17.70853835534744</v>
       </c>
       <c r="CS113" t="n">
-        <v>28.64167031697379</v>
+        <v>28.64167031609415</v>
       </c>
       <c r="CT113" t="n">
         <v>43.95885076728991</v>
@@ -56355,10 +56355,10 @@
         <v>0</v>
       </c>
       <c r="CM115" t="n">
-        <v>3.331469393315909</v>
+        <v>3.331469393305006</v>
       </c>
       <c r="CN115" t="n">
-        <v>6.17987572460101</v>
+        <v>6.179875724580786</v>
       </c>
       <c r="CO115" t="n">
         <v>14.76476111603741</v>
@@ -56367,23 +56367,23 @@
         <v>15.71944051824731</v>
       </c>
       <c r="CQ115" t="n">
-        <v>10.25113356801908</v>
+        <v>10.25113356802674</v>
       </c>
       <c r="CR115" t="n">
-        <v>13.00142957086294</v>
+        <v>13.00142957086482</v>
       </c>
       <c r="CS115" t="n">
-        <v>7.578884469348979</v>
+        <v>7.57888446935982</v>
       </c>
       <c r="CT115" t="inlineStr"/>
       <c r="CU115" t="n">
-        <v>11.24925416118612</v>
+        <v>11.24925416118615</v>
       </c>
       <c r="CV115" t="n">
-        <v>11.62628156944101</v>
+        <v>11.62628156944578</v>
       </c>
       <c r="CW115" t="n">
-        <v>10.46365341249691</v>
+        <v>10.4636534125012</v>
       </c>
       <c r="CX115" t="n">
         <v>6</v>
@@ -56395,10 +56395,10 @@
         <v>4.7</v>
       </c>
       <c r="DA115" t="n">
-        <v>-41.01660908963262</v>
+        <v>-41.01660908960839</v>
       </c>
       <c r="DB115" t="n">
-        <v>-36.58819444011147</v>
+        <v>-36.58819444011133</v>
       </c>
       <c r="DC115" t="inlineStr">
         <is>
@@ -57055,10 +57055,10 @@
         <v>0</v>
       </c>
       <c r="CM117" t="n">
-        <v>1.303237661166353</v>
+        <v>1.303237661186293</v>
       </c>
       <c r="CN117" t="n">
-        <v>2.417505861463584</v>
+        <v>2.417505861500574</v>
       </c>
       <c r="CO117" t="n">
         <v>2.370527277221787</v>
@@ -57067,7 +57067,7 @@
         <v>3.99173753228638</v>
       </c>
       <c r="CQ117" t="n">
-        <v>4.598179202435936</v>
+        <v>4.59817920244908</v>
       </c>
       <c r="CR117" t="n">
         <v>2.490846657242768</v>
@@ -57079,13 +57079,13 @@
         <v>5.373039997618077</v>
       </c>
       <c r="CU117" t="n">
-        <v>3.088732198720716</v>
+        <v>3.088732198729475</v>
       </c>
       <c r="CV117" t="n">
-        <v>2.454176259353176</v>
+        <v>2.454176259371671</v>
       </c>
       <c r="CW117" t="n">
-        <v>2.208758633417858</v>
+        <v>2.208758633434504</v>
       </c>
       <c r="CX117" t="n">
         <v>8</v>
@@ -57097,10 +57097,10 @@
         <v>4.1</v>
       </c>
       <c r="DA117" t="n">
-        <v>-41.87477207541772</v>
+        <v>-41.87477207497967</v>
       </c>
       <c r="DB117" t="n">
-        <v>-18.71757269791586</v>
+        <v>-18.71757269768536</v>
       </c>
       <c r="DC117" t="inlineStr">
         <is>
@@ -57424,25 +57424,25 @@
         <v>0</v>
       </c>
       <c r="CM118" t="n">
-        <v>1.385969549893153</v>
+        <v>1.385969549935518</v>
       </c>
       <c r="CN118" t="n">
-        <v>2.566824815069988</v>
+        <v>2.5668248151222</v>
       </c>
       <c r="CO118" t="n">
-        <v>8.734545308525231</v>
+        <v>8.734545308435909</v>
       </c>
       <c r="CP118" t="n">
         <v>10.76105602888196</v>
       </c>
       <c r="CQ118" t="n">
-        <v>4.818793502165946</v>
+        <v>4.818793502142094</v>
       </c>
       <c r="CR118" t="n">
-        <v>7.689753633974236</v>
+        <v>7.689753633968709</v>
       </c>
       <c r="CS118" t="n">
-        <v>4.249077459328551</v>
+        <v>4.249077459296936</v>
       </c>
       <c r="CT118" t="n">
         <v>12.10586855084149</v>
@@ -57779,25 +57779,25 @@
         <v>0</v>
       </c>
       <c r="CM119" t="n">
-        <v>4.313523366740695</v>
+        <v>4.313523380771215</v>
       </c>
       <c r="CN119" t="n">
-        <v>5.371995823899579</v>
+        <v>5.371995838757273</v>
       </c>
       <c r="CO119" t="n">
-        <v>13.96479114215317</v>
+        <v>13.96479113535352</v>
       </c>
       <c r="CP119" t="n">
         <v>37.02868912025743</v>
       </c>
       <c r="CQ119" t="n">
-        <v>9.443307067487209</v>
+        <v>9.443307077625168</v>
       </c>
       <c r="CR119" t="n">
-        <v>48.30742124602636</v>
+        <v>48.30742124364938</v>
       </c>
       <c r="CS119" t="n">
-        <v>6.640663801428888</v>
+        <v>6.640663796453104</v>
       </c>
       <c r="CT119" t="n">
         <v>23.55589235584143</v>
@@ -57849,7 +57849,7 @@
         <v>1.848535822781505</v>
       </c>
       <c r="DO119" t="n">
-        <v>-46.5686603478323</v>
+        <v>-46.56866357632883</v>
       </c>
       <c r="DP119" t="b">
         <v>0</v>
@@ -58134,10 +58134,10 @@
         <v>0</v>
       </c>
       <c r="CM120" t="n">
-        <v>12.1328197213893</v>
+        <v>12.13281975612021</v>
       </c>
       <c r="CN120" t="n">
-        <v>15.13964895669012</v>
+        <v>15.13964900002826</v>
       </c>
       <c r="CO120" t="inlineStr"/>
       <c r="CP120" t="inlineStr"/>
@@ -58481,10 +58481,10 @@
         <v>0</v>
       </c>
       <c r="CM121" t="n">
-        <v>2.433630216918474</v>
+        <v>2.433630218761886</v>
       </c>
       <c r="CN121" t="n">
-        <v>4.514384052383769</v>
+        <v>4.514384055803299</v>
       </c>
       <c r="CO121" t="n">
         <v>12.16393421907894</v>
@@ -58493,13 +58493,13 @@
         <v>12.67500423009855</v>
       </c>
       <c r="CQ121" t="n">
-        <v>9.610893240681413</v>
+        <v>9.610893239748908</v>
       </c>
       <c r="CR121" t="n">
-        <v>0.7923097205868522</v>
+        <v>0.7923097205623658</v>
       </c>
       <c r="CS121" t="n">
-        <v>6.738186466403493</v>
+        <v>6.738186464487673</v>
       </c>
       <c r="CT121" t="n">
         <v>7.386557878337924</v>
@@ -58836,10 +58836,10 @@
         <v>0</v>
       </c>
       <c r="CM122" t="n">
-        <v>1.587487369630221</v>
+        <v>1.587487375924325</v>
       </c>
       <c r="CN122" t="n">
-        <v>1.654514614125719</v>
+        <v>1.654514620685574</v>
       </c>
       <c r="CO122" t="inlineStr"/>
       <c r="CP122" t="inlineStr"/>
@@ -59193,25 +59193,25 @@
         <v>0</v>
       </c>
       <c r="CM123" t="n">
-        <v>2.440509519837817</v>
+        <v>2.440509519424208</v>
       </c>
       <c r="CN123" t="n">
-        <v>2.582847804534458</v>
+        <v>2.582847804216131</v>
       </c>
       <c r="CO123" t="n">
-        <v>3.131348372426038</v>
+        <v>3.1313483725708</v>
       </c>
       <c r="CP123" t="n">
         <v>9.968961369836157</v>
       </c>
       <c r="CQ123" t="n">
-        <v>1.773614900803139</v>
+        <v>1.773614900775639</v>
       </c>
       <c r="CR123" t="n">
-        <v>5.893793317047879</v>
+        <v>5.89379331707971</v>
       </c>
       <c r="CS123" t="n">
-        <v>1.284000035907338</v>
+        <v>1.284000036048924</v>
       </c>
       <c r="CT123" t="n">
         <v>14.17567566803012</v>
@@ -59556,10 +59556,10 @@
         <v>0</v>
       </c>
       <c r="CM124" t="n">
-        <v>1.695762283515031</v>
+        <v>1.695762287256657</v>
       </c>
       <c r="CN124" t="n">
-        <v>3.145639035920382</v>
+        <v>3.145639042861098</v>
       </c>
       <c r="CO124" t="n">
         <v>1.164835184210863</v>
@@ -59568,7 +59568,7 @@
         <v>4.685046848239709</v>
       </c>
       <c r="CQ124" t="n">
-        <v>1.617701830494396</v>
+        <v>1.617701831833081</v>
       </c>
       <c r="CR124" t="n">
         <v>0.7445919647652398</v>
@@ -59911,10 +59911,10 @@
         <v>0</v>
       </c>
       <c r="CM125" t="n">
-        <v>1.208150920922097</v>
+        <v>1.208150922139057</v>
       </c>
       <c r="CN125" t="n">
-        <v>2.24111995831049</v>
+        <v>2.241119960567951</v>
       </c>
       <c r="CO125" t="inlineStr"/>
       <c r="CP125" t="inlineStr"/>
@@ -60264,10 +60264,10 @@
         <v>0</v>
       </c>
       <c r="CM126" t="n">
-        <v>5.852737024143494</v>
+        <v>5.852737032525572</v>
       </c>
       <c r="CN126" t="n">
-        <v>8.521585107152928</v>
+        <v>8.521585119357233</v>
       </c>
       <c r="CO126" t="inlineStr"/>
       <c r="CP126" t="inlineStr"/>
@@ -60595,10 +60595,10 @@
         <v>0</v>
       </c>
       <c r="CM127" t="n">
-        <v>39.16484738813976</v>
+        <v>39.16484733271603</v>
       </c>
       <c r="CN127" t="n">
-        <v>72.65079190499925</v>
+        <v>72.65079180218822</v>
       </c>
       <c r="CO127" t="n">
         <v>19.70019868936262</v>
@@ -60617,7 +60617,7 @@
       </c>
       <c r="CT127" t="inlineStr"/>
       <c r="CU127" t="n">
-        <v>25.95832720510057</v>
+        <v>25.95832719586328</v>
       </c>
       <c r="CV127" t="n">
         <v>22.94099163326045</v>
@@ -60638,7 +60638,7 @@
         <v>-8.398883623331265</v>
       </c>
       <c r="DB127" t="n">
-        <v>15.16559960393973</v>
+        <v>15.16559956295795</v>
       </c>
       <c r="DC127" t="inlineStr">
         <is>
@@ -60970,10 +60970,10 @@
         <v>0</v>
       </c>
       <c r="CM128" t="n">
-        <v>7.023003877920084</v>
+        <v>7.023003872521314</v>
       </c>
       <c r="CN128" t="n">
-        <v>12.52125438379053</v>
+        <v>12.52125437416511</v>
       </c>
       <c r="CO128" t="inlineStr"/>
       <c r="CP128" t="inlineStr"/>
@@ -60982,13 +60982,13 @@
       <c r="CS128" t="inlineStr"/>
       <c r="CT128" t="inlineStr"/>
       <c r="CU128" t="n">
-        <v>9.772129130855307</v>
+        <v>9.772129123343211</v>
       </c>
       <c r="CV128" t="n">
-        <v>9.772129130855307</v>
+        <v>9.772129123343211</v>
       </c>
       <c r="CW128" t="n">
-        <v>8.794916217769776</v>
+        <v>8.794916211008889</v>
       </c>
       <c r="CX128" t="n">
         <v>2</v>
@@ -61000,10 +61000,10 @@
         <v>1.8</v>
       </c>
       <c r="DA128" t="n">
-        <v>37.85134890300041</v>
+        <v>37.8513487970304</v>
       </c>
       <c r="DB128" t="n">
-        <v>53.16816544777825</v>
+        <v>53.16816533003379</v>
       </c>
       <c r="DC128" t="inlineStr">
         <is>
@@ -61662,10 +61662,10 @@
         <v>0</v>
       </c>
       <c r="CM130" t="n">
-        <v>0.7898297413363614</v>
+        <v>0.7898297419195486</v>
       </c>
       <c r="CN130" t="n">
-        <v>1.46513417017895</v>
+        <v>1.465134171260762</v>
       </c>
       <c r="CO130" t="n">
         <v>15.55901742875274</v>
@@ -61674,13 +61674,13 @@
         <v>16.24752185378162</v>
       </c>
       <c r="CQ130" t="n">
-        <v>13.6293120720343</v>
+        <v>13.62931207190135</v>
       </c>
       <c r="CR130" t="n">
-        <v>1.677017488334814</v>
+        <v>1.677017488322422</v>
       </c>
       <c r="CS130" t="n">
-        <v>10.99975764150209</v>
+        <v>10.99975764089856</v>
       </c>
       <c r="CT130" t="inlineStr"/>
       <c r="CU130" t="inlineStr"/>
@@ -62023,25 +62023,25 @@
         <v>0</v>
       </c>
       <c r="CM131" t="n">
-        <v>3.718272701161162</v>
+        <v>3.718272697158386</v>
       </c>
       <c r="CN131" t="n">
-        <v>3.804269599121228</v>
+        <v>3.804269595688058</v>
       </c>
       <c r="CO131" t="n">
-        <v>4.346918087077542</v>
+        <v>4.34691808783418</v>
       </c>
       <c r="CP131" t="n">
         <v>18.92094732156112</v>
       </c>
       <c r="CQ131" t="n">
-        <v>3.380892018192205</v>
+        <v>3.380892015980546</v>
       </c>
       <c r="CR131" t="n">
-        <v>7.734015932635312</v>
+        <v>7.734015932797347</v>
       </c>
       <c r="CS131" t="n">
-        <v>1.693078863111775</v>
+        <v>1.69307886389728</v>
       </c>
       <c r="CT131" t="n">
         <v>21.99280021819457</v>
@@ -62378,25 +62378,25 @@
         <v>0</v>
       </c>
       <c r="CM132" t="n">
-        <v>0.6526494808978859</v>
+        <v>0.6526494784606154</v>
       </c>
       <c r="CN132" t="n">
-        <v>0.8701114310815128</v>
+        <v>0.8701114280785891</v>
       </c>
       <c r="CO132" t="n">
-        <v>4.575412018197043</v>
+        <v>4.575412019492939</v>
       </c>
       <c r="CP132" t="n">
         <v>11.53061776171596</v>
       </c>
       <c r="CQ132" t="n">
-        <v>1.75315303845725</v>
+        <v>1.753153038925816</v>
       </c>
       <c r="CR132" t="n">
-        <v>0.6736989119279402</v>
+        <v>0.6736989119460733</v>
       </c>
       <c r="CS132" t="n">
-        <v>2.239819127991233</v>
+        <v>2.239819128829849</v>
       </c>
       <c r="CT132" t="n">
         <v>18.94000053405762</v>
@@ -62741,10 +62741,10 @@
         <v>0</v>
       </c>
       <c r="CM133" t="n">
-        <v>1.399091230074434</v>
+        <v>1.399091222919376</v>
       </c>
       <c r="CN133" t="n">
-        <v>2.341569958697302</v>
+        <v>2.341569946722338</v>
       </c>
       <c r="CO133" t="inlineStr"/>
       <c r="CP133" t="inlineStr"/>
@@ -62755,13 +62755,13 @@
         <v>5.639999866485596</v>
       </c>
       <c r="CU133" t="n">
-        <v>3.12688701841911</v>
+        <v>3.126887012042437</v>
       </c>
       <c r="CV133" t="n">
-        <v>2.341569958697302</v>
+        <v>2.341569946722338</v>
       </c>
       <c r="CW133" t="n">
-        <v>2.107412962827572</v>
+        <v>2.107412952050104</v>
       </c>
       <c r="CX133" t="n">
         <v>3</v>
@@ -62773,10 +62773,10 @@
         <v>4</v>
       </c>
       <c r="DA133" t="n">
-        <v>-62.63452105113709</v>
+        <v>-62.63452124222695</v>
       </c>
       <c r="DB133" t="n">
-        <v>-44.55873949572378</v>
+        <v>-44.55873960878537</v>
       </c>
       <c r="DC133" t="inlineStr">
         <is>
@@ -63092,10 +63092,10 @@
         <v>0</v>
       </c>
       <c r="CM134" t="n">
-        <v>1.438248637260531</v>
+        <v>1.438248637558624</v>
       </c>
       <c r="CN134" t="n">
-        <v>2.094090015851333</v>
+        <v>2.094090016285357</v>
       </c>
       <c r="CO134" t="inlineStr"/>
       <c r="CP134" t="inlineStr"/>
@@ -63431,10 +63431,10 @@
         <v>0</v>
       </c>
       <c r="CM135" t="n">
-        <v>0.877351826466939</v>
+        <v>0.8773518260177365</v>
       </c>
       <c r="CN135" t="n">
-        <v>1.627487638096172</v>
+        <v>1.627487637262901</v>
       </c>
       <c r="CO135" t="inlineStr"/>
       <c r="CP135" t="inlineStr"/>
@@ -63443,13 +63443,13 @@
       <c r="CS135" t="inlineStr"/>
       <c r="CT135" t="inlineStr"/>
       <c r="CU135" t="n">
-        <v>1.252419732281555</v>
+        <v>1.252419731640319</v>
       </c>
       <c r="CV135" t="n">
-        <v>1.252419732281555</v>
+        <v>1.252419731640319</v>
       </c>
       <c r="CW135" t="n">
-        <v>1.1271777590534</v>
+        <v>1.127177758476287</v>
       </c>
       <c r="CX135" t="n">
         <v>2</v>
@@ -63461,10 +63461,10 @@
         <v>1.9</v>
       </c>
       <c r="DA135" t="n">
-        <v>-73.03402379560848</v>
+        <v>-73.03402380941499</v>
       </c>
       <c r="DB135" t="n">
-        <v>-70.03780421734275</v>
+        <v>-70.03780423268333</v>
       </c>
       <c r="DC135" t="inlineStr">
         <is>
@@ -63788,37 +63788,37 @@
         <v>0</v>
       </c>
       <c r="CM136" t="n">
-        <v>2.200632222687245</v>
+        <v>2.200632218687533</v>
       </c>
       <c r="CN136" t="n">
-        <v>3.822448462979644</v>
+        <v>3.822448459275172</v>
       </c>
       <c r="CO136" t="n">
-        <v>9.543028024166137</v>
+        <v>9.543028032262374</v>
       </c>
       <c r="CP136" t="n">
         <v>12.03991535229107</v>
       </c>
       <c r="CQ136" t="n">
-        <v>5.525841546131127</v>
+        <v>5.525841548907239</v>
       </c>
       <c r="CR136" t="n">
-        <v>5.528978025303302</v>
+        <v>5.528978025653175</v>
       </c>
       <c r="CS136" t="n">
-        <v>4.712422457005832</v>
+        <v>4.712422460233439</v>
       </c>
       <c r="CT136" t="n">
         <v>16.41330661932616</v>
       </c>
       <c r="CU136" t="n">
-        <v>6.862105644646185</v>
+        <v>6.862105646437079</v>
       </c>
       <c r="CV136" t="n">
-        <v>5.527409785717214</v>
+        <v>5.527409787280207</v>
       </c>
       <c r="CW136" t="n">
-        <v>4.974668807145493</v>
+        <v>4.974668808552186</v>
       </c>
       <c r="CX136" t="n">
         <v>6</v>
@@ -63830,10 +63830,10 @@
         <v>7.5</v>
       </c>
       <c r="DA136" t="n">
-        <v>-72.7564690865827</v>
+        <v>-72.75646907887901</v>
       </c>
       <c r="DB136" t="n">
-        <v>-62.42001337003055</v>
+        <v>-62.4200133602228</v>
       </c>
       <c r="DC136" t="inlineStr">
         <is>
@@ -64159,10 +64159,10 @@
         <v>0</v>
       </c>
       <c r="CM137" t="n">
-        <v>0.3624512125088824</v>
+        <v>0.3624512130540007</v>
       </c>
       <c r="CN137" t="n">
-        <v>0.6723469992039769</v>
+        <v>0.6723470002151714</v>
       </c>
       <c r="CO137" t="inlineStr"/>
       <c r="CP137" t="inlineStr"/>
@@ -64171,13 +64171,13 @@
       <c r="CS137" t="inlineStr"/>
       <c r="CT137" t="inlineStr"/>
       <c r="CU137" t="n">
-        <v>0.5173991058564297</v>
+        <v>0.517399106634586</v>
       </c>
       <c r="CV137" t="n">
-        <v>0.5173991058564297</v>
+        <v>0.517399106634586</v>
       </c>
       <c r="CW137" t="n">
-        <v>0.4656591952707867</v>
+        <v>0.4656591959711274</v>
       </c>
       <c r="CX137" t="n">
         <v>2</v>
@@ -64189,10 +64189,10 @@
         <v>1.9</v>
       </c>
       <c r="DA137" t="n">
-        <v>-62.14152942684093</v>
+        <v>-62.14152936990267</v>
       </c>
       <c r="DB137" t="n">
-        <v>-57.93503269648993</v>
+        <v>-57.93503263322519</v>
       </c>
       <c r="DC137" t="inlineStr">
         <is>
@@ -65577,10 +65577,10 @@
         <v>0</v>
       </c>
       <c r="CM141" t="n">
-        <v>8.766112185287829</v>
+        <v>8.766112190634384</v>
       </c>
       <c r="CN141" t="n">
-        <v>12.76345934177908</v>
+        <v>12.76345934956366</v>
       </c>
       <c r="CO141" t="n">
         <v>7.914899901388957</v>
@@ -65930,25 +65930,25 @@
         <v>0</v>
       </c>
       <c r="CM142" t="n">
-        <v>1.696102872433962</v>
+        <v>1.696102869941153</v>
       </c>
       <c r="CN142" t="n">
-        <v>1.830457451325592</v>
+        <v>1.830457449280859</v>
       </c>
       <c r="CO142" t="n">
-        <v>2.429282833234933</v>
+        <v>2.429282834091659</v>
       </c>
       <c r="CP142" t="n">
         <v>7.813514820721882</v>
       </c>
       <c r="CQ142" t="n">
-        <v>1.759689033554139</v>
+        <v>1.759689032676954</v>
       </c>
       <c r="CR142" t="n">
-        <v>2.001744399320021</v>
+        <v>2.001744399401084</v>
       </c>
       <c r="CS142" t="n">
-        <v>1.022042585991662</v>
+        <v>1.022042586801127</v>
       </c>
       <c r="CT142" t="n">
         <v>0.8825864735264446</v>
@@ -66291,10 +66291,10 @@
         <v>0</v>
       </c>
       <c r="CM143" t="n">
-        <v>0.6177256712755219</v>
+        <v>0.6177256719496104</v>
       </c>
       <c r="CN143" t="n">
-        <v>0.8994085773771601</v>
+        <v>0.8994085783586327</v>
       </c>
       <c r="CO143" t="n">
         <v>0.35406995505897</v>
@@ -66357,7 +66357,7 @@
         <v>-0.9009000301245074</v>
       </c>
       <c r="DO143" t="n">
-        <v>-48.28922798125726</v>
+        <v>-48.28923380415026</v>
       </c>
       <c r="DP143" t="b">
         <v>0</v>
@@ -66967,10 +66967,10 @@
         <v>0</v>
       </c>
       <c r="CM145" t="n">
-        <v>2.143258802263168</v>
+        <v>2.143258805706165</v>
       </c>
       <c r="CN145" t="n">
-        <v>3.120584816095172</v>
+        <v>3.120584821108177</v>
       </c>
       <c r="CO145" t="n">
         <v>1.700313992147943</v>
@@ -67330,10 +67330,10 @@
         <v>0</v>
       </c>
       <c r="CM146" t="n">
-        <v>27.83419723480975</v>
+        <v>27.83419719594345</v>
       </c>
       <c r="CN146" t="n">
-        <v>37.23597052301215</v>
+        <v>37.23597047101768</v>
       </c>
       <c r="CO146" t="n">
         <v>2.52532820565238</v>
@@ -67342,7 +67342,7 @@
         <v>6.99881250992301</v>
       </c>
       <c r="CQ146" t="n">
-        <v>6.451773327188653</v>
+        <v>6.451773319360598</v>
       </c>
       <c r="CR146" t="n">
         <v>3.046690502845772</v>
@@ -68349,10 +68349,10 @@
         <v>0</v>
       </c>
       <c r="CM149" t="n">
-        <v>0.6910740082647177</v>
+        <v>0.6910740062503334</v>
       </c>
       <c r="CN149" t="n">
-        <v>1.281942285331051</v>
+        <v>1.281942281594369</v>
       </c>
       <c r="CO149" t="inlineStr"/>
       <c r="CP149" t="inlineStr"/>
@@ -68363,13 +68363,13 @@
         <v>3.539220503764572</v>
       </c>
       <c r="CU149" t="n">
-        <v>0.9865081467978845</v>
+        <v>0.9865081439223511</v>
       </c>
       <c r="CV149" t="n">
-        <v>0.9865081467978845</v>
+        <v>0.9865081439223511</v>
       </c>
       <c r="CW149" t="n">
-        <v>0.887857332118096</v>
+        <v>0.887857329530116</v>
       </c>
       <c r="CX149" t="n">
         <v>2</v>
@@ -68381,10 +68381,10 @@
         <v>5.1</v>
       </c>
       <c r="DA149" t="n">
-        <v>-76.75766105670075</v>
+        <v>-76.75766112444893</v>
       </c>
       <c r="DB149" t="n">
-        <v>-74.17517895188972</v>
+        <v>-74.17517902716547</v>
       </c>
       <c r="DC149" t="inlineStr">
         <is>
@@ -69408,10 +69408,10 @@
         <v>0</v>
       </c>
       <c r="CM152" t="n">
-        <v>9.917600494573367</v>
+        <v>9.917600478364173</v>
       </c>
       <c r="CN152" t="n">
-        <v>14.44002632009883</v>
+        <v>14.44002629649824</v>
       </c>
       <c r="CO152" t="n">
         <v>4.677488950236854</v>
@@ -69761,10 +69761,10 @@
         <v>0</v>
       </c>
       <c r="CM153" t="n">
-        <v>6.213928486605696</v>
+        <v>6.213928479328587</v>
       </c>
       <c r="CN153" t="n">
-        <v>11.37379058548346</v>
+        <v>11.37379057216366</v>
       </c>
       <c r="CO153" t="inlineStr"/>
       <c r="CP153" t="inlineStr"/>
@@ -69775,13 +69775,13 @@
         <v>3.834479090399828</v>
       </c>
       <c r="CU153" t="n">
-        <v>7.140732720829662</v>
+        <v>7.140732713964024</v>
       </c>
       <c r="CV153" t="n">
-        <v>6.213928486605696</v>
+        <v>6.213928479328587</v>
       </c>
       <c r="CW153" t="n">
-        <v>5.592535637945127</v>
+        <v>5.592535631395728</v>
       </c>
       <c r="CX153" t="n">
         <v>3</v>
@@ -69793,10 +69793,10 @@
         <v>3</v>
       </c>
       <c r="DA153" t="n">
-        <v>-51.91284967400043</v>
+        <v>-51.91284973031512</v>
       </c>
       <c r="DB153" t="n">
-        <v>-38.60075106995875</v>
+        <v>-38.60075112899261</v>
       </c>
       <c r="DC153" t="inlineStr">
         <is>
@@ -70483,10 +70483,10 @@
         <v>0</v>
       </c>
       <c r="CM155" t="n">
-        <v>4.017914650233011</v>
+        <v>4.017914656072189</v>
       </c>
       <c r="CN155" t="n">
-        <v>5.850083730739264</v>
+        <v>5.850083739241107</v>
       </c>
       <c r="CO155" t="inlineStr"/>
       <c r="CP155" t="inlineStr"/>
@@ -70497,7 +70497,7 @@
         <v>5.785847480139832</v>
       </c>
       <c r="CU155" t="n">
-        <v>5.217948620370702</v>
+        <v>5.217948625151043</v>
       </c>
       <c r="CV155" t="n">
         <v>5.785847480139832</v>
@@ -70518,7 +70518,7 @@
         <v>-66.83272104848781</v>
       </c>
       <c r="DB155" t="n">
-        <v>-66.76465806520963</v>
+        <v>-66.76465803476161</v>
       </c>
       <c r="DC155" t="inlineStr">
         <is>

--- a/reports/screener_2026-09-04.xlsx
+++ b/reports/screener_2026-09-04.xlsx
@@ -1302,10 +1302,10 @@
         <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>14.34883233997342</v>
+        <v>14.34883242735353</v>
       </c>
       <c r="CN2" t="n">
-        <v>26.61708399065069</v>
+        <v>26.6170841527408</v>
       </c>
       <c r="CO2" t="n">
         <v>38.73764113094029</v>
@@ -1314,13 +1314,13 @@
         <v>23.42212306847306</v>
       </c>
       <c r="CQ2" t="n">
-        <v>77.21384545128907</v>
+        <v>77.21384529729626</v>
       </c>
       <c r="CR2" t="n">
-        <v>48.83647633066641</v>
+        <v>48.83647626610477</v>
       </c>
       <c r="CS2" t="n">
-        <v>27.96937483383525</v>
+        <v>27.96937456424314</v>
       </c>
       <c r="CT2" t="n">
         <v>9.042040250118818</v>
@@ -1661,10 +1661,10 @@
         <v>1</v>
       </c>
       <c r="CM3" t="n">
-        <v>6.7414967884217</v>
+        <v>6.741496747302762</v>
       </c>
       <c r="CN3" t="n">
-        <v>12.50547654252225</v>
+        <v>12.50547646624662</v>
       </c>
       <c r="CO3" t="n">
         <v>41.30882298882631</v>
@@ -1673,7 +1673,7 @@
         <v>27.77800617149056</v>
       </c>
       <c r="CQ3" t="n">
-        <v>72.00025474574477</v>
+        <v>72.00025459182361</v>
       </c>
       <c r="CR3" t="n">
         <v>19.57807411896471</v>
@@ -1705,12 +1705,12 @@
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>próxima</t>
+          <t>última</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr"/>
@@ -1735,7 +1735,7 @@
         <v>1.03986036356809</v>
       </c>
       <c r="DO3" t="n">
-        <v>-17.06074941778566</v>
+        <v>-17.06075516698471</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="CM4" t="n">
-        <v>17.16638305223679</v>
+        <v>17.16638307220182</v>
       </c>
       <c r="CN4" t="n">
-        <v>31.84364056189925</v>
+        <v>31.84364059893438</v>
       </c>
       <c r="CO4" t="n">
         <v>71.20842100924612</v>
@@ -2040,19 +2040,19 @@
         <v>51.68759722785042</v>
       </c>
       <c r="CQ4" t="n">
-        <v>122.3957204994831</v>
+        <v>122.3957204894488</v>
       </c>
       <c r="CR4" t="n">
-        <v>25.57411553292391</v>
+        <v>25.57411553006628</v>
       </c>
       <c r="CS4" t="n">
-        <v>59.88502642609916</v>
+        <v>59.88502638326539</v>
       </c>
       <c r="CT4" t="n">
         <v>44.43438321477654</v>
       </c>
       <c r="CU4" t="n">
-        <v>47.4388639954659</v>
+        <v>47.43886399402319</v>
       </c>
       <c r="CV4" t="n">
         <v>48.06099022131347</v>
@@ -2073,7 +2073,7 @@
         <v>67.33033098981652</v>
       </c>
       <c r="DB4" t="n">
-        <v>83.5159121679236</v>
+        <v>83.51591216234252</v>
       </c>
       <c r="DC4" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>5338021376</v>
+        <v>5337995264</v>
       </c>
       <c r="AX5" t="n">
         <v>4.48</v>
@@ -2395,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="CM5" t="n">
-        <v>3.907370941582745</v>
+        <v>3.907370934748664</v>
       </c>
       <c r="CN5" t="n">
-        <v>7.248173096635992</v>
+        <v>7.248173083958771</v>
       </c>
       <c r="CO5" t="n">
         <v>12.71763449268681</v>
@@ -2407,19 +2407,19 @@
         <v>8.551038591084707</v>
       </c>
       <c r="CQ5" t="n">
-        <v>23.90073394611848</v>
+        <v>23.90073395185774</v>
       </c>
       <c r="CR5" t="n">
-        <v>11.1350664234246</v>
+        <v>11.13506642622674</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.912220060941721</v>
+        <v>9.912220077973341</v>
       </c>
       <c r="CT5" t="n">
         <v>5.427221201663706</v>
       </c>
       <c r="CU5" t="n">
-        <v>8.414103544002897</v>
+        <v>8.414103544048963</v>
       </c>
       <c r="CV5" t="n">
         <v>8.551038591084707</v>
@@ -2440,7 +2440,7 @@
         <v>78.97521838623484</v>
       </c>
       <c r="DB5" t="n">
-        <v>95.67681792509268</v>
+        <v>95.67681792616401</v>
       </c>
       <c r="DC5" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>-0.9216580748084957</v>
       </c>
       <c r="DO5" t="n">
-        <v>-34.16760193805087</v>
+        <v>-34.16759691282044</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -2638,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="AW6" t="n">
-        <v>5660785152</v>
+        <v>5660757504</v>
       </c>
       <c r="AX6" t="n">
         <v>4.75</v>
@@ -2764,10 +2764,10 @@
         <v>1</v>
       </c>
       <c r="CM6" t="n">
-        <v>3.327945787913786</v>
+        <v>3.327945796066591</v>
       </c>
       <c r="CN6" t="n">
-        <v>6.173339436580072</v>
+        <v>6.173339451703526</v>
       </c>
       <c r="CO6" t="n">
         <v>12.71999984038503</v>
@@ -2776,25 +2776,25 @@
         <v>8.573475127812586</v>
       </c>
       <c r="CQ6" t="n">
-        <v>23.80124252119723</v>
+        <v>23.80124251290231</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.53241883287747</v>
+        <v>11.53241882948836</v>
       </c>
       <c r="CS6" t="n">
-        <v>11.35989495000031</v>
+        <v>11.35989492968222</v>
       </c>
       <c r="CT6" t="n">
         <v>5.406965820956791</v>
       </c>
       <c r="CU6" t="n">
-        <v>11.36676236140136</v>
+        <v>11.36676235899012</v>
       </c>
       <c r="CV6" t="n">
-        <v>11.35989495000031</v>
+        <v>11.35989492968222</v>
       </c>
       <c r="CW6" t="n">
-        <v>10.22390545500028</v>
+        <v>10.22390543671399</v>
       </c>
       <c r="CX6" t="n">
         <v>7</v>
@@ -2806,10 +2806,10 @@
         <v>7.2</v>
       </c>
       <c r="DA6" t="n">
-        <v>124.2084557739779</v>
+        <v>124.2084553729628</v>
       </c>
       <c r="DB6" t="n">
-        <v>149.2711075446366</v>
+        <v>149.2711074917585</v>
       </c>
       <c r="DC6" t="inlineStr">
         <is>
@@ -3123,10 +3123,10 @@
         <v>1</v>
       </c>
       <c r="CM7" t="n">
-        <v>19.52675456025717</v>
+        <v>19.52675458976631</v>
       </c>
       <c r="CN7" t="n">
-        <v>36.22212970927706</v>
+        <v>36.22212976401649</v>
       </c>
       <c r="CO7" t="n">
         <v>75.52058089429198</v>
@@ -3135,23 +3135,23 @@
         <v>56.61657821085305</v>
       </c>
       <c r="CQ7" t="n">
-        <v>98.15037110641777</v>
+        <v>98.15037105801352</v>
       </c>
       <c r="CR7" t="n">
-        <v>48.15705804455569</v>
+        <v>48.41140869607853</v>
       </c>
       <c r="CS7" t="n">
-        <v>57.80670633975764</v>
+        <v>57.80670628044665</v>
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>44.85663080209548</v>
+        <v>44.92021848603832</v>
       </c>
       <c r="CV7" t="n">
-        <v>42.18959387691638</v>
+        <v>42.31676923004751</v>
       </c>
       <c r="CW7" t="n">
-        <v>37.97063448922474</v>
+        <v>38.08509230704276</v>
       </c>
       <c r="CX7" t="n">
         <v>4</v>
@@ -3163,10 +3163,10 @@
         <v>3.9</v>
       </c>
       <c r="DA7" t="n">
-        <v>-25.89650030167426</v>
+        <v>-25.67312439599759</v>
       </c>
       <c r="DB7" t="n">
-        <v>-12.45778818749312</v>
+        <v>-12.3336904477197</v>
       </c>
       <c r="DC7" t="inlineStr">
         <is>
@@ -3490,10 +3490,10 @@
         <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>6.403626923493396</v>
+        <v>6.403626929435632</v>
       </c>
       <c r="CN8" t="n">
-        <v>11.87872794308025</v>
+        <v>11.87872795410309</v>
       </c>
       <c r="CO8" t="n">
         <v>25.4012199436746</v>
@@ -3502,19 +3502,19 @@
         <v>18.64745536395598</v>
       </c>
       <c r="CQ8" t="n">
-        <v>35.23268456040559</v>
+        <v>35.23268455074302</v>
       </c>
       <c r="CR8" t="n">
-        <v>12.29886663486247</v>
+        <v>12.29886663373466</v>
       </c>
       <c r="CS8" t="n">
-        <v>20.39539800428012</v>
+        <v>20.39539799182948</v>
       </c>
       <c r="CT8" t="n">
         <v>18.89184945304214</v>
       </c>
       <c r="CU8" t="n">
-        <v>20.39231455761445</v>
+        <v>20.392314555869</v>
       </c>
       <c r="CV8" t="n">
         <v>18.89184945304214</v>
@@ -3535,7 +3535,7 @@
         <v>8.159441596189932</v>
       </c>
       <c r="DB8" t="n">
-        <v>29.72210058027398</v>
+        <v>29.7221005691706</v>
       </c>
       <c r="DC8" t="inlineStr">
         <is>
@@ -3859,10 +3859,10 @@
         <v>1</v>
       </c>
       <c r="CM9" t="n">
-        <v>45.77695654203991</v>
+        <v>45.77695656449495</v>
       </c>
       <c r="CN9" t="n">
-        <v>84.91625438548404</v>
+        <v>84.91625442713813</v>
       </c>
       <c r="CO9" t="n">
         <v>68.18445585960495</v>
@@ -3883,7 +3883,7 @@
         <v>26.15892848466381</v>
       </c>
       <c r="CU9" t="n">
-        <v>71.11162369885957</v>
+        <v>71.11162370687322</v>
       </c>
       <c r="CV9" t="n">
         <v>65.22550777513155</v>
@@ -3904,7 +3904,7 @@
         <v>79.08163265306125</v>
       </c>
       <c r="DB9" t="n">
-        <v>116.9360169219168</v>
+        <v>116.9360169463635</v>
       </c>
       <c r="DC9" t="inlineStr">
         <is>
@@ -4236,37 +4236,37 @@
         <v>1</v>
       </c>
       <c r="CM10" t="n">
-        <v>24.36355405256904</v>
+        <v>24.36355402870555</v>
       </c>
       <c r="CN10" t="n">
-        <v>31.53570981245223</v>
+        <v>31.53570997693015</v>
       </c>
       <c r="CO10" t="n">
-        <v>32.96248457625602</v>
+        <v>32.96248478046137</v>
       </c>
       <c r="CP10" t="n">
         <v>20.75155156536448</v>
       </c>
       <c r="CQ10" t="n">
-        <v>47.31871796693122</v>
+        <v>47.31871815238542</v>
       </c>
       <c r="CR10" t="n">
-        <v>50.67251006901864</v>
+        <v>49.42305094651599</v>
       </c>
       <c r="CS10" t="n">
-        <v>15.96314843782849</v>
+        <v>15.96314857722565</v>
       </c>
       <c r="CT10" t="n">
         <v>24.59438222893265</v>
       </c>
       <c r="CU10" t="n">
-        <v>31.0202573386691</v>
+        <v>30.86407503206516</v>
       </c>
       <c r="CV10" t="n">
-        <v>28.06504602069244</v>
+        <v>28.0650461029314</v>
       </c>
       <c r="CW10" t="n">
-        <v>25.2585414186232</v>
+        <v>25.25854149263826</v>
       </c>
       <c r="CX10" t="n">
         <v>8</v>
@@ -4275,13 +4275,13 @@
         <v>1</v>
       </c>
       <c r="CZ10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="DA10" t="n">
-        <v>-22.9922499812631</v>
+        <v>-22.99224975560741</v>
       </c>
       <c r="DB10" t="n">
-        <v>-5.42604249935631</v>
+        <v>-5.902208079346527</v>
       </c>
       <c r="DC10" t="inlineStr">
         <is>
@@ -4615,10 +4615,10 @@
         <v>1</v>
       </c>
       <c r="CM11" t="n">
-        <v>139.3180003996247</v>
+        <v>139.3180008054895</v>
       </c>
       <c r="CN11" t="n">
-        <v>258.4348907413038</v>
+        <v>258.434891494183</v>
       </c>
       <c r="CO11" t="n">
         <v>136.9934822165448</v>
@@ -4630,7 +4630,7 @@
         <v>310.173921999724</v>
       </c>
       <c r="CR11" t="n">
-        <v>56.1476</v>
+        <v>195.5</v>
       </c>
       <c r="CS11" t="n">
         <v>125.103481873222</v>
@@ -4639,13 +4639,13 @@
         <v>58.37540514006138</v>
       </c>
       <c r="CU11" t="n">
-        <v>147.2354325900216</v>
+        <v>164.6544827348646</v>
       </c>
       <c r="CV11" t="n">
-        <v>131.0484820448834</v>
+        <v>138.1557415110171</v>
       </c>
       <c r="CW11" t="n">
-        <v>117.9436338403951</v>
+        <v>124.3401673599154</v>
       </c>
       <c r="CX11" t="n">
         <v>8</v>
@@ -4654,13 +4654,13 @@
         <v>1</v>
       </c>
       <c r="CZ11" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="DA11" t="n">
-        <v>147.9891304347826</v>
+        <v>161.4385276905038</v>
       </c>
       <c r="DB11" t="n">
-        <v>209.5782765740348</v>
+        <v>246.2036963424734</v>
       </c>
       <c r="DC11" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>-1.327799542568742</v>
       </c>
       <c r="DO11" t="n">
-        <v>-1.430048967272501</v>
+        <v>-3.31367615150312</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -4994,10 +4994,10 @@
         <v>1</v>
       </c>
       <c r="CM12" t="n">
-        <v>145.9241172852467</v>
+        <v>145.9241165475706</v>
       </c>
       <c r="CN12" t="n">
-        <v>270.6892375641326</v>
+        <v>270.6892361957434</v>
       </c>
       <c r="CO12" t="n">
         <v>137.1427213113139</v>
@@ -5009,7 +5009,7 @@
         <v>310.5118218369371</v>
       </c>
       <c r="CR12" t="n">
-        <v>56.1476</v>
+        <v>195.5</v>
       </c>
       <c r="CS12" t="n">
         <v>125.239768140898</v>
@@ -5018,13 +5018,13 @@
         <v>57.29814214194677</v>
       </c>
       <c r="CU12" t="n">
-        <v>149.5179563910809</v>
+        <v>166.9370061278227</v>
       </c>
       <c r="CV12" t="n">
-        <v>131.1912447261059</v>
+        <v>141.5334189294422</v>
       </c>
       <c r="CW12" t="n">
-        <v>118.0721202534953</v>
+        <v>127.380077036498</v>
       </c>
       <c r="CX12" t="n">
         <v>8</v>
@@ -5033,13 +5033,13 @@
         <v>1</v>
       </c>
       <c r="CZ12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="DA12" t="n">
-        <v>124.5570866141732</v>
+        <v>142.2595523023832</v>
       </c>
       <c r="DB12" t="n">
-        <v>184.362782777183</v>
+        <v>217.4914422106899</v>
       </c>
       <c r="DC12" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>-1.793050183146794</v>
       </c>
       <c r="DO12" t="n">
-        <v>-2.213127425289363</v>
+        <v>-3.593690963643992</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="CM13" t="n">
-        <v>13.58565532094829</v>
+        <v>13.58565534397649</v>
       </c>
       <c r="CN13" t="n">
-        <v>25.20139062035909</v>
+        <v>25.20139066307638</v>
       </c>
       <c r="CO13" t="n">
         <v>19.9811217441166</v>
@@ -5357,7 +5357,7 @@
         <v>12.48999788378355</v>
       </c>
       <c r="CQ13" t="n">
-        <v>33.81046379501534</v>
+        <v>33.81046381960686</v>
       </c>
       <c r="CR13" t="n">
         <v>22.8984489302328</v>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="n">
-        <v>20.41665415391419</v>
+        <v>20.41665417035057</v>
       </c>
       <c r="CV13" t="n">
         <v>21.4397853371747</v>
@@ -5388,7 +5388,7 @@
         <v>-2.398551559568773</v>
       </c>
       <c r="DB13" t="n">
-        <v>3.270883566907457</v>
+        <v>3.27088365004542</v>
       </c>
       <c r="DC13" t="inlineStr">
         <is>
@@ -5720,10 +5720,10 @@
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>3.241822751043931</v>
+        <v>3.241822754874634</v>
       </c>
       <c r="CN14" t="n">
-        <v>6.013581203186491</v>
+        <v>6.013581210292446</v>
       </c>
       <c r="CO14" t="n">
         <v>19.81979119280974</v>
@@ -5732,7 +5732,7 @@
         <v>13.58186553210178</v>
       </c>
       <c r="CQ14" t="n">
-        <v>31.89281582076967</v>
+        <v>31.89281583194255</v>
       </c>
       <c r="CR14" t="n">
         <v>10.95072400487419</v>
@@ -6087,10 +6087,10 @@
         <v>0</v>
       </c>
       <c r="CM15" t="n">
-        <v>10.89909385310484</v>
+        <v>10.89909387042541</v>
       </c>
       <c r="CN15" t="n">
-        <v>20.21781909750947</v>
+        <v>20.21781912963913</v>
       </c>
       <c r="CO15" t="n">
         <v>37.45389651797344</v>
@@ -6099,25 +6099,25 @@
         <v>36.91124241178991</v>
       </c>
       <c r="CQ15" t="n">
-        <v>41.40373335666359</v>
+        <v>41.40373336325502</v>
       </c>
       <c r="CR15" t="n">
-        <v>34.46332758610621</v>
+        <v>33.9846702548987</v>
       </c>
       <c r="CS15" t="n">
-        <v>18.32822066472938</v>
+        <v>18.32822064464029</v>
       </c>
       <c r="CT15" t="n">
         <v>32.58677052647363</v>
       </c>
       <c r="CU15" t="n">
-        <v>31.62357288017795</v>
+        <v>31.55519326409573</v>
       </c>
       <c r="CV15" t="n">
-        <v>34.46332758610621</v>
+        <v>33.9846702548987</v>
       </c>
       <c r="CW15" t="n">
-        <v>31.01699482749559</v>
+        <v>30.58620322940883</v>
       </c>
       <c r="CX15" t="n">
         <v>7</v>
@@ -6129,10 +6129,10 @@
         <v>3.8</v>
       </c>
       <c r="DA15" t="n">
-        <v>74.44878306890246</v>
+        <v>72.02588328571895</v>
       </c>
       <c r="DB15" t="n">
-        <v>77.86035803660174</v>
+        <v>77.4757707844</v>
       </c>
       <c r="DC15" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>-1.222218407524955</v>
       </c>
       <c r="DO15" t="n">
-        <v>-22.12628936839648</v>
+        <v>-22.12628280376486</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -6464,37 +6464,37 @@
         <v>0</v>
       </c>
       <c r="CM16" t="n">
-        <v>24.6452661183992</v>
+        <v>24.64526620056351</v>
       </c>
       <c r="CN16" t="n">
-        <v>31.16419473185438</v>
+        <v>31.16419460305564</v>
       </c>
       <c r="CO16" t="n">
-        <v>34.75021176353649</v>
+        <v>34.75021150406412</v>
       </c>
       <c r="CP16" t="n">
         <v>36.07661496384414</v>
       </c>
       <c r="CQ16" t="n">
-        <v>48.86831569478055</v>
+        <v>48.86831552998098</v>
       </c>
       <c r="CR16" t="n">
-        <v>48.59901755120379</v>
+        <v>48.59901751503249</v>
       </c>
       <c r="CS16" t="n">
-        <v>16.65417721304533</v>
+        <v>16.6541770283071</v>
       </c>
       <c r="CT16" t="n">
         <v>31.14870262855163</v>
       </c>
       <c r="CU16" t="n">
-        <v>33.98831258315194</v>
+        <v>33.98831249667495</v>
       </c>
       <c r="CV16" t="n">
-        <v>32.95720324769543</v>
+        <v>32.95720305355988</v>
       </c>
       <c r="CW16" t="n">
-        <v>29.66148292292589</v>
+        <v>29.66148274820389</v>
       </c>
       <c r="CX16" t="n">
         <v>8</v>
@@ -6506,10 +6506,10 @@
         <v>2.9</v>
       </c>
       <c r="DA16" t="n">
-        <v>-13.47291721363859</v>
+        <v>-13.47291772332938</v>
       </c>
       <c r="DB16" t="n">
-        <v>-0.8508932512596767</v>
+        <v>-0.8508935035262732</v>
       </c>
       <c r="DC16" t="inlineStr">
         <is>
@@ -6835,10 +6835,10 @@
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>5.334787411855786</v>
+        <v>5.334787426705602</v>
       </c>
       <c r="CN17" t="n">
-        <v>9.896030648992484</v>
+        <v>9.89603067653889</v>
       </c>
       <c r="CO17" t="n">
         <v>8.503043610116709</v>
@@ -6909,7 +6909,7 @@
         <v>0.2717388663546538</v>
       </c>
       <c r="DO17" t="n">
-        <v>-24.42029364136734</v>
+        <v>-24.4203010953975</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="CM18" t="n">
-        <v>3.558471602966997</v>
+        <v>3.558471586714633</v>
       </c>
       <c r="CN18" t="n">
-        <v>6.60096482350378</v>
+        <v>6.600964793355645</v>
       </c>
       <c r="CO18" t="n">
         <v>19.66796809186538</v>
@@ -7206,13 +7206,13 @@
         <v>18.52055498018046</v>
       </c>
       <c r="CQ18" t="n">
-        <v>20.69777961533053</v>
+        <v>20.69777961849134</v>
       </c>
       <c r="CR18" t="n">
-        <v>15.89091661176179</v>
+        <v>15.89091661496516</v>
       </c>
       <c r="CS18" t="n">
-        <v>12.89801917568821</v>
+        <v>12.89801919629751</v>
       </c>
       <c r="CT18" t="n">
         <v>29.41436415825995</v>
@@ -7268,7 +7268,7 @@
         <v>-0.9556959875251736</v>
       </c>
       <c r="DO18" t="n">
-        <v>-30.95849087040471</v>
+        <v>-30.95848265146315</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -7561,37 +7561,37 @@
         <v>0</v>
       </c>
       <c r="CM19" t="n">
-        <v>10.71852592981897</v>
+        <v>10.71852589667536</v>
       </c>
       <c r="CN19" t="n">
-        <v>16.81931635082226</v>
+        <v>16.81931642158801</v>
       </c>
       <c r="CO19" t="n">
-        <v>20.69399620161987</v>
+        <v>20.69399635267754</v>
       </c>
       <c r="CP19" t="n">
         <v>17.56096669750601</v>
       </c>
       <c r="CQ19" t="n">
-        <v>34.52474409552667</v>
+        <v>34.5247441309253</v>
       </c>
       <c r="CR19" t="n">
-        <v>23.92681846053856</v>
+        <v>23.92681847484472</v>
       </c>
       <c r="CS19" t="n">
-        <v>10.34281212568361</v>
+        <v>10.34281219830788</v>
       </c>
       <c r="CT19" t="n">
         <v>10.6899995803833</v>
       </c>
       <c r="CU19" t="n">
-        <v>18.15964743023741</v>
+        <v>18.15964746911352</v>
       </c>
       <c r="CV19" t="n">
-        <v>17.19014152416413</v>
+        <v>17.19014155954701</v>
       </c>
       <c r="CW19" t="n">
-        <v>15.47112737174772</v>
+        <v>15.47112740359231</v>
       </c>
       <c r="CX19" t="n">
         <v>8</v>
@@ -7603,10 +7603,10 @@
         <v>3.3</v>
       </c>
       <c r="DA19" t="n">
-        <v>44.72523834461168</v>
+        <v>44.72523864250309</v>
       </c>
       <c r="DB19" t="n">
-        <v>69.87509956091387</v>
+        <v>69.87509992458187</v>
       </c>
       <c r="DC19" t="inlineStr">
         <is>
@@ -7938,37 +7938,37 @@
         <v>1</v>
       </c>
       <c r="CM20" t="n">
-        <v>9.929939060311767</v>
+        <v>9.929939056665846</v>
       </c>
       <c r="CN20" t="n">
-        <v>17.62243046603763</v>
+        <v>17.62243048562545</v>
       </c>
       <c r="CO20" t="n">
-        <v>20.83047589898358</v>
+        <v>20.83047592978545</v>
       </c>
       <c r="CP20" t="n">
         <v>12.8457780532356</v>
       </c>
       <c r="CQ20" t="n">
-        <v>29.22488338744555</v>
+        <v>29.2248833989064</v>
       </c>
       <c r="CR20" t="n">
-        <v>24.9773450146415</v>
+        <v>24.97734501734207</v>
       </c>
       <c r="CS20" t="n">
-        <v>10.24067493805693</v>
+        <v>10.24067494985747</v>
       </c>
       <c r="CT20" t="n">
         <v>9.713052205096755</v>
       </c>
       <c r="CU20" t="n">
-        <v>16.92307237797617</v>
+        <v>16.92307238706438</v>
       </c>
       <c r="CV20" t="n">
-        <v>15.23410425963662</v>
+        <v>15.23410426943053</v>
       </c>
       <c r="CW20" t="n">
-        <v>13.71069383367296</v>
+        <v>13.71069384248748</v>
       </c>
       <c r="CX20" t="n">
         <v>8</v>
@@ -7980,10 +7980,10 @@
         <v>3</v>
       </c>
       <c r="DA20" t="n">
-        <v>19.53525295971572</v>
+        <v>19.5352530365642</v>
       </c>
       <c r="DB20" t="n">
-        <v>47.54203996509516</v>
+        <v>47.5420400443298</v>
       </c>
       <c r="DC20" t="inlineStr">
         <is>
@@ -8287,10 +8287,10 @@
         <v>1</v>
       </c>
       <c r="CM21" t="n">
-        <v>4.411578432089268</v>
+        <v>4.411578436242657</v>
       </c>
       <c r="CN21" t="n">
-        <v>8.183477991525592</v>
+        <v>8.183477999230128</v>
       </c>
       <c r="CO21" t="n">
         <v>13.99193579150784</v>
@@ -8299,23 +8299,23 @@
         <v>9.385319019937953</v>
       </c>
       <c r="CQ21" t="n">
-        <v>16.24838538185653</v>
+        <v>16.24838536882942</v>
       </c>
       <c r="CR21" t="n">
-        <v>9.212292051566077</v>
+        <v>9.212292050273723</v>
       </c>
       <c r="CS21" t="n">
-        <v>10.67142032642342</v>
+        <v>10.67142031601037</v>
       </c>
       <c r="CT21" t="inlineStr"/>
       <c r="CU21" t="n">
-        <v>8.949821066672195</v>
+        <v>8.949821069313588</v>
       </c>
       <c r="CV21" t="n">
-        <v>8.697885021545835</v>
+        <v>8.697885024751926</v>
       </c>
       <c r="CW21" t="n">
-        <v>7.828096519391251</v>
+        <v>7.828096522276733</v>
       </c>
       <c r="CX21" t="n">
         <v>4</v>
@@ -8327,10 +8327,10 @@
         <v>3.2</v>
       </c>
       <c r="DA21" t="n">
-        <v>-54.88128906468572</v>
+        <v>-54.8812890480547</v>
       </c>
       <c r="DB21" t="n">
-        <v>-48.41601804095147</v>
+        <v>-48.4160180257273</v>
       </c>
       <c r="DC21" t="inlineStr">
         <is>
@@ -8642,10 +8642,10 @@
         <v>1</v>
       </c>
       <c r="CM22" t="n">
-        <v>38.13263668885346</v>
+        <v>38.13263672211311</v>
       </c>
       <c r="CN22" t="n">
-        <v>55.52111901897064</v>
+        <v>55.52111906739669</v>
       </c>
       <c r="CO22" t="n">
         <v>49.21407329373137</v>
@@ -8662,13 +8662,13 @@
       </c>
       <c r="CT22" t="inlineStr"/>
       <c r="CU22" t="n">
-        <v>50.5929984963433</v>
+        <v>50.59299851676472</v>
       </c>
       <c r="CV22" t="n">
-        <v>52.36759615635101</v>
+        <v>52.36759618056404</v>
       </c>
       <c r="CW22" t="n">
-        <v>47.13083654071591</v>
+        <v>47.13083656250763</v>
       </c>
       <c r="CX22" t="n">
         <v>4</v>
@@ -8680,10 +8680,10 @@
         <v>1.6</v>
       </c>
       <c r="DA22" t="n">
-        <v>13.05070303005771</v>
+        <v>13.05070308232856</v>
       </c>
       <c r="DB22" t="n">
-        <v>21.3552414557542</v>
+        <v>21.3552415047382</v>
       </c>
       <c r="DC22" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>-0.239297168287933</v>
       </c>
       <c r="DO22" t="n">
-        <v>-1.044392191433507</v>
+        <v>-3.00139816022954</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -9007,10 +9007,10 @@
         <v>0</v>
       </c>
       <c r="CM23" t="n">
-        <v>8.042725692874045</v>
+        <v>8.042725668300724</v>
       </c>
       <c r="CN23" t="n">
-        <v>14.91925616028136</v>
+        <v>14.91925611469784</v>
       </c>
       <c r="CO23" t="n">
         <v>35.8092168347706</v>
@@ -9019,25 +9019,25 @@
         <v>28.26533205663885</v>
       </c>
       <c r="CQ23" t="n">
-        <v>42.37839881633204</v>
+        <v>42.37839885629169</v>
       </c>
       <c r="CR23" t="n">
-        <v>26.26934027562648</v>
+        <v>26.2693402817547</v>
       </c>
       <c r="CS23" t="n">
-        <v>27.55520349529375</v>
+        <v>27.55520353966727</v>
       </c>
       <c r="CT23" t="n">
         <v>25.97235352964724</v>
       </c>
       <c r="CU23" t="n">
-        <v>28.73844302408433</v>
+        <v>28.73844303049546</v>
       </c>
       <c r="CV23" t="n">
-        <v>27.55520349529375</v>
+        <v>27.55520353966727</v>
       </c>
       <c r="CW23" t="n">
-        <v>24.79968314576438</v>
+        <v>24.79968318570054</v>
       </c>
       <c r="CX23" t="n">
         <v>7</v>
@@ -9049,10 +9049,10 @@
         <v>5.3</v>
       </c>
       <c r="DA23" t="n">
-        <v>-18.28770071151008</v>
+        <v>-18.28770057992469</v>
       </c>
       <c r="DB23" t="n">
-        <v>-5.309908853804624</v>
+        <v>-5.309908832680643</v>
       </c>
       <c r="DC23" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>3.126062068481006</v>
       </c>
       <c r="DO23" t="n">
-        <v>-13.9694512434398</v>
+        <v>-13.96944189921097</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -9384,10 +9384,10 @@
         <v>0</v>
       </c>
       <c r="CM24" t="n">
-        <v>3.282331942632095</v>
+        <v>3.282331949433095</v>
       </c>
       <c r="CN24" t="n">
-        <v>6.088725753582535</v>
+        <v>6.088725766198391</v>
       </c>
       <c r="CO24" t="n">
         <v>32.87073625430369</v>
@@ -9396,13 +9396,13 @@
         <v>27.40079604823567</v>
       </c>
       <c r="CQ24" t="n">
-        <v>42.09062502875422</v>
+        <v>42.09062502138559</v>
       </c>
       <c r="CR24" t="n">
-        <v>10.8526242958474</v>
+        <v>10.85262429518091</v>
       </c>
       <c r="CS24" t="n">
-        <v>30.00489852392306</v>
+        <v>30.00489851291088</v>
       </c>
       <c r="CT24" t="n">
         <v>15.129152615152</v>
@@ -9751,10 +9751,10 @@
         <v>1</v>
       </c>
       <c r="CM25" t="n">
-        <v>3.454280447251831</v>
+        <v>3.454280456708807</v>
       </c>
       <c r="CN25" t="n">
-        <v>6.407690229652147</v>
+        <v>6.407690247194836</v>
       </c>
       <c r="CO25" t="n">
         <v>32.60530006759157</v>
@@ -9763,7 +9763,7 @@
         <v>22.82658483654052</v>
       </c>
       <c r="CQ25" t="n">
-        <v>40.32932308720063</v>
+        <v>40.32932309655735</v>
       </c>
       <c r="CR25" t="n">
         <v>10.59424454785779</v>
@@ -9825,7 +9825,7 @@
         <v>-1.777153891556071</v>
       </c>
       <c r="DO25" t="n">
-        <v>-26.9772502415444</v>
+        <v>-26.97724421931233</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -10090,35 +10090,35 @@
         <v>1</v>
       </c>
       <c r="CM26" t="n">
-        <v>9.776498548817115</v>
+        <v>9.776498615230746</v>
       </c>
       <c r="CN26" t="n">
-        <v>17.80202359127176</v>
+        <v>17.80202357989377</v>
       </c>
       <c r="CO26" t="n">
-        <v>30.4195084706888</v>
+        <v>30.41950824460092</v>
       </c>
       <c r="CP26" t="n">
         <v>29.46192052472633</v>
       </c>
       <c r="CQ26" t="n">
-        <v>34.13596352020357</v>
+        <v>34.13596352759888</v>
       </c>
       <c r="CR26" t="n">
-        <v>25.40854575380762</v>
+        <v>25.52456649713004</v>
       </c>
       <c r="CS26" t="n">
-        <v>14.86407026428921</v>
+        <v>14.86407018170784</v>
       </c>
       <c r="CT26" t="inlineStr"/>
       <c r="CU26" t="n">
-        <v>20.85164409114633</v>
+        <v>20.88064923421387</v>
       </c>
       <c r="CV26" t="n">
-        <v>21.60528467253969</v>
+        <v>21.66329503851191</v>
       </c>
       <c r="CW26" t="n">
-        <v>19.44475620528572</v>
+        <v>19.49696553466072</v>
       </c>
       <c r="CX26" t="n">
         <v>4</v>
@@ -10130,10 +10130,10 @@
         <v>3.1</v>
       </c>
       <c r="DA26" t="n">
-        <v>24.08906260761505</v>
+        <v>24.42224275516323</v>
       </c>
       <c r="DB26" t="n">
-        <v>33.06728774488859</v>
+        <v>33.25238757211466</v>
       </c>
       <c r="DC26" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>0.5131489603787731</v>
       </c>
       <c r="DO26" t="n">
-        <v>-13.75743191410359</v>
+        <v>-13.75742256022964</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -10445,35 +10445,35 @@
         <v>1</v>
       </c>
       <c r="CM27" t="n">
-        <v>9.277652160030563</v>
+        <v>9.277652092641643</v>
       </c>
       <c r="CN27" t="n">
-        <v>13.27564817199024</v>
+        <v>13.27564823727591</v>
       </c>
       <c r="CO27" t="n">
-        <v>16.56076849138475</v>
+        <v>16.56076869311605</v>
       </c>
       <c r="CP27" t="n">
         <v>17.47664780944146</v>
       </c>
       <c r="CQ27" t="n">
-        <v>21.53940887428282</v>
+        <v>21.53940894567846</v>
       </c>
       <c r="CR27" t="n">
-        <v>17.16868986752019</v>
+        <v>17.16868988615829</v>
       </c>
       <c r="CS27" t="n">
-        <v>8.239775043451273</v>
+        <v>8.239775158260425</v>
       </c>
       <c r="CT27" t="inlineStr"/>
       <c r="CU27" t="n">
-        <v>14.07068967273144</v>
+        <v>14.07068972729797</v>
       </c>
       <c r="CV27" t="n">
-        <v>14.9182083316875</v>
+        <v>14.91820846519598</v>
       </c>
       <c r="CW27" t="n">
-        <v>13.42638749851875</v>
+        <v>13.42638761867638</v>
       </c>
       <c r="CX27" t="n">
         <v>4</v>
@@ -10485,10 +10485,10 @@
         <v>1.9</v>
       </c>
       <c r="DA27" t="n">
-        <v>-2.282476548934431</v>
+        <v>-2.282475674424711</v>
       </c>
       <c r="DB27" t="n">
-        <v>2.406767882983463</v>
+        <v>2.406768280119831</v>
       </c>
       <c r="DC27" t="inlineStr">
         <is>
@@ -10816,37 +10816,37 @@
         <v>0</v>
       </c>
       <c r="CM28" t="n">
-        <v>17.67458159617798</v>
+        <v>17.67458143755837</v>
       </c>
       <c r="CN28" t="n">
-        <v>28.38448060874346</v>
+        <v>28.38448059186818</v>
       </c>
       <c r="CO28" t="n">
-        <v>45.95076147675917</v>
+        <v>45.95076186182303</v>
       </c>
       <c r="CP28" t="n">
         <v>53.20634261756088</v>
       </c>
       <c r="CQ28" t="n">
-        <v>55.32499944818458</v>
+        <v>55.32499940859542</v>
       </c>
       <c r="CR28" t="n">
-        <v>42.93273386196931</v>
+        <v>42.93273389081794</v>
       </c>
       <c r="CS28" t="n">
-        <v>22.93541916167177</v>
+        <v>22.93541933908462</v>
       </c>
       <c r="CT28" t="n">
         <v>32.58624815427083</v>
       </c>
       <c r="CU28" t="n">
-        <v>37.37444586566725</v>
+        <v>37.37444591269741</v>
       </c>
       <c r="CV28" t="n">
-        <v>37.75949100812007</v>
+        <v>37.75949102254438</v>
       </c>
       <c r="CW28" t="n">
-        <v>33.98354190730807</v>
+        <v>33.98354192028994</v>
       </c>
       <c r="CX28" t="n">
         <v>8</v>
@@ -10858,10 +10858,10 @@
         <v>3.1</v>
       </c>
       <c r="DA28" t="n">
-        <v>22.95058848675435</v>
+        <v>22.95058853372207</v>
       </c>
       <c r="DB28" t="n">
-        <v>35.2186928038229</v>
+        <v>35.21869297397546</v>
       </c>
       <c r="DC28" t="inlineStr">
         <is>
@@ -11175,10 +11175,10 @@
         <v>1</v>
       </c>
       <c r="CM29" t="n">
-        <v>21.46693980023627</v>
+        <v>21.46693990747076</v>
       </c>
       <c r="CN29" t="n">
-        <v>39.82117332943828</v>
+        <v>39.82117352835825</v>
       </c>
       <c r="CO29" t="n">
         <v>55.9919330381578</v>
@@ -11187,23 +11187,23 @@
         <v>42.27700822726509</v>
       </c>
       <c r="CQ29" t="n">
-        <v>57.6948432981931</v>
+        <v>57.69484311249409</v>
       </c>
       <c r="CR29" t="n">
-        <v>44.75889535946022</v>
+        <v>45.2917393179109</v>
       </c>
       <c r="CS29" t="n">
-        <v>28.51101662362118</v>
+        <v>28.51101641176873</v>
       </c>
       <c r="CT29" t="inlineStr"/>
       <c r="CU29" t="n">
-        <v>40.50973538182314</v>
+        <v>40.64294644797442</v>
       </c>
       <c r="CV29" t="n">
-        <v>42.29003434444925</v>
+        <v>42.55645642313458</v>
       </c>
       <c r="CW29" t="n">
-        <v>38.06103091000433</v>
+        <v>38.30081078082112</v>
       </c>
       <c r="CX29" t="n">
         <v>4</v>
@@ -11215,10 +11215,10 @@
         <v>2.6</v>
       </c>
       <c r="DA29" t="n">
-        <v>-9.205552069417166</v>
+        <v>-8.633558077789505</v>
       </c>
       <c r="DB29" t="n">
-        <v>-3.364176642943906</v>
+        <v>-3.0464021391989</v>
       </c>
       <c r="DC29" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>1.231582524541053</v>
       </c>
       <c r="DO29" t="n">
-        <v>-13.88060552690588</v>
+        <v>-13.88059194684089</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -11550,10 +11550,10 @@
         <v>1</v>
       </c>
       <c r="CM30" t="n">
-        <v>7.897647825800325</v>
+        <v>7.897647775668966</v>
       </c>
       <c r="CN30" t="n">
-        <v>14.6501367168596</v>
+        <v>14.65013662386593</v>
       </c>
       <c r="CO30" t="n">
         <v>5.689554995371402</v>
@@ -11574,7 +11574,7 @@
         <v>5.468016983754021</v>
       </c>
       <c r="CU30" t="n">
-        <v>7.691147604628489</v>
+        <v>7.691147586737859</v>
       </c>
       <c r="CV30" t="n">
         <v>5.911444164352368</v>
@@ -11595,7 +11595,7 @@
         <v>-20.11561757040502</v>
       </c>
       <c r="DB30" t="n">
-        <v>15.48269941202858</v>
+        <v>15.4826991434005</v>
       </c>
       <c r="DC30" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>4.06249606516218</v>
       </c>
       <c r="DO30" t="n">
-        <v>3.576983284817814</v>
+        <v>-2.058828520527212</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -11923,37 +11923,37 @@
         <v>1</v>
       </c>
       <c r="CM31" t="n">
-        <v>6.114135551504001</v>
+        <v>6.114135551223865</v>
       </c>
       <c r="CN31" t="n">
-        <v>8.34073842373572</v>
+        <v>8.340738423949674</v>
       </c>
       <c r="CO31" t="n">
-        <v>10.22416123297895</v>
+        <v>10.22416123370966</v>
       </c>
       <c r="CP31" t="n">
         <v>11.61068843321866</v>
       </c>
       <c r="CQ31" t="n">
-        <v>9.255439677680009</v>
+        <v>9.255439678140526</v>
       </c>
       <c r="CR31" t="n">
-        <v>14.83896367844126</v>
+        <v>14.83896367853997</v>
       </c>
       <c r="CS31" t="n">
-        <v>5.038565262754045</v>
+        <v>5.03856526320764</v>
       </c>
       <c r="CT31" t="n">
         <v>11.35371417455445</v>
       </c>
       <c r="CU31" t="n">
-        <v>9.597050804358386</v>
+        <v>9.597050804568056</v>
       </c>
       <c r="CV31" t="n">
-        <v>9.739800455329476</v>
+        <v>9.739800455925092</v>
       </c>
       <c r="CW31" t="n">
-        <v>8.765820409796529</v>
+        <v>8.765820410332584</v>
       </c>
       <c r="CX31" t="n">
         <v>8</v>
@@ -11965,10 +11965,10 @@
         <v>2.9</v>
       </c>
       <c r="DA31" t="n">
-        <v>-44.37931292835736</v>
+        <v>-44.379312924956</v>
       </c>
       <c r="DB31" t="n">
-        <v>-39.10500847093395</v>
+        <v>-39.10500846960354</v>
       </c>
       <c r="DC31" t="inlineStr">
         <is>
@@ -12292,37 +12292,37 @@
         <v>0</v>
       </c>
       <c r="CM32" t="n">
-        <v>33.11882880409752</v>
+        <v>33.11882886960528</v>
       </c>
       <c r="CN32" t="n">
-        <v>34.05828924298923</v>
+        <v>34.05828919941593</v>
       </c>
       <c r="CO32" t="n">
-        <v>34.64295544463105</v>
+        <v>34.64295533178732</v>
       </c>
       <c r="CP32" t="n">
         <v>49.91001401454295</v>
       </c>
       <c r="CQ32" t="n">
-        <v>54.23229194888883</v>
+        <v>54.23229186828175</v>
       </c>
       <c r="CR32" t="n">
-        <v>17.39224951718627</v>
+        <v>17.72671584713629</v>
       </c>
       <c r="CS32" t="n">
-        <v>13.60670822940412</v>
+        <v>13.6067081133034</v>
       </c>
       <c r="CT32" t="n">
         <v>30.48327237497478</v>
       </c>
       <c r="CU32" t="n">
-        <v>33.43057619708934</v>
+        <v>33.47238445238096</v>
       </c>
       <c r="CV32" t="n">
-        <v>33.58855902354338</v>
+        <v>33.58855903451061</v>
       </c>
       <c r="CW32" t="n">
-        <v>30.22970312118904</v>
+        <v>30.22970313105955</v>
       </c>
       <c r="CX32" t="n">
         <v>8</v>
@@ -12334,10 +12334,10 @@
         <v>4</v>
       </c>
       <c r="DA32" t="n">
-        <v>-27.24499716903571</v>
+        <v>-27.24499714527998</v>
       </c>
       <c r="DB32" t="n">
-        <v>-19.54133138161186</v>
+        <v>-19.44070982671583</v>
       </c>
       <c r="DC32" t="inlineStr">
         <is>
@@ -12643,35 +12643,35 @@
         <v>1</v>
       </c>
       <c r="CM33" t="n">
-        <v>10.62685337831266</v>
+        <v>10.62685331697454</v>
       </c>
       <c r="CN33" t="n">
-        <v>17.64942994959144</v>
+        <v>17.64942995979905</v>
       </c>
       <c r="CO33" t="n">
-        <v>27.73251600690513</v>
+        <v>27.73251618301623</v>
       </c>
       <c r="CP33" t="n">
         <v>29.43493108570705</v>
       </c>
       <c r="CQ33" t="n">
-        <v>31.55991137143432</v>
+        <v>31.5599113799306</v>
       </c>
       <c r="CR33" t="n">
-        <v>27.78221465689651</v>
+        <v>27.90907409833193</v>
       </c>
       <c r="CS33" t="n">
-        <v>13.79408525206323</v>
+        <v>13.79408532833351</v>
       </c>
       <c r="CT33" t="inlineStr"/>
       <c r="CU33" t="n">
-        <v>20.94775349792643</v>
+        <v>20.97946838953044</v>
       </c>
       <c r="CV33" t="n">
-        <v>22.69097297824829</v>
+        <v>22.69097307140764</v>
       </c>
       <c r="CW33" t="n">
-        <v>20.42187568042346</v>
+        <v>20.42187576426688</v>
       </c>
       <c r="CX33" t="n">
         <v>4</v>
@@ -12683,10 +12683,10 @@
         <v>2.6</v>
       </c>
       <c r="DA33" t="n">
-        <v>14.79412383053324</v>
+        <v>14.79412430182843</v>
       </c>
       <c r="DB33" t="n">
-        <v>17.75015413092511</v>
+        <v>17.92842782385293</v>
       </c>
       <c r="DC33" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>0.2253572705765761</v>
       </c>
       <c r="DO33" t="n">
-        <v>-16.14745557185274</v>
+        <v>-16.147447880327</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -13022,10 +13022,10 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>27.71225737706116</v>
+        <v>27.71225729867693</v>
       </c>
       <c r="CN34" t="n">
-        <v>51.40623743444844</v>
+        <v>51.4062372890457</v>
       </c>
       <c r="CO34" t="n">
         <v>69.02703388345945</v>
@@ -13034,25 +13034,25 @@
         <v>48.07470647599711</v>
       </c>
       <c r="CQ34" t="n">
-        <v>78.40063158340526</v>
+        <v>78.40063175110375</v>
       </c>
       <c r="CR34" t="n">
-        <v>61.78172618496546</v>
+        <v>61.78172621718767</v>
       </c>
       <c r="CS34" t="n">
-        <v>36.01038484387148</v>
+        <v>36.01038502618065</v>
       </c>
       <c r="CT34" t="n">
         <v>80.3272793905405</v>
       </c>
       <c r="CU34" t="n">
-        <v>56.59253214671861</v>
+        <v>56.59253216652397</v>
       </c>
       <c r="CV34" t="n">
-        <v>56.59398180970695</v>
+        <v>56.59398175311668</v>
       </c>
       <c r="CW34" t="n">
-        <v>50.93458362873626</v>
+        <v>50.93458357780501</v>
       </c>
       <c r="CX34" t="n">
         <v>8</v>
@@ -13064,10 +13064,10 @@
         <v>2.9</v>
       </c>
       <c r="DA34" t="n">
-        <v>8.997612085785844</v>
+        <v>8.997611976795383</v>
       </c>
       <c r="DB34" t="n">
-        <v>21.10535566251859</v>
+        <v>21.10535570490111</v>
       </c>
       <c r="DC34" t="inlineStr">
         <is>
@@ -13373,10 +13373,10 @@
         <v>0</v>
       </c>
       <c r="CM35" t="n">
-        <v>11.49820300028505</v>
+        <v>11.4982029728858</v>
       </c>
       <c r="CN35" t="n">
-        <v>21.32916656552876</v>
+        <v>21.32916651470316</v>
       </c>
       <c r="CO35" t="n">
         <v>61.99144933938789</v>
@@ -13385,7 +13385,7 @@
         <v>46.3637511199616</v>
       </c>
       <c r="CQ35" t="n">
-        <v>82.98527148793602</v>
+        <v>82.98527145741976</v>
       </c>
       <c r="CR35" t="n">
         <v>11.76833333333333</v>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="CT35" t="inlineStr"/>
       <c r="CU35" t="n">
-        <v>14.86523429971571</v>
+        <v>14.86523427364077</v>
       </c>
       <c r="CV35" t="n">
         <v>11.76833333333333</v>
@@ -13416,7 +13416,7 @@
         <v>-81.99030819133732</v>
       </c>
       <c r="DB35" t="n">
-        <v>-74.72328863697857</v>
+        <v>-74.72328868131616</v>
       </c>
       <c r="DC35" t="inlineStr">
         <is>
@@ -13730,10 +13730,10 @@
         <v>0</v>
       </c>
       <c r="CM36" t="n">
-        <v>15.91082428045713</v>
+        <v>15.91082430405249</v>
       </c>
       <c r="CN36" t="n">
-        <v>29.51457904024798</v>
+        <v>29.51457908401737</v>
       </c>
       <c r="CO36" t="n">
         <v>54.72591683531388</v>
@@ -13742,23 +13742,23 @@
         <v>49.38251180555442</v>
       </c>
       <c r="CQ36" t="n">
-        <v>60.07811897656059</v>
+        <v>60.07811896955261</v>
       </c>
       <c r="CR36" t="n">
-        <v>36.56479138755189</v>
+        <v>36.56479138327277</v>
       </c>
       <c r="CS36" t="n">
-        <v>29.7990788230786</v>
+        <v>29.79907879050002</v>
       </c>
       <c r="CT36" t="inlineStr"/>
       <c r="CU36" t="n">
-        <v>34.17902788589272</v>
+        <v>34.17902790166413</v>
       </c>
       <c r="CV36" t="n">
-        <v>33.03968521389994</v>
+        <v>33.03968523364507</v>
       </c>
       <c r="CW36" t="n">
-        <v>29.73571669250994</v>
+        <v>29.73571671028056</v>
       </c>
       <c r="CX36" t="n">
         <v>4</v>
@@ -13770,10 +13770,10 @@
         <v>3.4</v>
       </c>
       <c r="DA36" t="n">
-        <v>-2.31367880811858</v>
+        <v>-2.313678749739423</v>
       </c>
       <c r="DB36" t="n">
-        <v>12.2832696656878</v>
+        <v>12.28326971749924</v>
       </c>
       <c r="DC36" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>1.4328567207472</v>
       </c>
       <c r="DO36" t="n">
-        <v>-16.5091286271213</v>
+        <v>-16.50913757078116</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -14103,10 +14103,10 @@
         <v>0</v>
       </c>
       <c r="CM37" t="n">
-        <v>13.92259633446643</v>
+        <v>13.92259625117415</v>
       </c>
       <c r="CN37" t="n">
-        <v>20.27130026298312</v>
+        <v>20.27130014170956</v>
       </c>
       <c r="CO37" t="n">
         <v>16.70574758244657</v>
@@ -14125,7 +14125,7 @@
         <v>15.45433621078142</v>
       </c>
       <c r="CU37" t="n">
-        <v>16.60794748206458</v>
+        <v>16.60794744797028</v>
       </c>
       <c r="CV37" t="n">
         <v>16.080041896614</v>
@@ -14146,7 +14146,7 @@
         <v>29.44577202071063</v>
       </c>
       <c r="DB37" t="n">
-        <v>48.55051009592491</v>
+        <v>48.55050979096687</v>
       </c>
       <c r="DC37" t="inlineStr">
         <is>
@@ -14478,10 +14478,10 @@
         <v>0</v>
       </c>
       <c r="CM38" t="n">
-        <v>9.424600952514027</v>
+        <v>9.42460095746508</v>
       </c>
       <c r="CN38" t="n">
-        <v>17.48263476691352</v>
+        <v>17.48263477609772</v>
       </c>
       <c r="CO38" t="n">
         <v>17.0502564055361</v>
@@ -14490,7 +14490,7 @@
         <v>16.93163083998861</v>
       </c>
       <c r="CQ38" t="n">
-        <v>26.97723552038159</v>
+        <v>26.97723552481916</v>
       </c>
       <c r="CR38" t="n">
         <v>19.94489718117502</v>
@@ -14502,7 +14502,7 @@
         <v>17.36889744184579</v>
       </c>
       <c r="CU38" t="n">
-        <v>17.53315800732909</v>
+        <v>17.5331580096507</v>
       </c>
       <c r="CV38" t="n">
         <v>17.20957692369095</v>
@@ -14523,7 +14523,7 @@
         <v>-22.94219434144452</v>
       </c>
       <c r="DB38" t="n">
-        <v>-12.77035982798795</v>
+        <v>-12.77035981643767</v>
       </c>
       <c r="DC38" t="inlineStr">
         <is>
@@ -15478,10 +15478,10 @@
         <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>14.34883233997342</v>
+        <v>14.34883242735353</v>
       </c>
       <c r="CN2" t="n">
-        <v>26.61708399065069</v>
+        <v>26.6170841527408</v>
       </c>
       <c r="CO2" t="n">
         <v>38.73764113094029</v>
@@ -15490,13 +15490,13 @@
         <v>23.42212306847306</v>
       </c>
       <c r="CQ2" t="n">
-        <v>77.21384545128907</v>
+        <v>77.21384529729626</v>
       </c>
       <c r="CR2" t="n">
-        <v>48.83647633066641</v>
+        <v>48.83647626610477</v>
       </c>
       <c r="CS2" t="n">
-        <v>27.96937483383525</v>
+        <v>27.96937456424314</v>
       </c>
       <c r="CT2" t="n">
         <v>9.042040250118818</v>
@@ -15837,10 +15837,10 @@
         <v>1</v>
       </c>
       <c r="CM3" t="n">
-        <v>6.7414967884217</v>
+        <v>6.741496747302762</v>
       </c>
       <c r="CN3" t="n">
-        <v>12.50547654252225</v>
+        <v>12.50547646624662</v>
       </c>
       <c r="CO3" t="n">
         <v>41.30882298882631</v>
@@ -15849,7 +15849,7 @@
         <v>27.77800617149056</v>
       </c>
       <c r="CQ3" t="n">
-        <v>72.00025474574477</v>
+        <v>72.00025459182361</v>
       </c>
       <c r="CR3" t="n">
         <v>19.57807411896471</v>
@@ -15881,12 +15881,12 @@
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>próxima</t>
+          <t>última</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr"/>
@@ -15911,7 +15911,7 @@
         <v>1.03986036356809</v>
       </c>
       <c r="DO3" t="n">
-        <v>-17.06074941778566</v>
+        <v>-17.06075516698471</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -16204,10 +16204,10 @@
         <v>0</v>
       </c>
       <c r="CM4" t="n">
-        <v>17.16638305223679</v>
+        <v>17.16638307220182</v>
       </c>
       <c r="CN4" t="n">
-        <v>31.84364056189925</v>
+        <v>31.84364059893438</v>
       </c>
       <c r="CO4" t="n">
         <v>71.20842100924612</v>
@@ -16216,19 +16216,19 @@
         <v>51.68759722785042</v>
       </c>
       <c r="CQ4" t="n">
-        <v>122.3957204994831</v>
+        <v>122.3957204894488</v>
       </c>
       <c r="CR4" t="n">
-        <v>25.57411553292391</v>
+        <v>25.57411553006628</v>
       </c>
       <c r="CS4" t="n">
-        <v>59.88502642609916</v>
+        <v>59.88502638326539</v>
       </c>
       <c r="CT4" t="n">
         <v>44.43438321477654</v>
       </c>
       <c r="CU4" t="n">
-        <v>47.4388639954659</v>
+        <v>47.43886399402319</v>
       </c>
       <c r="CV4" t="n">
         <v>48.06099022131347</v>
@@ -16249,7 +16249,7 @@
         <v>67.33033098981652</v>
       </c>
       <c r="DB4" t="n">
-        <v>83.5159121679236</v>
+        <v>83.51591216234252</v>
       </c>
       <c r="DC4" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>5338021376</v>
+        <v>5337995264</v>
       </c>
       <c r="AX5" t="n">
         <v>4.48</v>
@@ -16571,10 +16571,10 @@
         <v>0</v>
       </c>
       <c r="CM5" t="n">
-        <v>3.907370941582745</v>
+        <v>3.907370934748664</v>
       </c>
       <c r="CN5" t="n">
-        <v>7.248173096635992</v>
+        <v>7.248173083958771</v>
       </c>
       <c r="CO5" t="n">
         <v>12.71763449268681</v>
@@ -16583,19 +16583,19 @@
         <v>8.551038591084707</v>
       </c>
       <c r="CQ5" t="n">
-        <v>23.90073394611848</v>
+        <v>23.90073395185774</v>
       </c>
       <c r="CR5" t="n">
-        <v>11.1350664234246</v>
+        <v>11.13506642622674</v>
       </c>
       <c r="CS5" t="n">
-        <v>9.912220060941721</v>
+        <v>9.912220077973341</v>
       </c>
       <c r="CT5" t="n">
         <v>5.427221201663706</v>
       </c>
       <c r="CU5" t="n">
-        <v>8.414103544002897</v>
+        <v>8.414103544048963</v>
       </c>
       <c r="CV5" t="n">
         <v>8.551038591084707</v>
@@ -16616,7 +16616,7 @@
         <v>78.97521838623484</v>
       </c>
       <c r="DB5" t="n">
-        <v>95.67681792509268</v>
+        <v>95.67681792616401</v>
       </c>
       <c r="DC5" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>-0.9216580748084957</v>
       </c>
       <c r="DO5" t="n">
-        <v>-34.16760193805087</v>
+        <v>-34.16759691282044</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -16814,7 +16814,7 @@
         <v>1</v>
       </c>
       <c r="AW6" t="n">
-        <v>5660785152</v>
+        <v>5660757504</v>
       </c>
       <c r="AX6" t="n">
         <v>4.75</v>
@@ -16940,10 +16940,10 @@
         <v>1</v>
       </c>
       <c r="CM6" t="n">
-        <v>3.327945787913786</v>
+        <v>3.327945796066591</v>
       </c>
       <c r="CN6" t="n">
-        <v>6.173339436580072</v>
+        <v>6.173339451703526</v>
       </c>
       <c r="CO6" t="n">
         <v>12.71999984038503</v>
@@ -16952,25 +16952,25 @@
         <v>8.573475127812586</v>
       </c>
       <c r="CQ6" t="n">
-        <v>23.80124252119723</v>
+        <v>23.80124251290231</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.53241883287747</v>
+        <v>11.53241882948836</v>
       </c>
       <c r="CS6" t="n">
-        <v>11.35989495000031</v>
+        <v>11.35989492968222</v>
       </c>
       <c r="CT6" t="n">
         <v>5.406965820956791</v>
       </c>
       <c r="CU6" t="n">
-        <v>11.36676236140136</v>
+        <v>11.36676235899012</v>
       </c>
       <c r="CV6" t="n">
-        <v>11.35989495000031</v>
+        <v>11.35989492968222</v>
       </c>
       <c r="CW6" t="n">
-        <v>10.22390545500028</v>
+        <v>10.22390543671399</v>
       </c>
       <c r="CX6" t="n">
         <v>7</v>
@@ -16982,10 +16982,10 @@
         <v>7.2</v>
       </c>
       <c r="DA6" t="n">
-        <v>124.2084557739779</v>
+        <v>124.2084553729628</v>
       </c>
       <c r="DB6" t="n">
-        <v>149.2711075446366</v>
+        <v>149.2711074917585</v>
       </c>
       <c r="DC6" t="inlineStr">
         <is>
@@ -17299,10 +17299,10 @@
         <v>1</v>
       </c>
       <c r="CM7" t="n">
-        <v>19.52675456025717</v>
+        <v>19.52675458976631</v>
       </c>
       <c r="CN7" t="n">
-        <v>36.22212970927706</v>
+        <v>36.22212976401649</v>
       </c>
       <c r="CO7" t="n">
         <v>75.52058089429198</v>
@@ -17311,23 +17311,23 @@
         <v>56.61657821085305</v>
       </c>
       <c r="CQ7" t="n">
-        <v>98.15037110641777</v>
+        <v>98.15037105801352</v>
       </c>
       <c r="CR7" t="n">
-        <v>48.15705804455569</v>
+        <v>48.41140869607853</v>
       </c>
       <c r="CS7" t="n">
-        <v>57.80670633975764</v>
+        <v>57.80670628044665</v>
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>44.85663080209548</v>
+        <v>44.92021848603832</v>
       </c>
       <c r="CV7" t="n">
-        <v>42.18959387691638</v>
+        <v>42.31676923004751</v>
       </c>
       <c r="CW7" t="n">
-        <v>37.97063448922474</v>
+        <v>38.08509230704276</v>
       </c>
       <c r="CX7" t="n">
         <v>4</v>
@@ -17339,10 +17339,10 @@
         <v>3.9</v>
       </c>
       <c r="DA7" t="n">
-        <v>-25.89650030167426</v>
+        <v>-25.67312439599759</v>
       </c>
       <c r="DB7" t="n">
-        <v>-12.45778818749312</v>
+        <v>-12.3336904477197</v>
       </c>
       <c r="DC7" t="inlineStr">
         <is>
@@ -17666,10 +17666,10 @@
         <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>6.403626923493396</v>
+        <v>6.403626929435632</v>
       </c>
       <c r="CN8" t="n">
-        <v>11.87872794308025</v>
+        <v>11.87872795410309</v>
       </c>
       <c r="CO8" t="n">
         <v>25.4012199436746</v>
@@ -17678,19 +17678,19 @@
         <v>18.64745536395598</v>
       </c>
       <c r="CQ8" t="n">
-        <v>35.23268456040559</v>
+        <v>35.23268455074302</v>
       </c>
       <c r="CR8" t="n">
-        <v>12.29886663486247</v>
+        <v>12.29886663373466</v>
       </c>
       <c r="CS8" t="n">
-        <v>20.39539800428012</v>
+        <v>20.39539799182948</v>
       </c>
       <c r="CT8" t="n">
         <v>18.89184945304214</v>
       </c>
       <c r="CU8" t="n">
-        <v>20.39231455761445</v>
+        <v>20.392314555869</v>
       </c>
       <c r="CV8" t="n">
         <v>18.89184945304214</v>
@@ -17711,7 +17711,7 @@
         <v>8.159441596189932</v>
       </c>
       <c r="DB8" t="n">
-        <v>29.72210058027398</v>
+        <v>29.7221005691706</v>
       </c>
       <c r="DC8" t="inlineStr">
         <is>
@@ -18035,10 +18035,10 @@
         <v>1</v>
       </c>
       <c r="CM9" t="n">
-        <v>45.77695654203991</v>
+        <v>45.77695656449495</v>
       </c>
       <c r="CN9" t="n">
-        <v>84.91625438548404</v>
+        <v>84.91625442713813</v>
       </c>
       <c r="CO9" t="n">
         <v>68.18445585960495</v>
@@ -18059,7 +18059,7 @@
         <v>26.15892848466381</v>
       </c>
       <c r="CU9" t="n">
-        <v>71.11162369885957</v>
+        <v>71.11162370687322</v>
       </c>
       <c r="CV9" t="n">
         <v>65.22550777513155</v>
@@ -18080,7 +18080,7 @@
         <v>79.08163265306125</v>
       </c>
       <c r="DB9" t="n">
-        <v>116.9360169219168</v>
+        <v>116.9360169463635</v>
       </c>
       <c r="DC9" t="inlineStr">
         <is>
@@ -18412,37 +18412,37 @@
         <v>1</v>
       </c>
       <c r="CM10" t="n">
-        <v>24.36355405256904</v>
+        <v>24.36355402870555</v>
       </c>
       <c r="CN10" t="n">
-        <v>31.53570981245223</v>
+        <v>31.53570997693015</v>
       </c>
       <c r="CO10" t="n">
-        <v>32.96248457625602</v>
+        <v>32.96248478046137</v>
       </c>
       <c r="CP10" t="n">
         <v>20.75155156536448</v>
       </c>
       <c r="CQ10" t="n">
-        <v>47.31871796693122</v>
+        <v>47.31871815238542</v>
       </c>
       <c r="CR10" t="n">
-        <v>50.67251006901864</v>
+        <v>49.42305094651599</v>
       </c>
       <c r="CS10" t="n">
-        <v>15.96314843782849</v>
+        <v>15.96314857722565</v>
       </c>
       <c r="CT10" t="n">
         <v>24.59438222893265</v>
       </c>
       <c r="CU10" t="n">
-        <v>31.0202573386691</v>
+        <v>30.86407503206516</v>
       </c>
       <c r="CV10" t="n">
-        <v>28.06504602069244</v>
+        <v>28.0650461029314</v>
       </c>
       <c r="CW10" t="n">
-        <v>25.2585414186232</v>
+        <v>25.25854149263826</v>
       </c>
       <c r="CX10" t="n">
         <v>8</v>
@@ -18451,13 +18451,13 @@
         <v>1</v>
       </c>
       <c r="CZ10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="DA10" t="n">
-        <v>-22.9922499812631</v>
+        <v>-22.99224975560741</v>
       </c>
       <c r="DB10" t="n">
-        <v>-5.42604249935631</v>
+        <v>-5.902208079346527</v>
       </c>
       <c r="DC10" t="inlineStr">
         <is>
@@ -18791,10 +18791,10 @@
         <v>1</v>
       </c>
       <c r="CM11" t="n">
-        <v>139.3180003996247</v>
+        <v>139.3180008054895</v>
       </c>
       <c r="CN11" t="n">
-        <v>258.4348907413038</v>
+        <v>258.434891494183</v>
       </c>
       <c r="CO11" t="n">
         <v>136.9934822165448</v>
@@ -18806,7 +18806,7 @@
         <v>310.173921999724</v>
       </c>
       <c r="CR11" t="n">
-        <v>56.1476</v>
+        <v>195.5</v>
       </c>
       <c r="CS11" t="n">
         <v>125.103481873222</v>
@@ -18815,13 +18815,13 @@
         <v>58.37540514006138</v>
       </c>
       <c r="CU11" t="n">
-        <v>147.2354325900216</v>
+        <v>164.6544827348646</v>
       </c>
       <c r="CV11" t="n">
-        <v>131.0484820448834</v>
+        <v>138.1557415110171</v>
       </c>
       <c r="CW11" t="n">
-        <v>117.9436338403951</v>
+        <v>124.3401673599154</v>
       </c>
       <c r="CX11" t="n">
         <v>8</v>
@@ -18830,13 +18830,13 @@
         <v>1</v>
       </c>
       <c r="CZ11" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="DA11" t="n">
-        <v>147.9891304347826</v>
+        <v>161.4385276905038</v>
       </c>
       <c r="DB11" t="n">
-        <v>209.5782765740348</v>
+        <v>246.2036963424734</v>
       </c>
       <c r="DC11" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>-1.327799542568742</v>
       </c>
       <c r="DO11" t="n">
-        <v>-1.430048967272501</v>
+        <v>-3.31367615150312</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -19160,10 +19160,10 @@
         <v>0</v>
       </c>
       <c r="CM12" t="n">
-        <v>6.912918036445349</v>
+        <v>6.9129180550752</v>
       </c>
       <c r="CN12" t="n">
-        <v>12.82346295760612</v>
+        <v>12.82346299216449</v>
       </c>
       <c r="CO12" t="n">
         <v>40.40975051302138</v>
@@ -19172,7 +19172,7 @@
         <v>27.23426223219501</v>
       </c>
       <c r="CQ12" t="n">
-        <v>85.90491746046615</v>
+        <v>85.90491756868936</v>
       </c>
       <c r="CR12" t="n">
         <v>51.88018214566937</v>
@@ -20109,10 +20109,10 @@
         <v>1</v>
       </c>
       <c r="CM15" t="n">
-        <v>145.9241172852467</v>
+        <v>145.9241165475706</v>
       </c>
       <c r="CN15" t="n">
-        <v>270.6892375641326</v>
+        <v>270.6892361957434</v>
       </c>
       <c r="CO15" t="n">
         <v>137.1427213113139</v>
@@ -20124,7 +20124,7 @@
         <v>310.5118218369371</v>
       </c>
       <c r="CR15" t="n">
-        <v>56.1476</v>
+        <v>195.5</v>
       </c>
       <c r="CS15" t="n">
         <v>125.239768140898</v>
@@ -20133,13 +20133,13 @@
         <v>57.29814214194677</v>
       </c>
       <c r="CU15" t="n">
-        <v>149.5179563910809</v>
+        <v>166.9370061278227</v>
       </c>
       <c r="CV15" t="n">
-        <v>131.1912447261059</v>
+        <v>141.5334189294422</v>
       </c>
       <c r="CW15" t="n">
-        <v>118.0721202534953</v>
+        <v>127.380077036498</v>
       </c>
       <c r="CX15" t="n">
         <v>8</v>
@@ -20148,13 +20148,13 @@
         <v>1</v>
       </c>
       <c r="CZ15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="DA15" t="n">
-        <v>124.5570866141732</v>
+        <v>142.2595523023832</v>
       </c>
       <c r="DB15" t="n">
-        <v>184.362782777183</v>
+        <v>217.4914422106899</v>
       </c>
       <c r="DC15" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>-1.793050183146794</v>
       </c>
       <c r="DO15" t="n">
-        <v>-2.213127425289363</v>
+        <v>-3.593690963643992</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -20460,10 +20460,10 @@
         <v>0</v>
       </c>
       <c r="CM16" t="n">
-        <v>13.58565532094829</v>
+        <v>13.58565534397649</v>
       </c>
       <c r="CN16" t="n">
-        <v>25.20139062035909</v>
+        <v>25.20139066307638</v>
       </c>
       <c r="CO16" t="n">
         <v>19.9811217441166</v>
@@ -20472,7 +20472,7 @@
         <v>12.48999788378355</v>
       </c>
       <c r="CQ16" t="n">
-        <v>33.81046379501534</v>
+        <v>33.81046381960686</v>
       </c>
       <c r="CR16" t="n">
         <v>22.8984489302328</v>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="CT16" t="inlineStr"/>
       <c r="CU16" t="n">
-        <v>20.41665415391419</v>
+        <v>20.41665417035057</v>
       </c>
       <c r="CV16" t="n">
         <v>21.4397853371747</v>
@@ -20503,7 +20503,7 @@
         <v>-2.398551559568773</v>
       </c>
       <c r="DB16" t="n">
-        <v>3.270883566907457</v>
+        <v>3.27088365004542</v>
       </c>
       <c r="DC16" t="inlineStr">
         <is>
@@ -20835,10 +20835,10 @@
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>3.241822751043931</v>
+        <v>3.241822754874634</v>
       </c>
       <c r="CN17" t="n">
-        <v>6.013581203186491</v>
+        <v>6.013581210292446</v>
       </c>
       <c r="CO17" t="n">
         <v>19.81979119280974</v>
@@ -20847,7 +20847,7 @@
         <v>13.58186553210178</v>
       </c>
       <c r="CQ17" t="n">
-        <v>31.89281582076967</v>
+        <v>31.89281583194255</v>
       </c>
       <c r="CR17" t="n">
         <v>10.95072400487419</v>
@@ -21176,10 +21176,10 @@
         <v>0</v>
       </c>
       <c r="CM18" t="n">
-        <v>10.89032244259161</v>
+        <v>10.8903224473678</v>
       </c>
       <c r="CN18" t="n">
-        <v>20.20154813100745</v>
+        <v>20.20154813986726</v>
       </c>
       <c r="CO18" t="n">
         <v>49.68749999999999</v>
@@ -21188,23 +21188,23 @@
         <v>48.8668773108453</v>
       </c>
       <c r="CQ18" t="n">
-        <v>67.62433396664358</v>
+        <v>67.62433397449371</v>
       </c>
       <c r="CR18" t="n">
-        <v>33.80819015720991</v>
+        <v>33.80819015646885</v>
       </c>
       <c r="CS18" t="n">
-        <v>28.56587197676012</v>
+        <v>28.5658719711869</v>
       </c>
       <c r="CT18" t="inlineStr"/>
       <c r="CU18" t="n">
-        <v>28.64689018270224</v>
+        <v>28.64689018592598</v>
       </c>
       <c r="CV18" t="n">
-        <v>27.00486914410867</v>
+        <v>27.00486914816805</v>
       </c>
       <c r="CW18" t="n">
-        <v>24.30438222969781</v>
+        <v>24.30438223335125</v>
       </c>
       <c r="CX18" t="n">
         <v>4</v>
@@ -21216,10 +21216,10 @@
         <v>4.6</v>
       </c>
       <c r="DA18" t="n">
-        <v>62.02921486465205</v>
+        <v>62.02921488900834</v>
       </c>
       <c r="DB18" t="n">
-        <v>90.9792678846816</v>
+        <v>90.97926790617316</v>
       </c>
       <c r="DC18" t="inlineStr">
         <is>
@@ -21551,10 +21551,10 @@
         <v>0</v>
       </c>
       <c r="CM19" t="n">
-        <v>10.89909385310484</v>
+        <v>10.89909387042541</v>
       </c>
       <c r="CN19" t="n">
-        <v>20.21781909750947</v>
+        <v>20.21781912963913</v>
       </c>
       <c r="CO19" t="n">
         <v>37.45389651797344</v>
@@ -21563,25 +21563,25 @@
         <v>36.91124241178991</v>
       </c>
       <c r="CQ19" t="n">
-        <v>41.40373335666359</v>
+        <v>41.40373336325502</v>
       </c>
       <c r="CR19" t="n">
-        <v>34.46332758610621</v>
+        <v>33.9846702548987</v>
       </c>
       <c r="CS19" t="n">
-        <v>18.32822066472938</v>
+        <v>18.32822064464029</v>
       </c>
       <c r="CT19" t="n">
         <v>32.58677052647363</v>
       </c>
       <c r="CU19" t="n">
-        <v>31.62357288017795</v>
+        <v>31.55519326409573</v>
       </c>
       <c r="CV19" t="n">
-        <v>34.46332758610621</v>
+        <v>33.9846702548987</v>
       </c>
       <c r="CW19" t="n">
-        <v>31.01699482749559</v>
+        <v>30.58620322940883</v>
       </c>
       <c r="CX19" t="n">
         <v>7</v>
@@ -21593,10 +21593,10 @@
         <v>3.8</v>
       </c>
       <c r="DA19" t="n">
-        <v>74.44878306890246</v>
+        <v>72.02588328571895</v>
       </c>
       <c r="DB19" t="n">
-        <v>77.86035803660174</v>
+        <v>77.4757707844</v>
       </c>
       <c r="DC19" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>-1.222218407524955</v>
       </c>
       <c r="DO19" t="n">
-        <v>-22.12628936839648</v>
+        <v>-22.12628280376486</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -21928,37 +21928,37 @@
         <v>0</v>
       </c>
       <c r="CM20" t="n">
-        <v>24.6452661183992</v>
+        <v>24.64526620056351</v>
       </c>
       <c r="CN20" t="n">
-        <v>31.16419473185438</v>
+        <v>31.16419460305564</v>
       </c>
       <c r="CO20" t="n">
-        <v>34.75021176353649</v>
+        <v>34.75021150406412</v>
       </c>
       <c r="CP20" t="n">
         <v>36.07661496384414</v>
       </c>
       <c r="CQ20" t="n">
-        <v>48.86831569478055</v>
+        <v>48.86831552998098</v>
       </c>
       <c r="CR20" t="n">
-        <v>48.59901755120379</v>
+        <v>48.59901751503249</v>
       </c>
       <c r="CS20" t="n">
-        <v>16.65417721304533</v>
+        <v>16.6541770283071</v>
       </c>
       <c r="CT20" t="n">
         <v>31.14870262855163</v>
       </c>
       <c r="CU20" t="n">
-        <v>33.98831258315194</v>
+        <v>33.98831249667495</v>
       </c>
       <c r="CV20" t="n">
-        <v>32.95720324769543</v>
+        <v>32.95720305355988</v>
       </c>
       <c r="CW20" t="n">
-        <v>29.66148292292589</v>
+        <v>29.66148274820389</v>
       </c>
       <c r="CX20" t="n">
         <v>8</v>
@@ -21970,10 +21970,10 @@
         <v>2.9</v>
       </c>
       <c r="DA20" t="n">
-        <v>-13.47291721363859</v>
+        <v>-13.47291772332938</v>
       </c>
       <c r="DB20" t="n">
-        <v>-0.8508932512596767</v>
+        <v>-0.8508935035262732</v>
       </c>
       <c r="DC20" t="inlineStr">
         <is>
@@ -22299,10 +22299,10 @@
         <v>0</v>
       </c>
       <c r="CM21" t="n">
-        <v>5.334787411855786</v>
+        <v>5.334787426705602</v>
       </c>
       <c r="CN21" t="n">
-        <v>9.896030648992484</v>
+        <v>9.89603067653889</v>
       </c>
       <c r="CO21" t="n">
         <v>8.503043610116709</v>
@@ -22373,7 +22373,7 @@
         <v>0.2717388663546538</v>
       </c>
       <c r="DO21" t="n">
-        <v>-24.42029364136734</v>
+        <v>-24.4203010953975</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -22658,10 +22658,10 @@
         <v>0</v>
       </c>
       <c r="CM22" t="n">
-        <v>3.558471602966997</v>
+        <v>3.558471586714633</v>
       </c>
       <c r="CN22" t="n">
-        <v>6.60096482350378</v>
+        <v>6.600964793355645</v>
       </c>
       <c r="CO22" t="n">
         <v>19.66796809186538</v>
@@ -22670,13 +22670,13 @@
         <v>18.52055498018046</v>
       </c>
       <c r="CQ22" t="n">
-        <v>20.69777961533053</v>
+        <v>20.69777961849134</v>
       </c>
       <c r="CR22" t="n">
-        <v>15.89091661176179</v>
+        <v>15.89091661496516</v>
       </c>
       <c r="CS22" t="n">
-        <v>12.89801917568821</v>
+        <v>12.89801919629751</v>
       </c>
       <c r="CT22" t="n">
         <v>29.41436415825995</v>
@@ -22732,7 +22732,7 @@
         <v>-0.9556959875251736</v>
       </c>
       <c r="DO22" t="n">
-        <v>-30.95849087040471</v>
+        <v>-30.95848265146315</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -23025,37 +23025,37 @@
         <v>0</v>
       </c>
       <c r="CM23" t="n">
-        <v>10.71852592981897</v>
+        <v>10.71852589667536</v>
       </c>
       <c r="CN23" t="n">
-        <v>16.81931635082226</v>
+        <v>16.81931642158801</v>
       </c>
       <c r="CO23" t="n">
-        <v>20.69399620161987</v>
+        <v>20.69399635267754</v>
       </c>
       <c r="CP23" t="n">
         <v>17.56096669750601</v>
       </c>
       <c r="CQ23" t="n">
-        <v>34.52474409552667</v>
+        <v>34.5247441309253</v>
       </c>
       <c r="CR23" t="n">
-        <v>23.92681846053856</v>
+        <v>23.92681847484472</v>
       </c>
       <c r="CS23" t="n">
-        <v>10.34281212568361</v>
+        <v>10.34281219830788</v>
       </c>
       <c r="CT23" t="n">
         <v>10.6899995803833</v>
       </c>
       <c r="CU23" t="n">
-        <v>18.15964743023741</v>
+        <v>18.15964746911352</v>
       </c>
       <c r="CV23" t="n">
-        <v>17.19014152416413</v>
+        <v>17.19014155954701</v>
       </c>
       <c r="CW23" t="n">
-        <v>15.47112737174772</v>
+        <v>15.47112740359231</v>
       </c>
       <c r="CX23" t="n">
         <v>8</v>
@@ -23067,10 +23067,10 @@
         <v>3.3</v>
       </c>
       <c r="DA23" t="n">
-        <v>44.72523834461168</v>
+        <v>44.72523864250309</v>
       </c>
       <c r="DB23" t="n">
-        <v>69.87509956091387</v>
+        <v>69.87509992458187</v>
       </c>
       <c r="DC23" t="inlineStr">
         <is>
@@ -23384,10 +23384,10 @@
         <v>0</v>
       </c>
       <c r="CM24" t="n">
-        <v>6.908311428687161</v>
+        <v>6.908311434566198</v>
       </c>
       <c r="CN24" t="n">
-        <v>12.81491770021468</v>
+        <v>12.8149177111203</v>
       </c>
       <c r="CO24" t="n">
         <v>31.4652624130249</v>
@@ -23396,7 +23396,7 @@
         <v>19.46950820333509</v>
       </c>
       <c r="CQ24" t="n">
-        <v>55.98239073603961</v>
+        <v>55.9823907533673</v>
       </c>
       <c r="CR24" t="n">
         <v>12.77531889407378</v>
@@ -23406,13 +23406,13 @@
       </c>
       <c r="CT24" t="inlineStr"/>
       <c r="CU24" t="n">
-        <v>15.99095260900013</v>
+        <v>15.99095261319629</v>
       </c>
       <c r="CV24" t="n">
-        <v>12.79511829714423</v>
+        <v>12.79511830259704</v>
       </c>
       <c r="CW24" t="n">
-        <v>11.51560646742981</v>
+        <v>11.51560647233734</v>
       </c>
       <c r="CX24" t="n">
         <v>4</v>
@@ -23424,10 +23424,10 @@
         <v>4.6</v>
       </c>
       <c r="DA24" t="n">
-        <v>2.088712234362422</v>
+        <v>2.088712277868865</v>
       </c>
       <c r="DB24" t="n">
-        <v>41.76376762012615</v>
+        <v>41.76376765732617</v>
       </c>
       <c r="DC24" t="inlineStr">
         <is>
@@ -23747,37 +23747,37 @@
         <v>1</v>
       </c>
       <c r="CM25" t="n">
-        <v>9.929939060311767</v>
+        <v>9.929939056665846</v>
       </c>
       <c r="CN25" t="n">
-        <v>17.62243046603763</v>
+        <v>17.62243048562545</v>
       </c>
       <c r="CO25" t="n">
-        <v>20.83047589898358</v>
+        <v>20.83047592978545</v>
       </c>
       <c r="CP25" t="n">
         <v>12.8457780532356</v>
       </c>
       <c r="CQ25" t="n">
-        <v>29.22488338744555</v>
+        <v>29.2248833989064</v>
       </c>
       <c r="CR25" t="n">
-        <v>24.9773450146415</v>
+        <v>24.97734501734207</v>
       </c>
       <c r="CS25" t="n">
-        <v>10.24067493805693</v>
+        <v>10.24067494985747</v>
       </c>
       <c r="CT25" t="n">
         <v>9.713052205096755</v>
       </c>
       <c r="CU25" t="n">
-        <v>16.92307237797617</v>
+        <v>16.92307238706438</v>
       </c>
       <c r="CV25" t="n">
-        <v>15.23410425963662</v>
+        <v>15.23410426943053</v>
       </c>
       <c r="CW25" t="n">
-        <v>13.71069383367296</v>
+        <v>13.71069384248748</v>
       </c>
       <c r="CX25" t="n">
         <v>8</v>
@@ -23789,10 +23789,10 @@
         <v>3</v>
       </c>
       <c r="DA25" t="n">
-        <v>19.53525295971572</v>
+        <v>19.5352530365642</v>
       </c>
       <c r="DB25" t="n">
-        <v>47.54203996509516</v>
+        <v>47.5420400443298</v>
       </c>
       <c r="DC25" t="inlineStr">
         <is>
@@ -24096,10 +24096,10 @@
         <v>1</v>
       </c>
       <c r="CM26" t="n">
-        <v>4.411578432089268</v>
+        <v>4.411578436242657</v>
       </c>
       <c r="CN26" t="n">
-        <v>8.183477991525592</v>
+        <v>8.183477999230128</v>
       </c>
       <c r="CO26" t="n">
         <v>13.99193579150784</v>
@@ -24108,23 +24108,23 @@
         <v>9.385319019937953</v>
       </c>
       <c r="CQ26" t="n">
-        <v>16.24838538185653</v>
+        <v>16.24838536882942</v>
       </c>
       <c r="CR26" t="n">
-        <v>9.212292051566077</v>
+        <v>9.212292050273723</v>
       </c>
       <c r="CS26" t="n">
-        <v>10.67142032642342</v>
+        <v>10.67142031601037</v>
       </c>
       <c r="CT26" t="inlineStr"/>
       <c r="CU26" t="n">
-        <v>8.949821066672195</v>
+        <v>8.949821069313588</v>
       </c>
       <c r="CV26" t="n">
-        <v>8.697885021545835</v>
+        <v>8.697885024751926</v>
       </c>
       <c r="CW26" t="n">
-        <v>7.828096519391251</v>
+        <v>7.828096522276733</v>
       </c>
       <c r="CX26" t="n">
         <v>4</v>
@@ -24136,10 +24136,10 @@
         <v>3.2</v>
       </c>
       <c r="DA26" t="n">
-        <v>-54.88128906468572</v>
+        <v>-54.8812890480547</v>
       </c>
       <c r="DB26" t="n">
-        <v>-48.41601804095147</v>
+        <v>-48.4160180257273</v>
       </c>
       <c r="DC26" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>14.3</v>
       </c>
       <c r="BN27" t="n">
-        <v>7.62</v>
+        <v>7.58</v>
       </c>
       <c r="BO27" t="n">
         <v>5.97</v>
@@ -24479,10 +24479,10 @@
         <v>1</v>
       </c>
       <c r="CM27" t="n">
-        <v>4.644659461827183</v>
+        <v>4.644659465455039</v>
       </c>
       <c r="CN27" t="n">
-        <v>8.615843301689424</v>
+        <v>8.615843308419096</v>
       </c>
       <c r="CO27" t="n">
         <v>24.12424807657547</v>
@@ -24491,25 +24491,25 @@
         <v>20.32750370736387</v>
       </c>
       <c r="CQ27" t="n">
-        <v>28.97489049750424</v>
+        <v>28.9748904944384</v>
       </c>
       <c r="CR27" t="n">
-        <v>16.67294824692233</v>
+        <v>16.67294824616935</v>
       </c>
       <c r="CS27" t="n">
-        <v>18.15812060241079</v>
+        <v>18.15812059664192</v>
       </c>
       <c r="CT27" t="n">
         <v>14.57260791194931</v>
       </c>
       <c r="CU27" t="n">
-        <v>18.77802319205935</v>
+        <v>18.77802319165106</v>
       </c>
       <c r="CV27" t="n">
-        <v>18.15812060241079</v>
+        <v>18.15812059664192</v>
       </c>
       <c r="CW27" t="n">
-        <v>16.34230854216971</v>
+        <v>16.34230853697773</v>
       </c>
       <c r="CX27" t="n">
         <v>7</v>
@@ -24521,10 +24521,10 @@
         <v>6.2</v>
       </c>
       <c r="DA27" t="n">
-        <v>8.012613473622521</v>
+        <v>8.012613439306659</v>
       </c>
       <c r="DB27" t="n">
-        <v>24.1111900199958</v>
+        <v>24.11119001729727</v>
       </c>
       <c r="DC27" t="inlineStr">
         <is>
@@ -24852,10 +24852,10 @@
         <v>0</v>
       </c>
       <c r="CM28" t="n">
-        <v>8.621278985813751</v>
+        <v>8.621278995024001</v>
       </c>
       <c r="CN28" t="n">
-        <v>15.99247251868451</v>
+        <v>15.99247253576952</v>
       </c>
       <c r="CO28" t="n">
         <v>13.59634032616248</v>
@@ -24867,7 +24867,7 @@
         <v>30.78416677621694</v>
       </c>
       <c r="CR28" t="n">
-        <v>10.32999</v>
+        <v>10.01696</v>
       </c>
       <c r="CS28" t="n">
         <v>12.41628059974084</v>
@@ -24876,7 +24876,7 @@
         <v>6.385031628683394</v>
       </c>
       <c r="CU28" t="n">
-        <v>11.20122792536668</v>
+        <v>11.15650935769457</v>
       </c>
       <c r="CV28" t="n">
         <v>11.06720141848175</v>
@@ -24897,7 +24897,7 @@
         <v>-27.5074130818345</v>
       </c>
       <c r="DB28" t="n">
-        <v>-18.47723353742736</v>
+        <v>-18.80269618966195</v>
       </c>
       <c r="DC28" t="inlineStr">
         <is>
@@ -25215,10 +25215,10 @@
         <v>0</v>
       </c>
       <c r="CM29" t="n">
-        <v>4.318415205437831</v>
+        <v>4.31841520070981</v>
       </c>
       <c r="CN29" t="n">
-        <v>8.010660206087175</v>
+        <v>8.010660197316698</v>
       </c>
       <c r="CO29" t="n">
         <v>24.16633971749919</v>
@@ -25227,13 +25227,13 @@
         <v>22.43313195736019</v>
       </c>
       <c r="CQ29" t="n">
-        <v>29.86467075988262</v>
+        <v>29.86467075671898</v>
       </c>
       <c r="CR29" t="n">
-        <v>9.538227155629455</v>
+        <v>9.538227156095363</v>
       </c>
       <c r="CS29" t="n">
-        <v>16.20762859948123</v>
+        <v>16.20762860563484</v>
       </c>
       <c r="CT29" t="n">
         <v>69.18887812396798</v>
@@ -25585,7 +25585,7 @@
         <v>36.62717723722163</v>
       </c>
       <c r="CR30" t="n">
-        <v>9.051566069197181</v>
+        <v>8.83808573737649</v>
       </c>
       <c r="CS30" t="n">
         <v>23.75254966096238</v>
@@ -25640,7 +25640,7 @@
         <v>-2.052790906142299</v>
       </c>
       <c r="DO30" t="n">
-        <v>-2.906980854295338</v>
+        <v>-4.022991498185347</v>
       </c>
       <c r="DP30" t="b">
         <v>0</v>
@@ -25905,10 +25905,10 @@
         <v>1</v>
       </c>
       <c r="CM31" t="n">
-        <v>38.13263668885346</v>
+        <v>38.13263672211311</v>
       </c>
       <c r="CN31" t="n">
-        <v>55.52111901897064</v>
+        <v>55.52111906739669</v>
       </c>
       <c r="CO31" t="n">
         <v>49.21407329373137</v>
@@ -25925,13 +25925,13 @@
       </c>
       <c r="CT31" t="inlineStr"/>
       <c r="CU31" t="n">
-        <v>50.5929984963433</v>
+        <v>50.59299851676472</v>
       </c>
       <c r="CV31" t="n">
-        <v>52.36759615635101</v>
+        <v>52.36759618056404</v>
       </c>
       <c r="CW31" t="n">
-        <v>47.13083654071591</v>
+        <v>47.13083656250763</v>
       </c>
       <c r="CX31" t="n">
         <v>4</v>
@@ -25943,10 +25943,10 @@
         <v>1.6</v>
       </c>
       <c r="DA31" t="n">
-        <v>13.05070303005771</v>
+        <v>13.05070308232856</v>
       </c>
       <c r="DB31" t="n">
-        <v>21.3552414557542</v>
+        <v>21.3552415047382</v>
       </c>
       <c r="DC31" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>-0.239297168287933</v>
       </c>
       <c r="DO31" t="n">
-        <v>-1.044392191433507</v>
+        <v>-3.00139816022954</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -26270,10 +26270,10 @@
         <v>0</v>
       </c>
       <c r="CM32" t="n">
-        <v>8.042725692874045</v>
+        <v>8.042725668300724</v>
       </c>
       <c r="CN32" t="n">
-        <v>14.91925616028136</v>
+        <v>14.91925611469784</v>
       </c>
       <c r="CO32" t="n">
         <v>35.8092168347706</v>
@@ -26282,25 +26282,25 @@
         <v>28.26533205663885</v>
       </c>
       <c r="CQ32" t="n">
-        <v>42.37839881633204</v>
+        <v>42.37839885629169</v>
       </c>
       <c r="CR32" t="n">
-        <v>26.26934027562648</v>
+        <v>26.2693402817547</v>
       </c>
       <c r="CS32" t="n">
-        <v>27.55520349529375</v>
+        <v>27.55520353966727</v>
       </c>
       <c r="CT32" t="n">
         <v>25.97235352964724</v>
       </c>
       <c r="CU32" t="n">
-        <v>28.73844302408433</v>
+        <v>28.73844303049546</v>
       </c>
       <c r="CV32" t="n">
-        <v>27.55520349529375</v>
+        <v>27.55520353966727</v>
       </c>
       <c r="CW32" t="n">
-        <v>24.79968314576438</v>
+        <v>24.79968318570054</v>
       </c>
       <c r="CX32" t="n">
         <v>7</v>
@@ -26312,10 +26312,10 @@
         <v>5.3</v>
       </c>
       <c r="DA32" t="n">
-        <v>-18.28770071151008</v>
+        <v>-18.28770057992469</v>
       </c>
       <c r="DB32" t="n">
-        <v>-5.309908853804624</v>
+        <v>-5.309908832680643</v>
       </c>
       <c r="DC32" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>3.126062068481006</v>
       </c>
       <c r="DO32" t="n">
-        <v>-13.9694512434398</v>
+        <v>-13.96944189921097</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -26647,10 +26647,10 @@
         <v>0</v>
       </c>
       <c r="CM33" t="n">
-        <v>3.282331942632095</v>
+        <v>3.282331949433095</v>
       </c>
       <c r="CN33" t="n">
-        <v>6.088725753582535</v>
+        <v>6.088725766198391</v>
       </c>
       <c r="CO33" t="n">
         <v>32.87073625430369</v>
@@ -26659,13 +26659,13 @@
         <v>27.40079604823567</v>
       </c>
       <c r="CQ33" t="n">
-        <v>42.09062502875422</v>
+        <v>42.09062502138559</v>
       </c>
       <c r="CR33" t="n">
-        <v>10.8526242958474</v>
+        <v>10.85262429518091</v>
       </c>
       <c r="CS33" t="n">
-        <v>30.00489852392306</v>
+        <v>30.00489851291088</v>
       </c>
       <c r="CT33" t="n">
         <v>15.129152615152</v>
@@ -27006,10 +27006,10 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>13.14701705493896</v>
+        <v>13.14701705110638</v>
       </c>
       <c r="CN34" t="n">
-        <v>24.38771663691178</v>
+        <v>24.38771662980233</v>
       </c>
       <c r="CO34" t="n">
         <v>59.63676767704965</v>
@@ -27018,13 +27018,13 @@
         <v>49.91430890839086</v>
       </c>
       <c r="CQ34" t="n">
-        <v>81.2695875466511</v>
+        <v>81.26958754691829</v>
       </c>
       <c r="CR34" t="n">
-        <v>33.53978665180114</v>
+        <v>33.53978665246012</v>
       </c>
       <c r="CS34" t="n">
-        <v>42.55803032161366</v>
+        <v>42.55803032777216</v>
       </c>
       <c r="CT34" t="n">
         <v>5.692431800859927</v>
@@ -27381,10 +27381,10 @@
         <v>0</v>
       </c>
       <c r="CM35" t="n">
-        <v>7.969295189440922</v>
+        <v>7.969295202639334</v>
       </c>
       <c r="CN35" t="n">
-        <v>14.78304257641291</v>
+        <v>14.78304260089596</v>
       </c>
       <c r="CO35" t="n">
         <v>62.5653070010496</v>
@@ -27393,7 +27393,7 @@
         <v>36.50745516551758</v>
       </c>
       <c r="CQ35" t="n">
-        <v>86.49861188629836</v>
+        <v>86.49861191225031</v>
       </c>
       <c r="CR35" t="n">
         <v>22.51480113099953</v>
@@ -27736,10 +27736,10 @@
         <v>0</v>
       </c>
       <c r="CM36" t="n">
-        <v>3.195182294719609</v>
+        <v>3.195182292349107</v>
       </c>
       <c r="CN36" t="n">
-        <v>5.927063156704874</v>
+        <v>5.927063152307593</v>
       </c>
       <c r="CO36" t="n">
         <v>3.991172536103332</v>
@@ -27748,10 +27748,10 @@
         <v>7.379439294118062</v>
       </c>
       <c r="CQ36" t="n">
-        <v>5.414017017058142</v>
+        <v>5.414017015611454</v>
       </c>
       <c r="CR36" t="n">
-        <v>1.754303359441048</v>
+        <v>1.816957050849657</v>
       </c>
       <c r="CS36" t="n">
         <v>2.982083630748904</v>
@@ -27760,13 +27760,13 @@
         <v>9.959526148434405</v>
       </c>
       <c r="CU36" t="n">
-        <v>5.54978343969819</v>
+        <v>5.549783438524694</v>
       </c>
       <c r="CV36" t="n">
-        <v>5.414017017058142</v>
+        <v>5.414017015611454</v>
       </c>
       <c r="CW36" t="n">
-        <v>4.872615315352328</v>
+        <v>4.872615314050308</v>
       </c>
       <c r="CX36" t="n">
         <v>7</v>
@@ -27775,13 +27775,13 @@
         <v>1</v>
       </c>
       <c r="CZ36" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="DA36" t="n">
-        <v>-29.48458143342522</v>
+        <v>-29.48458145226775</v>
       </c>
       <c r="DB36" t="n">
-        <v>-19.68475307887799</v>
+        <v>-19.68475309586058</v>
       </c>
       <c r="DC36" t="inlineStr">
         <is>
@@ -28091,35 +28091,35 @@
         <v>1</v>
       </c>
       <c r="CM37" t="n">
-        <v>17.82992267775515</v>
+        <v>17.82992264158821</v>
       </c>
       <c r="CN37" t="n">
-        <v>29.42177614165288</v>
+        <v>29.42177614707935</v>
       </c>
       <c r="CO37" t="n">
-        <v>46.107254253965</v>
+        <v>46.10725435599473</v>
       </c>
       <c r="CP37" t="n">
         <v>49.56338817261216</v>
       </c>
       <c r="CQ37" t="n">
-        <v>59.19955305859294</v>
+        <v>59.19955304999518</v>
       </c>
       <c r="CR37" t="n">
-        <v>45.4807162369368</v>
+        <v>45.48071624480776</v>
       </c>
       <c r="CS37" t="n">
-        <v>22.95208725221064</v>
+        <v>22.95208729692744</v>
       </c>
       <c r="CT37" t="inlineStr"/>
       <c r="CU37" t="n">
-        <v>34.70991732757746</v>
+        <v>34.70991734736751</v>
       </c>
       <c r="CV37" t="n">
-        <v>37.45124618929484</v>
+        <v>37.45124619594355</v>
       </c>
       <c r="CW37" t="n">
-        <v>33.70612157036536</v>
+        <v>33.7061215763492</v>
       </c>
       <c r="CX37" t="n">
         <v>4</v>
@@ -28131,10 +28131,10 @@
         <v>2.6</v>
       </c>
       <c r="DA37" t="n">
-        <v>35.69292014216745</v>
+        <v>35.69292016625698</v>
       </c>
       <c r="DB37" t="n">
-        <v>39.73396583880977</v>
+        <v>39.73396591847986</v>
       </c>
       <c r="DC37" t="inlineStr">
         <is>
@@ -28462,10 +28462,10 @@
         <v>1</v>
       </c>
       <c r="CM38" t="n">
-        <v>3.454280447251831</v>
+        <v>3.454280456708807</v>
       </c>
       <c r="CN38" t="n">
-        <v>6.407690229652147</v>
+        <v>6.407690247194836</v>
       </c>
       <c r="CO38" t="n">
         <v>32.60530006759157</v>
@@ -28474,7 +28474,7 @@
         <v>22.82658483654052</v>
       </c>
       <c r="CQ38" t="n">
-        <v>40.32932308720063</v>
+        <v>40.32932309655735</v>
       </c>
       <c r="CR38" t="n">
         <v>10.59424454785779</v>
@@ -28536,7 +28536,7 @@
         <v>-1.777153891556071</v>
       </c>
       <c r="DO38" t="n">
-        <v>-26.9772502415444</v>
+        <v>-26.97724421931233</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -28821,10 +28821,10 @@
         <v>0</v>
       </c>
       <c r="CM39" t="n">
-        <v>16.09429141767125</v>
+        <v>16.09429141897903</v>
       </c>
       <c r="CN39" t="n">
-        <v>29.85491057978017</v>
+        <v>29.8549105822061</v>
       </c>
       <c r="CO39" t="n">
         <v>19.95366741986068</v>
@@ -28833,7 +28833,7 @@
         <v>36.76842331976568</v>
       </c>
       <c r="CQ39" t="n">
-        <v>26.87383632506486</v>
+        <v>26.87383632584132</v>
       </c>
       <c r="CR39" t="n">
         <v>15.03391666666667</v>
@@ -28845,7 +28845,7 @@
         <v>81.2268791476879</v>
       </c>
       <c r="CU39" t="n">
-        <v>22.78397480715196</v>
+        <v>22.78397480779627</v>
       </c>
       <c r="CV39" t="n">
         <v>19.95366741986068</v>
@@ -28866,7 +28866,7 @@
         <v>-49.42748091603054</v>
       </c>
       <c r="DB39" t="n">
-        <v>-35.83786008422367</v>
+        <v>-35.83786008240924</v>
       </c>
       <c r="DC39" t="inlineStr">
         <is>
@@ -29166,35 +29166,35 @@
         <v>1</v>
       </c>
       <c r="CM40" t="n">
-        <v>9.776498548817115</v>
+        <v>9.776498615230746</v>
       </c>
       <c r="CN40" t="n">
-        <v>17.80202359127176</v>
+        <v>17.80202357989377</v>
       </c>
       <c r="CO40" t="n">
-        <v>30.4195084706888</v>
+        <v>30.41950824460092</v>
       </c>
       <c r="CP40" t="n">
         <v>29.46192052472633</v>
       </c>
       <c r="CQ40" t="n">
-        <v>34.13596352020357</v>
+        <v>34.13596352759888</v>
       </c>
       <c r="CR40" t="n">
-        <v>25.40854575380762</v>
+        <v>25.52456649713004</v>
       </c>
       <c r="CS40" t="n">
-        <v>14.86407026428921</v>
+        <v>14.86407018170784</v>
       </c>
       <c r="CT40" t="inlineStr"/>
       <c r="CU40" t="n">
-        <v>20.85164409114633</v>
+        <v>20.88064923421387</v>
       </c>
       <c r="CV40" t="n">
-        <v>21.60528467253969</v>
+        <v>21.66329503851191</v>
       </c>
       <c r="CW40" t="n">
-        <v>19.44475620528572</v>
+        <v>19.49696553466072</v>
       </c>
       <c r="CX40" t="n">
         <v>4</v>
@@ -29206,10 +29206,10 @@
         <v>3.1</v>
       </c>
       <c r="DA40" t="n">
-        <v>24.08906260761505</v>
+        <v>24.42224275516323</v>
       </c>
       <c r="DB40" t="n">
-        <v>33.06728774488859</v>
+        <v>33.25238757211466</v>
       </c>
       <c r="DC40" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>0.5131489603787731</v>
       </c>
       <c r="DO40" t="n">
-        <v>-13.75743191410359</v>
+        <v>-13.75742256022964</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -29886,10 +29886,10 @@
         <v>0</v>
       </c>
       <c r="CM42" t="n">
-        <v>1.614287383142542</v>
+        <v>1.614287380435111</v>
       </c>
       <c r="CN42" t="n">
-        <v>2.994503095729415</v>
+        <v>2.994503090707131</v>
       </c>
       <c r="CO42" t="n">
         <v>12.71611758640834</v>
@@ -29898,7 +29898,7 @@
         <v>9.286655171963359</v>
       </c>
       <c r="CQ42" t="n">
-        <v>16.05128418212758</v>
+        <v>16.05128417935073</v>
       </c>
       <c r="CR42" t="n">
         <v>6.104046666666666</v>
@@ -29956,7 +29956,7 @@
         <v>-3.034787864293342</v>
       </c>
       <c r="DO42" t="n">
-        <v>-27.93431471010997</v>
+        <v>-27.93430711557779</v>
       </c>
       <c r="DP42" t="b">
         <v>0</v>
@@ -30229,35 +30229,35 @@
         <v>1</v>
       </c>
       <c r="CM43" t="n">
-        <v>9.277652160030563</v>
+        <v>9.277652092641643</v>
       </c>
       <c r="CN43" t="n">
-        <v>13.27564817199024</v>
+        <v>13.27564823727591</v>
       </c>
       <c r="CO43" t="n">
-        <v>16.56076849138475</v>
+        <v>16.56076869311605</v>
       </c>
       <c r="CP43" t="n">
         <v>17.47664780944146</v>
       </c>
       <c r="CQ43" t="n">
-        <v>21.53940887428282</v>
+        <v>21.53940894567846</v>
       </c>
       <c r="CR43" t="n">
-        <v>17.16868986752019</v>
+        <v>17.16868988615829</v>
       </c>
       <c r="CS43" t="n">
-        <v>8.239775043451273</v>
+        <v>8.239775158260425</v>
       </c>
       <c r="CT43" t="inlineStr"/>
       <c r="CU43" t="n">
-        <v>14.07068967273144</v>
+        <v>14.07068972729797</v>
       </c>
       <c r="CV43" t="n">
-        <v>14.9182083316875</v>
+        <v>14.91820846519598</v>
       </c>
       <c r="CW43" t="n">
-        <v>13.42638749851875</v>
+        <v>13.42638761867638</v>
       </c>
       <c r="CX43" t="n">
         <v>4</v>
@@ -30269,10 +30269,10 @@
         <v>1.9</v>
       </c>
       <c r="DA43" t="n">
-        <v>-2.282476548934431</v>
+        <v>-2.282475674424711</v>
       </c>
       <c r="DB43" t="n">
-        <v>2.406767882983463</v>
+        <v>2.406768280119831</v>
       </c>
       <c r="DC43" t="inlineStr">
         <is>
@@ -30600,37 +30600,37 @@
         <v>0</v>
       </c>
       <c r="CM44" t="n">
-        <v>17.67458159617798</v>
+        <v>17.67458143755837</v>
       </c>
       <c r="CN44" t="n">
-        <v>28.38448060874346</v>
+        <v>28.38448059186818</v>
       </c>
       <c r="CO44" t="n">
-        <v>45.95076147675917</v>
+        <v>45.95076186182303</v>
       </c>
       <c r="CP44" t="n">
         <v>53.20634261756088</v>
       </c>
       <c r="CQ44" t="n">
-        <v>55.32499944818458</v>
+        <v>55.32499940859542</v>
       </c>
       <c r="CR44" t="n">
-        <v>42.93273386196931</v>
+        <v>42.93273389081794</v>
       </c>
       <c r="CS44" t="n">
-        <v>22.93541916167177</v>
+        <v>22.93541933908462</v>
       </c>
       <c r="CT44" t="n">
         <v>32.58624815427083</v>
       </c>
       <c r="CU44" t="n">
-        <v>37.37444586566725</v>
+        <v>37.37444591269741</v>
       </c>
       <c r="CV44" t="n">
-        <v>37.75949100812007</v>
+        <v>37.75949102254438</v>
       </c>
       <c r="CW44" t="n">
-        <v>33.98354190730807</v>
+        <v>33.98354192028994</v>
       </c>
       <c r="CX44" t="n">
         <v>8</v>
@@ -30642,10 +30642,10 @@
         <v>3.1</v>
       </c>
       <c r="DA44" t="n">
-        <v>22.95058848675435</v>
+        <v>22.95058853372207</v>
       </c>
       <c r="DB44" t="n">
-        <v>35.2186928038229</v>
+        <v>35.21869297397546</v>
       </c>
       <c r="DC44" t="inlineStr">
         <is>
@@ -30959,10 +30959,10 @@
         <v>1</v>
       </c>
       <c r="CM45" t="n">
-        <v>21.46693980023627</v>
+        <v>21.46693990747076</v>
       </c>
       <c r="CN45" t="n">
-        <v>39.82117332943828</v>
+        <v>39.82117352835825</v>
       </c>
       <c r="CO45" t="n">
         <v>55.9919330381578</v>
@@ -30971,23 +30971,23 @@
         <v>42.27700822726509</v>
       </c>
       <c r="CQ45" t="n">
-        <v>57.6948432981931</v>
+        <v>57.69484311249409</v>
       </c>
       <c r="CR45" t="n">
-        <v>44.75889535946022</v>
+        <v>45.2917393179109</v>
       </c>
       <c r="CS45" t="n">
-        <v>28.51101662362118</v>
+        <v>28.51101641176873</v>
       </c>
       <c r="CT45" t="inlineStr"/>
       <c r="CU45" t="n">
-        <v>40.50973538182314</v>
+        <v>40.64294644797442</v>
       </c>
       <c r="CV45" t="n">
-        <v>42.29003434444925</v>
+        <v>42.55645642313458</v>
       </c>
       <c r="CW45" t="n">
-        <v>38.06103091000433</v>
+        <v>38.30081078082112</v>
       </c>
       <c r="CX45" t="n">
         <v>4</v>
@@ -30999,10 +30999,10 @@
         <v>2.6</v>
       </c>
       <c r="DA45" t="n">
-        <v>-9.205552069417166</v>
+        <v>-8.633558077789505</v>
       </c>
       <c r="DB45" t="n">
-        <v>-3.364176642943906</v>
+        <v>-3.0464021391989</v>
       </c>
       <c r="DC45" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>1.231582524541053</v>
       </c>
       <c r="DO45" t="n">
-        <v>-13.88060552690588</v>
+        <v>-13.88059194684089</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -31334,10 +31334,10 @@
         <v>1</v>
       </c>
       <c r="CM46" t="n">
-        <v>7.897647825800325</v>
+        <v>7.897647775668966</v>
       </c>
       <c r="CN46" t="n">
-        <v>14.6501367168596</v>
+        <v>14.65013662386593</v>
       </c>
       <c r="CO46" t="n">
         <v>5.689554995371402</v>
@@ -31358,7 +31358,7 @@
         <v>5.468016983754021</v>
       </c>
       <c r="CU46" t="n">
-        <v>7.691147604628489</v>
+        <v>7.691147586737859</v>
       </c>
       <c r="CV46" t="n">
         <v>5.911444164352368</v>
@@ -31379,7 +31379,7 @@
         <v>-20.11561757040502</v>
       </c>
       <c r="DB46" t="n">
-        <v>15.48269941202858</v>
+        <v>15.4826991434005</v>
       </c>
       <c r="DC46" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>4.06249606516218</v>
       </c>
       <c r="DO46" t="n">
-        <v>3.576983284817814</v>
+        <v>-2.058828520527212</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -31707,37 +31707,37 @@
         <v>1</v>
       </c>
       <c r="CM47" t="n">
-        <v>6.114135551504001</v>
+        <v>6.114135551223865</v>
       </c>
       <c r="CN47" t="n">
-        <v>8.34073842373572</v>
+        <v>8.340738423949674</v>
       </c>
       <c r="CO47" t="n">
-        <v>10.22416123297895</v>
+        <v>10.22416123370966</v>
       </c>
       <c r="CP47" t="n">
         <v>11.61068843321866</v>
       </c>
       <c r="CQ47" t="n">
-        <v>9.255439677680009</v>
+        <v>9.255439678140526</v>
       </c>
       <c r="CR47" t="n">
-        <v>14.83896367844126</v>
+        <v>14.83896367853997</v>
       </c>
       <c r="CS47" t="n">
-        <v>5.038565262754045</v>
+        <v>5.03856526320764</v>
       </c>
       <c r="CT47" t="n">
         <v>11.35371417455445</v>
       </c>
       <c r="CU47" t="n">
-        <v>9.597050804358386</v>
+        <v>9.597050804568056</v>
       </c>
       <c r="CV47" t="n">
-        <v>9.739800455329476</v>
+        <v>9.739800455925092</v>
       </c>
       <c r="CW47" t="n">
-        <v>8.765820409796529</v>
+        <v>8.765820410332584</v>
       </c>
       <c r="CX47" t="n">
         <v>8</v>
@@ -31749,10 +31749,10 @@
         <v>2.9</v>
       </c>
       <c r="DA47" t="n">
-        <v>-44.37931292835736</v>
+        <v>-44.379312924956</v>
       </c>
       <c r="DB47" t="n">
-        <v>-39.10500847093395</v>
+        <v>-39.10500846960354</v>
       </c>
       <c r="DC47" t="inlineStr">
         <is>
@@ -32076,10 +32076,10 @@
         <v>0</v>
       </c>
       <c r="CM48" t="n">
-        <v>2.590450526884343</v>
+        <v>2.590450538467818</v>
       </c>
       <c r="CN48" t="n">
-        <v>4.805285727370455</v>
+        <v>4.805285748857802</v>
       </c>
       <c r="CO48" t="n">
         <v>13.29197465681098</v>
@@ -32088,25 +32088,25 @@
         <v>15.02374045273446</v>
       </c>
       <c r="CQ48" t="n">
-        <v>10.24745785689306</v>
+        <v>10.24745785776823</v>
       </c>
       <c r="CR48" t="n">
-        <v>7.299560394763578</v>
+        <v>7.299560393652292</v>
       </c>
       <c r="CS48" t="n">
-        <v>6.71397377470123</v>
+        <v>6.713973764487386</v>
       </c>
       <c r="CT48" t="n">
         <v>10.63504853252629</v>
       </c>
       <c r="CU48" t="n">
-        <v>9.716720199400006</v>
+        <v>9.716720200976777</v>
       </c>
       <c r="CV48" t="n">
-        <v>10.24745785689306</v>
+        <v>10.24745785776823</v>
       </c>
       <c r="CW48" t="n">
-        <v>9.222712071203755</v>
+        <v>9.222712071991404</v>
       </c>
       <c r="CX48" t="n">
         <v>7</v>
@@ -32118,10 +32118,10 @@
         <v>5.8</v>
       </c>
       <c r="DA48" t="n">
-        <v>-2.918820303118363</v>
+        <v>-2.918820294827318</v>
       </c>
       <c r="DB48" t="n">
-        <v>2.28126525684218</v>
+        <v>2.281265273439748</v>
       </c>
       <c r="DC48" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>-1.758015252871625</v>
       </c>
       <c r="DO48" t="n">
-        <v>-33.48766084780972</v>
+        <v>-33.48766547717843</v>
       </c>
       <c r="DP48" t="b">
         <v>0</v>
@@ -32439,10 +32439,10 @@
         <v>0</v>
       </c>
       <c r="CM49" t="n">
-        <v>7.861807093574793</v>
+        <v>7.861807159285413</v>
       </c>
       <c r="CN49" t="n">
-        <v>11.4467911282449</v>
+        <v>11.44679122391956</v>
       </c>
       <c r="CO49" t="n">
         <v>8.08480553688795</v>
@@ -32461,7 +32461,7 @@
         <v>5.466181493173686</v>
       </c>
       <c r="CU49" t="n">
-        <v>8.423033985922972</v>
+        <v>8.423034012820519</v>
       </c>
       <c r="CV49" t="n">
         <v>8.443472131649713</v>
@@ -32482,7 +32482,7 @@
         <v>15.13825800438093</v>
       </c>
       <c r="DB49" t="n">
-        <v>27.62172890352328</v>
+        <v>27.62172931106188</v>
       </c>
       <c r="DC49" t="inlineStr">
         <is>
@@ -32810,37 +32810,37 @@
         <v>0</v>
       </c>
       <c r="CM50" t="n">
-        <v>33.11882880409752</v>
+        <v>33.11882886960528</v>
       </c>
       <c r="CN50" t="n">
-        <v>34.05828924298923</v>
+        <v>34.05828919941593</v>
       </c>
       <c r="CO50" t="n">
-        <v>34.64295544463105</v>
+        <v>34.64295533178732</v>
       </c>
       <c r="CP50" t="n">
         <v>49.91001401454295</v>
       </c>
       <c r="CQ50" t="n">
-        <v>54.23229194888883</v>
+        <v>54.23229186828175</v>
       </c>
       <c r="CR50" t="n">
-        <v>17.39224951718627</v>
+        <v>17.72671584713629</v>
       </c>
       <c r="CS50" t="n">
-        <v>13.60670822940412</v>
+        <v>13.6067081133034</v>
       </c>
       <c r="CT50" t="n">
         <v>30.48327237497478</v>
       </c>
       <c r="CU50" t="n">
-        <v>33.43057619708934</v>
+        <v>33.47238445238096</v>
       </c>
       <c r="CV50" t="n">
-        <v>33.58855902354338</v>
+        <v>33.58855903451061</v>
       </c>
       <c r="CW50" t="n">
-        <v>30.22970312118904</v>
+        <v>30.22970313105955</v>
       </c>
       <c r="CX50" t="n">
         <v>8</v>
@@ -32852,10 +32852,10 @@
         <v>4</v>
       </c>
       <c r="DA50" t="n">
-        <v>-27.24499716903571</v>
+        <v>-27.24499714527998</v>
       </c>
       <c r="DB50" t="n">
-        <v>-19.54133138161186</v>
+        <v>-19.44070982671583</v>
       </c>
       <c r="DC50" t="inlineStr">
         <is>
@@ -33187,10 +33187,10 @@
         <v>0</v>
       </c>
       <c r="CM51" t="n">
-        <v>5.386293093495071</v>
+        <v>5.386293084721254</v>
       </c>
       <c r="CN51" t="n">
-        <v>9.991573688433357</v>
+        <v>9.991573672157925</v>
       </c>
       <c r="CO51" t="n">
         <v>25.37030346820809</v>
@@ -33199,25 +33199,25 @@
         <v>28.55650608967326</v>
       </c>
       <c r="CQ51" t="n">
-        <v>22.67781209635897</v>
+        <v>22.67781209107606</v>
       </c>
       <c r="CR51" t="n">
-        <v>14.10274633882044</v>
+        <v>14.18873869541528</v>
       </c>
       <c r="CS51" t="n">
-        <v>12.52009430533942</v>
+        <v>12.52009431317619</v>
       </c>
       <c r="CT51" t="n">
         <v>4.937022761450113</v>
       </c>
       <c r="CU51" t="n">
-        <v>16.94361844004694</v>
+        <v>16.95590305920401</v>
       </c>
       <c r="CV51" t="n">
-        <v>14.10274633882044</v>
+        <v>14.18873869541528</v>
       </c>
       <c r="CW51" t="n">
-        <v>12.69247170493839</v>
+        <v>12.76986482587376</v>
       </c>
       <c r="CX51" t="n">
         <v>7</v>
@@ -33229,10 +33229,10 @@
         <v>5.8</v>
       </c>
       <c r="DA51" t="n">
-        <v>-4.207760717446085</v>
+        <v>-3.623661691518831</v>
       </c>
       <c r="DB51" t="n">
-        <v>27.87636558525994</v>
+        <v>27.96907969210572</v>
       </c>
       <c r="DC51" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>0</v>
       </c>
       <c r="CM52" t="n">
-        <v>11.37352796015599</v>
+        <v>11.37352796846464</v>
       </c>
       <c r="CN52" t="n">
-        <v>21.09789436608936</v>
+        <v>21.0978943815019</v>
       </c>
       <c r="CO52" t="n">
         <v>55.71325580079352</v>
@@ -33564,19 +33564,19 @@
         <v>52.70332650902633</v>
       </c>
       <c r="CQ52" t="n">
-        <v>57.57115634929421</v>
+        <v>57.57115634718044</v>
       </c>
       <c r="CR52" t="n">
-        <v>28.90928458493641</v>
+        <v>28.90928460499965</v>
       </c>
       <c r="CS52" t="n">
-        <v>34.84658794794007</v>
+        <v>34.84658793742596</v>
       </c>
       <c r="CT52" t="n">
         <v>57.18228375268124</v>
       </c>
       <c r="CU52" t="n">
-        <v>44.00339847296588</v>
+        <v>44.00339847622986</v>
       </c>
       <c r="CV52" t="n">
         <v>52.70332650902633</v>
@@ -33597,7 +33597,7 @@
         <v>41.71793285978029</v>
       </c>
       <c r="DB52" t="n">
-        <v>31.4711588529828</v>
+        <v>31.47115886273473</v>
       </c>
       <c r="DC52" t="inlineStr">
         <is>
@@ -33899,35 +33899,35 @@
         <v>1</v>
       </c>
       <c r="CM53" t="n">
-        <v>10.62685337831266</v>
+        <v>10.62685331697454</v>
       </c>
       <c r="CN53" t="n">
-        <v>17.64942994959144</v>
+        <v>17.64942995979905</v>
       </c>
       <c r="CO53" t="n">
-        <v>27.73251600690513</v>
+        <v>27.73251618301623</v>
       </c>
       <c r="CP53" t="n">
         <v>29.43493108570705</v>
       </c>
       <c r="CQ53" t="n">
-        <v>31.55991137143432</v>
+        <v>31.5599113799306</v>
       </c>
       <c r="CR53" t="n">
-        <v>27.78221465689651</v>
+        <v>27.90907409833193</v>
       </c>
       <c r="CS53" t="n">
-        <v>13.79408525206323</v>
+        <v>13.79408532833351</v>
       </c>
       <c r="CT53" t="inlineStr"/>
       <c r="CU53" t="n">
-        <v>20.94775349792643</v>
+        <v>20.97946838953044</v>
       </c>
       <c r="CV53" t="n">
-        <v>22.69097297824829</v>
+        <v>22.69097307140764</v>
       </c>
       <c r="CW53" t="n">
-        <v>20.42187568042346</v>
+        <v>20.42187576426688</v>
       </c>
       <c r="CX53" t="n">
         <v>4</v>
@@ -33939,10 +33939,10 @@
         <v>2.6</v>
       </c>
       <c r="DA53" t="n">
-        <v>14.79412383053324</v>
+        <v>14.79412430182843</v>
       </c>
       <c r="DB53" t="n">
-        <v>17.75015413092511</v>
+        <v>17.92842782385293</v>
       </c>
       <c r="DC53" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>0.2253572705765761</v>
       </c>
       <c r="DO53" t="n">
-        <v>-16.14745557185274</v>
+        <v>-16.147447880327</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -34250,35 +34250,35 @@
         <v>0</v>
       </c>
       <c r="CM54" t="n">
-        <v>27.14751956164674</v>
+        <v>27.14751970996743</v>
       </c>
       <c r="CN54" t="n">
-        <v>33.13500175059818</v>
+        <v>33.1350015844693</v>
       </c>
       <c r="CO54" t="n">
-        <v>36.86133017151097</v>
+        <v>36.86132978530724</v>
       </c>
       <c r="CP54" t="n">
         <v>42.33938507434554</v>
       </c>
       <c r="CQ54" t="n">
-        <v>44.68926978659407</v>
+        <v>44.68926951215713</v>
       </c>
       <c r="CR54" t="n">
-        <v>43.05815821043025</v>
+        <v>43.87831355760955</v>
       </c>
       <c r="CS54" t="n">
-        <v>17.32645951713102</v>
+        <v>17.32645922410868</v>
       </c>
       <c r="CT54" t="inlineStr"/>
       <c r="CU54" t="n">
-        <v>35.05050242354653</v>
+        <v>35.25554115933838</v>
       </c>
       <c r="CV54" t="n">
-        <v>34.99816596105457</v>
+        <v>34.99816568488827</v>
       </c>
       <c r="CW54" t="n">
-        <v>31.49834936494912</v>
+        <v>31.49834911639945</v>
       </c>
       <c r="CX54" t="n">
         <v>4</v>
@@ -34290,10 +34290,10 @@
         <v>1.6</v>
       </c>
       <c r="DA54" t="n">
-        <v>-31.21129343706115</v>
+        <v>-31.21129397986453</v>
       </c>
       <c r="DB54" t="n">
-        <v>-23.45380711346319</v>
+        <v>-23.00602652448679</v>
       </c>
       <c r="DC54" t="inlineStr">
         <is>
@@ -34621,10 +34621,10 @@
         <v>0</v>
       </c>
       <c r="CM55" t="n">
-        <v>15.96156250809131</v>
+        <v>15.96156238267994</v>
       </c>
       <c r="CN55" t="n">
-        <v>29.60869845250937</v>
+        <v>29.60869821987128</v>
       </c>
       <c r="CO55" t="n">
         <v>55.8955933463928</v>
@@ -34633,25 +34633,25 @@
         <v>43.14492745892942</v>
       </c>
       <c r="CQ55" t="n">
-        <v>68.20208790766242</v>
+        <v>68.20208808408729</v>
       </c>
       <c r="CR55" t="n">
-        <v>38.13201687328891</v>
+        <v>38.1320169042643</v>
       </c>
       <c r="CS55" t="n">
-        <v>38.06826123087426</v>
+        <v>38.0682614680422</v>
       </c>
       <c r="CT55" t="n">
         <v>22.28433325274179</v>
       </c>
       <c r="CU55" t="n">
-        <v>38.91218512881129</v>
+        <v>38.91218513962613</v>
       </c>
       <c r="CV55" t="n">
-        <v>38.10013905208159</v>
+        <v>38.10013918615326</v>
       </c>
       <c r="CW55" t="n">
-        <v>34.29012514687343</v>
+        <v>34.29012526753793</v>
       </c>
       <c r="CX55" t="n">
         <v>8</v>
@@ -34663,10 +34663,10 @@
         <v>4.3</v>
       </c>
       <c r="DA55" t="n">
-        <v>-6.997216869405143</v>
+        <v>-6.997216542134987</v>
       </c>
       <c r="DB55" t="n">
-        <v>5.538883254917759</v>
+        <v>5.53888328425014</v>
       </c>
       <c r="DC55" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>1.430537770541807</v>
       </c>
       <c r="DO55" t="n">
-        <v>0.6551948041804367</v>
+        <v>-0.753708162835709</v>
       </c>
       <c r="DP55" t="b">
         <v>0</v>
@@ -34994,10 +34994,10 @@
         <v>0</v>
       </c>
       <c r="CM56" t="n">
-        <v>27.71225737706116</v>
+        <v>27.71225729867693</v>
       </c>
       <c r="CN56" t="n">
-        <v>51.40623743444844</v>
+        <v>51.4062372890457</v>
       </c>
       <c r="CO56" t="n">
         <v>69.02703388345945</v>
@@ -35006,25 +35006,25 @@
         <v>48.07470647599711</v>
       </c>
       <c r="CQ56" t="n">
-        <v>78.40063158340526</v>
+        <v>78.40063175110375</v>
       </c>
       <c r="CR56" t="n">
-        <v>61.78172618496546</v>
+        <v>61.78172621718767</v>
       </c>
       <c r="CS56" t="n">
-        <v>36.01038484387148</v>
+        <v>36.01038502618065</v>
       </c>
       <c r="CT56" t="n">
         <v>80.3272793905405</v>
       </c>
       <c r="CU56" t="n">
-        <v>56.59253214671861</v>
+        <v>56.59253216652397</v>
       </c>
       <c r="CV56" t="n">
-        <v>56.59398180970695</v>
+        <v>56.59398175311668</v>
       </c>
       <c r="CW56" t="n">
-        <v>50.93458362873626</v>
+        <v>50.93458357780501</v>
       </c>
       <c r="CX56" t="n">
         <v>8</v>
@@ -35036,10 +35036,10 @@
         <v>2.9</v>
       </c>
       <c r="DA56" t="n">
-        <v>8.997612085785844</v>
+        <v>8.997611976795383</v>
       </c>
       <c r="DB56" t="n">
-        <v>21.10535566251859</v>
+        <v>21.10535570490111</v>
       </c>
       <c r="DC56" t="inlineStr">
         <is>
@@ -35371,37 +35371,37 @@
         <v>0</v>
       </c>
       <c r="CM57" t="n">
-        <v>8.751143342402919</v>
+        <v>8.751143371553811</v>
       </c>
       <c r="CN57" t="n">
-        <v>11.64085681335524</v>
+        <v>11.64085682009164</v>
       </c>
       <c r="CO57" t="n">
-        <v>16.15113541352812</v>
+        <v>16.1511353690736</v>
       </c>
       <c r="CP57" t="n">
         <v>23.9940157354355</v>
       </c>
       <c r="CQ57" t="n">
-        <v>23.54948248923467</v>
+        <v>23.54948250392199</v>
       </c>
       <c r="CR57" t="n">
-        <v>20.91483982539174</v>
+        <v>20.91483981991003</v>
       </c>
       <c r="CS57" t="n">
-        <v>7.900760724524837</v>
+        <v>7.900760695639799</v>
       </c>
       <c r="CT57" t="n">
         <v>10.33126260605547</v>
       </c>
       <c r="CU57" t="n">
-        <v>15.40418711874106</v>
+        <v>15.40418711521023</v>
       </c>
       <c r="CV57" t="n">
-        <v>13.89599611344168</v>
+        <v>13.89599609458262</v>
       </c>
       <c r="CW57" t="n">
-        <v>12.50639650209751</v>
+        <v>12.50639648512436</v>
       </c>
       <c r="CX57" t="n">
         <v>8</v>
@@ -35413,10 +35413,10 @@
         <v>3</v>
       </c>
       <c r="DA57" t="n">
-        <v>9.321651755501925</v>
+        <v>9.321651607135163</v>
       </c>
       <c r="DB57" t="n">
-        <v>34.65199024268617</v>
+        <v>34.65199021182226</v>
       </c>
       <c r="DC57" t="inlineStr">
         <is>
@@ -35718,10 +35718,10 @@
         <v>0</v>
       </c>
       <c r="CM58" t="n">
-        <v>11.49820300028505</v>
+        <v>11.4982029728858</v>
       </c>
       <c r="CN58" t="n">
-        <v>21.32916656552876</v>
+        <v>21.32916651470316</v>
       </c>
       <c r="CO58" t="n">
         <v>61.99144933938789</v>
@@ -35730,7 +35730,7 @@
         <v>46.3637511199616</v>
       </c>
       <c r="CQ58" t="n">
-        <v>82.98527148793602</v>
+        <v>82.98527145741976</v>
       </c>
       <c r="CR58" t="n">
         <v>11.76833333333333</v>
@@ -35740,7 +35740,7 @@
       </c>
       <c r="CT58" t="inlineStr"/>
       <c r="CU58" t="n">
-        <v>14.86523429971571</v>
+        <v>14.86523427364077</v>
       </c>
       <c r="CV58" t="n">
         <v>11.76833333333333</v>
@@ -35761,7 +35761,7 @@
         <v>-81.99030819133732</v>
       </c>
       <c r="DB58" t="n">
-        <v>-74.72328863697857</v>
+        <v>-74.72328868131616</v>
       </c>
       <c r="DC58" t="inlineStr">
         <is>
@@ -36075,10 +36075,10 @@
         <v>0</v>
       </c>
       <c r="CM59" t="n">
-        <v>15.91082428045713</v>
+        <v>15.91082430405249</v>
       </c>
       <c r="CN59" t="n">
-        <v>29.51457904024798</v>
+        <v>29.51457908401737</v>
       </c>
       <c r="CO59" t="n">
         <v>54.72591683531388</v>
@@ -36087,23 +36087,23 @@
         <v>49.38251180555442</v>
       </c>
       <c r="CQ59" t="n">
-        <v>60.07811897656059</v>
+        <v>60.07811896955261</v>
       </c>
       <c r="CR59" t="n">
-        <v>36.56479138755189</v>
+        <v>36.56479138327277</v>
       </c>
       <c r="CS59" t="n">
-        <v>29.7990788230786</v>
+        <v>29.79907879050002</v>
       </c>
       <c r="CT59" t="inlineStr"/>
       <c r="CU59" t="n">
-        <v>34.17902788589272</v>
+        <v>34.17902790166413</v>
       </c>
       <c r="CV59" t="n">
-        <v>33.03968521389994</v>
+        <v>33.03968523364507</v>
       </c>
       <c r="CW59" t="n">
-        <v>29.73571669250994</v>
+        <v>29.73571671028056</v>
       </c>
       <c r="CX59" t="n">
         <v>4</v>
@@ -36115,10 +36115,10 @@
         <v>3.4</v>
       </c>
       <c r="DA59" t="n">
-        <v>-2.31367880811858</v>
+        <v>-2.313678749739423</v>
       </c>
       <c r="DB59" t="n">
-        <v>12.2832696656878</v>
+        <v>12.28326971749924</v>
       </c>
       <c r="DC59" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>1.4328567207472</v>
       </c>
       <c r="DO59" t="n">
-        <v>-16.5091286271213</v>
+        <v>-16.50913757078116</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -36448,10 +36448,10 @@
         <v>0</v>
       </c>
       <c r="CM60" t="n">
-        <v>13.92259633446643</v>
+        <v>13.92259625117415</v>
       </c>
       <c r="CN60" t="n">
-        <v>20.27130026298312</v>
+        <v>20.27130014170956</v>
       </c>
       <c r="CO60" t="n">
         <v>16.70574758244657</v>
@@ -36470,7 +36470,7 @@
         <v>15.45433621078142</v>
       </c>
       <c r="CU60" t="n">
-        <v>16.60794748206458</v>
+        <v>16.60794744797028</v>
       </c>
       <c r="CV60" t="n">
         <v>16.080041896614</v>
@@ -36491,7 +36491,7 @@
         <v>29.44577202071063</v>
       </c>
       <c r="DB60" t="n">
-        <v>48.55051009592491</v>
+        <v>48.55050979096687</v>
       </c>
       <c r="DC60" t="inlineStr">
         <is>
@@ -36821,10 +36821,10 @@
         <v>0</v>
       </c>
       <c r="CM61" t="n">
-        <v>1.11051121586904</v>
+        <v>1.110511219248652</v>
       </c>
       <c r="CN61" t="n">
-        <v>2.05999830543707</v>
+        <v>2.05999831170625</v>
       </c>
       <c r="CO61" t="n">
         <v>9.339207419564895</v>
@@ -36833,13 +36833,13 @@
         <v>8.768824142136653</v>
       </c>
       <c r="CQ61" t="n">
-        <v>10.25990372426347</v>
+        <v>10.2599037243412</v>
       </c>
       <c r="CR61" t="n">
-        <v>4.217375374006328</v>
+        <v>4.217375373637055</v>
       </c>
       <c r="CS61" t="n">
-        <v>6.897005828886923</v>
+        <v>6.89700582456859</v>
       </c>
       <c r="CT61" t="n">
         <v>7.048791965539855</v>
@@ -36891,7 +36891,7 @@
         <v>0.4184096244488567</v>
       </c>
       <c r="DO61" t="n">
-        <v>-33.71841038490954</v>
+        <v>-33.71840595466463</v>
       </c>
       <c r="DP61" t="b">
         <v>0</v>
@@ -37184,10 +37184,10 @@
         <v>0</v>
       </c>
       <c r="CM62" t="n">
-        <v>8.663823172436274</v>
+        <v>8.663823179292404</v>
       </c>
       <c r="CN62" t="n">
-        <v>16.07139198486929</v>
+        <v>16.07139199758741</v>
       </c>
       <c r="CO62" t="n">
         <v>19.74227298786794</v>
@@ -37196,25 +37196,25 @@
         <v>12.2713478206253</v>
       </c>
       <c r="CQ62" t="n">
-        <v>12.65837955249128</v>
+        <v>12.65837952340954</v>
       </c>
       <c r="CR62" t="n">
-        <v>20.4466872949171</v>
+        <v>20.44668729080296</v>
       </c>
       <c r="CS62" t="n">
-        <v>9.755005139996184</v>
+        <v>9.75500511998945</v>
       </c>
       <c r="CT62" t="n">
         <v>13.40282426495203</v>
       </c>
       <c r="CU62" t="n">
-        <v>14.12646652726943</v>
+        <v>14.12646652306588</v>
       </c>
       <c r="CV62" t="n">
-        <v>13.03060190872166</v>
+        <v>13.03060189418079</v>
       </c>
       <c r="CW62" t="n">
-        <v>11.72754171784949</v>
+        <v>11.72754170476271</v>
       </c>
       <c r="CX62" t="n">
         <v>8</v>
@@ -37226,10 +37226,10 @@
         <v>2.4</v>
       </c>
       <c r="DA62" t="n">
-        <v>-77.47302841243064</v>
+        <v>-77.47302843756852</v>
       </c>
       <c r="DB62" t="n">
-        <v>-72.8650285158907</v>
+        <v>-72.86502852396512</v>
       </c>
       <c r="DC62" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>2.399687681041485</v>
       </c>
       <c r="DO62" t="n">
-        <v>-4.099425827904291</v>
+        <v>-4.09943271084231</v>
       </c>
       <c r="DP62" t="b">
         <v>0</v>
@@ -37494,7 +37494,7 @@
         <v>44.3</v>
       </c>
       <c r="BN63" t="n">
-        <v>13.54</v>
+        <v>13.17</v>
       </c>
       <c r="BO63" t="n">
         <v>9.73</v>
@@ -37569,10 +37569,10 @@
         <v>0</v>
       </c>
       <c r="CM63" t="n">
-        <v>12.8634642525334</v>
+        <v>12.86346420342884</v>
       </c>
       <c r="CN63" t="n">
-        <v>23.86172618844947</v>
+        <v>23.8617260973605</v>
       </c>
       <c r="CO63" t="n">
         <v>41.03334835250192</v>
@@ -37581,25 +37581,25 @@
         <v>33.52326806093615</v>
       </c>
       <c r="CQ63" t="n">
-        <v>40.2480882423156</v>
+        <v>40.24808831624426</v>
       </c>
       <c r="CR63" t="n">
-        <v>23.66731486065639</v>
+        <v>23.66731487001607</v>
       </c>
       <c r="CS63" t="n">
-        <v>23.9542858381351</v>
+        <v>23.95428592131823</v>
       </c>
       <c r="CT63" t="n">
         <v>27.87070045516446</v>
       </c>
       <c r="CU63" t="n">
-        <v>28.37777453133656</v>
+        <v>28.3777745346213</v>
       </c>
       <c r="CV63" t="n">
-        <v>25.91249314664978</v>
+        <v>25.91249318824134</v>
       </c>
       <c r="CW63" t="n">
-        <v>23.3212438319848</v>
+        <v>23.32124386941721</v>
       </c>
       <c r="CX63" t="n">
         <v>8</v>
@@ -37611,10 +37611,10 @@
         <v>3.2</v>
       </c>
       <c r="DA63" t="n">
-        <v>-36.01853677957483</v>
+        <v>-36.01853667687961</v>
       </c>
       <c r="DB63" t="n">
-        <v>-22.14602486321572</v>
+        <v>-22.14602485420408</v>
       </c>
       <c r="DC63" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>-0.7623163157813306</v>
       </c>
       <c r="DO63" t="n">
-        <v>-1.353179944996097</v>
+        <v>-2.799997965494794</v>
       </c>
       <c r="DP63" t="b">
         <v>0</v>
@@ -37934,10 +37934,10 @@
         <v>0</v>
       </c>
       <c r="CM64" t="n">
-        <v>2.820078487862132</v>
+        <v>2.82007848281616</v>
       </c>
       <c r="CN64" t="n">
-        <v>5.231245594984254</v>
+        <v>5.231245585623975</v>
       </c>
       <c r="CO64" t="n">
         <v>13.12899589538574</v>
@@ -37946,13 +37946,13 @@
         <v>14.66350162681555</v>
       </c>
       <c r="CQ64" t="n">
-        <v>15.14141162444082</v>
+        <v>15.14141161557431</v>
       </c>
       <c r="CR64" t="n">
-        <v>9.468686826999447</v>
+        <v>9.468686827653004</v>
       </c>
       <c r="CS64" t="n">
-        <v>6.498579674732867</v>
+        <v>6.498579679297657</v>
       </c>
       <c r="CT64" t="n">
         <v>1.548212604646662</v>
@@ -38289,37 +38289,37 @@
         <v>0</v>
       </c>
       <c r="CM65" t="n">
-        <v>11.06062713723358</v>
+        <v>11.06062714254328</v>
       </c>
       <c r="CN65" t="n">
-        <v>14.33571137743339</v>
+        <v>14.33571137465222</v>
       </c>
       <c r="CO65" t="n">
-        <v>17.27401472455022</v>
+        <v>17.27401471290655</v>
       </c>
       <c r="CP65" t="n">
         <v>21.47246571889108</v>
       </c>
       <c r="CQ65" t="n">
-        <v>16.9246654346756</v>
+        <v>16.92466542759999</v>
       </c>
       <c r="CR65" t="n">
-        <v>23.12339237449257</v>
+        <v>22.63400840740754</v>
       </c>
       <c r="CS65" t="n">
-        <v>8.370034384218625</v>
+        <v>8.370034376289331</v>
       </c>
       <c r="CT65" t="n">
         <v>19.12184394629235</v>
       </c>
       <c r="CU65" t="n">
-        <v>16.46034438722343</v>
+        <v>16.39917138832279</v>
       </c>
       <c r="CV65" t="n">
-        <v>17.09934007961291</v>
+        <v>17.09934007025327</v>
       </c>
       <c r="CW65" t="n">
-        <v>15.38940607165162</v>
+        <v>15.38940606322794</v>
       </c>
       <c r="CX65" t="n">
         <v>8</v>
@@ -38328,13 +38328,13 @@
         <v>1</v>
       </c>
       <c r="CZ65" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="DA65" t="n">
-        <v>-38.5407128235821</v>
+        <v>-38.54071285722299</v>
       </c>
       <c r="DB65" t="n">
-        <v>-34.26380277399933</v>
+        <v>-34.50810387888749</v>
       </c>
       <c r="DC65" t="inlineStr">
         <is>
@@ -38654,10 +38654,10 @@
         <v>0</v>
       </c>
       <c r="CM66" t="n">
-        <v>4.660126896920231</v>
+        <v>4.66012687432314</v>
       </c>
       <c r="CN66" t="n">
-        <v>8.644535393787027</v>
+        <v>8.644535351869424</v>
       </c>
       <c r="CO66" t="n">
         <v>28.50627497622841</v>
@@ -38666,13 +38666,13 @@
         <v>28.35236807680409</v>
       </c>
       <c r="CQ66" t="n">
-        <v>24.66479477791244</v>
+        <v>24.66479479320155</v>
       </c>
       <c r="CR66" t="n">
-        <v>2.961410462909572</v>
+        <v>2.961410463426096</v>
       </c>
       <c r="CS66" t="n">
-        <v>17.93036582619652</v>
+        <v>17.93036585190839</v>
       </c>
       <c r="CT66" t="n">
         <v>19.20891215999163</v>
@@ -39013,37 +39013,37 @@
         <v>0</v>
       </c>
       <c r="CM67" t="n">
-        <v>14.15683946601539</v>
+        <v>14.15683948135738</v>
       </c>
       <c r="CN67" t="n">
-        <v>14.52327153882082</v>
+        <v>14.5232715418342</v>
       </c>
       <c r="CO67" t="n">
-        <v>14.98676299896405</v>
+        <v>14.98676298583222</v>
       </c>
       <c r="CP67" t="n">
         <v>30.59566885157829</v>
       </c>
       <c r="CQ67" t="n">
-        <v>14.00921129486131</v>
+        <v>14.00921128776824</v>
       </c>
       <c r="CR67" t="n">
-        <v>30.25195519417974</v>
+        <v>30.25195519099669</v>
       </c>
       <c r="CS67" t="n">
-        <v>5.863199624271166</v>
+        <v>5.863199610702716</v>
       </c>
       <c r="CT67" t="n">
         <v>38.29441237884694</v>
       </c>
       <c r="CU67" t="n">
-        <v>19.75395155740327</v>
+        <v>19.75395155656117</v>
       </c>
       <c r="CV67" t="n">
-        <v>14.75501726889243</v>
+        <v>14.75501726383321</v>
       </c>
       <c r="CW67" t="n">
-        <v>13.27951554200319</v>
+        <v>13.27951553744989</v>
       </c>
       <c r="CX67" t="n">
         <v>6</v>
@@ -39055,10 +39055,10 @@
         <v>6.5</v>
       </c>
       <c r="DA67" t="n">
-        <v>-56.18767477404734</v>
+        <v>-56.18767478906979</v>
       </c>
       <c r="DB67" t="n">
-        <v>-34.82694851380762</v>
+        <v>-34.8269485165859</v>
       </c>
       <c r="DC67" t="inlineStr">
         <is>
@@ -39093,7 +39093,7 @@
         <v>0.3642341067021215</v>
       </c>
       <c r="DO67" t="n">
-        <v>-26.21121146516747</v>
+        <v>-26.21120456655161</v>
       </c>
       <c r="DP67" t="b">
         <v>0</v>
@@ -39386,10 +39386,10 @@
         <v>0</v>
       </c>
       <c r="CM68" t="n">
-        <v>9.424600952514027</v>
+        <v>9.42460095746508</v>
       </c>
       <c r="CN68" t="n">
-        <v>17.48263476691352</v>
+        <v>17.48263477609772</v>
       </c>
       <c r="CO68" t="n">
         <v>17.0502564055361</v>
@@ -39398,7 +39398,7 @@
         <v>16.93163083998861</v>
       </c>
       <c r="CQ68" t="n">
-        <v>26.97723552038159</v>
+        <v>26.97723552481916</v>
       </c>
       <c r="CR68" t="n">
         <v>19.94489718117502</v>
@@ -39410,7 +39410,7 @@
         <v>17.36889744184579</v>
       </c>
       <c r="CU68" t="n">
-        <v>17.53315800732909</v>
+        <v>17.5331580096507</v>
       </c>
       <c r="CV68" t="n">
         <v>17.20957692369095</v>
@@ -39431,7 +39431,7 @@
         <v>-22.94219434144452</v>
       </c>
       <c r="DB68" t="n">
-        <v>-12.77035982798795</v>
+        <v>-12.77035981643767</v>
       </c>
       <c r="DC68" t="inlineStr">
         <is>
@@ -39755,35 +39755,35 @@
         <v>0</v>
       </c>
       <c r="CM69" t="n">
-        <v>2.878501270730353</v>
+        <v>2.87850125024679</v>
       </c>
       <c r="CN69" t="n">
-        <v>3.149870568444909</v>
+        <v>3.149870562729182</v>
       </c>
       <c r="CO69" t="n">
-        <v>3.544247204741002</v>
+        <v>3.544247223530688</v>
       </c>
       <c r="CP69" t="n">
         <v>6.959150461939593</v>
       </c>
       <c r="CQ69" t="n">
-        <v>5.357798585066147</v>
+        <v>5.35779857794881</v>
       </c>
       <c r="CR69" t="n">
-        <v>8.422443922406046</v>
+        <v>8.422443927470702</v>
       </c>
       <c r="CS69" t="n">
-        <v>1.516132261813737</v>
+        <v>1.516132279136276</v>
       </c>
       <c r="CT69" t="inlineStr"/>
       <c r="CU69" t="n">
-        <v>4.546877753591684</v>
+        <v>4.546877754714577</v>
       </c>
       <c r="CV69" t="n">
-        <v>3.544247204741002</v>
+        <v>3.544247223530688</v>
       </c>
       <c r="CW69" t="n">
-        <v>3.189822484266902</v>
+        <v>3.189822501177619</v>
       </c>
       <c r="CX69" t="n">
         <v>7</v>
@@ -39795,10 +39795,10 @@
         <v>5.6</v>
       </c>
       <c r="DA69" t="n">
-        <v>-14.93806708621594</v>
+        <v>-14.93806663526349</v>
       </c>
       <c r="DB69" t="n">
-        <v>21.25007342911158</v>
+        <v>21.25007345905539</v>
       </c>
       <c r="DC69" t="inlineStr">
         <is>
@@ -40128,25 +40128,25 @@
         <v>0</v>
       </c>
       <c r="CM70" t="n">
-        <v>0.6891133919765345</v>
+        <v>0.6891133942948757</v>
       </c>
       <c r="CN70" t="n">
-        <v>0.9671622930578618</v>
+        <v>0.9671622958097639</v>
       </c>
       <c r="CO70" t="n">
-        <v>3.407902715511942</v>
+        <v>3.407902713743577</v>
       </c>
       <c r="CP70" t="n">
         <v>7.140833667637913</v>
       </c>
       <c r="CQ70" t="n">
-        <v>2.61063263844501</v>
+        <v>2.610632641383746</v>
       </c>
       <c r="CR70" t="n">
-        <v>2.229099968172907</v>
+        <v>1.666778043856264</v>
       </c>
       <c r="CS70" t="n">
-        <v>1.690151944926594</v>
+        <v>1.690151943884082</v>
       </c>
       <c r="CT70" t="n">
         <v>6.495080194769218</v>
@@ -40155,7 +40155,7 @@
       <c r="CV70" t="inlineStr"/>
       <c r="CW70" t="inlineStr"/>
       <c r="CX70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CY70" t="b">
         <v>0</v>
@@ -40465,10 +40465,10 @@
         <v>0</v>
       </c>
       <c r="CM71" t="n">
-        <v>12.00267477472071</v>
+        <v>12.00267473275751</v>
       </c>
       <c r="CN71" t="n">
-        <v>17.47589447199335</v>
+        <v>17.47589441089493</v>
       </c>
       <c r="CO71" t="n">
         <v>15.80042779828547</v>
@@ -40485,13 +40485,13 @@
       </c>
       <c r="CT71" t="inlineStr"/>
       <c r="CU71" t="n">
-        <v>13.15308259458322</v>
+        <v>13.15308256881781</v>
       </c>
       <c r="CV71" t="n">
-        <v>13.90155128650309</v>
+        <v>13.90155126552149</v>
       </c>
       <c r="CW71" t="n">
-        <v>12.51139615785278</v>
+        <v>12.51139613896934</v>
       </c>
       <c r="CX71" t="n">
         <v>4</v>
@@ -40503,10 +40503,10 @@
         <v>2.4</v>
       </c>
       <c r="DA71" t="n">
-        <v>-11.82948183346724</v>
+        <v>-11.82948196654292</v>
       </c>
       <c r="DB71" t="n">
-        <v>-7.307378551536758</v>
+        <v>-7.307378733111126</v>
       </c>
       <c r="DC71" t="inlineStr">
         <is>
@@ -40826,10 +40826,10 @@
         <v>0</v>
       </c>
       <c r="CM72" t="n">
-        <v>0.5420072205954749</v>
+        <v>0.5420072203619124</v>
       </c>
       <c r="CN72" t="n">
-        <v>1.005423394204606</v>
+        <v>1.005423393771347</v>
       </c>
       <c r="CO72" t="n">
         <v>9.43764624323483</v>
@@ -40838,13 +40838,13 @@
         <v>8.675079879982691</v>
       </c>
       <c r="CQ72" t="n">
-        <v>10.27283933708304</v>
+        <v>10.27283933732473</v>
       </c>
       <c r="CR72" t="n">
-        <v>0.7349993033565885</v>
+        <v>0.7349993033611067</v>
       </c>
       <c r="CS72" t="n">
-        <v>7.987084277056502</v>
+        <v>7.98708427736912</v>
       </c>
       <c r="CT72" t="inlineStr"/>
       <c r="CU72" t="inlineStr"/>
@@ -41179,10 +41179,10 @@
         <v>0</v>
       </c>
       <c r="CM73" t="n">
-        <v>10.70577920793021</v>
+        <v>10.70577928536454</v>
       </c>
       <c r="CN73" t="n">
-        <v>19.85922043071054</v>
+        <v>19.85922057435123</v>
       </c>
       <c r="CO73" t="n">
         <v>28.52144455456774</v>
@@ -41191,25 +41191,25 @@
         <v>21.17171920104553</v>
       </c>
       <c r="CQ73" t="n">
-        <v>23.83501173952666</v>
+        <v>23.83501154978059</v>
       </c>
       <c r="CR73" t="n">
-        <v>22.6919985730501</v>
+        <v>22.69199854822198</v>
       </c>
       <c r="CS73" t="n">
-        <v>15.3086542199726</v>
+        <v>15.30865406147382</v>
       </c>
       <c r="CT73" t="n">
         <v>27.78248952102578</v>
       </c>
       <c r="CU73" t="n">
-        <v>21.23453968097865</v>
+        <v>21.2345396619789</v>
       </c>
       <c r="CV73" t="n">
-        <v>21.93185888704781</v>
+        <v>21.93185887463375</v>
       </c>
       <c r="CW73" t="n">
-        <v>19.73867299834303</v>
+        <v>19.73867298717038</v>
       </c>
       <c r="CX73" t="n">
         <v>8</v>
@@ -41221,10 +41221,10 @@
         <v>2.7</v>
       </c>
       <c r="DA73" t="n">
-        <v>-47.2086832828145</v>
+        <v>-47.2086833126959</v>
       </c>
       <c r="DB73" t="n">
-        <v>-43.20796997162425</v>
+        <v>-43.20797002243931</v>
       </c>
       <c r="DC73" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>0.7002378509395557</v>
       </c>
       <c r="DO73" t="n">
-        <v>-16.82238905225601</v>
+        <v>-16.82238194827477</v>
       </c>
       <c r="DP73" t="b">
         <v>0</v>
@@ -41430,7 +41430,7 @@
         <v>0</v>
       </c>
       <c r="AW74" t="n">
-        <v>3756431616</v>
+        <v>3756432896</v>
       </c>
       <c r="AX74" t="n">
         <v>8.27</v>
@@ -41556,10 +41556,10 @@
         <v>0</v>
       </c>
       <c r="CM74" t="n">
-        <v>0.9179473571863965</v>
+        <v>0.9179473608571372</v>
       </c>
       <c r="CN74" t="n">
-        <v>1.702792347580765</v>
+        <v>1.702792354389989</v>
       </c>
       <c r="CO74" t="n">
         <v>6.072249031989433</v>
@@ -41568,10 +41568,10 @@
         <v>4.035265264444879</v>
       </c>
       <c r="CQ74" t="n">
-        <v>8.428205855913539</v>
+        <v>8.42820586212761</v>
       </c>
       <c r="CR74" t="n">
-        <v>3.760485277130923</v>
+        <v>3.664062577717309</v>
       </c>
       <c r="CS74" t="n">
         <v>5.545223644307333</v>
@@ -41626,7 +41626,7 @@
         <v>-7.560974390006048</v>
       </c>
       <c r="DO74" t="n">
-        <v>-48.18735446403307</v>
+        <v>-48.18735101364662</v>
       </c>
       <c r="DP74" t="b">
         <v>0</v>
@@ -41911,10 +41911,10 @@
         <v>0</v>
       </c>
       <c r="CM75" t="n">
-        <v>1.735754949540076</v>
+        <v>1.735754952364224</v>
       </c>
       <c r="CN75" t="n">
-        <v>3.21982543139684</v>
+        <v>3.219825436635634</v>
       </c>
       <c r="CO75" t="n">
         <v>24.06414080147791</v>
@@ -41923,13 +41923,13 @@
         <v>23.77341994112827</v>
       </c>
       <c r="CQ75" t="n">
-        <v>25.47035323011449</v>
+        <v>25.47035323293435</v>
       </c>
       <c r="CR75" t="n">
-        <v>6.701307224090082</v>
+        <v>6.701307223918797</v>
       </c>
       <c r="CS75" t="n">
-        <v>17.77589564733433</v>
+        <v>17.77589564408611</v>
       </c>
       <c r="CT75" t="n">
         <v>13.5886920342512</v>
@@ -42266,25 +42266,25 @@
         <v>0</v>
       </c>
       <c r="CM76" t="n">
-        <v>4.10500971959998</v>
+        <v>4.105009714843777</v>
       </c>
       <c r="CN76" t="n">
-        <v>7.002256959106598</v>
+        <v>7.002256953325391</v>
       </c>
       <c r="CO76" t="n">
-        <v>23.32321844270555</v>
+        <v>23.3232184504725</v>
       </c>
       <c r="CP76" t="n">
         <v>32.93553447863792</v>
       </c>
       <c r="CQ76" t="n">
-        <v>16.4873163117269</v>
+        <v>16.48731630959095</v>
       </c>
       <c r="CR76" t="n">
-        <v>20.28919693310452</v>
+        <v>20.289196933617</v>
       </c>
       <c r="CS76" t="n">
-        <v>11.5548998262044</v>
+        <v>11.55489982940628</v>
       </c>
       <c r="CT76" t="n">
         <v>23.19375865248643</v>
@@ -42336,7 +42336,7 @@
         <v>0.05674416036882679</v>
       </c>
       <c r="DO76" t="n">
-        <v>-38.77461953705444</v>
+        <v>-38.77462365715461</v>
       </c>
       <c r="DP76" t="b">
         <v>0</v>
@@ -42621,10 +42621,10 @@
         <v>0</v>
       </c>
       <c r="CM77" t="n">
-        <v>6.28591120640838</v>
+        <v>6.285911212418188</v>
       </c>
       <c r="CN77" t="n">
-        <v>11.66036528788754</v>
+        <v>11.66036529903574</v>
       </c>
       <c r="CO77" t="n">
         <v>32.87909322430473</v>
@@ -42633,25 +42633,25 @@
         <v>33.81282523448726</v>
       </c>
       <c r="CQ77" t="n">
-        <v>28.98439036293557</v>
+        <v>28.98439036194025</v>
       </c>
       <c r="CR77" t="n">
-        <v>25.24883989943697</v>
+        <v>25.24883989847612</v>
       </c>
       <c r="CS77" t="n">
-        <v>18.80888537605768</v>
+        <v>18.80888536965844</v>
       </c>
       <c r="CT77" t="n">
         <v>14.34677086089842</v>
       </c>
       <c r="CU77" t="n">
-        <v>23.67731003514402</v>
+        <v>23.677310035543</v>
       </c>
       <c r="CV77" t="n">
-        <v>25.24883989943697</v>
+        <v>25.24883989847612</v>
       </c>
       <c r="CW77" t="n">
-        <v>22.72395590949328</v>
+        <v>22.72395590862851</v>
       </c>
       <c r="CX77" t="n">
         <v>7</v>
@@ -42663,10 +42663,10 @@
         <v>5.4</v>
       </c>
       <c r="DA77" t="n">
-        <v>-0.02658879394968894</v>
+        <v>-0.0265887977542234</v>
       </c>
       <c r="DB77" t="n">
-        <v>4.167666132801395</v>
+        <v>4.16766613455668</v>
       </c>
       <c r="DC77" t="inlineStr">
         <is>
@@ -42990,35 +42990,35 @@
         <v>0</v>
       </c>
       <c r="CM78" t="n">
-        <v>24.10609638975475</v>
+        <v>24.10609634978476</v>
       </c>
       <c r="CN78" t="n">
-        <v>29.25244933210383</v>
+        <v>29.25244932223856</v>
       </c>
       <c r="CO78" t="n">
-        <v>36.92263444005793</v>
+        <v>36.92263448882684</v>
       </c>
       <c r="CP78" t="n">
         <v>61.78228988979415</v>
       </c>
       <c r="CQ78" t="n">
-        <v>66.70460295184607</v>
+        <v>66.70460291632433</v>
       </c>
       <c r="CR78" t="n">
-        <v>41.55372099035571</v>
+        <v>41.5537209960329</v>
       </c>
       <c r="CS78" t="n">
-        <v>17.29235884900663</v>
+        <v>17.29235888639616</v>
       </c>
       <c r="CT78" t="inlineStr"/>
       <c r="CU78" t="n">
-        <v>39.65916469184559</v>
+        <v>39.65916469277111</v>
       </c>
       <c r="CV78" t="n">
-        <v>36.92263444005793</v>
+        <v>36.92263448882684</v>
       </c>
       <c r="CW78" t="n">
-        <v>33.23037099605214</v>
+        <v>33.23037103994416</v>
       </c>
       <c r="CX78" t="n">
         <v>7</v>
@@ -43030,10 +43030,10 @@
         <v>3.9</v>
       </c>
       <c r="DA78" t="n">
-        <v>32.44468231948026</v>
+        <v>32.44468249441854</v>
       </c>
       <c r="DB78" t="n">
-        <v>58.0676143908073</v>
+        <v>58.06761439449608</v>
       </c>
       <c r="DC78" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>207.7</v>
       </c>
       <c r="BN79" t="n">
-        <v>7.86</v>
+        <v>8.08</v>
       </c>
       <c r="BO79" t="n">
         <v>7.28</v>
@@ -43361,10 +43361,10 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>2.135335883556526</v>
+        <v>2.135335881795349</v>
       </c>
       <c r="CN79" t="n">
-        <v>3.961048063997356</v>
+        <v>3.961048060730372</v>
       </c>
       <c r="CO79" t="n">
         <v>16.12499952316284</v>
@@ -43373,10 +43373,10 @@
         <v>12.78795644154861</v>
       </c>
       <c r="CQ79" t="n">
-        <v>21.07497138186278</v>
+        <v>21.0749713795367</v>
       </c>
       <c r="CR79" t="n">
-        <v>9.294207014285712</v>
+        <v>9.14667991882086</v>
       </c>
       <c r="CS79" t="n">
         <v>14.72547126266192</v>
@@ -43716,10 +43716,10 @@
         <v>0</v>
       </c>
       <c r="CM80" t="n">
-        <v>4.815933250401771</v>
+        <v>4.815933248510231</v>
       </c>
       <c r="CN80" t="n">
-        <v>8.933556179495284</v>
+        <v>8.933556175986478</v>
       </c>
       <c r="CO80" t="n">
         <v>30.21828844483058</v>
@@ -43728,19 +43728,19 @@
         <v>25.63338582679529</v>
       </c>
       <c r="CQ80" t="n">
-        <v>34.45161054378895</v>
+        <v>34.45161054620193</v>
       </c>
       <c r="CR80" t="n">
-        <v>11.7657808850967</v>
+        <v>11.76578088531278</v>
       </c>
       <c r="CS80" t="n">
-        <v>24.06579218263496</v>
+        <v>24.06579218559787</v>
       </c>
       <c r="CT80" t="n">
         <v>26.25</v>
       </c>
       <c r="CU80" t="n">
-        <v>25.39747631385775</v>
+        <v>25.39747631478974</v>
       </c>
       <c r="CV80" t="n">
         <v>25.94169291339765</v>
@@ -43761,7 +43761,7 @@
         <v>-11.05705286835093</v>
       </c>
       <c r="DB80" t="n">
-        <v>-3.247709280541911</v>
+        <v>-3.247709276991462</v>
       </c>
       <c r="DC80" t="inlineStr">
         <is>
@@ -44079,10 +44079,10 @@
         <v>0</v>
       </c>
       <c r="CM81" t="n">
-        <v>41.36674087878255</v>
+        <v>41.36674046399108</v>
       </c>
       <c r="CN81" t="n">
-        <v>60.2299747195074</v>
+        <v>60.22997411557101</v>
       </c>
       <c r="CO81" t="n">
         <v>35.35875738842788</v>
@@ -44101,13 +44101,13 @@
         <v>50.38275929312339</v>
       </c>
       <c r="CU81" t="n">
-        <v>43.89473758371173</v>
+        <v>43.89473741392374</v>
       </c>
       <c r="CV81" t="n">
-        <v>41.7977330458784</v>
+        <v>41.79773283848266</v>
       </c>
       <c r="CW81" t="n">
-        <v>37.61795974129056</v>
+        <v>37.6179595546344</v>
       </c>
       <c r="CX81" t="n">
         <v>6</v>
@@ -44119,10 +44119,10 @@
         <v>6.6</v>
       </c>
       <c r="DA81" t="n">
-        <v>-33.86434768831649</v>
+        <v>-33.86434801647429</v>
       </c>
       <c r="DB81" t="n">
-        <v>-22.82922510647165</v>
+        <v>-22.82922540497373</v>
       </c>
       <c r="DC81" t="inlineStr">
         <is>
@@ -44442,10 +44442,10 @@
         <v>0</v>
       </c>
       <c r="CM82" t="n">
-        <v>14.18574108782111</v>
+        <v>14.18574108874411</v>
       </c>
       <c r="CN82" t="n">
-        <v>26.31454971790815</v>
+        <v>26.31454971962032</v>
       </c>
       <c r="CO82" t="n">
         <v>37.04143720876227</v>
@@ -44454,25 +44454,25 @@
         <v>25.8401544888617</v>
       </c>
       <c r="CQ82" t="n">
-        <v>39.63585741703417</v>
+        <v>39.63585741481651</v>
       </c>
       <c r="CR82" t="n">
-        <v>41.79465739799126</v>
+        <v>42.03764959168957</v>
       </c>
       <c r="CS82" t="n">
-        <v>20.88726876110701</v>
+        <v>20.88726875896513</v>
       </c>
       <c r="CT82" t="n">
         <v>26.58328431841265</v>
       </c>
       <c r="CU82" t="n">
-        <v>29.03536879973729</v>
+        <v>29.06574282373403</v>
       </c>
       <c r="CV82" t="n">
-        <v>26.4489170181604</v>
+        <v>26.44891701901648</v>
       </c>
       <c r="CW82" t="n">
-        <v>23.80402531634436</v>
+        <v>23.80402531711484</v>
       </c>
       <c r="CX82" t="n">
         <v>8</v>
@@ -44481,13 +44481,13 @@
         <v>1</v>
       </c>
       <c r="CZ82" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="DA82" t="n">
-        <v>-21.59412108763882</v>
+        <v>-21.59412108510103</v>
       </c>
       <c r="DB82" t="n">
-        <v>-4.363082292437848</v>
+        <v>-4.263036102101514</v>
       </c>
       <c r="DC82" t="inlineStr">
         <is>
@@ -44807,10 +44807,10 @@
         <v>0</v>
       </c>
       <c r="CM83" t="n">
-        <v>10.3051541765418</v>
+        <v>10.30515412440752</v>
       </c>
       <c r="CN83" t="n">
-        <v>19.11606099748504</v>
+        <v>19.11606090077594</v>
       </c>
       <c r="CO83" t="n">
         <v>13.92043917855315</v>
@@ -44831,7 +44831,7 @@
         <v>12.84315041940997</v>
       </c>
       <c r="CU83" t="n">
-        <v>15.35077742329135</v>
+        <v>15.35077740468593</v>
       </c>
       <c r="CV83" t="n">
         <v>13.33695414803924</v>
@@ -44852,7 +44852,7 @@
         <v>-23.93372030193791</v>
       </c>
       <c r="DB83" t="n">
-        <v>-2.720040031325288</v>
+        <v>-2.720040149230374</v>
       </c>
       <c r="DC83" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>58.4</v>
       </c>
       <c r="BN84" t="n">
-        <v>10.95</v>
+        <v>11.04</v>
       </c>
       <c r="BO84" t="n">
         <v>6.62</v>
@@ -45172,10 +45172,10 @@
         <v>0</v>
       </c>
       <c r="CM84" t="n">
-        <v>2.656011983420766</v>
+        <v>2.656011982894293</v>
       </c>
       <c r="CN84" t="n">
-        <v>4.92690222924552</v>
+        <v>4.926902228268913</v>
       </c>
       <c r="CO84" t="n">
         <v>25.41899625515882</v>
@@ -45184,10 +45184,10 @@
         <v>19.49200968885813</v>
       </c>
       <c r="CQ84" t="n">
-        <v>33.11004126281825</v>
+        <v>33.1100412619592</v>
       </c>
       <c r="CR84" t="n">
-        <v>10.38593205872702</v>
+        <v>10.57139513120429</v>
       </c>
       <c r="CS84" t="n">
         <v>23.21281922169221</v>
@@ -45531,10 +45531,10 @@
         <v>0</v>
       </c>
       <c r="CM85" t="n">
-        <v>6.802827532049957</v>
+        <v>6.80282755234149</v>
       </c>
       <c r="CN85" t="n">
-        <v>12.61924507195267</v>
+        <v>12.61924510959346</v>
       </c>
       <c r="CO85" t="n">
         <v>7.958604169614386</v>
@@ -45555,7 +45555,7 @@
         <v>38.97525852693097</v>
       </c>
       <c r="CU85" t="n">
-        <v>10.40409276049598</v>
+        <v>10.40409276877203</v>
       </c>
       <c r="CV85" t="n">
         <v>7.958604169614386</v>
@@ -45576,7 +45576,7 @@
         <v>-35.47077922077923</v>
       </c>
       <c r="DB85" t="n">
-        <v>-6.269437811330969</v>
+        <v>-6.269437736771999</v>
       </c>
       <c r="DC85" t="inlineStr">
         <is>
@@ -45896,38 +45896,38 @@
         <v>0</v>
       </c>
       <c r="CM86" t="n">
-        <v>1.329575621128058</v>
+        <v>1.329575625393409</v>
       </c>
       <c r="CN86" t="n">
-        <v>1.787970922844959</v>
+        <v>1.787970926749053</v>
       </c>
       <c r="CO86" t="n">
-        <v>3.657425220422971</v>
+        <v>3.657425216675863</v>
       </c>
       <c r="CP86" t="n">
         <v>7.182036549729029</v>
       </c>
       <c r="CQ86" t="n">
-        <v>3.6902511848637</v>
+        <v>3.690251188933408</v>
       </c>
       <c r="CR86" t="n">
-        <v>1.338423448955536</v>
+        <v>3.203195550035498</v>
       </c>
       <c r="CS86" t="n">
-        <v>1.795233808957797</v>
+        <v>1.795233806570566</v>
       </c>
       <c r="CT86" t="inlineStr"/>
       <c r="CU86" t="n">
-        <v>2.266480034528837</v>
+        <v>3.235098409155261</v>
       </c>
       <c r="CV86" t="n">
-        <v>1.791602365901378</v>
+        <v>3.203195550035498</v>
       </c>
       <c r="CW86" t="n">
-        <v>1.612442129311241</v>
+        <v>2.882875995031948</v>
       </c>
       <c r="CX86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CY86" t="b">
         <v>1</v>
@@ -45936,10 +45936,10 @@
         <v>5.4</v>
       </c>
       <c r="DA86" t="n">
-        <v>-44.20615672037476</v>
+        <v>-0.2465089831705458</v>
       </c>
       <c r="DB86" t="n">
-        <v>-21.57508815716849</v>
+        <v>11.94111736070436</v>
       </c>
       <c r="DC86" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>-89.7</v>
       </c>
       <c r="BN87" t="n">
-        <v>9.199999999999999</v>
+        <v>12.32</v>
       </c>
       <c r="BO87" t="n">
         <v>6.86</v>
@@ -46267,10 +46267,10 @@
         <v>0</v>
       </c>
       <c r="CM87" t="n">
-        <v>1.377772800503275</v>
+        <v>1.377772800118704</v>
       </c>
       <c r="CN87" t="n">
-        <v>2.555768544933575</v>
+        <v>2.555768544220195</v>
       </c>
       <c r="CO87" t="n">
         <v>10.39322363767291</v>
@@ -46279,13 +46279,13 @@
         <v>10.22375130073559</v>
       </c>
       <c r="CQ87" t="n">
-        <v>9.83557185591361</v>
+        <v>9.835571856075832</v>
       </c>
       <c r="CR87" t="n">
-        <v>1.868392251412359</v>
+        <v>1.868392251427839</v>
       </c>
       <c r="CS87" t="n">
-        <v>7.033007633460143</v>
+        <v>7.033007633909569</v>
       </c>
       <c r="CT87" t="n">
         <v>12.04041800117484</v>
@@ -46622,25 +46622,25 @@
         <v>0</v>
       </c>
       <c r="CM88" t="n">
-        <v>13.21935662650175</v>
+        <v>13.21935662965554</v>
       </c>
       <c r="CN88" t="n">
-        <v>13.22957926204111</v>
+        <v>13.22957926333024</v>
       </c>
       <c r="CO88" t="n">
-        <v>13.2468718569344</v>
+        <v>13.24687185506487</v>
       </c>
       <c r="CP88" t="n">
         <v>32.57919652771017</v>
       </c>
       <c r="CQ88" t="n">
-        <v>11.83565786124041</v>
+        <v>11.83565786084996</v>
       </c>
       <c r="CR88" t="n">
-        <v>24.511764018493</v>
+        <v>25.03053151051435</v>
       </c>
       <c r="CS88" t="n">
-        <v>4.961556373276609</v>
+        <v>4.961556371258943</v>
       </c>
       <c r="CT88" t="n">
         <v>52.78009373526422</v>
@@ -47340,10 +47340,10 @@
         <v>0</v>
       </c>
       <c r="CM90" t="n">
-        <v>3.383236084754814</v>
+        <v>3.383236108061455</v>
       </c>
       <c r="CN90" t="n">
-        <v>4.925991739403009</v>
+        <v>4.92599177333748</v>
       </c>
       <c r="CO90" t="n">
         <v>4.345361418407098</v>
@@ -47701,10 +47701,10 @@
         <v>0</v>
       </c>
       <c r="CM91" t="n">
-        <v>4.913572775517932</v>
+        <v>4.913572781207685</v>
       </c>
       <c r="CN91" t="n">
-        <v>9.114677498585765</v>
+        <v>9.114677509140256</v>
       </c>
       <c r="CO91" t="n">
         <v>32.34981869328296</v>
@@ -47713,13 +47713,13 @@
         <v>34.95455687527223</v>
       </c>
       <c r="CQ91" t="n">
-        <v>27.58750279175195</v>
+        <v>27.58750279259848</v>
       </c>
       <c r="CR91" t="n">
-        <v>11.10529429086175</v>
+        <v>11.10529429049238</v>
       </c>
       <c r="CS91" t="n">
-        <v>18.64714224676803</v>
+        <v>18.64714224126036</v>
       </c>
       <c r="CT91" t="n">
         <v>46.20055014188909</v>
@@ -48056,25 +48056,25 @@
         <v>0</v>
       </c>
       <c r="CM92" t="n">
-        <v>0.1365068429769334</v>
+        <v>0.1365068427818428</v>
       </c>
       <c r="CN92" t="n">
-        <v>0.1559108857056716</v>
+        <v>0.1559108854910455</v>
       </c>
       <c r="CO92" t="n">
-        <v>0.749221800713936</v>
+        <v>0.7492218007533213</v>
       </c>
       <c r="CP92" t="n">
         <v>3.095196412037962</v>
       </c>
       <c r="CQ92" t="n">
-        <v>0.2572541516749456</v>
+        <v>0.2572541515645369</v>
       </c>
       <c r="CR92" t="n">
-        <v>0.5416204958898752</v>
+        <v>0.541620495892984</v>
       </c>
       <c r="CS92" t="n">
-        <v>0.3349334271307651</v>
+        <v>0.3349334271644144</v>
       </c>
       <c r="CT92" t="inlineStr"/>
       <c r="CU92" t="inlineStr"/>
@@ -48415,10 +48415,10 @@
         <v>0</v>
       </c>
       <c r="CM93" t="n">
-        <v>6.397417148493972</v>
+        <v>6.397417132450321</v>
       </c>
       <c r="CN93" t="n">
-        <v>9.314639368207223</v>
+        <v>9.314639344847667</v>
       </c>
       <c r="CO93" t="n">
         <v>3.748248950052818</v>
@@ -48768,10 +48768,10 @@
         <v>0</v>
       </c>
       <c r="CM94" t="n">
-        <v>12.66669287399413</v>
+        <v>12.66669277517566</v>
       </c>
       <c r="CN94" t="n">
-        <v>23.49671528125911</v>
+        <v>23.49671509795085</v>
       </c>
       <c r="CO94" t="n">
         <v>14.98448006805406</v>
@@ -48792,7 +48792,7 @@
         <v>22.80124355576588</v>
       </c>
       <c r="CU94" t="n">
-        <v>19.9592913746044</v>
+        <v>19.95929133933856</v>
       </c>
       <c r="CV94" t="n">
         <v>18.89286181190997</v>
@@ -48813,7 +48813,7 @@
         <v>-32.36445487854582</v>
       </c>
       <c r="DB94" t="n">
-        <v>-20.60743094996742</v>
+        <v>-20.60743109024525</v>
       </c>
       <c r="DC94" t="inlineStr">
         <is>
@@ -49109,10 +49109,10 @@
         <v>0</v>
       </c>
       <c r="CM95" t="n">
-        <v>12.45258438185869</v>
+        <v>12.45258434511232</v>
       </c>
       <c r="CN95" t="n">
-        <v>18.13096285998625</v>
+        <v>18.13096280648353</v>
       </c>
       <c r="CO95" t="inlineStr"/>
       <c r="CP95" t="inlineStr"/>
@@ -49123,13 +49123,13 @@
       <c r="CS95" t="inlineStr"/>
       <c r="CT95" t="inlineStr"/>
       <c r="CU95" t="n">
-        <v>18.97041574728165</v>
+        <v>18.97041571719862</v>
       </c>
       <c r="CV95" t="n">
-        <v>18.13096285998625</v>
+        <v>18.13096280648353</v>
       </c>
       <c r="CW95" t="n">
-        <v>16.31786657398763</v>
+        <v>16.31786652583518</v>
       </c>
       <c r="CX95" t="n">
         <v>3</v>
@@ -49141,10 +49141,10 @@
         <v>2.1</v>
       </c>
       <c r="DA95" t="n">
-        <v>-72.55194892417894</v>
+        <v>-72.55194900517549</v>
       </c>
       <c r="DB95" t="n">
-        <v>-68.09013371937984</v>
+        <v>-68.09013376998207</v>
       </c>
       <c r="DC95" t="inlineStr">
         <is>
@@ -49478,10 +49478,10 @@
         <v>0</v>
       </c>
       <c r="CM96" t="n">
-        <v>4.925587001491358</v>
+        <v>4.92558700989325</v>
       </c>
       <c r="CN96" t="n">
-        <v>7.171654674171419</v>
+        <v>7.171654686404572</v>
       </c>
       <c r="CO96" t="n">
         <v>5.841409764450903</v>
@@ -49500,13 +49500,13 @@
         <v>7.680081469140733</v>
       </c>
       <c r="CU96" t="n">
-        <v>6.566379710977722</v>
+        <v>6.566379714416897</v>
       </c>
       <c r="CV96" t="n">
-        <v>6.506532219311161</v>
+        <v>6.506532225427738</v>
       </c>
       <c r="CW96" t="n">
-        <v>5.855878997380045</v>
+        <v>5.855879002884964</v>
       </c>
       <c r="CX96" t="n">
         <v>6</v>
@@ -49518,10 +49518,10 @@
         <v>5.9</v>
       </c>
       <c r="DA96" t="n">
-        <v>-23.45256308001673</v>
+        <v>-23.45256300805701</v>
       </c>
       <c r="DB96" t="n">
-        <v>-14.1649721683783</v>
+        <v>-14.16497212342176</v>
       </c>
       <c r="DC96" t="inlineStr">
         <is>
@@ -49841,10 +49841,10 @@
         <v>0</v>
       </c>
       <c r="CM97" t="n">
-        <v>3.22996433520729</v>
+        <v>3.229964323003265</v>
       </c>
       <c r="CN97" t="n">
-        <v>5.991583841809523</v>
+        <v>5.991583819171056</v>
       </c>
       <c r="CO97" t="n">
         <v>14.24099764995627</v>
@@ -49853,23 +49853,23 @@
         <v>15.31578992542467</v>
       </c>
       <c r="CQ97" t="n">
-        <v>13.1614664740454</v>
+        <v>13.16146646931197</v>
       </c>
       <c r="CR97" t="n">
-        <v>14.93686465661174</v>
+        <v>14.93686465908398</v>
       </c>
       <c r="CS97" t="n">
-        <v>7.207353941012969</v>
+        <v>7.207353952912384</v>
       </c>
       <c r="CT97" t="inlineStr"/>
       <c r="CU97" t="n">
-        <v>11.8090094148101</v>
+        <v>11.80900941264339</v>
       </c>
       <c r="CV97" t="n">
-        <v>13.70123206200084</v>
+        <v>13.70123205963412</v>
       </c>
       <c r="CW97" t="n">
-        <v>12.33110885580075</v>
+        <v>12.33110885367071</v>
       </c>
       <c r="CX97" t="n">
         <v>6</v>
@@ -49881,10 +49881,10 @@
         <v>4.7</v>
       </c>
       <c r="DA97" t="n">
-        <v>58.90603726924866</v>
+        <v>58.90603724179968</v>
       </c>
       <c r="DB97" t="n">
-        <v>52.17795188791761</v>
+        <v>52.17795185999612</v>
       </c>
       <c r="DC97" t="inlineStr">
         <is>
@@ -50210,10 +50210,10 @@
         <v>0</v>
       </c>
       <c r="CM98" t="n">
-        <v>58.65081362158386</v>
+        <v>58.65081388775756</v>
       </c>
       <c r="CN98" t="n">
-        <v>85.39558463302612</v>
+        <v>85.395585020575</v>
       </c>
       <c r="CO98" t="n">
         <v>24.28937089198329</v>
@@ -50581,10 +50581,10 @@
         <v>0</v>
       </c>
       <c r="CM99" t="n">
-        <v>35.87629932900714</v>
+        <v>35.87629941395353</v>
       </c>
       <c r="CN99" t="n">
-        <v>66.55053525530823</v>
+        <v>66.55053541288379</v>
       </c>
       <c r="CO99" t="n">
         <v>4.727868169088458</v>
@@ -50596,7 +50596,7 @@
         <v>10.70460717529462</v>
       </c>
       <c r="CR99" t="n">
-        <v>6.468000000000001</v>
+        <v>6.647666666666668</v>
       </c>
       <c r="CS99" t="n">
         <v>2.702658440162481</v>
@@ -50936,10 +50936,10 @@
         <v>0</v>
       </c>
       <c r="CM100" t="n">
-        <v>9.104082299018605</v>
+        <v>9.104082313710959</v>
       </c>
       <c r="CN100" t="n">
-        <v>16.88807266467951</v>
+        <v>16.88807269193383</v>
       </c>
       <c r="CO100" t="n">
         <v>40.34279204639602</v>
@@ -50948,19 +50948,19 @@
         <v>40.6980099339037</v>
       </c>
       <c r="CQ100" t="n">
-        <v>32.91704586994907</v>
+        <v>32.91704586101173</v>
       </c>
       <c r="CR100" t="n">
-        <v>49.93410688478379</v>
+        <v>49.93410688081464</v>
       </c>
       <c r="CS100" t="n">
-        <v>22.18690972235424</v>
+        <v>22.18690970602456</v>
       </c>
       <c r="CT100" t="n">
         <v>52.35439300971267</v>
       </c>
       <c r="CU100" t="n">
-        <v>36.47447573311128</v>
+        <v>36.47447573282817</v>
       </c>
       <c r="CV100" t="n">
         <v>40.34279204639602</v>
@@ -50981,7 +50981,7 @@
         <v>-1.201325600662806</v>
       </c>
       <c r="DB100" t="n">
-        <v>-0.7497258962958275</v>
+        <v>-0.7497258970662113</v>
       </c>
       <c r="DC100" t="inlineStr">
         <is>
@@ -51301,10 +51301,10 @@
         <v>0</v>
       </c>
       <c r="CM101" t="n">
-        <v>2.092381673636715</v>
+        <v>2.092381679814538</v>
       </c>
       <c r="CN101" t="n">
-        <v>3.881368004596106</v>
+        <v>3.881368016055967</v>
       </c>
       <c r="CO101" t="n">
         <v>10.15032146883479</v>
@@ -51313,19 +51313,19 @@
         <v>8.470043037007597</v>
       </c>
       <c r="CQ101" t="n">
-        <v>9.817377101668169</v>
+        <v>9.817377089014139</v>
       </c>
       <c r="CR101" t="n">
-        <v>7.521390903306457</v>
+        <v>7.521390901902731</v>
       </c>
       <c r="CS101" t="n">
-        <v>7.521523642958505</v>
+        <v>7.521523632949937</v>
       </c>
       <c r="CT101" t="n">
         <v>14.41306252244503</v>
       </c>
       <c r="CU101" t="n">
-        <v>8.825012382973808</v>
+        <v>8.825012381172884</v>
       </c>
       <c r="CV101" t="n">
         <v>8.470043037007597</v>
@@ -51346,7 +51346,7 @@
         <v>-62.39250833175431</v>
       </c>
       <c r="DB101" t="n">
-        <v>-56.46269272976896</v>
+        <v>-56.46269273865363</v>
       </c>
       <c r="DC101" t="inlineStr">
         <is>
@@ -51652,35 +51652,35 @@
         <v>0</v>
       </c>
       <c r="CM102" t="n">
-        <v>13.60549015875526</v>
+        <v>13.60549021288936</v>
       </c>
       <c r="CN102" t="n">
-        <v>16.14563409297981</v>
+        <v>16.14563412128148</v>
       </c>
       <c r="CO102" t="n">
-        <v>21.4297089172464</v>
+        <v>21.42970886954509</v>
       </c>
       <c r="CP102" t="n">
         <v>42.41036028560193</v>
       </c>
       <c r="CQ102" t="n">
-        <v>26.43094018572041</v>
+        <v>26.43094021051255</v>
       </c>
       <c r="CR102" t="n">
-        <v>15.65417287562044</v>
+        <v>15.65417287194339</v>
       </c>
       <c r="CS102" t="n">
-        <v>9.884596451481841</v>
+        <v>9.884596413419072</v>
       </c>
       <c r="CT102" t="inlineStr"/>
       <c r="CU102" t="n">
-        <v>16.70875151115047</v>
+        <v>16.70875151891483</v>
       </c>
       <c r="CV102" t="n">
-        <v>15.89990348430012</v>
+        <v>15.89990349661243</v>
       </c>
       <c r="CW102" t="n">
-        <v>14.30991313587011</v>
+        <v>14.30991314695119</v>
       </c>
       <c r="CX102" t="n">
         <v>4</v>
@@ -51692,10 +51692,10 @@
         <v>1.6</v>
       </c>
       <c r="DA102" t="n">
-        <v>-36.25874098190246</v>
+        <v>-36.25874093254352</v>
       </c>
       <c r="DB102" t="n">
-        <v>-25.57349245736622</v>
+        <v>-25.57349242278111</v>
       </c>
       <c r="DC102" t="inlineStr">
         <is>
@@ -52027,10 +52027,10 @@
         <v>0</v>
       </c>
       <c r="CM103" t="n">
-        <v>8.303309923197489</v>
+        <v>8.303309932447243</v>
       </c>
       <c r="CN103" t="n">
-        <v>15.40263990753134</v>
+        <v>15.40263992468964</v>
       </c>
       <c r="CO103" t="n">
         <v>10.31598191535957</v>
@@ -52042,7 +52042,7 @@
         <v>23.35694018571978</v>
       </c>
       <c r="CR103" t="n">
-        <v>9.032508696563744</v>
+        <v>9.17819432070187</v>
       </c>
       <c r="CS103" t="n">
         <v>9.420632541573644</v>
@@ -52051,7 +52051,7 @@
         <v>11.57306829296474</v>
       </c>
       <c r="CU103" t="n">
-        <v>12.64884099123127</v>
+        <v>12.66705169754954</v>
       </c>
       <c r="CV103" t="n">
         <v>10.94452510416216</v>
@@ -52072,7 +52072,7 @@
         <v>-40.26638732283001</v>
       </c>
       <c r="DB103" t="n">
-        <v>-23.29386800001413</v>
+        <v>-23.18343315119037</v>
       </c>
       <c r="DC103" t="inlineStr">
         <is>
@@ -52404,37 +52404,37 @@
         <v>0</v>
       </c>
       <c r="CM104" t="n">
-        <v>4.982255763131928</v>
+        <v>4.982255755876897</v>
       </c>
       <c r="CN104" t="n">
-        <v>7.147480710563958</v>
+        <v>7.147480708897301</v>
       </c>
       <c r="CO104" t="n">
-        <v>10.70833403426296</v>
+        <v>10.70833404735918</v>
       </c>
       <c r="CP104" t="n">
         <v>14.54062870725391</v>
       </c>
       <c r="CQ104" t="n">
-        <v>7.241976140055904</v>
+        <v>7.241976147192775</v>
       </c>
       <c r="CR104" t="n">
-        <v>8.443565473267835</v>
+        <v>8.443565474185981</v>
       </c>
       <c r="CS104" t="n">
-        <v>5.329827780659808</v>
+        <v>5.329827788078513</v>
       </c>
       <c r="CT104" t="n">
         <v>10.99014349695177</v>
       </c>
       <c r="CU104" t="n">
-        <v>8.67302651326851</v>
+        <v>8.673026515724541</v>
       </c>
       <c r="CV104" t="n">
-        <v>7.84277080666187</v>
+        <v>7.842770810689378</v>
       </c>
       <c r="CW104" t="n">
-        <v>7.058493725995683</v>
+        <v>7.05849372962044</v>
       </c>
       <c r="CX104" t="n">
         <v>8</v>
@@ -52446,10 +52446,10 @@
         <v>2.9</v>
       </c>
       <c r="DA104" t="n">
-        <v>-68.97365395166733</v>
+        <v>-68.97365393573433</v>
       </c>
       <c r="DB104" t="n">
-        <v>-61.87680653508347</v>
+        <v>-61.87680652428773</v>
       </c>
       <c r="DC104" t="inlineStr">
         <is>
@@ -52769,10 +52769,10 @@
         <v>0</v>
       </c>
       <c r="CM105" t="n">
-        <v>10.23710461032054</v>
+        <v>10.2371045872032</v>
       </c>
       <c r="CN105" t="n">
-        <v>18.9898290521446</v>
+        <v>18.98982900926194</v>
       </c>
       <c r="CO105" t="n">
         <v>85.63087184126204</v>
@@ -52781,13 +52781,13 @@
         <v>75.61388439108377</v>
       </c>
       <c r="CQ105" t="n">
-        <v>102.4806943376925</v>
+        <v>102.4806943461973</v>
       </c>
       <c r="CR105" t="n">
-        <v>15.99314352011496</v>
+        <v>15.99314352128231</v>
       </c>
       <c r="CS105" t="n">
-        <v>69.23820781267064</v>
+        <v>69.23820784611496</v>
       </c>
       <c r="CT105" t="n">
         <v>22.15363857936098</v>
@@ -53128,37 +53128,37 @@
         <v>0</v>
       </c>
       <c r="CM106" t="n">
-        <v>17.02987093832519</v>
+        <v>17.02987094097669</v>
       </c>
       <c r="CN106" t="n">
-        <v>25.12863950587515</v>
+        <v>25.12863950729911</v>
       </c>
       <c r="CO106" t="n">
-        <v>43.17340780894378</v>
+        <v>43.17340780466833</v>
       </c>
       <c r="CP106" t="n">
         <v>61.92338218449162</v>
       </c>
       <c r="CQ106" t="n">
-        <v>34.39888703377872</v>
+        <v>34.39888703284607</v>
       </c>
       <c r="CR106" t="n">
-        <v>26.69270852437185</v>
+        <v>26.69270852414278</v>
       </c>
       <c r="CS106" t="n">
-        <v>21.5537724501939</v>
+        <v>21.55377244789325</v>
       </c>
       <c r="CT106" t="n">
         <v>22.74915071652201</v>
       </c>
       <c r="CU106" t="n">
-        <v>31.58122739531278</v>
+        <v>31.58122739485498</v>
       </c>
       <c r="CV106" t="n">
-        <v>25.9106740151235</v>
+        <v>25.91067401572095</v>
       </c>
       <c r="CW106" t="n">
-        <v>23.31960661361115</v>
+        <v>23.31960661414885</v>
       </c>
       <c r="CX106" t="n">
         <v>8</v>
@@ -53170,10 +53170,10 @@
         <v>3.6</v>
       </c>
       <c r="DA106" t="n">
-        <v>-58.17110921325354</v>
+        <v>-58.17110921228905</v>
       </c>
       <c r="DB106" t="n">
-        <v>-43.3520584837439</v>
+        <v>-43.35205848456506</v>
       </c>
       <c r="DC106" t="inlineStr">
         <is>
@@ -53517,25 +53517,25 @@
         <v>0</v>
       </c>
       <c r="CM107" t="n">
-        <v>19.74422615408849</v>
+        <v>19.74422623876977</v>
       </c>
       <c r="CN107" t="n">
-        <v>20.81901952839438</v>
+        <v>20.8190195636227</v>
       </c>
       <c r="CO107" t="n">
-        <v>22.6789346651506</v>
+        <v>22.67893460625812</v>
       </c>
       <c r="CP107" t="n">
         <v>51.15469290785368</v>
       </c>
       <c r="CQ107" t="n">
-        <v>18.12400023564574</v>
+        <v>18.12400021290314</v>
       </c>
       <c r="CR107" t="n">
-        <v>23.14674993313622</v>
+        <v>23.14674992609104</v>
       </c>
       <c r="CS107" t="n">
-        <v>9.251671433787523</v>
+        <v>9.25167137581133</v>
       </c>
       <c r="CT107" t="n">
         <v>121.0340831371104</v>
@@ -53797,7 +53797,7 @@
         <v>301.7</v>
       </c>
       <c r="BN108" t="n">
-        <v>5.79</v>
+        <v>5.95</v>
       </c>
       <c r="BO108" t="n">
         <v>1.64</v>
@@ -53872,10 +53872,10 @@
         <v>0</v>
       </c>
       <c r="CM108" t="n">
-        <v>2.30879514807204</v>
+        <v>2.308795154281636</v>
       </c>
       <c r="CN108" t="n">
-        <v>4.282814999673634</v>
+        <v>4.282815011192436</v>
       </c>
       <c r="CO108" t="inlineStr"/>
       <c r="CP108" t="inlineStr"/>
@@ -53886,13 +53886,13 @@
         <v>9.788598190877345</v>
       </c>
       <c r="CU108" t="n">
-        <v>5.460069446207673</v>
+        <v>5.460069452117139</v>
       </c>
       <c r="CV108" t="n">
-        <v>4.282814999673634</v>
+        <v>4.282815011192436</v>
       </c>
       <c r="CW108" t="n">
-        <v>3.854533499706271</v>
+        <v>3.854533510073192</v>
       </c>
       <c r="CX108" t="n">
         <v>3</v>
@@ -53904,10 +53904,10 @@
         <v>4.2</v>
       </c>
       <c r="DA108" t="n">
-        <v>-50.64617761911967</v>
+        <v>-50.64617748638058</v>
       </c>
       <c r="DB108" t="n">
-        <v>-30.08873897296776</v>
+        <v>-30.08873889730239</v>
       </c>
       <c r="DC108" t="inlineStr">
         <is>
@@ -54235,10 +54235,10 @@
         <v>0</v>
       </c>
       <c r="CM109" t="n">
-        <v>2.288285996794644</v>
+        <v>2.288285994391622</v>
       </c>
       <c r="CN109" t="n">
-        <v>4.244770524054065</v>
+        <v>4.244770519596459</v>
       </c>
       <c r="CO109" t="n">
         <v>12.12775768334331</v>
@@ -54247,25 +54247,25 @@
         <v>13.42256100698398</v>
       </c>
       <c r="CQ109" t="n">
-        <v>8.497290993621979</v>
+        <v>8.497290994743128</v>
       </c>
       <c r="CR109" t="n">
-        <v>5.723505655254661</v>
+        <v>5.723505655460515</v>
       </c>
       <c r="CS109" t="n">
-        <v>6.353086989354603</v>
+        <v>6.353086991564422</v>
       </c>
       <c r="CT109" t="n">
         <v>12.85999965667725</v>
       </c>
       <c r="CU109" t="n">
-        <v>9.032710358469979</v>
+        <v>9.032710358338438</v>
       </c>
       <c r="CV109" t="n">
-        <v>8.497290993621979</v>
+        <v>8.497290994743128</v>
       </c>
       <c r="CW109" t="n">
-        <v>7.647561894259781</v>
+        <v>7.647561895268816</v>
       </c>
       <c r="CX109" t="n">
         <v>7</v>
@@ -54277,10 +54277,10 @@
         <v>5.9</v>
       </c>
       <c r="DA109" t="n">
-        <v>-40.53217652856647</v>
+        <v>-40.53217652072018</v>
       </c>
       <c r="DB109" t="n">
-        <v>-29.76119284902188</v>
+        <v>-29.76119285004475</v>
       </c>
       <c r="DC109" t="inlineStr">
         <is>
@@ -54315,7 +54315,7 @@
         <v>0.862742405311745</v>
       </c>
       <c r="DO109" t="n">
-        <v>-21.08144412126176</v>
+        <v>-21.08143475388732</v>
       </c>
       <c r="DP109" t="b">
         <v>0</v>
@@ -54600,25 +54600,25 @@
         <v>0</v>
       </c>
       <c r="CM110" t="n">
-        <v>0.7081894167676014</v>
+        <v>0.7081894203948603</v>
       </c>
       <c r="CN110" t="n">
-        <v>1.295936842709595</v>
+        <v>1.295936846108846</v>
       </c>
       <c r="CO110" t="n">
-        <v>3.377655403610311</v>
+        <v>3.377655395169988</v>
       </c>
       <c r="CP110" t="n">
         <v>3.9650539013691</v>
       </c>
       <c r="CQ110" t="n">
-        <v>2.282150459318896</v>
+        <v>2.282150458341482</v>
       </c>
       <c r="CR110" t="n">
-        <v>2.625382004265233</v>
+        <v>2.531618360806168</v>
       </c>
       <c r="CS110" t="n">
-        <v>1.648360171492814</v>
+        <v>1.648360168438082</v>
       </c>
       <c r="CT110" t="n">
         <v>9.207389804930452</v>
@@ -54829,7 +54829,7 @@
         <v>1</v>
       </c>
       <c r="AW111" t="n">
-        <v>6389252096</v>
+        <v>6392538624</v>
       </c>
       <c r="AX111" t="n">
         <v>24.3</v>
@@ -54953,10 +54953,10 @@
         <v>0</v>
       </c>
       <c r="CM111" t="n">
-        <v>64.79503914059254</v>
+        <v>64.79503925346701</v>
       </c>
       <c r="CN111" t="n">
-        <v>94.34157698870274</v>
+        <v>94.34157715304796</v>
       </c>
       <c r="CO111" t="n">
         <v>24.49777849613394</v>
@@ -55304,10 +55304,10 @@
         <v>0</v>
       </c>
       <c r="CM112" t="n">
-        <v>0.07108092301721451</v>
+        <v>0.07108092265919706</v>
       </c>
       <c r="CN112" t="n">
-        <v>0.1318551121969329</v>
+        <v>0.1318551115328105</v>
       </c>
       <c r="CO112" t="inlineStr"/>
       <c r="CP112" t="inlineStr"/>
@@ -55647,10 +55647,10 @@
         <v>0</v>
       </c>
       <c r="CM113" t="n">
-        <v>4.791995452485938</v>
+        <v>4.791995431740906</v>
       </c>
       <c r="CN113" t="n">
-        <v>8.889151564361413</v>
+        <v>8.889151525879379</v>
       </c>
       <c r="CO113" t="n">
         <v>41.68025800547819</v>
@@ -55659,13 +55659,13 @@
         <v>41.39375437682286</v>
       </c>
       <c r="CQ113" t="n">
-        <v>34.44390369935719</v>
+        <v>34.44390372741578</v>
       </c>
       <c r="CR113" t="n">
-        <v>17.70853835534744</v>
+        <v>17.98697449497007</v>
       </c>
       <c r="CS113" t="n">
-        <v>28.64167031609415</v>
+        <v>28.64167033984472</v>
       </c>
       <c r="CT113" t="n">
         <v>43.95885076728991</v>
@@ -56241,7 +56241,7 @@
         <v>5.69</v>
       </c>
       <c r="BA115" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="BB115" t="n">
         <v>11.3</v>
@@ -56271,10 +56271,10 @@
         <v>2.24</v>
       </c>
       <c r="BK115" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="BL115" t="n">
-        <v>41.86</v>
+        <v>42.01</v>
       </c>
       <c r="BM115" t="n">
         <v>-6.3</v>
@@ -56295,10 +56295,10 @@
         <v>26.34</v>
       </c>
       <c r="BS115" t="n">
-        <v>16.61</v>
+        <v>16.55</v>
       </c>
       <c r="BT115" t="n">
-        <v>26.03</v>
+        <v>25.93</v>
       </c>
       <c r="BU115" t="n">
         <v>6.8</v>
@@ -56310,10 +56310,10 @@
         <v>-5.5</v>
       </c>
       <c r="BX115" t="n">
-        <v>20.57</v>
+        <v>20.49</v>
       </c>
       <c r="BY115" t="n">
-        <v>21</v>
+        <v>20.92</v>
       </c>
       <c r="BZ115" t="n">
         <v>-36.2</v>
@@ -56325,10 +56325,10 @@
         <v>-22.3</v>
       </c>
       <c r="CC115" t="n">
-        <v>16.61</v>
+        <v>16.55</v>
       </c>
       <c r="CD115" t="n">
-        <v>23.41</v>
+        <v>23.32</v>
       </c>
       <c r="CE115" t="n">
         <v>-37.65</v>
@@ -56343,7 +56343,7 @@
         <v>0.06</v>
       </c>
       <c r="CI115" t="n">
-        <v>17.73999977111816</v>
+        <v>17.67464828491211</v>
       </c>
       <c r="CJ115" t="b">
         <v>0</v>
@@ -56355,35 +56355,35 @@
         <v>0</v>
       </c>
       <c r="CM115" t="n">
-        <v>3.331469393305006</v>
+        <v>3.331469245698618</v>
       </c>
       <c r="CN115" t="n">
-        <v>6.179875724580786</v>
+        <v>6.179875450770935</v>
       </c>
       <c r="CO115" t="n">
-        <v>14.76476111603741</v>
+        <v>14.71036996074657</v>
       </c>
       <c r="CP115" t="n">
-        <v>15.71944051824731</v>
+        <v>15.66153246788377</v>
       </c>
       <c r="CQ115" t="n">
-        <v>10.25113356802674</v>
+        <v>10.20474725250626</v>
       </c>
       <c r="CR115" t="n">
-        <v>13.00142957086482</v>
+        <v>12.99929610320874</v>
       </c>
       <c r="CS115" t="n">
-        <v>7.57888446935982</v>
+        <v>7.538761243147705</v>
       </c>
       <c r="CT115" t="inlineStr"/>
       <c r="CU115" t="n">
-        <v>11.24925416118615</v>
+        <v>11.21576374637733</v>
       </c>
       <c r="CV115" t="n">
-        <v>11.62628156944578</v>
+        <v>11.6020216778575</v>
       </c>
       <c r="CW115" t="n">
-        <v>10.4636534125012</v>
+        <v>10.44181951007175</v>
       </c>
       <c r="CX115" t="n">
         <v>6</v>
@@ -56395,10 +56395,10 @@
         <v>4.7</v>
       </c>
       <c r="DA115" t="n">
-        <v>-41.01660908960839</v>
+        <v>-40.92205207282474</v>
       </c>
       <c r="DB115" t="n">
-        <v>-36.58819444011133</v>
+        <v>-36.54321395491858</v>
       </c>
       <c r="DC115" t="inlineStr">
         <is>
@@ -56427,13 +56427,13 @@
         </is>
       </c>
       <c r="DM115" t="n">
-        <v>17.71999931335449</v>
+        <v>17.65472221374512</v>
       </c>
       <c r="DN115" t="n">
-        <v>0.1128694048458501</v>
+        <v>0.1128653904929777</v>
       </c>
       <c r="DO115" t="n">
-        <v>-32.81266688836438</v>
+        <v>-32.81267014832668</v>
       </c>
       <c r="DP115" t="b">
         <v>0</v>
@@ -56770,7 +56770,7 @@
         <v>-0.5063286249386678</v>
       </c>
       <c r="DO116" t="n">
-        <v>-2.567033420840603</v>
+        <v>-4.146337605600536</v>
       </c>
       <c r="DP116" t="b">
         <v>0</v>
@@ -57055,10 +57055,10 @@
         <v>0</v>
       </c>
       <c r="CM117" t="n">
-        <v>1.303237661186293</v>
+        <v>1.303237663938029</v>
       </c>
       <c r="CN117" t="n">
-        <v>2.417505861500574</v>
+        <v>2.417505866605044</v>
       </c>
       <c r="CO117" t="n">
         <v>2.370527277221787</v>
@@ -57067,10 +57067,10 @@
         <v>3.99173753228638</v>
       </c>
       <c r="CQ117" t="n">
-        <v>4.59817920244908</v>
+        <v>4.598179204262841</v>
       </c>
       <c r="CR117" t="n">
-        <v>2.490846657242768</v>
+        <v>2.637367048845283</v>
       </c>
       <c r="CS117" t="n">
         <v>2.16478340033084</v>
@@ -57079,13 +57079,13 @@
         <v>5.373039997618077</v>
       </c>
       <c r="CU117" t="n">
-        <v>3.088732198729475</v>
+        <v>3.107047248888535</v>
       </c>
       <c r="CV117" t="n">
-        <v>2.454176259371671</v>
+        <v>2.527436457725163</v>
       </c>
       <c r="CW117" t="n">
-        <v>2.208758633434504</v>
+        <v>2.274692811952647</v>
       </c>
       <c r="CX117" t="n">
         <v>8</v>
@@ -57097,10 +57097,10 @@
         <v>4.1</v>
       </c>
       <c r="DA117" t="n">
-        <v>-41.87477207497967</v>
+        <v>-40.13966209220315</v>
       </c>
       <c r="DB117" t="n">
-        <v>-18.71757269768536</v>
+        <v>-18.23559768745157</v>
       </c>
       <c r="DC117" t="inlineStr">
         <is>
@@ -57424,25 +57424,25 @@
         <v>0</v>
       </c>
       <c r="CM118" t="n">
-        <v>1.385969549935518</v>
+        <v>1.385969549891897</v>
       </c>
       <c r="CN118" t="n">
-        <v>2.5668248151222</v>
+        <v>2.566824815068441</v>
       </c>
       <c r="CO118" t="n">
-        <v>8.734545308435909</v>
+        <v>8.734545308527879</v>
       </c>
       <c r="CP118" t="n">
         <v>10.76105602888196</v>
       </c>
       <c r="CQ118" t="n">
-        <v>4.818793502142094</v>
+        <v>4.818793502166653</v>
       </c>
       <c r="CR118" t="n">
-        <v>7.689753633968709</v>
+        <v>7.806265052670983</v>
       </c>
       <c r="CS118" t="n">
-        <v>4.249077459296936</v>
+        <v>4.249077459329486</v>
       </c>
       <c r="CT118" t="n">
         <v>12.10586855084149</v>
@@ -57779,25 +57779,25 @@
         <v>0</v>
       </c>
       <c r="CM119" t="n">
-        <v>4.313523380771215</v>
+        <v>4.313523384898213</v>
       </c>
       <c r="CN119" t="n">
-        <v>5.371995838757273</v>
+        <v>5.37199584312758</v>
       </c>
       <c r="CO119" t="n">
-        <v>13.96479113535352</v>
+        <v>13.96479113335344</v>
       </c>
       <c r="CP119" t="n">
         <v>37.02868912025743</v>
       </c>
       <c r="CQ119" t="n">
-        <v>9.443307077625168</v>
+        <v>9.443307080607191</v>
       </c>
       <c r="CR119" t="n">
-        <v>48.30742124364938</v>
+        <v>48.30742124295021</v>
       </c>
       <c r="CS119" t="n">
-        <v>6.640663796453104</v>
+        <v>6.640663794989506</v>
       </c>
       <c r="CT119" t="n">
         <v>23.55589235584143</v>
@@ -58134,10 +58134,10 @@
         <v>0</v>
       </c>
       <c r="CM120" t="n">
-        <v>12.13281975612021</v>
+        <v>12.13281972853702</v>
       </c>
       <c r="CN120" t="n">
-        <v>15.13964900002826</v>
+        <v>15.13964896560923</v>
       </c>
       <c r="CO120" t="inlineStr"/>
       <c r="CP120" t="inlineStr"/>
@@ -58481,10 +58481,10 @@
         <v>0</v>
       </c>
       <c r="CM121" t="n">
-        <v>2.433630218761886</v>
+        <v>2.433630214525158</v>
       </c>
       <c r="CN121" t="n">
-        <v>4.514384055803299</v>
+        <v>4.514384047944168</v>
       </c>
       <c r="CO121" t="n">
         <v>12.16393421907894</v>
@@ -58493,13 +58493,13 @@
         <v>12.67500423009855</v>
       </c>
       <c r="CQ121" t="n">
-        <v>9.610893239748908</v>
+        <v>9.610893241892093</v>
       </c>
       <c r="CR121" t="n">
-        <v>0.7923097205623658</v>
+        <v>0.7923097206186429</v>
       </c>
       <c r="CS121" t="n">
-        <v>6.738186464487673</v>
+        <v>6.738186468890818</v>
       </c>
       <c r="CT121" t="n">
         <v>7.386557878337924</v>
@@ -58836,10 +58836,10 @@
         <v>0</v>
       </c>
       <c r="CM122" t="n">
-        <v>1.587487375924325</v>
+        <v>1.58748737090429</v>
       </c>
       <c r="CN122" t="n">
-        <v>1.654514620685574</v>
+        <v>1.654514615453582</v>
       </c>
       <c r="CO122" t="inlineStr"/>
       <c r="CP122" t="inlineStr"/>
@@ -59193,25 +59193,25 @@
         <v>0</v>
       </c>
       <c r="CM123" t="n">
-        <v>2.440509519424208</v>
+        <v>2.440509518041118</v>
       </c>
       <c r="CN123" t="n">
-        <v>2.582847804216131</v>
+        <v>2.58284780315166</v>
       </c>
       <c r="CO123" t="n">
-        <v>3.1313483725708</v>
+        <v>3.131348373054878</v>
       </c>
       <c r="CP123" t="n">
         <v>9.968961369836157</v>
       </c>
       <c r="CQ123" t="n">
-        <v>1.773614900775639</v>
+        <v>1.773614900683681</v>
       </c>
       <c r="CR123" t="n">
-        <v>5.89379331707971</v>
+        <v>5.893793317186157</v>
       </c>
       <c r="CS123" t="n">
-        <v>1.284000036048924</v>
+        <v>1.284000036522383</v>
       </c>
       <c r="CT123" t="n">
         <v>14.17567566803012</v>
@@ -59556,10 +59556,10 @@
         <v>0</v>
       </c>
       <c r="CM124" t="n">
-        <v>1.695762287256657</v>
+        <v>1.695762281679787</v>
       </c>
       <c r="CN124" t="n">
-        <v>3.145639042861098</v>
+        <v>3.145639032516006</v>
       </c>
       <c r="CO124" t="n">
         <v>1.164835184210863</v>
@@ -59568,7 +59568,7 @@
         <v>4.685046848239709</v>
       </c>
       <c r="CQ124" t="n">
-        <v>1.617701831833081</v>
+        <v>1.617701829837779</v>
       </c>
       <c r="CR124" t="n">
         <v>0.7445919647652398</v>
@@ -59911,10 +59911,10 @@
         <v>0</v>
       </c>
       <c r="CM125" t="n">
-        <v>1.208150922139057</v>
+        <v>1.208150926242185</v>
       </c>
       <c r="CN125" t="n">
-        <v>2.241119960567951</v>
+        <v>2.241119968179252</v>
       </c>
       <c r="CO125" t="inlineStr"/>
       <c r="CP125" t="inlineStr"/>
@@ -60264,10 +60264,10 @@
         <v>0</v>
       </c>
       <c r="CM126" t="n">
-        <v>5.852737032525572</v>
+        <v>5.852737024467463</v>
       </c>
       <c r="CN126" t="n">
-        <v>8.521585119357233</v>
+        <v>8.521585107624627</v>
       </c>
       <c r="CO126" t="inlineStr"/>
       <c r="CP126" t="inlineStr"/>
@@ -60595,10 +60595,10 @@
         <v>0</v>
       </c>
       <c r="CM127" t="n">
-        <v>39.16484733271603</v>
+        <v>39.16484747160163</v>
       </c>
       <c r="CN127" t="n">
-        <v>72.65079180218822</v>
+        <v>72.65079205982101</v>
       </c>
       <c r="CO127" t="n">
         <v>19.70019868936262</v>
@@ -60617,7 +60617,7 @@
       </c>
       <c r="CT127" t="inlineStr"/>
       <c r="CU127" t="n">
-        <v>25.95832719586328</v>
+        <v>25.95832721901087</v>
       </c>
       <c r="CV127" t="n">
         <v>22.94099163326045</v>
@@ -60638,7 +60638,7 @@
         <v>-8.398883623331265</v>
       </c>
       <c r="DB127" t="n">
-        <v>15.16559956295795</v>
+        <v>15.16559966565358</v>
       </c>
       <c r="DC127" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>5.7</v>
       </c>
       <c r="BN128" t="n">
-        <v>126.46</v>
+        <v>-61.8</v>
       </c>
       <c r="BO128" t="n">
         <v>2.17</v>
@@ -60970,10 +60970,10 @@
         <v>0</v>
       </c>
       <c r="CM128" t="n">
-        <v>7.023003872521314</v>
+        <v>7.023003894581971</v>
       </c>
       <c r="CN128" t="n">
-        <v>12.52125437416511</v>
+        <v>12.52125441349687</v>
       </c>
       <c r="CO128" t="inlineStr"/>
       <c r="CP128" t="inlineStr"/>
@@ -60982,13 +60982,13 @@
       <c r="CS128" t="inlineStr"/>
       <c r="CT128" t="inlineStr"/>
       <c r="CU128" t="n">
-        <v>9.772129123343211</v>
+        <v>9.772129154039419</v>
       </c>
       <c r="CV128" t="n">
-        <v>9.772129123343211</v>
+        <v>9.772129154039419</v>
       </c>
       <c r="CW128" t="n">
-        <v>8.794916211008889</v>
+        <v>8.794916238635478</v>
       </c>
       <c r="CX128" t="n">
         <v>2</v>
@@ -61000,10 +61000,10 @@
         <v>1.8</v>
       </c>
       <c r="DA128" t="n">
-        <v>37.8513487970304</v>
+        <v>37.85134923004905</v>
       </c>
       <c r="DB128" t="n">
-        <v>53.16816533003379</v>
+        <v>53.16816581116559</v>
       </c>
       <c r="DC128" t="inlineStr">
         <is>
@@ -61662,10 +61662,10 @@
         <v>0</v>
       </c>
       <c r="CM130" t="n">
-        <v>0.7898297419195486</v>
+        <v>0.7898297416842991</v>
       </c>
       <c r="CN130" t="n">
-        <v>1.465134171260762</v>
+        <v>1.465134170824375</v>
       </c>
       <c r="CO130" t="n">
         <v>15.55901742875274</v>
@@ -61674,13 +61674,13 @@
         <v>16.24752185378162</v>
       </c>
       <c r="CQ130" t="n">
-        <v>13.62931207190135</v>
+        <v>13.62931207195498</v>
       </c>
       <c r="CR130" t="n">
-        <v>1.677017488322422</v>
+        <v>1.67701748832742</v>
       </c>
       <c r="CS130" t="n">
-        <v>10.99975764089856</v>
+        <v>10.99975764114201</v>
       </c>
       <c r="CT130" t="inlineStr"/>
       <c r="CU130" t="inlineStr"/>
@@ -62023,25 +62023,25 @@
         <v>0</v>
       </c>
       <c r="CM131" t="n">
-        <v>3.718272697158386</v>
+        <v>3.718272694106523</v>
       </c>
       <c r="CN131" t="n">
-        <v>3.804269595688058</v>
+        <v>3.804269593070484</v>
       </c>
       <c r="CO131" t="n">
-        <v>4.34691808783418</v>
+        <v>4.346918088411069</v>
       </c>
       <c r="CP131" t="n">
         <v>18.92094732156112</v>
       </c>
       <c r="CQ131" t="n">
-        <v>3.380892015980546</v>
+        <v>3.380892014294296</v>
       </c>
       <c r="CR131" t="n">
-        <v>7.734015932797347</v>
+        <v>7.734015932920891</v>
       </c>
       <c r="CS131" t="n">
-        <v>1.69307886389728</v>
+        <v>1.693078864496178</v>
       </c>
       <c r="CT131" t="n">
         <v>21.99280021819457</v>
@@ -62378,25 +62378,25 @@
         <v>0</v>
       </c>
       <c r="CM132" t="n">
-        <v>0.6526494784606154</v>
+        <v>0.6526494814980326</v>
       </c>
       <c r="CN132" t="n">
-        <v>0.8701114280785891</v>
+        <v>0.8701114318209445</v>
       </c>
       <c r="CO132" t="n">
-        <v>4.575412019492939</v>
+        <v>4.575412017877945</v>
       </c>
       <c r="CP132" t="n">
         <v>11.53061776171596</v>
       </c>
       <c r="CQ132" t="n">
-        <v>1.753153038925816</v>
+        <v>1.753153038341872</v>
       </c>
       <c r="CR132" t="n">
-        <v>0.6736989119460733</v>
+        <v>0.6736989119234752</v>
       </c>
       <c r="CS132" t="n">
-        <v>2.239819128829849</v>
+        <v>2.239819127784735</v>
       </c>
       <c r="CT132" t="n">
         <v>18.94000053405762</v>
@@ -62741,10 +62741,10 @@
         <v>0</v>
       </c>
       <c r="CM133" t="n">
-        <v>1.399091222919376</v>
+        <v>1.3990912293205</v>
       </c>
       <c r="CN133" t="n">
-        <v>2.341569946722338</v>
+        <v>2.341569957435492</v>
       </c>
       <c r="CO133" t="inlineStr"/>
       <c r="CP133" t="inlineStr"/>
@@ -62755,13 +62755,13 @@
         <v>5.639999866485596</v>
       </c>
       <c r="CU133" t="n">
-        <v>3.126887012042437</v>
+        <v>3.126887017747196</v>
       </c>
       <c r="CV133" t="n">
-        <v>2.341569946722338</v>
+        <v>2.341569957435492</v>
       </c>
       <c r="CW133" t="n">
-        <v>2.107412952050104</v>
+        <v>2.107412961691943</v>
       </c>
       <c r="CX133" t="n">
         <v>3</v>
@@ -62773,10 +62773,10 @@
         <v>4</v>
       </c>
       <c r="DA133" t="n">
-        <v>-62.63452124222695</v>
+        <v>-62.63452107127235</v>
       </c>
       <c r="DB133" t="n">
-        <v>-44.55873960878537</v>
+        <v>-44.55873950763716</v>
       </c>
       <c r="DC133" t="inlineStr">
         <is>
@@ -63092,10 +63092,10 @@
         <v>0</v>
       </c>
       <c r="CM134" t="n">
-        <v>1.438248637558624</v>
+        <v>1.438248637260531</v>
       </c>
       <c r="CN134" t="n">
-        <v>2.094090016285357</v>
+        <v>2.094090015851333</v>
       </c>
       <c r="CO134" t="inlineStr"/>
       <c r="CP134" t="inlineStr"/>
@@ -63431,10 +63431,10 @@
         <v>0</v>
       </c>
       <c r="CM135" t="n">
-        <v>0.8773518260177365</v>
+        <v>0.8773518262455486</v>
       </c>
       <c r="CN135" t="n">
-        <v>1.627487637262901</v>
+        <v>1.627487637685493</v>
       </c>
       <c r="CO135" t="inlineStr"/>
       <c r="CP135" t="inlineStr"/>
@@ -63443,13 +63443,13 @@
       <c r="CS135" t="inlineStr"/>
       <c r="CT135" t="inlineStr"/>
       <c r="CU135" t="n">
-        <v>1.252419731640319</v>
+        <v>1.252419731965521</v>
       </c>
       <c r="CV135" t="n">
-        <v>1.252419731640319</v>
+        <v>1.252419731965521</v>
       </c>
       <c r="CW135" t="n">
-        <v>1.127177758476287</v>
+        <v>1.127177758768969</v>
       </c>
       <c r="CX135" t="n">
         <v>2</v>
@@ -63461,10 +63461,10 @@
         <v>1.9</v>
       </c>
       <c r="DA135" t="n">
-        <v>-73.03402380941499</v>
+        <v>-73.03402380241305</v>
       </c>
       <c r="DB135" t="n">
-        <v>-70.03780423268333</v>
+        <v>-70.03780422490338</v>
       </c>
       <c r="DC135" t="inlineStr">
         <is>
@@ -63788,37 +63788,37 @@
         <v>0</v>
       </c>
       <c r="CM136" t="n">
-        <v>2.200632218687533</v>
+        <v>2.200632218331861</v>
       </c>
       <c r="CN136" t="n">
-        <v>3.822448459275172</v>
+        <v>3.822448458945755</v>
       </c>
       <c r="CO136" t="n">
-        <v>9.543028032262374</v>
+        <v>9.543028032982331</v>
       </c>
       <c r="CP136" t="n">
         <v>12.03991535229107</v>
       </c>
       <c r="CQ136" t="n">
-        <v>5.525841548907239</v>
+        <v>5.525841549154104</v>
       </c>
       <c r="CR136" t="n">
-        <v>5.528978025653175</v>
+        <v>5.528978025684288</v>
       </c>
       <c r="CS136" t="n">
-        <v>4.712422460233439</v>
+        <v>4.712422460520452</v>
       </c>
       <c r="CT136" t="n">
         <v>16.41330661932616</v>
       </c>
       <c r="CU136" t="n">
-        <v>6.862105646437079</v>
+        <v>6.862105646596333</v>
       </c>
       <c r="CV136" t="n">
-        <v>5.527409787280207</v>
+        <v>5.527409787419196</v>
       </c>
       <c r="CW136" t="n">
-        <v>4.974668808552186</v>
+        <v>4.974668808677277</v>
       </c>
       <c r="CX136" t="n">
         <v>6</v>
@@ -63830,10 +63830,10 @@
         <v>7.5</v>
       </c>
       <c r="DA136" t="n">
-        <v>-72.75646907887901</v>
+        <v>-72.75646907819396</v>
       </c>
       <c r="DB136" t="n">
-        <v>-62.4200133602228</v>
+        <v>-62.42001335935065</v>
       </c>
       <c r="DC136" t="inlineStr">
         <is>
@@ -64159,10 +64159,10 @@
         <v>0</v>
       </c>
       <c r="CM137" t="n">
-        <v>0.3624512130540007</v>
+        <v>0.3624512133894581</v>
       </c>
       <c r="CN137" t="n">
-        <v>0.6723470002151714</v>
+        <v>0.6723470008374448</v>
       </c>
       <c r="CO137" t="inlineStr"/>
       <c r="CP137" t="inlineStr"/>
@@ -64171,13 +64171,13 @@
       <c r="CS137" t="inlineStr"/>
       <c r="CT137" t="inlineStr"/>
       <c r="CU137" t="n">
-        <v>0.517399106634586</v>
+        <v>0.5173991071134515</v>
       </c>
       <c r="CV137" t="n">
-        <v>0.517399106634586</v>
+        <v>0.5173991071134515</v>
       </c>
       <c r="CW137" t="n">
-        <v>0.4656591959711274</v>
+        <v>0.4656591964021063</v>
       </c>
       <c r="CX137" t="n">
         <v>2</v>
@@ -64189,10 +64189,10 @@
         <v>1.9</v>
       </c>
       <c r="DA137" t="n">
-        <v>-62.14152936990267</v>
+        <v>-62.14152933486373</v>
       </c>
       <c r="DB137" t="n">
-        <v>-57.93503263322519</v>
+        <v>-57.93503259429303</v>
       </c>
       <c r="DC137" t="inlineStr">
         <is>
@@ -64518,10 +64518,10 @@
         <v>0</v>
       </c>
       <c r="CM138" t="n">
-        <v>1.071777359185295</v>
+        <v>1.071777356656385</v>
       </c>
       <c r="CN138" t="n">
-        <v>1.988147001288722</v>
+        <v>1.988146996597594</v>
       </c>
       <c r="CO138" t="inlineStr"/>
       <c r="CP138" t="inlineStr"/>
@@ -64532,13 +64532,13 @@
         <v>3.183717762190965</v>
       </c>
       <c r="CU138" t="n">
-        <v>2.081214040888328</v>
+        <v>2.081214038481648</v>
       </c>
       <c r="CV138" t="n">
-        <v>1.988147001288722</v>
+        <v>1.988146996597594</v>
       </c>
       <c r="CW138" t="n">
-        <v>1.78933230115985</v>
+        <v>1.789332296937835</v>
       </c>
       <c r="CX138" t="n">
         <v>3</v>
@@ -64550,10 +64550,10 @@
         <v>3</v>
       </c>
       <c r="DA138" t="n">
-        <v>-68.10459432130322</v>
+        <v>-68.10459439656196</v>
       </c>
       <c r="DB138" t="n">
-        <v>-62.90171138401482</v>
+        <v>-62.90171142691463</v>
       </c>
       <c r="DC138" t="inlineStr">
         <is>
@@ -65228,10 +65228,10 @@
         <v>0</v>
       </c>
       <c r="CM140" t="n">
-        <v>0.9333520886592623</v>
+        <v>0.9333520865091519</v>
       </c>
       <c r="CN140" t="n">
-        <v>1.358960641087886</v>
+        <v>1.358960637957325</v>
       </c>
       <c r="CO140" t="n">
         <v>1.186376680445368</v>
@@ -65241,7 +65241,7 @@
       </c>
       <c r="CQ140" t="inlineStr"/>
       <c r="CR140" t="n">
-        <v>1.833333333333333</v>
+        <v>0.417266685</v>
       </c>
       <c r="CS140" t="n">
         <v>0.3047423615979173</v>
@@ -65251,7 +65251,7 @@
       <c r="CV140" t="inlineStr"/>
       <c r="CW140" t="inlineStr"/>
       <c r="CX140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CY140" t="b">
         <v>0</v>
@@ -65577,10 +65577,10 @@
         <v>0</v>
       </c>
       <c r="CM141" t="n">
-        <v>8.766112190634384</v>
+        <v>8.766112195309146</v>
       </c>
       <c r="CN141" t="n">
-        <v>12.76345934956366</v>
+        <v>12.76345935637012</v>
       </c>
       <c r="CO141" t="n">
         <v>7.914899901388957</v>
@@ -65590,7 +65590,7 @@
       </c>
       <c r="CQ141" t="inlineStr"/>
       <c r="CR141" t="n">
-        <v>6.267048420977274</v>
+        <v>6.378959999923297</v>
       </c>
       <c r="CS141" t="n">
         <v>2.033085551593043</v>
@@ -65930,25 +65930,25 @@
         <v>0</v>
       </c>
       <c r="CM142" t="n">
-        <v>1.696102869941153</v>
+        <v>1.696102882157941</v>
       </c>
       <c r="CN142" t="n">
-        <v>1.830457449280859</v>
+        <v>1.83045745930171</v>
       </c>
       <c r="CO142" t="n">
-        <v>2.429282834091659</v>
+        <v>2.429282829893004</v>
       </c>
       <c r="CP142" t="n">
         <v>7.813514820721882</v>
       </c>
       <c r="CQ142" t="n">
-        <v>1.759689032676954</v>
+        <v>1.759689036975875</v>
       </c>
       <c r="CR142" t="n">
-        <v>2.001744399401084</v>
+        <v>2.00174439900381</v>
       </c>
       <c r="CS142" t="n">
-        <v>1.022042586801127</v>
+        <v>1.022042582834092</v>
       </c>
       <c r="CT142" t="n">
         <v>0.8825864735264446</v>
@@ -66291,10 +66291,10 @@
         <v>0</v>
       </c>
       <c r="CM143" t="n">
-        <v>0.6177256719496104</v>
+        <v>0.6177256730140767</v>
       </c>
       <c r="CN143" t="n">
-        <v>0.8994085783586327</v>
+        <v>0.8994085799084958</v>
       </c>
       <c r="CO143" t="n">
         <v>0.35406995505897</v>
@@ -66514,7 +66514,7 @@
         <v>1</v>
       </c>
       <c r="AW144" t="n">
-        <v>34620808</v>
+        <v>34620812</v>
       </c>
       <c r="AX144" t="n">
         <v>-0.06</v>
@@ -66967,10 +66967,10 @@
         <v>0</v>
       </c>
       <c r="CM145" t="n">
-        <v>2.143258805706165</v>
+        <v>2.143258821002009</v>
       </c>
       <c r="CN145" t="n">
-        <v>3.120584821108177</v>
+        <v>3.120584843378925</v>
       </c>
       <c r="CO145" t="n">
         <v>1.700313992147943</v>
@@ -67330,10 +67330,10 @@
         <v>0</v>
       </c>
       <c r="CM146" t="n">
-        <v>27.83419719594345</v>
+        <v>27.83419715314913</v>
       </c>
       <c r="CN146" t="n">
-        <v>37.23597047101768</v>
+        <v>37.2359704137684</v>
       </c>
       <c r="CO146" t="n">
         <v>2.52532820565238</v>
@@ -67342,7 +67342,7 @@
         <v>6.99881250992301</v>
       </c>
       <c r="CQ146" t="n">
-        <v>6.451773319360598</v>
+        <v>6.451773310741401</v>
       </c>
       <c r="CR146" t="n">
         <v>3.046690502845772</v>
@@ -68349,10 +68349,10 @@
         <v>0</v>
       </c>
       <c r="CM149" t="n">
-        <v>0.6910740062503334</v>
+        <v>0.6910740085710853</v>
       </c>
       <c r="CN149" t="n">
-        <v>1.281942281594369</v>
+        <v>1.281942285899363</v>
       </c>
       <c r="CO149" t="inlineStr"/>
       <c r="CP149" t="inlineStr"/>
@@ -68363,13 +68363,13 @@
         <v>3.539220503764572</v>
       </c>
       <c r="CU149" t="n">
-        <v>0.9865081439223511</v>
+        <v>0.9865081472352242</v>
       </c>
       <c r="CV149" t="n">
-        <v>0.9865081439223511</v>
+        <v>0.9865081472352242</v>
       </c>
       <c r="CW149" t="n">
-        <v>0.887857329530116</v>
+        <v>0.8878573325117017</v>
       </c>
       <c r="CX149" t="n">
         <v>2</v>
@@ -68381,10 +68381,10 @@
         <v>5.1</v>
       </c>
       <c r="DA149" t="n">
-        <v>-76.75766112444893</v>
+        <v>-76.75766104639695</v>
       </c>
       <c r="DB149" t="n">
-        <v>-74.17517902716547</v>
+        <v>-74.17517894044104</v>
       </c>
       <c r="DC149" t="inlineStr">
         <is>
@@ -69408,10 +69408,10 @@
         <v>0</v>
       </c>
       <c r="CM152" t="n">
-        <v>9.917600478364173</v>
+        <v>9.917600447279529</v>
       </c>
       <c r="CN152" t="n">
-        <v>14.44002629649824</v>
+        <v>14.440026251239</v>
       </c>
       <c r="CO152" t="n">
         <v>4.677488950236854</v>
@@ -69761,10 +69761,10 @@
         <v>0</v>
       </c>
       <c r="CM153" t="n">
-        <v>6.213928479328587</v>
+        <v>6.213928465413137</v>
       </c>
       <c r="CN153" t="n">
-        <v>11.37379057216366</v>
+        <v>11.37379054669323</v>
       </c>
       <c r="CO153" t="inlineStr"/>
       <c r="CP153" t="inlineStr"/>
@@ -69775,13 +69775,13 @@
         <v>3.834479090399828</v>
       </c>
       <c r="CU153" t="n">
-        <v>7.140732713964024</v>
+        <v>7.140732700835397</v>
       </c>
       <c r="CV153" t="n">
-        <v>6.213928479328587</v>
+        <v>6.213928465413137</v>
       </c>
       <c r="CW153" t="n">
-        <v>5.592535631395728</v>
+        <v>5.592535618871823</v>
       </c>
       <c r="CX153" t="n">
         <v>3</v>
@@ -69793,10 +69793,10 @@
         <v>3</v>
       </c>
       <c r="DA153" t="n">
-        <v>-51.91284973031512</v>
+        <v>-51.91284983800132</v>
       </c>
       <c r="DB153" t="n">
-        <v>-38.60075112899261</v>
+        <v>-38.60075124187848</v>
       </c>
       <c r="DC153" t="inlineStr">
         <is>
@@ -70483,10 +70483,10 @@
         <v>0</v>
       </c>
       <c r="CM155" t="n">
-        <v>4.017914656072189</v>
+        <v>4.017914650079432</v>
       </c>
       <c r="CN155" t="n">
-        <v>5.850083739241107</v>
+        <v>5.850083730515654</v>
       </c>
       <c r="CO155" t="inlineStr"/>
       <c r="CP155" t="inlineStr"/>
@@ -70497,7 +70497,7 @@
         <v>5.785847480139832</v>
       </c>
       <c r="CU155" t="n">
-        <v>5.217948625151043</v>
+        <v>5.217948620244973</v>
       </c>
       <c r="CV155" t="n">
         <v>5.785847480139832</v>
@@ -70518,7 +70518,7 @@
         <v>-66.83272104848781</v>
       </c>
       <c r="DB155" t="n">
-        <v>-66.76465803476161</v>
+        <v>-66.76465806601047</v>
       </c>
       <c r="DC155" t="inlineStr">
         <is>
